--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -605,25 +605,25 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="J2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="K2" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1649473486776882</v>
+        <v>0.1590214067278287</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2495913828675545</v>
+        <v>0.2446483180428135</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5854612684547574</v>
+        <v>0.5963302752293578</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05435488883238682</v>
+        <v>0.04807692307692313</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -641,19 +641,19 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.286323316151555</v>
+        <v>0.291266380976296</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.286323316151555</v>
+        <v>0.291266380976296</v>
       </c>
       <c r="X2" t="n">
         <v>0.5359146990191095</v>
       </c>
       <c r="Y2" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
@@ -1585,25 +1585,25 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.83</v>
+        <v>1.53</v>
       </c>
       <c r="J12" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>5.25</v>
       </c>
       <c r="L12" t="n">
-        <v>0.5010684547933092</v>
+        <v>0.5826050769870995</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2696927271387518</v>
+        <v>0.2476071577195173</v>
       </c>
       <c r="N12" t="n">
-        <v>0.229238818067939</v>
+        <v>0.1697877652933833</v>
       </c>
       <c r="O12" t="n">
-        <v>0.09056573449051752</v>
+        <v>0.1218487394957983</v>
       </c>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
@@ -1617,7 +1617,7 @@
       <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="n">
-        <v>1.25557461406518</v>
+        <v>1.184734513274336</v>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
@@ -1663,25 +1663,25 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>4.14</v>
+        <v>3.25</v>
       </c>
       <c r="J13" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>1.73</v>
+        <v>1.91</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2216320651496475</v>
+        <v>0.2734143106751153</v>
       </c>
       <c r="M13" t="n">
-        <v>0.247988310735011</v>
+        <v>0.261351914615919</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5303796241153415</v>
+        <v>0.4652337747089658</v>
       </c>
       <c r="O13" t="n">
-        <v>0.08985084607100191</v>
+        <v>0.125370164175215</v>
       </c>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
@@ -1695,7 +1695,7 @@
       <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr"/>
       <c r="Y13" t="n">
-        <v>1.220136286201022</v>
+        <v>1.203003875968992</v>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
@@ -1741,25 +1741,25 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="J14" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="K14" t="n">
-        <v>6.17</v>
+        <v>5</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6227621063893677</v>
+        <v>0.5713922925528538</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2288650740980926</v>
+        <v>0.2491905275855502</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1483728195125398</v>
+        <v>0.1794171798615961</v>
       </c>
       <c r="O14" t="n">
-        <v>0.09234666313851303</v>
+        <v>0.1147204529370134</v>
       </c>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -1773,7 +1773,7 @@
       <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="n">
-        <v>1.187159685863874</v>
+        <v>1.19482496194825</v>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
@@ -1819,25 +1819,25 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>3.15</v>
+        <v>2.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.05</v>
+        <v>3.25</v>
       </c>
       <c r="K15" t="n">
-        <v>2.23</v>
+        <v>2.38</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2902468687989416</v>
+        <v>0.3457292271934921</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2997631595792349</v>
+        <v>0.2765833817547937</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4099899716218234</v>
+        <v>0.3776873910517141</v>
       </c>
       <c r="O15" t="n">
-        <v>0.09375966319287654</v>
+        <v>0.1124757595345831</v>
       </c>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
@@ -1851,7 +1851,7 @@
       <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="n">
-        <v>1.305669144981413</v>
+        <v>1.242570281124498</v>
       </c>
       <c r="Z15" t="inlineStr">
         <is>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB37"/>
+  <dimension ref="A1:AB64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,28 +629,28 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2287387667007373</v>
+        <v>0.231089286465845</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5359146990191095</v>
+        <v>0.5286117119289155</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2353465342801532</v>
+        <v>0.2402990016052396</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.291266380976296</v>
+        <v>0.283963393886102</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.291266380976296</v>
+        <v>0.283963393886102</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5359146990191095</v>
+        <v>0.5286117119289155</v>
       </c>
       <c r="Y2" t="n">
         <v>3.9</v>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>6.408519536582851</v>
+        <v>6.321189714264894</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.408519536582851</v>
+        <v>6.321189714264894</v>
       </c>
     </row>
     <row r="3">
@@ -727,28 +727,28 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2725231151948335</v>
+        <v>0.2721984624866746</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3956846156670256</v>
+        <v>0.3955889392848772</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3317922691381407</v>
+        <v>0.3322125982284482</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1008662714144943</v>
+        <v>0.1007705950323459</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1008662714144943</v>
+        <v>0.1007705950323459</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3956846156670256</v>
+        <v>0.3955889392848772</v>
       </c>
       <c r="Y3" t="n">
         <v>3.2</v>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>4.731634706920012</v>
+        <v>4.730490599536298</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.731634706920012</v>
+        <v>4.730490599536298</v>
       </c>
     </row>
     <row r="4">
@@ -825,28 +825,28 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4400086634656995</v>
+        <v>0.4409651627399412</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4942897790766149</v>
+        <v>0.4922799098103214</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06570155745768574</v>
+        <v>0.06675492744973731</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2175066496673598</v>
+        <v>0.2154967804010663</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2175066496673598</v>
+        <v>0.2154967804010663</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4942897790766149</v>
+        <v>0.4922799098103214</v>
       </c>
       <c r="Y4" t="n">
         <v>3.4</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>5.910764738760704</v>
+        <v>5.886730528684745</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.910764738760704</v>
+        <v>5.886730528684745</v>
       </c>
     </row>
     <row r="5">
@@ -923,28 +923,28 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3447548041594359</v>
+        <v>0.3432792651049772</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3527536688143402</v>
+        <v>0.3543279564632452</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3024915270262238</v>
+        <v>0.3023927784317775</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.05863602175551663</v>
+        <v>0.06021030940442168</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.05863602175551663</v>
+        <v>0.06021030940442168</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3527536688143402</v>
+        <v>0.3543279564632452</v>
       </c>
       <c r="Y5" t="n">
         <v>3.2</v>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>4.218262313639893</v>
+        <v>4.237087796823457</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.218262313639893</v>
+        <v>4.237087796823457</v>
       </c>
     </row>
     <row r="6">
@@ -1003,46 +1003,46 @@
         <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>0.511293669135136</v>
+        <v>0.5078597339782346</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2702552251142862</v>
+        <v>0.2684401451027811</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2184511057505777</v>
+        <v>0.2237001209189843</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0572017084719163</v>
+        <v>0.0643500643500643</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4272144406220799</v>
+        <v>0.4263244288423755</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3766028498451762</v>
+        <v>0.3762490824269034</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1961827095327438</v>
+        <v>0.1974264887307212</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0840792285130561</v>
+        <v>-0.0815353051358591</v>
       </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0840792285130561</v>
+        <v>-0.0815353051358591</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4272144406220799</v>
+        <v>0.4263244288423755</v>
       </c>
       <c r="Y6" t="n">
         <v>1.85</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>5.108671387532308</v>
+        <v>5.098028541033669</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.108671387532308</v>
+        <v>5.098028541033669</v>
       </c>
     </row>
     <row r="7">
@@ -1098,52 +1098,52 @@
         <v>4.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2259083728278041</v>
+        <v>0.2255174329768023</v>
       </c>
       <c r="M7" t="n">
-        <v>0.287519747235387</v>
+        <v>0.2785803583831088</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4865718799368088</v>
+        <v>0.4959022086400889</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05394605394605412</v>
+        <v>0.05577309457814539</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2314049743946865</v>
+        <v>0.2328120564895247</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5173633450324683</v>
+        <v>0.5140106702717958</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2512316805728451</v>
+        <v>0.2531772732386793</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2298435977970813</v>
+        <v>0.235430311888687</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2298435977970813</v>
+        <v>0.235430311888687</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5173633450324683</v>
+        <v>0.5140106702717958</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>6.186680660599315</v>
+        <v>6.146589053216828</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.186680660599315</v>
+        <v>6.146589053216828</v>
       </c>
     </row>
     <row r="8">
@@ -1217,28 +1217,28 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.243982251206936</v>
+        <v>0.2448521973339274</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4947117110728264</v>
+        <v>0.4929704812753666</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2613060377202377</v>
+        <v>0.262177321390706</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2181159663919753</v>
+        <v>0.2163747365945156</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2181159663919753</v>
+        <v>0.2163747365945156</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4947117110728264</v>
+        <v>0.4929704812753666</v>
       </c>
       <c r="Y8" t="n">
         <v>3.4</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>5.915810242169697</v>
+        <v>5.894988448710542</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.915810242169697</v>
+        <v>5.894988448710542</v>
       </c>
     </row>
     <row r="9">
@@ -1291,55 +1291,55 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="K9" t="n">
-        <v>7.5</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6380263717566993</v>
+        <v>0.620779043590968</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2360697575499787</v>
+        <v>0.243536394024149</v>
       </c>
       <c r="N9" t="n">
-        <v>0.125903870693322</v>
+        <v>0.135684562384883</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05900900900900896</v>
+        <v>0.05286217050922937</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4688481526967667</v>
+        <v>0.468856395386621</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4645031770758087</v>
+        <v>0.4642418806297189</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06664867022742459</v>
+        <v>0.06690172398366027</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1691782190599326</v>
+        <v>-0.151922648204347</v>
       </c>
       <c r="V9" t="n">
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.1691782190599326</v>
+        <v>-0.151922648204347</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4688481526967667</v>
+        <v>0.468856395386621</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>5.606531322517188</v>
+        <v>5.606629889395578</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.606531322517188</v>
+        <v>5.606629889395578</v>
       </c>
     </row>
     <row r="10">
@@ -1413,28 +1413,28 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2651006284586224</v>
+        <v>0.2649340803901595</v>
       </c>
       <c r="R10" t="n">
-        <v>0.406726162603766</v>
+        <v>0.4079691971374362</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3281732089376114</v>
+        <v>0.3270967224724041</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1504761626037661</v>
+        <v>0.1517191971374362</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1504761626037661</v>
+        <v>0.1517191971374362</v>
       </c>
       <c r="X10" t="n">
-        <v>0.406726162603766</v>
+        <v>0.4079691971374362</v>
       </c>
       <c r="Y10" t="n">
         <v>3.7</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>4.8636705876072</v>
+        <v>4.87853491416561</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.8636705876072</v>
+        <v>4.87853491416561</v>
       </c>
     </row>
     <row r="11">
@@ -1511,28 +1511,28 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4889679156451812</v>
+        <v>0.4893694367471452</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4566736230579956</v>
+        <v>0.4557035722872</v>
       </c>
       <c r="S11" t="n">
-        <v>0.05435846129682308</v>
+        <v>0.05492699096565484</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2222696376976354</v>
+        <v>-0.2218681165956714</v>
       </c>
       <c r="V11" t="n">
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2222696376976354</v>
+        <v>-0.2218681165956714</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4889679156451812</v>
+        <v>0.4893694367471452</v>
       </c>
       <c r="Y11" t="n">
         <v>1.33</v>
@@ -1543,36 +1543,36 @@
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>5.847125383777921</v>
+        <v>5.851926811749566</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.847125383777921</v>
+        <v>5.851926811749566</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>f9bfyqFM</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45507.54166666666</v>
+        <v>45528.5625</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>carrarese</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>catania</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>77</v>
       </c>
       <c r="F12" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1581,76 +1581,76 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>coppa italia</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K12" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.5826050769870995</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.2476071577195173</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.1697877652933833</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.1218487394957983</v>
-      </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr"/>
-      <c r="R12" t="inlineStr"/>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.224658399682957</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.495380450945221</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.2799611493718221</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="n">
-        <v>1.184734513274336</v>
-      </c>
+      <c r="X12" t="n">
+        <v>0.504619549054779</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
+      <c r="AA12" t="n">
+        <v>6.034289122090057</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>6.034289122090057</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bHLf4sq9</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45507.64583333334</v>
+        <v>45528.5625</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>UiGfvfvT</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>mantova</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>77</v>
       </c>
       <c r="F13" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1659,76 +1659,76 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>coppa italia</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.2734143106751153</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.261351914615919</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.4652337747089658</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.125370164175215</v>
-      </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr"/>
-      <c r="R13" t="inlineStr"/>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.2476237725704289</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.500742939995815</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.2516332874337562</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="n">
-        <v>1.203003875968992</v>
-      </c>
+      <c r="X13" t="n">
+        <v>0.499257060004185</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
+      <c r="AA13" t="n">
+        <v>5.970163962044358</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>5.970163962044358</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>SzxylMbS</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45508.64583333334</v>
+        <v>45528.65625</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>cesena</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>padova</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>77</v>
       </c>
       <c r="F14" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1737,76 +1737,76 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>coppa italia</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="J14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K14" t="n">
-        <v>5</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.5713922925528538</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.2491905275855502</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.1794171798615961</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.1147204529370134</v>
-      </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr"/>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3489453164034246</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.6141992265002049</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.03685545709637053</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W14" t="inlineStr"/>
-      <c r="X14" t="inlineStr"/>
-      <c r="Y14" t="n">
-        <v>1.19482496194825</v>
-      </c>
+      <c r="X14" t="n">
+        <v>0.3858007734997951</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA14" t="inlineStr"/>
-      <c r="AB14" t="inlineStr"/>
+      <c r="AA14" t="n">
+        <v>4.613442771260976</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>4.613442771260976</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>WlhYT07d</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45508.65625</v>
+        <v>45528.65625</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>avellino</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>juve stabia</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>77</v>
       </c>
       <c r="F15" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1815,76 +1815,76 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>coppa italia</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K15" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.3457292271934921</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2765833817547937</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.3776873910517141</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.1124757595345831</v>
-      </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr"/>
-      <c r="R15" t="inlineStr"/>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr"/>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.4034853929127025</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.357237577853434</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2392770292338635</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>-100</v>
+        <v>-1</v>
       </c>
       <c r="W15" t="inlineStr"/>
-      <c r="X15" t="inlineStr"/>
-      <c r="Y15" t="n">
-        <v>1.242570281124498</v>
-      </c>
+      <c r="X15" t="n">
+        <v>0.5965146070872975</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA15" t="inlineStr"/>
-      <c r="AB15" t="inlineStr"/>
+      <c r="AA15" t="n">
+        <v>7.133179068185398</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>7.133179068185398</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45513.54166666666</v>
+        <v>45529.5625</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>sassuolo</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>cittadella</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>77</v>
       </c>
       <c r="F16" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -1907,13 +1907,13 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4694967552742121</v>
+        <v>0.4791886494945383</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4042830898537844</v>
+        <v>0.4226214921002333</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1262201548720035</v>
+        <v>0.09818985840522836</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
@@ -1924,7 +1924,7 @@
       </c>
       <c r="W16" t="inlineStr"/>
       <c r="X16" t="n">
-        <v>0.5305032447257878</v>
+        <v>0.5208113505054617</v>
       </c>
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr">
@@ -1933,36 +1933,36 @@
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>6.343808845453178</v>
+        <v>6.227912241812456</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.343808845453178</v>
+        <v>6.227912241812456</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45513.65625</v>
+        <v>45529.5625</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>reggiana</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>77</v>
       </c>
       <c r="F17" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1971,7 +1971,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -1982,27 +1982,27 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4727240812949189</v>
+        <v>0.3039414411183158</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4071627836349588</v>
+        <v>0.3698546877699536</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1201131350701222</v>
+        <v>0.3262038711117304</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W17" t="inlineStr"/>
       <c r="X17" t="n">
-        <v>0.5272759187050811</v>
+        <v>0.6301453122300464</v>
       </c>
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr">
@@ -2011,36 +2011,36 @@
         </is>
       </c>
       <c r="AA17" t="n">
-        <v>6.305216170364257</v>
+        <v>7.535338276228838</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.305216170364257</v>
+        <v>7.535338276228838</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45513.67708333334</v>
+        <v>45529.65625</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>sudtirol</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>77</v>
       </c>
       <c r="F18" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2060,27 +2060,27 @@
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.4738402187299073</v>
+        <v>0.4103593250455935</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3970833715775151</v>
+        <v>0.5360227798097519</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1290764096925773</v>
+        <v>0.05361789514465451</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W18" t="inlineStr"/>
       <c r="X18" t="n">
-        <v>0.5261597812700927</v>
+        <v>0.4639772201902481</v>
       </c>
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr">
@@ -2089,36 +2089,36 @@
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>6.291869291521921</v>
+        <v>5.548284242923113</v>
       </c>
       <c r="AB18" t="n">
-        <v>6.291869291521921</v>
+        <v>5.548284242923113</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45514.54166666666</v>
+        <v>45529.65625</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>cremonese</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>bari</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>77</v>
       </c>
       <c r="F19" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2141,13 +2141,13 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.3997746834822209</v>
+        <v>0.4758337980065067</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3808697754406668</v>
+        <v>0.4235865151183359</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2193555410771125</v>
+        <v>0.1005796868751575</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="W19" t="inlineStr"/>
       <c r="X19" t="n">
-        <v>0.6002253165177791</v>
+        <v>0.5241662019934934</v>
       </c>
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr">
@@ -2167,36 +2167,36 @@
         </is>
       </c>
       <c r="AA19" t="n">
-        <v>7.177552088599557</v>
+        <v>6.268029878710149</v>
       </c>
       <c r="AB19" t="n">
-        <v>7.177552088599557</v>
+        <v>6.268029878710149</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45514.65625</v>
+        <v>45530.5625</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>catanzaro</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>77</v>
       </c>
       <c r="F20" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2205,7 +2205,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2219,13 +2219,13 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.4375459700908128</v>
+        <v>0.4061804169336982</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3730150628421344</v>
+        <v>0.3718016552817088</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1894389670670526</v>
+        <v>0.2220179277845932</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="W20" t="inlineStr"/>
       <c r="X20" t="n">
-        <v>0.5624540299091871</v>
+        <v>0.5938195830663018</v>
       </c>
       <c r="Y20" t="inlineStr"/>
       <c r="Z20" t="inlineStr">
@@ -2245,36 +2245,36 @@
         </is>
       </c>
       <c r="AA20" t="n">
-        <v>6.725879408980817</v>
+        <v>7.100951711627119</v>
       </c>
       <c r="AB20" t="n">
-        <v>6.725879408980817</v>
+        <v>7.100951711627119</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45514.67708333334</v>
+        <v>45530.65625</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>modena</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="E21" t="n">
         <v>77</v>
       </c>
       <c r="F21" t="n">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2283,7 +2283,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie a</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2297,24 +2297,24 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.4762256520660549</v>
+        <v>0.2393281307484554</v>
       </c>
       <c r="R21" t="n">
-        <v>0.4803533188099261</v>
+        <v>0.503249337379427</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0434210291240188</v>
+        <v>0.2574225318721173</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="W21" t="inlineStr"/>
       <c r="X21" t="n">
-        <v>0.519646681190074</v>
+        <v>0.496750662620573</v>
       </c>
       <c r="Y21" t="inlineStr"/>
       <c r="Z21" t="inlineStr">
@@ -2323,29 +2323,29 @@
         </is>
       </c>
       <c r="AA21" t="n">
-        <v>6.213985014074568</v>
+        <v>5.940192220965569</v>
       </c>
       <c r="AB21" t="n">
-        <v>6.213985014074568</v>
+        <v>5.940192220965569</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>QT6wuRFc</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45515.54166666666</v>
+        <v>45513.54166666666</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>brescia</t>
+          <t>sassuolo</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>cittadella</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2364,66 +2364,86 @@
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
+      <c r="I22" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K22" t="n">
+        <v>5</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.562008242787561</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.2502810041213938</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.1877107530910453</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.06546906187624746</v>
+      </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.3405749389402209</v>
+        <v>0.4692999801089652</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3558480852076204</v>
+        <v>0.403883942822817</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3035769758521589</v>
+        <v>0.1268160770682178</v>
       </c>
       <c r="T22" t="n">
         <v>1</v>
       </c>
-      <c r="U22" t="inlineStr"/>
+      <c r="U22" t="n">
+        <v>-0.09270826267859583</v>
+      </c>
       <c r="V22" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W22" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>-0.09270826267859583</v>
+      </c>
       <c r="X22" t="n">
-        <v>0.6441519147923795</v>
-      </c>
-      <c r="Y22" t="inlineStr"/>
+        <v>0.4692999801089652</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>1.67</v>
+      </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA22" t="n">
-        <v>7.702830577384516</v>
+        <v>5.611934318187092</v>
       </c>
       <c r="AB22" t="n">
-        <v>7.702830577384516</v>
+        <v>5.611934318187092</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>dnnqk0iD</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45515.5625</v>
+        <v>45513.5625</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>palermo</t>
+          <t>avellino</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2442,66 +2462,86 @@
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="I23" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="J23" t="n">
+        <v>7</v>
+      </c>
+      <c r="K23" t="n">
+        <v>19</v>
+      </c>
+      <c r="L23" t="n">
+        <v>0.8177570093457945</v>
+      </c>
+      <c r="M23" t="n">
+        <v>0.1331775700934579</v>
+      </c>
+      <c r="N23" t="n">
+        <v>0.04906542056074766</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.07268170426065157</v>
+      </c>
       <c r="P23" t="n">
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.403847330668933</v>
+        <v>0.4148266945885991</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3641302640579551</v>
+        <v>0.3528763251408008</v>
       </c>
       <c r="S23" t="n">
-        <v>0.232022405273112</v>
+        <v>0.2322969802706001</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
-      <c r="U23" t="inlineStr"/>
+      <c r="U23" t="n">
+        <v>-0.4029303147571955</v>
+      </c>
       <c r="V23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W23" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>-0.4029303147571955</v>
+      </c>
       <c r="X23" t="n">
-        <v>0.596152669331067</v>
-      </c>
-      <c r="Y23" t="inlineStr"/>
+        <v>0.4148266945885991</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>1.14</v>
+      </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA23" t="n">
-        <v>7.128850981670743</v>
+        <v>4.960537528515021</v>
       </c>
       <c r="AB23" t="n">
-        <v>7.128850981670743</v>
+        <v>4.960537528515021</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>hvcjgHz8</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45515.65625</v>
+        <v>45513.65625</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>sampdoria</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>reggiana</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2520,66 +2560,86 @@
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="I24" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J24" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K24" t="n">
+        <v>8</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.6728971962616822</v>
+      </c>
+      <c r="M24" t="n">
+        <v>0.2093457943925233</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.1177570093457944</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.06150793650793651</v>
+      </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.3742469639595186</v>
+        <v>0.4732307370264151</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3749425523620097</v>
+        <v>0.4078961431180815</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2508104836784718</v>
+        <v>0.1188731198555035</v>
       </c>
       <c r="T24" t="n">
         <v>1</v>
       </c>
-      <c r="U24" t="inlineStr"/>
+      <c r="U24" t="n">
+        <v>-0.1996664592352671</v>
+      </c>
       <c r="V24" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W24" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.1996664592352671</v>
+      </c>
       <c r="X24" t="n">
-        <v>0.6250574476379902</v>
-      </c>
-      <c r="Y24" t="inlineStr"/>
+        <v>0.4732307370264151</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>1.4</v>
+      </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA24" t="n">
-        <v>7.474497101882698</v>
+        <v>5.658938687623388</v>
       </c>
       <c r="AB24" t="n">
-        <v>7.474497101882698</v>
+        <v>5.658938687623388</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>AZ3PVMxp</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45515.67708333334</v>
+        <v>45513.67708333334</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>cosenza</t>
+          <t>sudtirol</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2598,66 +2658,86 @@
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
+      <c r="I25" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J25" t="n">
+        <v>4</v>
+      </c>
+      <c r="K25" t="n">
+        <v>8</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.6493506493506493</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.2337662337662338</v>
+      </c>
+      <c r="N25" t="n">
+        <v>0.1168831168831169</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.06944444444444442</v>
+      </c>
       <c r="P25" t="n">
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.4739942378041332</v>
+        <v>0.4746242130978113</v>
       </c>
       <c r="R25" t="n">
-        <v>0.422798329895286</v>
+        <v>0.3982831758119963</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1032074323005807</v>
+        <v>0.1270926110901921</v>
       </c>
       <c r="T25" t="n">
         <v>1</v>
       </c>
-      <c r="U25" t="inlineStr"/>
+      <c r="U25" t="n">
+        <v>-0.1747264362528381</v>
+      </c>
       <c r="V25" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W25" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.1747264362528381</v>
+      </c>
       <c r="X25" t="n">
-        <v>0.5260057621958667</v>
-      </c>
-      <c r="Y25" t="inlineStr"/>
+        <v>0.4746242130978113</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>1.44</v>
+      </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA25" t="n">
-        <v>6.290027516612613</v>
+        <v>5.675602008565411</v>
       </c>
       <c r="AB25" t="n">
-        <v>6.290027516612613</v>
+        <v>5.675602008565411</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>bs5ow5pA</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45516.54166666666</v>
+        <v>45514.54166666666</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>frosinone</t>
+          <t>cremonese</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>pisa</t>
+          <t>bari</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2676,66 +2756,86 @@
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
+      <c r="I26" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.4929020010297615</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.2896747144513368</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.2174232845189017</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.06219939933348151</v>
+      </c>
       <c r="P26" t="n">
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.4214803559717588</v>
+        <v>0.3995295474610169</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3823090013622199</v>
+        <v>0.380966358890452</v>
       </c>
       <c r="S26" t="n">
-        <v>0.196210642666021</v>
+        <v>0.2195040936485314</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
-      <c r="U26" t="inlineStr"/>
+      <c r="U26" t="n">
+        <v>-0.09337245356874457</v>
+      </c>
       <c r="V26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W26" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>-0.09337245356874457</v>
+      </c>
       <c r="X26" t="n">
-        <v>0.5785196440282412</v>
-      </c>
-      <c r="Y26" t="inlineStr"/>
+        <v>0.3995295474610169</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.91</v>
+      </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA26" t="n">
-        <v>6.917993568449856</v>
+        <v>4.777612771271897</v>
       </c>
       <c r="AB26" t="n">
-        <v>6.917993568449856</v>
+        <v>4.777612771271897</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>02s0k9od</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45516.65625</v>
+        <v>45514.5625</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>salernitana</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>spezia</t>
+          <t>cesena</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2754,73 +2854,75 @@
           <t>coppa italia</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr"/>
-      <c r="P27" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q27" t="n">
-        <v>0.4455732802592645</v>
-      </c>
-      <c r="R27" t="n">
-        <v>0.3852067815535028</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0.1692199381872326</v>
-      </c>
+      <c r="I27" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0.595120015869867</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0.249156913310851</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0.1557230708192819</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0.0702760084925691</v>
+      </c>
+      <c r="P27" t="inlineStr"/>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
       <c r="T27" t="n">
         <v>1</v>
       </c>
       <c r="U27" t="inlineStr"/>
       <c r="V27" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="W27" t="inlineStr"/>
-      <c r="X27" t="n">
-        <v>0.5544267197407355</v>
-      </c>
-      <c r="Y27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="n">
+        <v>1.244385733157199</v>
+      </c>
       <c r="Z27" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA27" t="n">
-        <v>6.629888061598689</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>6.629888061598689</v>
-      </c>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
+          <t>Ob5Zdayq</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45520.64583333334</v>
+        <v>45514.65625</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>brescia</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>palermo</t>
+          <t>catanzaro</t>
         </is>
       </c>
       <c r="E28" t="n">
         <v>77</v>
       </c>
       <c r="F28" t="n">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2829,59 +2931,59 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>coppa italia</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>2.7</v>
+        <v>1.57</v>
       </c>
       <c r="J28" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="K28" t="n">
-        <v>2.55</v>
+        <v>6</v>
       </c>
       <c r="L28" t="n">
-        <v>0.3445218492716909</v>
+        <v>0.595120015869867</v>
       </c>
       <c r="M28" t="n">
-        <v>0.2906903103229892</v>
+        <v>0.249156913310851</v>
       </c>
       <c r="N28" t="n">
-        <v>0.3647878404053199</v>
+        <v>0.1557230708192819</v>
       </c>
       <c r="O28" t="n">
-        <v>0.07502723311546844</v>
+        <v>0.0702760084925691</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.3388659580677731</v>
+        <v>0.4383381881163518</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3746946149815555</v>
+        <v>0.3736696587172924</v>
       </c>
       <c r="S28" t="n">
-        <v>0.2864394269506713</v>
+        <v>0.1879921531663555</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>0.08400430465856634</v>
+        <v>-0.1567818277535151</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W28" t="n">
-        <v>0.08400430465856634</v>
+        <v>-0.1567818277535151</v>
       </c>
       <c r="X28" t="n">
-        <v>0.3746946149815555</v>
+        <v>0.4383381881163518</v>
       </c>
       <c r="Y28" t="n">
-        <v>3.2</v>
+        <v>1.57</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -2889,36 +2991,36 @@
         </is>
       </c>
       <c r="AA28" t="n">
-        <v>4.480634259065295</v>
+        <v>5.241690230395796</v>
       </c>
       <c r="AB28" t="n">
-        <v>4.480634259065295</v>
+        <v>5.241690230395796</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>EL1P0u6m</t>
+          <t>dC3sew6e</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45514.67708333334</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>bari</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>juve stabia</t>
+          <t>modena</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>77</v>
       </c>
       <c r="F29" t="n">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -2927,78 +3029,96 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>coppa italia</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.9</v>
+        <v>1.18</v>
       </c>
       <c r="J29" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>4.1</v>
+        <v>13</v>
       </c>
       <c r="L29" t="n">
-        <v>0.4882740930743861</v>
+        <v>0.794066317626527</v>
       </c>
       <c r="M29" t="n">
-        <v>0.2854525467204104</v>
+        <v>0.1338568935427574</v>
       </c>
       <c r="N29" t="n">
-        <v>0.2262733602052034</v>
+        <v>0.07207678883071553</v>
       </c>
       <c r="O29" t="n">
-        <v>0.07791053619038224</v>
-      </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr"/>
-      <c r="R29" t="inlineStr"/>
-      <c r="S29" t="inlineStr"/>
+        <v>0.06723784689886392</v>
+      </c>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.4771256045687979</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.4787009139308176</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.04417348150038463</v>
+      </c>
       <c r="T29" t="n">
         <v>1</v>
       </c>
-      <c r="U29" t="inlineStr"/>
+      <c r="U29" t="n">
+        <v>0.3448440203880602</v>
+      </c>
       <c r="V29" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W29" t="inlineStr"/>
-      <c r="X29" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0.3448440203880602</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0.4787009139308176</v>
+      </c>
       <c r="Y29" t="n">
-        <v>1.298333333333333</v>
+        <v>7</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr"/>
-      <c r="AB29" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA29" t="n">
+        <v>5.724351589386655</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>5.724351589386655</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>M5TEBdK5</t>
+          <t>6sP22LDL</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45515.54166666666</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>pisa</t>
+          <t>brescia</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>spezia</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="E30" t="n">
         <v>77</v>
       </c>
       <c r="F30" t="n">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3007,59 +3127,59 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>coppa italia</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="J30" t="n">
         <v>3.2</v>
       </c>
       <c r="K30" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3717001055966209</v>
+        <v>0.3126950238134341</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2903907074973601</v>
+        <v>0.2931515848250945</v>
       </c>
       <c r="N30" t="n">
-        <v>0.337909186906019</v>
+        <v>0.3941533913614715</v>
       </c>
       <c r="O30" t="n">
-        <v>0.07613636363636367</v>
+        <v>0.06600140056022408</v>
       </c>
       <c r="P30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.3771596572542751</v>
+        <v>0.3392938152055934</v>
       </c>
       <c r="R30" t="n">
-        <v>0.3703923812577244</v>
+        <v>0.3561153239435523</v>
       </c>
       <c r="S30" t="n">
-        <v>0.2524479614880006</v>
+        <v>0.3045908608508543</v>
       </c>
       <c r="T30" t="n">
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0.00545955165765416</v>
+        <v>0.06296373911845782</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>0.00545955165765416</v>
+        <v>0.06296373911845782</v>
       </c>
       <c r="X30" t="n">
-        <v>0.3771596572542751</v>
+        <v>0.3561153239435523</v>
       </c>
       <c r="Y30" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -3067,36 +3187,36 @@
         </is>
       </c>
       <c r="AA30" t="n">
-        <v>4.510111471748842</v>
+        <v>4.258461309133468</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.510111471748842</v>
+        <v>4.258461309133468</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>joLV7EJU</t>
+          <t>bepKi4a3</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45515.5625</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>salernitana</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>cittadella</t>
+          <t>palermo</t>
         </is>
       </c>
       <c r="E31" t="n">
         <v>77</v>
       </c>
       <c r="F31" t="n">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3105,59 +3225,59 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>coppa italia</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="J31" t="n">
         <v>3.4</v>
       </c>
       <c r="K31" t="n">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="L31" t="n">
-        <v>0.5038814396612561</v>
+        <v>0.5141647343482205</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2741707833450953</v>
+        <v>0.2767416070168364</v>
       </c>
       <c r="N31" t="n">
-        <v>0.2219477769936486</v>
+        <v>0.209093658634943</v>
       </c>
       <c r="O31" t="n">
-        <v>0.07275342569460208</v>
+        <v>0.06278795671273985</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.451102352483415</v>
+        <v>0.4035638632982508</v>
       </c>
       <c r="R31" t="n">
-        <v>0.3894999314195416</v>
+        <v>0.3642107603159362</v>
       </c>
       <c r="S31" t="n">
-        <v>0.1593977160970436</v>
+        <v>0.2322253763858126</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.05277908717784108</v>
+        <v>-0.1106008710499697</v>
       </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.05277908717784108</v>
+        <v>-0.1106008710499697</v>
       </c>
       <c r="X31" t="n">
-        <v>0.451102352483415</v>
+        <v>0.4035638632982508</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.85</v>
+        <v>1.83</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
@@ -3165,36 +3285,36 @@
         </is>
       </c>
       <c r="AA31" t="n">
-        <v>5.394325336065033</v>
+        <v>4.82585550823541</v>
       </c>
       <c r="AB31" t="n">
-        <v>5.394325336065033</v>
+        <v>4.82585550823541</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>WvwvCQVo</t>
+          <t>ILr8tvi2</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45521.64583333334</v>
+        <v>45515.65625</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sudtirol</t>
+          <t>sampdoria</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>modena</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E32" t="n">
         <v>77</v>
       </c>
       <c r="F32" t="n">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -3203,59 +3323,59 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>coppa italia</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>2.63</v>
+        <v>3.25</v>
       </c>
       <c r="J32" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K32" t="n">
-        <v>2.75</v>
+        <v>2.2</v>
       </c>
       <c r="L32" t="n">
-        <v>0.3565379226699568</v>
+        <v>0.2875816993464052</v>
       </c>
       <c r="M32" t="n">
-        <v>0.3024821731038665</v>
+        <v>0.2875816993464052</v>
       </c>
       <c r="N32" t="n">
-        <v>0.3409799042261768</v>
+        <v>0.4248366013071895</v>
       </c>
       <c r="O32" t="n">
-        <v>0.06644514567978321</v>
+        <v>0.06993006993007</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.3613841827993978</v>
+        <v>0.3733539654536731</v>
       </c>
       <c r="R32" t="n">
-        <v>0.3730405837229831</v>
+        <v>0.375385077520563</v>
       </c>
       <c r="S32" t="n">
-        <v>0.265575233477619</v>
+        <v>0.2512609570257634</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0.07055841061911661</v>
+        <v>0.08780337817415779</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0.07055841061911661</v>
+        <v>0.08780337817415779</v>
       </c>
       <c r="X32" t="n">
-        <v>0.3730405837229831</v>
+        <v>0.375385077520563</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
@@ -3263,36 +3383,36 @@
         </is>
       </c>
       <c r="AA32" t="n">
-        <v>4.460855194124398</v>
+        <v>4.488890876543051</v>
       </c>
       <c r="AB32" t="n">
-        <v>4.460855194124398</v>
+        <v>4.488890876543051</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>tYhtcc5C</t>
+          <t>ALOjHNNj</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45515.67708333334</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>catanzaro</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>sassuolo</t>
+          <t>cosenza</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>77</v>
       </c>
       <c r="F33" t="n">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3301,59 +3421,59 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>coppa italia</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>2.75</v>
+        <v>1.29</v>
       </c>
       <c r="J33" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="K33" t="n">
-        <v>2.5</v>
+        <v>9.5</v>
       </c>
       <c r="L33" t="n">
-        <v>0.337909186906019</v>
+        <v>0.7297486033519555</v>
       </c>
       <c r="M33" t="n">
-        <v>0.2903907074973601</v>
+        <v>0.171159217877095</v>
       </c>
       <c r="N33" t="n">
-        <v>0.3717001055966209</v>
+        <v>0.09909217877094974</v>
       </c>
       <c r="O33" t="n">
-        <v>0.07613636363636367</v>
+        <v>0.06227513816253083</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.310221098231573</v>
+        <v>0.4739078815334473</v>
       </c>
       <c r="R33" t="n">
-        <v>0.357962016962774</v>
+        <v>0.4223234754116267</v>
       </c>
       <c r="S33" t="n">
-        <v>0.3318168848056527</v>
+        <v>0.1037686430549262</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>0.06757130946541395</v>
+        <v>-0.2558407218185082</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W33" t="n">
-        <v>0.06757130946541395</v>
+        <v>-0.2558407218185082</v>
       </c>
       <c r="X33" t="n">
-        <v>0.357962016962774</v>
+        <v>0.4739078815334473</v>
       </c>
       <c r="Y33" t="n">
-        <v>3.2</v>
+        <v>1.29</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
@@ -3361,36 +3481,36 @@
         </is>
       </c>
       <c r="AA33" t="n">
-        <v>4.280544241946123</v>
+        <v>5.667036046793323</v>
       </c>
       <c r="AB33" t="n">
-        <v>4.280544241946123</v>
+        <v>5.667036046793323</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>x0nkeyzP</t>
+          <t>Aeu0r0Mk</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45516.54166666666</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>cesena</t>
+          <t>frosinone</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>carrarese</t>
+          <t>pisa</t>
         </is>
       </c>
       <c r="E34" t="n">
         <v>77</v>
       </c>
       <c r="F34" t="n">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3399,76 +3519,96 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>coppa italia</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="J34" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K34" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="L34" t="n">
-        <v>0.5008809239913865</v>
+        <v>0.5196419691695674</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2851168336566354</v>
+        <v>0.2834410740924913</v>
       </c>
       <c r="N34" t="n">
-        <v>0.2140022423519781</v>
+        <v>0.1969169567379413</v>
       </c>
       <c r="O34" t="n">
-        <v>0.0791797304499382</v>
-      </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr"/>
-      <c r="R34" t="inlineStr"/>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr"/>
-      <c r="U34" t="inlineStr"/>
+        <v>0.06911217437533224</v>
+      </c>
+      <c r="P34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q34" t="n">
+        <v>0.4203876243472634</v>
+      </c>
+      <c r="R34" t="n">
+        <v>0.3820936974019588</v>
+      </c>
+      <c r="S34" t="n">
+        <v>0.1975186782507778</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>-0.099254344822304</v>
+      </c>
       <c r="V34" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W34" t="inlineStr"/>
-      <c r="X34" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>-0.099254344822304</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0.4203876243472634</v>
+      </c>
       <c r="Y34" t="n">
-        <v>1.296197411003236</v>
+        <v>1.8</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA34" t="inlineStr"/>
-      <c r="AB34" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA34" t="n">
+        <v>5.02703566164179</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>5.02703566164179</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>SORbFvLt</t>
+          <t>42SH31wI</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45516.5625</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>cosenza</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>cremonese</t>
+          <t>mantova</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>77</v>
       </c>
       <c r="F35" t="n">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3477,59 +3617,59 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>coppa italia</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>3.2</v>
+        <v>1.44</v>
       </c>
       <c r="J35" t="n">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="K35" t="n">
-        <v>2.2</v>
+        <v>8</v>
       </c>
       <c r="L35" t="n">
-        <v>0.2894736842105263</v>
+        <v>0.6493506493506493</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2894736842105263</v>
+        <v>0.2337662337662338</v>
       </c>
       <c r="N35" t="n">
-        <v>0.4210526315789473</v>
+        <v>0.1168831168831169</v>
       </c>
       <c r="O35" t="n">
-        <v>0.07954545454545459</v>
+        <v>0.06944444444444442</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.3271006089805857</v>
+        <v>0.3819362896169821</v>
       </c>
       <c r="R35" t="n">
-        <v>0.3762116784915401</v>
+        <v>0.3698354440655963</v>
       </c>
       <c r="S35" t="n">
-        <v>0.2966877125278745</v>
+        <v>0.2482282663174216</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>0.08673799428101381</v>
+        <v>-0.2674143597336673</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W35" t="n">
-        <v>0.08673799428101381</v>
+        <v>-0.2674143597336673</v>
       </c>
       <c r="X35" t="n">
-        <v>0.3762116784915401</v>
+        <v>0.3819362896169821</v>
       </c>
       <c r="Y35" t="n">
-        <v>3.2</v>
+        <v>1.44</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -3537,36 +3677,36 @@
         </is>
       </c>
       <c r="AA35" t="n">
-        <v>4.498775450489541</v>
+        <v>4.567230901149658</v>
       </c>
       <c r="AB35" t="n">
-        <v>4.498775450489541</v>
+        <v>4.567230901149658</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>lvG7DIkg</t>
+          <t>fNwTkrUF</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45522.64583333334</v>
+        <v>45516.65625</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>frosinone</t>
+          <t>salernitana</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>sampdoria</t>
+          <t>spezia</t>
         </is>
       </c>
       <c r="E36" t="n">
         <v>77</v>
       </c>
       <c r="F36" t="n">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3575,59 +3715,59 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>serie b</t>
+          <t>coppa italia</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="J36" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K36" t="n">
-        <v>2.75</v>
+        <v>4.1</v>
       </c>
       <c r="L36" t="n">
-        <v>0.3717001055966209</v>
+        <v>0.481786133960047</v>
       </c>
       <c r="M36" t="n">
-        <v>0.2903907074973601</v>
+        <v>0.2890716803760282</v>
       </c>
       <c r="N36" t="n">
-        <v>0.337909186906019</v>
+        <v>0.2291421856639248</v>
       </c>
       <c r="O36" t="n">
-        <v>0.07613636363636367</v>
+        <v>0.06441525953721094</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.3792582472531151</v>
+        <v>0.4440924956845936</v>
       </c>
       <c r="R36" t="n">
-        <v>0.3804626357347388</v>
+        <v>0.3844438367580741</v>
       </c>
       <c r="S36" t="n">
-        <v>0.2402791170121459</v>
+        <v>0.1714636675573319</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>0.09007192823737875</v>
+        <v>-0.03769363827545341</v>
       </c>
       <c r="V36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W36" t="n">
-        <v>0.09007192823737875</v>
+        <v>-0.03769363827545341</v>
       </c>
       <c r="X36" t="n">
-        <v>0.3804626357347388</v>
+        <v>0.4440924956845936</v>
       </c>
       <c r="Y36" t="n">
-        <v>3.2</v>
+        <v>1.95</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -3635,91 +3775,2351 @@
         </is>
       </c>
       <c r="AA36" t="n">
-        <v>4.549608806230817</v>
+        <v>5.310500793976304</v>
       </c>
       <c r="AB36" t="n">
-        <v>4.549608806230817</v>
+        <v>5.310500793976304</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
+          <t>8KIdPmPc</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>45516.67708333334</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>carrarese</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>77</v>
+      </c>
+      <c r="F37" t="n">
+        <v>773</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J37" t="n">
+        <v>5</v>
+      </c>
+      <c r="K37" t="n">
+        <v>9</v>
+      </c>
+      <c r="L37" t="n">
+        <v>0.7073247406475951</v>
+      </c>
+      <c r="M37" t="n">
+        <v>0.1881483810122603</v>
+      </c>
+      <c r="N37" t="n">
+        <v>0.1045268783401446</v>
+      </c>
+      <c r="O37" t="n">
+        <v>0.06299081035923138</v>
+      </c>
+      <c r="P37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>0.4432416002942154</v>
+      </c>
+      <c r="R37" t="n">
+        <v>0.3602216223860056</v>
+      </c>
+      <c r="S37" t="n">
+        <v>0.1965367773197789</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>-0.2640831403533797</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
+        <v>-0.2640831403533797</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0.4432416002942154</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA37" t="n">
+        <v>5.300325705025008</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>5.300325705025008</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>8KfYbJz0</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>45520.64583333334</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>brescia</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>palermo</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>77</v>
+      </c>
+      <c r="F38" t="n">
+        <v>774</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K38" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L38" t="n">
+        <v>0.3445218492716909</v>
+      </c>
+      <c r="M38" t="n">
+        <v>0.2906903103229892</v>
+      </c>
+      <c r="N38" t="n">
+        <v>0.3647878404053199</v>
+      </c>
+      <c r="O38" t="n">
+        <v>0.07502723311546844</v>
+      </c>
+      <c r="P38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>0.3367780039401967</v>
+      </c>
+      <c r="R38" t="n">
+        <v>0.3764672773068026</v>
+      </c>
+      <c r="S38" t="n">
+        <v>0.2867547187530007</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0.08577696698381337</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0.08577696698381337</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0.3764672773068026</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA38" t="n">
+        <v>4.501831925716168</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>4.501831925716168</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>EL1P0u6m</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>bari</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>juve stabia</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>77</v>
+      </c>
+      <c r="F39" t="n">
+        <v>774</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J39" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K39" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L39" t="n">
+        <v>0.4882740930743861</v>
+      </c>
+      <c r="M39" t="n">
+        <v>0.2854525467204104</v>
+      </c>
+      <c r="N39" t="n">
+        <v>0.2262733602052034</v>
+      </c>
+      <c r="O39" t="n">
+        <v>0.07791053619038224</v>
+      </c>
+      <c r="P39" t="inlineStr"/>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr"/>
+      <c r="S39" t="inlineStr"/>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="inlineStr"/>
+      <c r="V39" t="n">
+        <v>0</v>
+      </c>
+      <c r="W39" t="inlineStr"/>
+      <c r="X39" t="inlineStr"/>
+      <c r="Y39" t="n">
+        <v>1.298333333333333</v>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr"/>
+      <c r="AB39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>M5TEBdK5</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>pisa</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>spezia</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>77</v>
+      </c>
+      <c r="F40" t="n">
+        <v>774</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K40" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L40" t="n">
+        <v>0.3717001055966209</v>
+      </c>
+      <c r="M40" t="n">
+        <v>0.2903907074973601</v>
+      </c>
+      <c r="N40" t="n">
+        <v>0.337909186906019</v>
+      </c>
+      <c r="O40" t="n">
+        <v>0.07613636363636367</v>
+      </c>
+      <c r="P40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q40" t="n">
+        <v>0.3756920060779301</v>
+      </c>
+      <c r="R40" t="n">
+        <v>0.3707025927836255</v>
+      </c>
+      <c r="S40" t="n">
+        <v>0.2536054011384444</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0.003991900481309207</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0.003991900481309207</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0.3756920060779301</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA40" t="n">
+        <v>4.492561157764714</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>4.492561157764714</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>joLV7EJU</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>salernitana</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>cittadella</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>77</v>
+      </c>
+      <c r="F41" t="n">
+        <v>774</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J41" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K41" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L41" t="n">
+        <v>0.5038814396612561</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.2741707833450953</v>
+      </c>
+      <c r="N41" t="n">
+        <v>0.2219477769936486</v>
+      </c>
+      <c r="O41" t="n">
+        <v>0.07275342569460208</v>
+      </c>
+      <c r="P41" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>0.451473230128809</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.3906070948948772</v>
+      </c>
+      <c r="S41" t="n">
+        <v>0.1579196749763142</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>-0.05240820953244713</v>
+      </c>
+      <c r="V41" t="n">
+        <v>1</v>
+      </c>
+      <c r="W41" t="n">
+        <v>-0.05240820953244713</v>
+      </c>
+      <c r="X41" t="n">
+        <v>0.451473230128809</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA41" t="n">
+        <v>5.3987603266345</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>5.3987603266345</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
+        <is>
+          <t>WvwvCQVo</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>45521.64583333334</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>sudtirol</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>modena</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>77</v>
+      </c>
+      <c r="F42" t="n">
+        <v>774</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K42" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L42" t="n">
+        <v>0.3565379226699568</v>
+      </c>
+      <c r="M42" t="n">
+        <v>0.3024821731038665</v>
+      </c>
+      <c r="N42" t="n">
+        <v>0.3409799042261768</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0.06644514567978321</v>
+      </c>
+      <c r="P42" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>0.3608228613228148</v>
+      </c>
+      <c r="R42" t="n">
+        <v>0.3731320384211683</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0.2660451002560169</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0.07064986531730177</v>
+      </c>
+      <c r="V42" t="n">
+        <v>0</v>
+      </c>
+      <c r="W42" t="n">
+        <v>0.07064986531730177</v>
+      </c>
+      <c r="X42" t="n">
+        <v>0.3731320384211683</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA42" t="n">
+        <v>4.461948818205067</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>4.461948818205067</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="inlineStr">
+        <is>
+          <t>tYhtcc5C</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>catanzaro</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>sassuolo</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>77</v>
+      </c>
+      <c r="F43" t="n">
+        <v>774</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K43" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L43" t="n">
+        <v>0.337909186906019</v>
+      </c>
+      <c r="M43" t="n">
+        <v>0.2903907074973601</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0.3717001055966209</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0.07613636363636367</v>
+      </c>
+      <c r="P43" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>0.3108635204583116</v>
+      </c>
+      <c r="R43" t="n">
+        <v>0.3578218819267946</v>
+      </c>
+      <c r="S43" t="n">
+        <v>0.3313145976148936</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0.06743117442943458</v>
+      </c>
+      <c r="V43" t="n">
+        <v>0</v>
+      </c>
+      <c r="W43" t="n">
+        <v>0.06743117442943458</v>
+      </c>
+      <c r="X43" t="n">
+        <v>0.3578218819267946</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA43" t="n">
+        <v>4.278868493702089</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>4.278868493702089</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="inlineStr">
+        <is>
+          <t>x0nkeyzP</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>cesena</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>carrarese</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>77</v>
+      </c>
+      <c r="F44" t="n">
+        <v>774</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J44" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K44" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L44" t="n">
+        <v>0.5008809239913865</v>
+      </c>
+      <c r="M44" t="n">
+        <v>0.2851168336566354</v>
+      </c>
+      <c r="N44" t="n">
+        <v>0.2140022423519781</v>
+      </c>
+      <c r="O44" t="n">
+        <v>0.0791797304499382</v>
+      </c>
+      <c r="P44" t="inlineStr"/>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr"/>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="inlineStr"/>
+      <c r="V44" t="n">
+        <v>0</v>
+      </c>
+      <c r="W44" t="inlineStr"/>
+      <c r="X44" t="inlineStr"/>
+      <c r="Y44" t="n">
+        <v>1.296197411003236</v>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr"/>
+      <c r="AB44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>SORbFvLt</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>cosenza</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>cremonese</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>77</v>
+      </c>
+      <c r="F45" t="n">
+        <v>774</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K45" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L45" t="n">
+        <v>0.2894736842105263</v>
+      </c>
+      <c r="M45" t="n">
+        <v>0.2894736842105263</v>
+      </c>
+      <c r="N45" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+      <c r="O45" t="n">
+        <v>0.07954545454545459</v>
+      </c>
+      <c r="P45" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="n">
+        <v>0.3280777917885559</v>
+      </c>
+      <c r="R45" t="n">
+        <v>0.3757227652145617</v>
+      </c>
+      <c r="S45" t="n">
+        <v>0.2961994429968821</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0.08624908100403533</v>
+      </c>
+      <c r="V45" t="n">
+        <v>0</v>
+      </c>
+      <c r="W45" t="n">
+        <v>0.08624908100403533</v>
+      </c>
+      <c r="X45" t="n">
+        <v>0.3757227652145617</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA45" t="n">
+        <v>4.492928978480197</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>4.492928978480197</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>lvG7DIkg</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>45522.64583333334</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>frosinone</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>sampdoria</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>77</v>
+      </c>
+      <c r="F46" t="n">
+        <v>774</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K46" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L46" t="n">
+        <v>0.3717001055966209</v>
+      </c>
+      <c r="M46" t="n">
+        <v>0.2903907074973601</v>
+      </c>
+      <c r="N46" t="n">
+        <v>0.337909186906019</v>
+      </c>
+      <c r="O46" t="n">
+        <v>0.07613636363636367</v>
+      </c>
+      <c r="P46" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0.3773957808071</v>
+      </c>
+      <c r="R46" t="n">
+        <v>0.3827954136711871</v>
+      </c>
+      <c r="S46" t="n">
+        <v>0.2398088055217128</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0.09240470617382701</v>
+      </c>
+      <c r="V46" t="n">
+        <v>0</v>
+      </c>
+      <c r="W46" t="n">
+        <v>0.09240470617382701</v>
+      </c>
+      <c r="X46" t="n">
+        <v>0.3827954136711871</v>
+      </c>
+      <c r="Y46" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA46" t="n">
+        <v>4.577504389254758</v>
+      </c>
+      <c r="AB46" t="n">
+        <v>4.577504389254758</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="inlineStr">
+        <is>
           <t>IXMN9zkI</t>
         </is>
       </c>
-      <c r="B37" s="2" t="n">
+      <c r="B47" s="2" t="n">
         <v>45522.64583333334</v>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>reggiana</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
+      <c r="D47" t="inlineStr">
         <is>
           <t>mantova</t>
         </is>
       </c>
-      <c r="E37" t="n">
-        <v>77</v>
-      </c>
-      <c r="F37" t="n">
+      <c r="E47" t="n">
+        <v>77</v>
+      </c>
+      <c r="F47" t="n">
         <v>774</v>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
         <is>
           <t>serie b</t>
         </is>
       </c>
-      <c r="I37" t="n">
+      <c r="I47" t="n">
         <v>2.55</v>
       </c>
-      <c r="J37" t="n">
+      <c r="J47" t="n">
         <v>3.1</v>
       </c>
-      <c r="K37" t="n">
+      <c r="K47" t="n">
         <v>2.75</v>
       </c>
-      <c r="L37" t="n">
+      <c r="L47" t="n">
         <v>0.3636557534392663</v>
       </c>
-      <c r="M37" t="n">
+      <c r="M47" t="n">
         <v>0.2991361842806867</v>
       </c>
-      <c r="N37" t="n">
+      <c r="N47" t="n">
         <v>0.3372080622800468</v>
       </c>
-      <c r="O37" t="n">
+      <c r="O47" t="n">
         <v>0.07837387154275222</v>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr"/>
-      <c r="R37" t="inlineStr"/>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="n">
-        <v>1</v>
-      </c>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="n">
-        <v>-100</v>
-      </c>
-      <c r="W37" t="inlineStr"/>
-      <c r="X37" t="inlineStr"/>
-      <c r="Y37" t="n">
-        <v>1.32311320754717</v>
-      </c>
-      <c r="Z37" t="inlineStr">
+      <c r="P47" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>0.3553690977034535</v>
+      </c>
+      <c r="R47" t="n">
+        <v>0.3685930125120004</v>
+      </c>
+      <c r="S47" t="n">
+        <v>0.2760378897845459</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0.06945682823131366</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0</v>
+      </c>
+      <c r="W47" t="n">
+        <v>0.06945682823131366</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.3685930125120004</v>
+      </c>
+      <c r="Y47" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA47" t="n">
+        <v>4.407670709638165</v>
+      </c>
+      <c r="AB47" t="n">
+        <v>4.407670709638165</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="inlineStr">
+        <is>
+          <t>4CX22Dbk</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>45527.64583333334</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>modena</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>bari</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>77</v>
+      </c>
+      <c r="F48" t="n">
+        <v>774</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr"/>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="n">
+        <v>0.3757608572110148</v>
+      </c>
+      <c r="R48" t="n">
+        <v>0.3768820209585328</v>
+      </c>
+      <c r="S48" t="n">
+        <v>0.2473571218304522</v>
+      </c>
+      <c r="T48" t="n">
+        <v>1</v>
+      </c>
+      <c r="U48" t="inlineStr"/>
+      <c r="V48" t="n">
+        <v>0</v>
+      </c>
+      <c r="W48" t="inlineStr"/>
+      <c r="X48" t="n">
+        <v>0.6231179790414672</v>
+      </c>
+      <c r="Y48" t="inlineStr"/>
+      <c r="Z48" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA37" t="inlineStr"/>
-      <c r="AB37" t="inlineStr"/>
+      <c r="AA48" t="n">
+        <v>7.451304749789808</v>
+      </c>
+      <c r="AB48" t="n">
+        <v>7.451304749789808</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="inlineStr">
+        <is>
+          <t>CjGqFjre</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>45528.60416666666</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>sudtirol</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>salernitana</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>77</v>
+      </c>
+      <c r="F49" t="n">
+        <v>774</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr"/>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>0.3137424962042789</v>
+      </c>
+      <c r="R49" t="n">
+        <v>0.3776364466040546</v>
+      </c>
+      <c r="S49" t="n">
+        <v>0.3086210571916663</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="inlineStr"/>
+      <c r="V49" t="n">
+        <v>0</v>
+      </c>
+      <c r="W49" t="inlineStr"/>
+      <c r="X49" t="n">
+        <v>0.6223635533959454</v>
+      </c>
+      <c r="Y49" t="inlineStr"/>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA49" t="n">
+        <v>7.442283255329823</v>
+      </c>
+      <c r="AB49" t="n">
+        <v>7.442283255329823</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="inlineStr">
+        <is>
+          <t>0IkylEqd</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>brescia</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>cittadella</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>77</v>
+      </c>
+      <c r="F50" t="n">
+        <v>774</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0.3890088333497214</v>
+      </c>
+      <c r="R50" t="n">
+        <v>0.3678489634003708</v>
+      </c>
+      <c r="S50" t="n">
+        <v>0.2431422032499077</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="inlineStr"/>
+      <c r="V50" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W50" t="inlineStr"/>
+      <c r="X50" t="n">
+        <v>0.6109911666502786</v>
+      </c>
+      <c r="Y50" t="inlineStr"/>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA50" t="n">
+        <v>7.306291160374087</v>
+      </c>
+      <c r="AB50" t="n">
+        <v>7.306291160374087</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr">
+        <is>
+          <t>CEhO9e6F</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>cremonese</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>carrarese</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>77</v>
+      </c>
+      <c r="F51" t="n">
+        <v>774</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0.4327026951974696</v>
+      </c>
+      <c r="R51" t="n">
+        <v>0.3652339324847403</v>
+      </c>
+      <c r="S51" t="n">
+        <v>0.2020633723177898</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="inlineStr"/>
+      <c r="V51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="n">
+        <v>0.5672973048025305</v>
+      </c>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA51" t="n">
+        <v>6.783795756175327</v>
+      </c>
+      <c r="AB51" t="n">
+        <v>6.783795756175327</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="inlineStr">
+        <is>
+          <t>CxyB0iT1</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>pisa</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>palermo</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>77</v>
+      </c>
+      <c r="F52" t="n">
+        <v>774</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0.354437542674017</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0.3704708076174809</v>
+      </c>
+      <c r="S52" t="n">
+        <v>0.275091649708502</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="inlineStr"/>
+      <c r="V52" t="n">
+        <v>0</v>
+      </c>
+      <c r="W52" t="inlineStr"/>
+      <c r="X52" t="n">
+        <v>0.6295291923825191</v>
+      </c>
+      <c r="Y52" t="inlineStr"/>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA52" t="n">
+        <v>7.527970655809055</v>
+      </c>
+      <c r="AB52" t="n">
+        <v>7.527970655809055</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="inlineStr">
+        <is>
+          <t>CSXdOfL8</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>sampdoria</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>reggiana</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>77</v>
+      </c>
+      <c r="F53" t="n">
+        <v>774</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>0.4490753614139523</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0.3975072312824112</v>
+      </c>
+      <c r="S53" t="n">
+        <v>0.1534174073036365</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="inlineStr"/>
+      <c r="V53" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W53" t="inlineStr"/>
+      <c r="X53" t="n">
+        <v>0.5509246385860477</v>
+      </c>
+      <c r="Y53" t="inlineStr"/>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA53" t="n">
+        <v>6.588009838180683</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>6.588009838180683</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="inlineStr">
+        <is>
+          <t>ptW4MYkL</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>sassuolo</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>cesena</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>77</v>
+      </c>
+      <c r="F54" t="n">
+        <v>774</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" t="inlineStr"/>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr"/>
+      <c r="S54" t="inlineStr"/>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="inlineStr"/>
+      <c r="V54" t="n">
+        <v>0</v>
+      </c>
+      <c r="W54" t="inlineStr"/>
+      <c r="X54" t="inlineStr"/>
+      <c r="Y54" t="inlineStr"/>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr"/>
+      <c r="AB54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="inlineStr">
+        <is>
+          <t>4QCyHCDr</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>45528.64583333334</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>spezia</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>frosinone</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>77</v>
+      </c>
+      <c r="F55" t="n">
+        <v>774</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>0.3456922516554832</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0.3768957475976318</v>
+      </c>
+      <c r="S55" t="n">
+        <v>0.2774120007468848</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="inlineStr"/>
+      <c r="V55" t="n">
+        <v>0</v>
+      </c>
+      <c r="W55" t="inlineStr"/>
+      <c r="X55" t="n">
+        <v>0.6231042524023682</v>
+      </c>
+      <c r="Y55" t="inlineStr"/>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA55" t="n">
+        <v>7.451140605318685</v>
+      </c>
+      <c r="AB55" t="n">
+        <v>7.451140605318685</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>hCxNBHy3</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>45529.64583333334</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>catanzaro</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>juve stabia</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>77</v>
+      </c>
+      <c r="F56" t="n">
+        <v>774</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" t="inlineStr"/>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr"/>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="inlineStr"/>
+      <c r="V56" t="n">
+        <v>0</v>
+      </c>
+      <c r="W56" t="inlineStr"/>
+      <c r="X56" t="inlineStr"/>
+      <c r="Y56" t="inlineStr"/>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr"/>
+      <c r="AB56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="inlineStr">
+        <is>
+          <t>KvdW7ZzS</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>45529.64583333334</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>mantova</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>cosenza</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>77</v>
+      </c>
+      <c r="F57" t="n">
+        <v>774</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>0.4144769306926992</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.3632828037410173</v>
+      </c>
+      <c r="S57" t="n">
+        <v>0.2222402655662838</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="inlineStr"/>
+      <c r="V57" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W57" t="inlineStr"/>
+      <c r="X57" t="n">
+        <v>0.5855230693073008</v>
+      </c>
+      <c r="Y57" t="inlineStr"/>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA57" t="n">
+        <v>7.001741201806432</v>
+      </c>
+      <c r="AB57" t="n">
+        <v>7.001741201806432</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="inlineStr">
+        <is>
+          <t>Y54hDUC7</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>bari</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>sassuolo</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>77</v>
+      </c>
+      <c r="F58" t="n">
+        <v>774</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
+      <c r="N58" t="inlineStr"/>
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0.303302606240299</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.3794820466945786</v>
+      </c>
+      <c r="S58" t="n">
+        <v>0.3172153470651222</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="inlineStr"/>
+      <c r="V58" t="n">
+        <v>0</v>
+      </c>
+      <c r="W58" t="inlineStr"/>
+      <c r="X58" t="n">
+        <v>0.6205179533054214</v>
+      </c>
+      <c r="Y58" t="inlineStr"/>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA58" t="n">
+        <v>7.420213391863696</v>
+      </c>
+      <c r="AB58" t="n">
+        <v>7.420213391863696</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="inlineStr">
+        <is>
+          <t>v3ivyY4E</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>carrarese</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>sudtirol</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>77</v>
+      </c>
+      <c r="F59" t="n">
+        <v>774</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0.3721384289361635</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0.3751764575966294</v>
+      </c>
+      <c r="S59" t="n">
+        <v>0.2526851134672073</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="inlineStr"/>
+      <c r="V59" t="n">
+        <v>0</v>
+      </c>
+      <c r="W59" t="inlineStr"/>
+      <c r="X59" t="n">
+        <v>0.6248235424033706</v>
+      </c>
+      <c r="Y59" t="inlineStr"/>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA59" t="n">
+        <v>7.471700040580755</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>7.471700040580755</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="inlineStr">
+        <is>
+          <t>W0WITkcl</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>cittadella</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>pisa</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>77</v>
+      </c>
+      <c r="F60" t="n">
+        <v>774</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>0.3694349518469551</v>
+      </c>
+      <c r="R60" t="n">
+        <v>0.3660894300422443</v>
+      </c>
+      <c r="S60" t="n">
+        <v>0.2644756181108006</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="inlineStr"/>
+      <c r="V60" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W60" t="inlineStr"/>
+      <c r="X60" t="n">
+        <v>0.6305650481530449</v>
+      </c>
+      <c r="Y60" t="inlineStr"/>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA60" t="n">
+        <v>7.540357518783044</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>7.540357518783044</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="inlineStr">
+        <is>
+          <t>YPSZP7dD</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>cremonese</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>palermo</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>77</v>
+      </c>
+      <c r="F61" t="n">
+        <v>774</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
+      <c r="N61" t="inlineStr"/>
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0.3649253957792764</v>
+      </c>
+      <c r="R61" t="n">
+        <v>0.3701258744827766</v>
+      </c>
+      <c r="S61" t="n">
+        <v>0.264948729737947</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="inlineStr"/>
+      <c r="V61" t="n">
+        <v>0</v>
+      </c>
+      <c r="W61" t="inlineStr"/>
+      <c r="X61" t="n">
+        <v>0.6298741255172234</v>
+      </c>
+      <c r="Y61" t="inlineStr"/>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA61" t="n">
+        <v>7.532095399423315</v>
+      </c>
+      <c r="AB61" t="n">
+        <v>7.532095399423315</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="inlineStr">
+        <is>
+          <t>EL5MmBlK</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>frosinone</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>modena</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>77</v>
+      </c>
+      <c r="F62" t="n">
+        <v>774</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0.4411561310487624</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0.3891545663301597</v>
+      </c>
+      <c r="S62" t="n">
+        <v>0.1696893026210779</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="inlineStr"/>
+      <c r="V62" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W62" t="inlineStr"/>
+      <c r="X62" t="n">
+        <v>0.5588438689512376</v>
+      </c>
+      <c r="Y62" t="inlineStr"/>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA62" t="n">
+        <v>6.68270875687597</v>
+      </c>
+      <c r="AB62" t="n">
+        <v>6.68270875687597</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="inlineStr">
+        <is>
+          <t>tWk1tTtf</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>reggiana</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>brescia</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>77</v>
+      </c>
+      <c r="F63" t="n">
+        <v>774</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0.3592825889470761</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0.3547347492945213</v>
+      </c>
+      <c r="S63" t="n">
+        <v>0.2859826617584027</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="inlineStr"/>
+      <c r="V63" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W63" t="inlineStr"/>
+      <c r="X63" t="n">
+        <v>0.6407174110529239</v>
+      </c>
+      <c r="Y63" t="inlineStr"/>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA63" t="n">
+        <v>7.661760451200156</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>7.661760451200156</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="inlineStr">
+        <is>
+          <t>Eql9v7B6</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>45531.64583333334</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>salernitana</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>sampdoria</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>77</v>
+      </c>
+      <c r="F64" t="n">
+        <v>774</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>serie b</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0.4082351488621532</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0.3819978722007473</v>
+      </c>
+      <c r="S64" t="n">
+        <v>0.2097669789370997</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="inlineStr"/>
+      <c r="V64" t="n">
+        <v>-1</v>
+      </c>
+      <c r="W64" t="inlineStr"/>
+      <c r="X64" t="n">
+        <v>0.5917648511378468</v>
+      </c>
+      <c r="Y64" t="inlineStr"/>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA64" t="n">
+        <v>7.076381029520348</v>
+      </c>
+      <c r="AB64" t="n">
+        <v>7.076381029520348</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB64"/>
+  <dimension ref="A1:AB38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -629,28 +629,28 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.231089286465845</v>
+        <v>0.2310892864658447</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5286117119289155</v>
+        <v>0.5286117119289154</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2402990016052396</v>
+        <v>0.2402990016052395</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.283963393886102</v>
+        <v>0.2839633938861019</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.283963393886102</v>
+        <v>0.2839633938861019</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5286117119289155</v>
+        <v>0.5286117119289154</v>
       </c>
       <c r="Y2" t="n">
         <v>3.9</v>
@@ -661,10 +661,10 @@
         </is>
       </c>
       <c r="AA2" t="n">
-        <v>6.321189714264894</v>
+        <v>6.321189714264892</v>
       </c>
       <c r="AB2" t="n">
-        <v>6.321189714264894</v>
+        <v>6.321189714264892</v>
       </c>
     </row>
     <row r="3">
@@ -730,25 +730,25 @@
         <v>0.2721984624866746</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3955889392848772</v>
+        <v>0.3955889392848773</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3322125982284482</v>
+        <v>0.332212598228448</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1007705950323459</v>
+        <v>0.100770595032346</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1007705950323459</v>
+        <v>0.100770595032346</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3955889392848772</v>
+        <v>0.3955889392848773</v>
       </c>
       <c r="Y3" t="n">
         <v>3.2</v>
@@ -759,10 +759,10 @@
         </is>
       </c>
       <c r="AA3" t="n">
-        <v>4.730490599536298</v>
+        <v>4.730490599536301</v>
       </c>
       <c r="AB3" t="n">
-        <v>4.730490599536298</v>
+        <v>4.730490599536301</v>
       </c>
     </row>
     <row r="4">
@@ -825,28 +825,28 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4409651627399412</v>
+        <v>0.4409651627399414</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4922799098103214</v>
+        <v>0.4922799098103212</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06675492744973731</v>
+        <v>0.06675492744973728</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2154967804010663</v>
+        <v>0.2154967804010661</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2154967804010663</v>
+        <v>0.2154967804010661</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4922799098103214</v>
+        <v>0.4922799098103212</v>
       </c>
       <c r="Y4" t="n">
         <v>3.4</v>
@@ -857,10 +857,10 @@
         </is>
       </c>
       <c r="AA4" t="n">
-        <v>5.886730528684745</v>
+        <v>5.886730528684742</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.886730528684745</v>
+        <v>5.886730528684742</v>
       </c>
     </row>
     <row r="5">
@@ -923,10 +923,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3432792651049772</v>
+        <v>0.3432792651049771</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3543279564632452</v>
+        <v>0.3543279564632453</v>
       </c>
       <c r="S5" t="n">
         <v>0.3023927784317775</v>
@@ -935,16 +935,16 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.06021030940442168</v>
+        <v>0.06021030940442179</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.06021030940442168</v>
+        <v>0.06021030940442179</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3543279564632452</v>
+        <v>0.3543279564632453</v>
       </c>
       <c r="Y5" t="n">
         <v>3.2</v>
@@ -955,10 +955,10 @@
         </is>
       </c>
       <c r="AA5" t="n">
-        <v>4.237087796823457</v>
+        <v>4.237087796823459</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.237087796823457</v>
+        <v>4.237087796823459</v>
       </c>
     </row>
     <row r="6">
@@ -1021,10 +1021,10 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4263244288423755</v>
+        <v>0.4263244288423754</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3762490824269034</v>
+        <v>0.3762490824269036</v>
       </c>
       <c r="S6" t="n">
         <v>0.1974264887307212</v>
@@ -1033,16 +1033,16 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0815353051358591</v>
+        <v>-0.08153530513585922</v>
       </c>
       <c r="V6" t="n">
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0815353051358591</v>
+        <v>-0.08153530513585922</v>
       </c>
       <c r="X6" t="n">
-        <v>0.4263244288423755</v>
+        <v>0.4263244288423754</v>
       </c>
       <c r="Y6" t="n">
         <v>1.85</v>
@@ -1053,10 +1053,10 @@
         </is>
       </c>
       <c r="AA6" t="n">
-        <v>5.098028541033669</v>
+        <v>5.098028541033668</v>
       </c>
       <c r="AB6" t="n">
-        <v>5.098028541033669</v>
+        <v>5.098028541033668</v>
       </c>
     </row>
     <row r="7">
@@ -1122,25 +1122,25 @@
         <v>0.2328120564895247</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5140106702717958</v>
+        <v>0.5140106702717956</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2531772732386793</v>
+        <v>0.2531772732386796</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.235430311888687</v>
+        <v>0.2354303118886868</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.235430311888687</v>
+        <v>0.2354303118886868</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5140106702717958</v>
+        <v>0.5140106702717956</v>
       </c>
       <c r="Y7" t="n">
         <v>3.4</v>
@@ -1151,10 +1151,10 @@
         </is>
       </c>
       <c r="AA7" t="n">
-        <v>6.146589053216828</v>
+        <v>6.146589053216825</v>
       </c>
       <c r="AB7" t="n">
-        <v>6.146589053216828</v>
+        <v>6.146589053216825</v>
       </c>
     </row>
     <row r="8">
@@ -1220,25 +1220,25 @@
         <v>0.2448521973339274</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4929704812753666</v>
+        <v>0.4929704812753667</v>
       </c>
       <c r="S8" t="n">
-        <v>0.262177321390706</v>
+        <v>0.2621773213907059</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2163747365945156</v>
+        <v>0.2163747365945157</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2163747365945156</v>
+        <v>0.2163747365945157</v>
       </c>
       <c r="X8" t="n">
-        <v>0.4929704812753666</v>
+        <v>0.4929704812753667</v>
       </c>
       <c r="Y8" t="n">
         <v>3.4</v>
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="AA8" t="n">
-        <v>5.894988448710542</v>
+        <v>5.894988448710544</v>
       </c>
       <c r="AB8" t="n">
-        <v>5.894988448710542</v>
+        <v>5.894988448710544</v>
       </c>
     </row>
     <row r="9">
@@ -1315,28 +1315,28 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.468856395386621</v>
+        <v>0.4688563953866209</v>
       </c>
       <c r="R9" t="n">
         <v>0.4642418806297189</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06690172398366027</v>
+        <v>0.06690172398366023</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.151922648204347</v>
+        <v>-0.1519226482043471</v>
       </c>
       <c r="V9" t="n">
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.151922648204347</v>
+        <v>-0.1519226482043471</v>
       </c>
       <c r="X9" t="n">
-        <v>0.468856395386621</v>
+        <v>0.4688563953866209</v>
       </c>
       <c r="Y9" t="n">
         <v>1.53</v>
@@ -1347,10 +1347,10 @@
         </is>
       </c>
       <c r="AA9" t="n">
-        <v>5.606629889395578</v>
+        <v>5.606629889395577</v>
       </c>
       <c r="AB9" t="n">
-        <v>5.606629889395578</v>
+        <v>5.606629889395577</v>
       </c>
     </row>
     <row r="10">
@@ -1413,28 +1413,28 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2649340803901595</v>
+        <v>0.2649340803901593</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4079691971374362</v>
+        <v>0.4079691971374361</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3270967224724041</v>
+        <v>0.3270967224724045</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1517191971374362</v>
+        <v>0.1517191971374361</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1517191971374362</v>
+        <v>0.1517191971374361</v>
       </c>
       <c r="X10" t="n">
-        <v>0.4079691971374362</v>
+        <v>0.4079691971374361</v>
       </c>
       <c r="Y10" t="n">
         <v>3.7</v>
@@ -1445,10 +1445,10 @@
         </is>
       </c>
       <c r="AA10" t="n">
-        <v>4.87853491416561</v>
+        <v>4.878534914165609</v>
       </c>
       <c r="AB10" t="n">
-        <v>4.87853491416561</v>
+        <v>4.878534914165609</v>
       </c>
     </row>
     <row r="11">
@@ -1511,28 +1511,28 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4893694367471452</v>
+        <v>0.4893694367471447</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4557035722872</v>
+        <v>0.4557035722872004</v>
       </c>
       <c r="S11" t="n">
-        <v>0.05492699096565484</v>
+        <v>0.05492699096565488</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2218681165956714</v>
+        <v>-0.2218681165956718</v>
       </c>
       <c r="V11" t="n">
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.2218681165956714</v>
+        <v>-0.2218681165956718</v>
       </c>
       <c r="X11" t="n">
-        <v>0.4893694367471452</v>
+        <v>0.4893694367471447</v>
       </c>
       <c r="Y11" t="n">
         <v>1.33</v>
@@ -1543,36 +1543,36 @@
         </is>
       </c>
       <c r="AA11" t="n">
-        <v>5.851926811749566</v>
+        <v>5.851926811749561</v>
       </c>
       <c r="AB11" t="n">
-        <v>5.851926811749566</v>
+        <v>5.851926811749561</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>QT6wuRFc</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45513.54166666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>sassuolo</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>cittadella</t>
         </is>
       </c>
       <c r="E12" t="n">
         <v>77</v>
       </c>
       <c r="F12" t="n">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -1581,60 +1581,80 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.562008242787561</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2502810041213938</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1877107530910453</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.06546906187624746</v>
+      </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.224658399682957</v>
+        <v>0.4725404168615687</v>
       </c>
       <c r="R12" t="n">
-        <v>0.495380450945221</v>
+        <v>0.3926188100065349</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2799611493718221</v>
+        <v>0.1348407731318965</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="n">
+        <v>-0.08946782592599234</v>
+      </c>
       <c r="V12" t="n">
-        <v>0</v>
-      </c>
-      <c r="W12" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>-0.08946782592599234</v>
+      </c>
       <c r="X12" t="n">
-        <v>0.504619549054779</v>
-      </c>
-      <c r="Y12" t="inlineStr"/>
+        <v>0.4725404168615687</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>1.67</v>
+      </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA12" t="n">
-        <v>6.034289122090057</v>
+        <v>5.650683772669549</v>
       </c>
       <c r="AB12" t="n">
-        <v>6.034289122090057</v>
+        <v>5.650683772669549</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>dnnqk0iD</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45513.5625</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1643,14 +1663,14 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>avellino</t>
         </is>
       </c>
       <c r="E13" t="n">
         <v>77</v>
       </c>
       <c r="F13" t="n">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1659,76 +1679,96 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="J13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>15</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.7935216082037927</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.1440546919508424</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.06242369984536501</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06797044763146465</v>
+      </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2476237725704289</v>
+        <v>0.4183089128910982</v>
       </c>
       <c r="R13" t="n">
-        <v>0.500742939995815</v>
+        <v>0.3536008815331639</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2516332874337562</v>
+        <v>0.2280902055757377</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
-      <c r="U13" t="inlineStr"/>
+      <c r="U13" t="n">
+        <v>-0.3752126953126945</v>
+      </c>
       <c r="V13" t="n">
-        <v>0</v>
-      </c>
-      <c r="W13" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-0.3752126953126945</v>
+      </c>
       <c r="X13" t="n">
-        <v>0.499257060004185</v>
-      </c>
-      <c r="Y13" t="inlineStr"/>
+        <v>0.4183089128910982</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.18</v>
+      </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA13" t="n">
-        <v>5.970163962044358</v>
+        <v>5.002178230035351</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.970163962044358</v>
+        <v>5.002178230035351</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>hvcjgHz8</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.65625</v>
+        <v>45513.65625</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>reggiana</t>
         </is>
       </c>
       <c r="E14" t="n">
         <v>77</v>
       </c>
       <c r="F14" t="n">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1737,60 +1777,80 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="K14" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6914119359534208</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.197962154294032</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.1106259097525473</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06346749226006176</v>
+      </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.3489453164034246</v>
+        <v>0.472582989195004</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6141992265002049</v>
+        <v>0.4100639129913397</v>
       </c>
       <c r="S14" t="n">
-        <v>0.03685545709637053</v>
+        <v>0.1173530978136564</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
-      <c r="U14" t="inlineStr"/>
+      <c r="U14" t="n">
+        <v>-0.2188289467584168</v>
+      </c>
       <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>-0.2188289467584168</v>
+      </c>
       <c r="X14" t="n">
-        <v>0.3858007734997951</v>
-      </c>
-      <c r="Y14" t="inlineStr"/>
+        <v>0.472582989195004</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>1.36</v>
+      </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA14" t="n">
-        <v>4.613442771260976</v>
+        <v>5.651192856729078</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.613442771260976</v>
+        <v>5.651192856729078</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>AZ3PVMxp</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45528.65625</v>
+        <v>45513.67708333334</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -1799,14 +1859,14 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>sudtirol</t>
         </is>
       </c>
       <c r="E15" t="n">
         <v>77</v>
       </c>
       <c r="F15" t="n">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1815,76 +1875,96 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.6530742274609749</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2293724115960497</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.1175533609429755</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06334688346883466</v>
+      </c>
       <c r="P15" t="n">
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.4034853929127025</v>
+        <v>0.4749577505329112</v>
       </c>
       <c r="R15" t="n">
-        <v>0.357237577853434</v>
+        <v>0.3973738417595458</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2392770292338635</v>
+        <v>0.1276684077075429</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
-      <c r="U15" t="inlineStr"/>
+      <c r="U15" t="n">
+        <v>-0.1781164769280637</v>
+      </c>
       <c r="V15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W15" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>-0.1781164769280637</v>
+      </c>
       <c r="X15" t="n">
-        <v>0.5965146070872975</v>
-      </c>
-      <c r="Y15" t="inlineStr"/>
+        <v>0.4749577505329112</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.44</v>
+      </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA15" t="n">
-        <v>7.133179068185398</v>
+        <v>5.679590481307308</v>
       </c>
       <c r="AB15" t="n">
-        <v>7.133179068185398</v>
+        <v>5.679590481307308</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>bs5ow5pA</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45514.54166666666</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>cremonese</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>bari</t>
         </is>
       </c>
       <c r="E16" t="n">
         <v>77</v>
       </c>
       <c r="F16" t="n">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1893,76 +1973,96 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.5071721311475409</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2843237704918032</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.2085040983606557</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06579306579306587</v>
+      </c>
       <c r="P16" t="n">
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4791886494945383</v>
+        <v>0.4008732509736669</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4226214921002333</v>
+        <v>0.3715855311020828</v>
       </c>
       <c r="S16" t="n">
-        <v>0.09818985840522836</v>
+        <v>0.2275412179242504</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
-      <c r="U16" t="inlineStr"/>
+      <c r="U16" t="n">
+        <v>-0.106298880173874</v>
+      </c>
       <c r="V16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W16" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>-0.106298880173874</v>
+      </c>
       <c r="X16" t="n">
-        <v>0.5208113505054617</v>
-      </c>
-      <c r="Y16" t="inlineStr"/>
+        <v>0.4008732509736669</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>1.85</v>
+      </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA16" t="n">
-        <v>6.227912241812456</v>
+        <v>4.793680907167317</v>
       </c>
       <c r="AB16" t="n">
-        <v>6.227912241812456</v>
+        <v>4.793680907167317</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>02s0k9od</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45514.5625</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>cesena</t>
         </is>
       </c>
       <c r="E17" t="n">
         <v>77</v>
       </c>
       <c r="F17" t="n">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1971,28 +2071,34 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.3039414411183158</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.3698546877699536</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.3262038711117304</v>
-      </c>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.5970774629445346</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2466872675849787</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.1562352694704865</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.06676723656274453</v>
+      </c>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
       <c r="T17" t="n">
         <v>1</v>
       </c>
@@ -2001,46 +2107,42 @@
         <v>0</v>
       </c>
       <c r="W17" t="inlineStr"/>
-      <c r="X17" t="n">
-        <v>0.6301453122300464</v>
-      </c>
-      <c r="Y17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="n">
+        <v>1.244385733157199</v>
+      </c>
       <c r="Z17" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
-      <c r="AA17" t="n">
-        <v>7.535338276228838</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>7.535338276228838</v>
-      </c>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>UilLdutJ</t>
+          <t>Ob5Zdayq</t>
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>45529.65625</v>
+        <v>45514.65625</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>catanzaro</t>
         </is>
       </c>
       <c r="E18" t="n">
         <v>77</v>
       </c>
       <c r="F18" t="n">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -2049,60 +2151,80 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.6263219741480611</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2291421856639248</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.1445358401880141</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06441525953721072</v>
+      </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.4103593250455935</v>
+        <v>0.4402219831272048</v>
       </c>
       <c r="R18" t="n">
-        <v>0.5360227798097519</v>
+        <v>0.3643307535591714</v>
       </c>
       <c r="S18" t="n">
-        <v>0.05361789514465451</v>
+        <v>0.1954472633136242</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
-      <c r="U18" t="inlineStr"/>
+      <c r="U18" t="n">
+        <v>-0.1860999910208563</v>
+      </c>
       <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>-0.1860999910208563</v>
+      </c>
       <c r="X18" t="n">
-        <v>0.4639772201902481</v>
-      </c>
-      <c r="Y18" t="inlineStr"/>
+        <v>0.4402219831272048</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>1.5</v>
+      </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA18" t="n">
-        <v>5.548284242923113</v>
+        <v>5.264216832394331</v>
       </c>
       <c r="AB18" t="n">
-        <v>5.548284242923113</v>
+        <v>5.264216832394331</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2uc40Ntf</t>
+          <t>dC3sew6e</t>
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>45529.65625</v>
+        <v>45514.67708333334</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2111,14 +2233,14 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>modena</t>
         </is>
       </c>
       <c r="E19" t="n">
         <v>77</v>
       </c>
       <c r="F19" t="n">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -2127,76 +2249,96 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K19" t="n">
+        <v>13</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.8025682182985554</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.1252006420545747</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.07223113964686999</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.06495726495726495</v>
+      </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.4758337980065067</v>
+        <v>0.4763906586701594</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4235865151183359</v>
+        <v>0.4799440635934727</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1005796868751575</v>
+        <v>0.04366527773636795</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
-      <c r="U19" t="inlineStr"/>
+      <c r="U19" t="n">
+        <v>0.354743421538898</v>
+      </c>
       <c r="V19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W19" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0.354743421538898</v>
+      </c>
       <c r="X19" t="n">
-        <v>0.5241662019934934</v>
-      </c>
-      <c r="Y19" t="inlineStr"/>
+        <v>0.4799440635934727</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>7.5</v>
+      </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA19" t="n">
-        <v>6.268029878710149</v>
+        <v>5.739217292668545</v>
       </c>
       <c r="AB19" t="n">
-        <v>6.268029878710149</v>
+        <v>5.739217292668545</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>6sP22LDL</t>
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>45530.5625</v>
+        <v>45515.54166666666</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>brescia</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="E20" t="n">
         <v>77</v>
       </c>
       <c r="F20" t="n">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -2205,76 +2347,96 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K20" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.325149303251493</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2926343729263438</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.3822163238221633</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.06788548752834456</v>
+      </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.4061804169336982</v>
+        <v>0.3392938152055931</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3718016552817088</v>
+        <v>0.3561153239435523</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2220179277845932</v>
+        <v>0.3045908608508545</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
-      <c r="U20" t="inlineStr"/>
+      <c r="U20" t="n">
+        <v>0.06348095101720852</v>
+      </c>
       <c r="V20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W20" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0.06348095101720852</v>
+      </c>
       <c r="X20" t="n">
-        <v>0.5938195830663018</v>
-      </c>
-      <c r="Y20" t="inlineStr"/>
+        <v>0.3561153239435523</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>3.2</v>
+      </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA20" t="n">
-        <v>7.100951711627119</v>
+        <v>4.258461309133468</v>
       </c>
       <c r="AB20" t="n">
-        <v>7.100951711627119</v>
+        <v>4.258461309133468</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>bepKi4a3</t>
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>45530.65625</v>
+        <v>45515.5625</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>palermo</t>
         </is>
       </c>
       <c r="E21" t="n">
         <v>77</v>
       </c>
       <c r="F21" t="n">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -2283,69 +2445,89 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
+          <t>coppa italia</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.4945015963107485</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2763391273501242</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.2291592763391274</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.0643358755568979</v>
+      </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.2393281307484554</v>
+        <v>0.4035638632982509</v>
       </c>
       <c r="R21" t="n">
-        <v>0.503249337379427</v>
+        <v>0.3642107603159362</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2574225318721173</v>
+        <v>0.2322253763858128</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
-      <c r="U21" t="inlineStr"/>
+      <c r="U21" t="n">
+        <v>-0.09093773301249763</v>
+      </c>
       <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-0.09093773301249763</v>
+      </c>
       <c r="X21" t="n">
-        <v>0.496750662620573</v>
-      </c>
-      <c r="Y21" t="inlineStr"/>
+        <v>0.4035638632982509</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>1.9</v>
+      </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AA21" t="n">
-        <v>5.940192220965569</v>
+        <v>4.825855508235411</v>
       </c>
       <c r="AB21" t="n">
-        <v>5.940192220965569</v>
+        <v>4.825855508235411</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>QT6wuRFc</t>
+          <t>ILr8tvi2</t>
         </is>
       </c>
       <c r="B22" s="2" t="n">
-        <v>45513.54166666666</v>
+        <v>45515.65625</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>sassuolo</t>
+          <t>sampdoria</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>cittadella</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2365,55 +2547,55 @@
         </is>
       </c>
       <c r="I22" t="n">
-        <v>1.67</v>
+        <v>3</v>
       </c>
       <c r="J22" t="n">
-        <v>3.75</v>
+        <v>3.3</v>
       </c>
       <c r="K22" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="L22" t="n">
-        <v>0.562008242787561</v>
+        <v>0.3111931119311193</v>
       </c>
       <c r="M22" t="n">
-        <v>0.2502810041213938</v>
+        <v>0.2829028290282903</v>
       </c>
       <c r="N22" t="n">
-        <v>0.1877107530910453</v>
+        <v>0.4059040590405905</v>
       </c>
       <c r="O22" t="n">
-        <v>0.06546906187624746</v>
+        <v>0.07114624505928857</v>
       </c>
       <c r="P22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.4692999801089652</v>
+        <v>0.3733539654536731</v>
       </c>
       <c r="R22" t="n">
-        <v>0.403883942822817</v>
+        <v>0.3753850775205632</v>
       </c>
       <c r="S22" t="n">
-        <v>0.1268160770682178</v>
+        <v>0.2512609570257635</v>
       </c>
       <c r="T22" t="n">
         <v>1</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.09270826267859583</v>
+        <v>0.09248224849227293</v>
       </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.09270826267859583</v>
+        <v>0.09248224849227293</v>
       </c>
       <c r="X22" t="n">
-        <v>0.4692999801089652</v>
+        <v>0.3753850775205632</v>
       </c>
       <c r="Y22" t="n">
-        <v>1.67</v>
+        <v>3.3</v>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
@@ -2421,29 +2603,29 @@
         </is>
       </c>
       <c r="AA22" t="n">
-        <v>5.611934318187092</v>
+        <v>4.488890876543054</v>
       </c>
       <c r="AB22" t="n">
-        <v>5.611934318187092</v>
+        <v>4.488890876543054</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>dnnqk0iD</t>
+          <t>ALOjHNNj</t>
         </is>
       </c>
       <c r="B23" s="2" t="n">
-        <v>45513.5625</v>
+        <v>45515.67708333334</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>avellino</t>
+          <t>cosenza</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -2463,55 +2645,55 @@
         </is>
       </c>
       <c r="I23" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="J23" t="n">
-        <v>7</v>
+        <v>5.5</v>
       </c>
       <c r="K23" t="n">
-        <v>19</v>
+        <v>8.5</v>
       </c>
       <c r="L23" t="n">
-        <v>0.8177570093457945</v>
+        <v>0.7197844495765973</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1331775700934579</v>
+        <v>0.170130869899923</v>
       </c>
       <c r="N23" t="n">
-        <v>0.04906542056074766</v>
+        <v>0.1100846805234796</v>
       </c>
       <c r="O23" t="n">
-        <v>0.07268170426065157</v>
+        <v>0.06869600987248048</v>
       </c>
       <c r="P23" t="n">
         <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.4148266945885991</v>
+        <v>0.4739078815334473</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3528763251408008</v>
+        <v>0.4223234754116265</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2322969802706001</v>
+        <v>0.1037686430549261</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4029303147571955</v>
+        <v>-0.2458765680431499</v>
       </c>
       <c r="V23" t="n">
         <v>1</v>
       </c>
       <c r="W23" t="n">
-        <v>-0.4029303147571955</v>
+        <v>-0.2458765680431499</v>
       </c>
       <c r="X23" t="n">
-        <v>0.4148266945885991</v>
+        <v>0.4739078815334473</v>
       </c>
       <c r="Y23" t="n">
-        <v>1.14</v>
+        <v>1.3</v>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
@@ -2519,29 +2701,29 @@
         </is>
       </c>
       <c r="AA23" t="n">
-        <v>4.960537528515021</v>
+        <v>5.667036046793324</v>
       </c>
       <c r="AB23" t="n">
-        <v>4.960537528515021</v>
+        <v>5.667036046793324</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hvcjgHz8</t>
+          <t>Aeu0r0Mk</t>
         </is>
       </c>
       <c r="B24" s="2" t="n">
-        <v>45513.65625</v>
+        <v>45516.54166666666</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>frosinone</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>reggiana</t>
+          <t>pisa</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -2561,55 +2743,55 @@
         </is>
       </c>
       <c r="I24" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="J24" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="K24" t="n">
-        <v>8</v>
+        <v>4.75</v>
       </c>
       <c r="L24" t="n">
-        <v>0.6728971962616822</v>
+        <v>0.5240103828682673</v>
       </c>
       <c r="M24" t="n">
-        <v>0.2093457943925233</v>
+        <v>0.2774172615184945</v>
       </c>
       <c r="N24" t="n">
-        <v>0.1177570093457944</v>
+        <v>0.1985723556132381</v>
       </c>
       <c r="O24" t="n">
-        <v>0.06150793650793651</v>
+        <v>0.06019951840385285</v>
       </c>
       <c r="P24" t="n">
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.4732307370264151</v>
+        <v>0.4203876243472635</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4078961431180815</v>
+        <v>0.382093697401959</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1188731198555035</v>
+        <v>0.1975186782507776</v>
       </c>
       <c r="T24" t="n">
         <v>1</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1996664592352671</v>
+        <v>-0.1036227585210038</v>
       </c>
       <c r="V24" t="n">
         <v>1</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.1996664592352671</v>
+        <v>-0.1036227585210038</v>
       </c>
       <c r="X24" t="n">
-        <v>0.4732307370264151</v>
+        <v>0.4203876243472635</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
@@ -2617,29 +2799,29 @@
         </is>
       </c>
       <c r="AA24" t="n">
-        <v>5.658938687623388</v>
+        <v>5.027035661641791</v>
       </c>
       <c r="AB24" t="n">
-        <v>5.658938687623388</v>
+        <v>5.027035661641791</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>AZ3PVMxp</t>
+          <t>42SH31wI</t>
         </is>
       </c>
       <c r="B25" s="2" t="n">
-        <v>45513.67708333334</v>
+        <v>45516.5625</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>sudtirol</t>
+          <t>mantova</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2665,46 +2847,46 @@
         <v>4</v>
       </c>
       <c r="K25" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="L25" t="n">
-        <v>0.6493506493506493</v>
+        <v>0.6538461538461539</v>
       </c>
       <c r="M25" t="n">
-        <v>0.2337662337662338</v>
+        <v>0.2353846153846154</v>
       </c>
       <c r="N25" t="n">
-        <v>0.1168831168831169</v>
+        <v>0.1107692307692308</v>
       </c>
       <c r="O25" t="n">
-        <v>0.06944444444444442</v>
+        <v>0.06209150326797386</v>
       </c>
       <c r="P25" t="n">
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.4746242130978113</v>
+        <v>0.388304129198316</v>
       </c>
       <c r="R25" t="n">
-        <v>0.3982831758119963</v>
+        <v>0.3675779794257129</v>
       </c>
       <c r="S25" t="n">
-        <v>0.1270926110901921</v>
+        <v>0.244117891375971</v>
       </c>
       <c r="T25" t="n">
         <v>1</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1747264362528381</v>
+        <v>-0.2655420246478378</v>
       </c>
       <c r="V25" t="n">
         <v>1</v>
       </c>
       <c r="W25" t="n">
-        <v>-0.1747264362528381</v>
+        <v>-0.2655420246478378</v>
       </c>
       <c r="X25" t="n">
-        <v>0.4746242130978113</v>
+        <v>0.388304129198316</v>
       </c>
       <c r="Y25" t="n">
         <v>1.44</v>
@@ -2715,29 +2897,29 @@
         </is>
       </c>
       <c r="AA25" t="n">
-        <v>5.675602008565411</v>
+        <v>4.643378139576774</v>
       </c>
       <c r="AB25" t="n">
-        <v>5.675602008565411</v>
+        <v>4.643378139576774</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bs5ow5pA</t>
+          <t>fNwTkrUF</t>
         </is>
       </c>
       <c r="B26" s="2" t="n">
-        <v>45514.54166666666</v>
+        <v>45516.65625</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>cremonese</t>
+          <t>salernitana</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>bari</t>
+          <t>spezia</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -2757,55 +2939,55 @@
         </is>
       </c>
       <c r="I26" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="J26" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K26" t="n">
-        <v>4.33</v>
+        <v>3.6</v>
       </c>
       <c r="L26" t="n">
-        <v>0.4929020010297615</v>
+        <v>0.4407039020657996</v>
       </c>
       <c r="M26" t="n">
-        <v>0.2896747144513368</v>
+        <v>0.2960979342004591</v>
       </c>
       <c r="N26" t="n">
-        <v>0.2174232845189017</v>
+        <v>0.2631981637337414</v>
       </c>
       <c r="O26" t="n">
-        <v>0.06219939933348151</v>
+        <v>0.05539405684754506</v>
       </c>
       <c r="P26" t="n">
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.3995295474610169</v>
+        <v>0.4440924956845937</v>
       </c>
       <c r="R26" t="n">
-        <v>0.380966358890452</v>
+        <v>0.3844438367580742</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2195040936485314</v>
+        <v>0.1714636675573318</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.09337245356874457</v>
+        <v>0.003388593618794067</v>
       </c>
       <c r="V26" t="n">
         <v>1</v>
       </c>
       <c r="W26" t="n">
-        <v>-0.09337245356874457</v>
+        <v>0.003388593618794067</v>
       </c>
       <c r="X26" t="n">
-        <v>0.3995295474610169</v>
+        <v>0.4440924956845937</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.91</v>
+        <v>2.15</v>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
@@ -2813,29 +2995,29 @@
         </is>
       </c>
       <c r="AA26" t="n">
-        <v>4.777612771271897</v>
+        <v>5.310500793976306</v>
       </c>
       <c r="AB26" t="n">
-        <v>4.777612771271897</v>
+        <v>5.310500793976306</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>02s0k9od</t>
+          <t>8KIdPmPc</t>
         </is>
       </c>
       <c r="B27" s="2" t="n">
-        <v>45514.5625</v>
+        <v>45516.67708333334</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>cesena</t>
+          <t>carrarese</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -2855,74 +3037,92 @@
         </is>
       </c>
       <c r="I27" t="n">
-        <v>1.57</v>
+        <v>1.42</v>
       </c>
       <c r="J27" t="n">
-        <v>3.75</v>
+        <v>4.5</v>
       </c>
       <c r="K27" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
       <c r="L27" t="n">
-        <v>0.595120015869867</v>
+        <v>0.6645008860011814</v>
       </c>
       <c r="M27" t="n">
-        <v>0.249156913310851</v>
+        <v>0.2096869462492617</v>
       </c>
       <c r="N27" t="n">
-        <v>0.1557230708192819</v>
+        <v>0.125812167749557</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0702760084925691</v>
-      </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr"/>
-      <c r="R27" t="inlineStr"/>
-      <c r="S27" t="inlineStr"/>
+        <v>0.05978090766823163</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.4464358758202748</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.3612273568598673</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.1923367673198579</v>
+      </c>
       <c r="T27" t="n">
         <v>1</v>
       </c>
-      <c r="U27" t="inlineStr"/>
+      <c r="U27" t="n">
+        <v>-0.2180650101809066</v>
+      </c>
       <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="inlineStr"/>
-      <c r="X27" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>-0.2180650101809066</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0.4464358758202748</v>
+      </c>
       <c r="Y27" t="n">
-        <v>1.244385733157199</v>
+        <v>1.42</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr"/>
-      <c r="AB27" t="inlineStr"/>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA27" t="n">
+        <v>5.338523159118818</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>5.338523159118818</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Ob5Zdayq</t>
+          <t>8KfYbJz0</t>
         </is>
       </c>
       <c r="B28" s="2" t="n">
-        <v>45514.65625</v>
+        <v>45520.64583333334</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>brescia</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>catanzaro</t>
+          <t>palermo</t>
         </is>
       </c>
       <c r="E28" t="n">
         <v>77</v>
       </c>
       <c r="F28" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -2931,59 +3131,59 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="I28" t="n">
-        <v>1.57</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
-        <v>3.75</v>
+        <v>3.2</v>
       </c>
       <c r="K28" t="n">
-        <v>6</v>
+        <v>2.55</v>
       </c>
       <c r="L28" t="n">
-        <v>0.595120015869867</v>
+        <v>0.3445218492716909</v>
       </c>
       <c r="M28" t="n">
-        <v>0.249156913310851</v>
+        <v>0.2906903103229892</v>
       </c>
       <c r="N28" t="n">
-        <v>0.1557230708192819</v>
+        <v>0.3647878404053199</v>
       </c>
       <c r="O28" t="n">
-        <v>0.0702760084925691</v>
+        <v>0.07502723311546844</v>
       </c>
       <c r="P28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.4383381881163518</v>
+        <v>0.3367780039401968</v>
       </c>
       <c r="R28" t="n">
-        <v>0.3736696587172924</v>
+        <v>0.3764672773068027</v>
       </c>
       <c r="S28" t="n">
-        <v>0.1879921531663555</v>
+        <v>0.2867547187530005</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
       </c>
       <c r="U28" t="n">
-        <v>-0.1567818277535151</v>
+        <v>0.08577696698381354</v>
       </c>
       <c r="V28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>-0.1567818277535151</v>
+        <v>0.08577696698381354</v>
       </c>
       <c r="X28" t="n">
-        <v>0.4383381881163518</v>
+        <v>0.3764672773068027</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.57</v>
+        <v>3.2</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
@@ -2991,36 +3191,36 @@
         </is>
       </c>
       <c r="AA28" t="n">
-        <v>5.241690230395796</v>
+        <v>4.50183192571617</v>
       </c>
       <c r="AB28" t="n">
-        <v>5.241690230395796</v>
+        <v>4.50183192571617</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>dC3sew6e</t>
+          <t>EL1P0u6m</t>
         </is>
       </c>
       <c r="B29" s="2" t="n">
-        <v>45514.67708333334</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>bari</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>modena</t>
+          <t>juve stabia</t>
         </is>
       </c>
       <c r="E29" t="n">
         <v>77</v>
       </c>
       <c r="F29" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -3029,96 +3229,78 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="I29" t="n">
-        <v>1.18</v>
+        <v>1.9</v>
       </c>
       <c r="J29" t="n">
-        <v>7</v>
+        <v>3.25</v>
       </c>
       <c r="K29" t="n">
-        <v>13</v>
+        <v>4.1</v>
       </c>
       <c r="L29" t="n">
-        <v>0.794066317626527</v>
+        <v>0.4882740930743861</v>
       </c>
       <c r="M29" t="n">
-        <v>0.1338568935427574</v>
+        <v>0.2854525467204104</v>
       </c>
       <c r="N29" t="n">
-        <v>0.07207678883071553</v>
+        <v>0.2262733602052034</v>
       </c>
       <c r="O29" t="n">
-        <v>0.06723784689886392</v>
-      </c>
-      <c r="P29" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q29" t="n">
-        <v>0.4771256045687979</v>
-      </c>
-      <c r="R29" t="n">
-        <v>0.4787009139308176</v>
-      </c>
-      <c r="S29" t="n">
-        <v>0.04417348150038463</v>
-      </c>
+        <v>0.07791053619038224</v>
+      </c>
+      <c r="P29" t="inlineStr"/>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
       <c r="T29" t="n">
         <v>1</v>
       </c>
-      <c r="U29" t="n">
-        <v>0.3448440203880602</v>
-      </c>
+      <c r="U29" t="inlineStr"/>
       <c r="V29" t="n">
         <v>0</v>
       </c>
-      <c r="W29" t="n">
-        <v>0.3448440203880602</v>
-      </c>
-      <c r="X29" t="n">
-        <v>0.4787009139308176</v>
-      </c>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
       <c r="Y29" t="n">
-        <v>7</v>
+        <v>1.298333333333333</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA29" t="n">
-        <v>5.724351589386655</v>
-      </c>
-      <c r="AB29" t="n">
-        <v>5.724351589386655</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>6sP22LDL</t>
+          <t>M5TEBdK5</t>
         </is>
       </c>
       <c r="B30" s="2" t="n">
-        <v>45515.54166666666</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>brescia</t>
+          <t>pisa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>spezia</t>
         </is>
       </c>
       <c r="E30" t="n">
         <v>77</v>
       </c>
       <c r="F30" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -3127,59 +3309,59 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="I30" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="J30" t="n">
         <v>3.2</v>
       </c>
       <c r="K30" t="n">
-        <v>2.38</v>
+        <v>2.75</v>
       </c>
       <c r="L30" t="n">
-        <v>0.3126950238134341</v>
+        <v>0.3717001055966209</v>
       </c>
       <c r="M30" t="n">
-        <v>0.2931515848250945</v>
+        <v>0.2903907074973601</v>
       </c>
       <c r="N30" t="n">
-        <v>0.3941533913614715</v>
+        <v>0.337909186906019</v>
       </c>
       <c r="O30" t="n">
-        <v>0.06600140056022408</v>
+        <v>0.07613636363636367</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.3392938152055934</v>
+        <v>0.3756920060779304</v>
       </c>
       <c r="R30" t="n">
-        <v>0.3561153239435523</v>
+        <v>0.3707025927836253</v>
       </c>
       <c r="S30" t="n">
-        <v>0.3045908608508543</v>
+        <v>0.2536054011384443</v>
       </c>
       <c r="T30" t="n">
         <v>1</v>
       </c>
       <c r="U30" t="n">
-        <v>0.06296373911845782</v>
+        <v>0.003991900481309429</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W30" t="n">
-        <v>0.06296373911845782</v>
+        <v>0.003991900481309429</v>
       </c>
       <c r="X30" t="n">
-        <v>0.3561153239435523</v>
+        <v>0.3756920060779304</v>
       </c>
       <c r="Y30" t="n">
-        <v>3.2</v>
+        <v>2.5</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
@@ -3187,36 +3369,36 @@
         </is>
       </c>
       <c r="AA30" t="n">
-        <v>4.258461309133468</v>
+        <v>4.492561157764716</v>
       </c>
       <c r="AB30" t="n">
-        <v>4.258461309133468</v>
+        <v>4.492561157764716</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bepKi4a3</t>
+          <t>joLV7EJU</t>
         </is>
       </c>
       <c r="B31" s="2" t="n">
-        <v>45515.5625</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>salernitana</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>palermo</t>
+          <t>cittadella</t>
         </is>
       </c>
       <c r="E31" t="n">
         <v>77</v>
       </c>
       <c r="F31" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -3225,59 +3407,59 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="I31" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="J31" t="n">
         <v>3.4</v>
       </c>
       <c r="K31" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="L31" t="n">
-        <v>0.5141647343482205</v>
+        <v>0.5038814396612561</v>
       </c>
       <c r="M31" t="n">
-        <v>0.2767416070168364</v>
+        <v>0.2741707833450953</v>
       </c>
       <c r="N31" t="n">
-        <v>0.209093658634943</v>
+        <v>0.2219477769936486</v>
       </c>
       <c r="O31" t="n">
-        <v>0.06278795671273985</v>
+        <v>0.07275342569460208</v>
       </c>
       <c r="P31" t="n">
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.4035638632982508</v>
+        <v>0.4514732301288088</v>
       </c>
       <c r="R31" t="n">
-        <v>0.3642107603159362</v>
+        <v>0.3906070948948772</v>
       </c>
       <c r="S31" t="n">
-        <v>0.2322253763858126</v>
+        <v>0.1579196749763142</v>
       </c>
       <c r="T31" t="n">
         <v>1</v>
       </c>
       <c r="U31" t="n">
-        <v>-0.1106008710499697</v>
+        <v>-0.05240820953244729</v>
       </c>
       <c r="V31" t="n">
         <v>1</v>
       </c>
       <c r="W31" t="n">
-        <v>-0.1106008710499697</v>
+        <v>-0.05240820953244729</v>
       </c>
       <c r="X31" t="n">
-        <v>0.4035638632982508</v>
+        <v>0.4514732301288088</v>
       </c>
       <c r="Y31" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
@@ -3285,36 +3467,36 @@
         </is>
       </c>
       <c r="AA31" t="n">
-        <v>4.82585550823541</v>
+        <v>5.398760326634498</v>
       </c>
       <c r="AB31" t="n">
-        <v>4.82585550823541</v>
+        <v>5.398760326634498</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>ILr8tvi2</t>
+          <t>WvwvCQVo</t>
         </is>
       </c>
       <c r="B32" s="2" t="n">
-        <v>45515.65625</v>
+        <v>45521.64583333334</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>sampdoria</t>
+          <t>sudtirol</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>modena</t>
         </is>
       </c>
       <c r="E32" t="n">
         <v>77</v>
       </c>
       <c r="F32" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -3323,59 +3505,59 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="I32" t="n">
-        <v>3.25</v>
+        <v>2.63</v>
       </c>
       <c r="J32" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K32" t="n">
-        <v>2.2</v>
+        <v>2.75</v>
       </c>
       <c r="L32" t="n">
-        <v>0.2875816993464052</v>
+        <v>0.3565379226699568</v>
       </c>
       <c r="M32" t="n">
-        <v>0.2875816993464052</v>
+        <v>0.3024821731038665</v>
       </c>
       <c r="N32" t="n">
-        <v>0.4248366013071895</v>
+        <v>0.3409799042261768</v>
       </c>
       <c r="O32" t="n">
-        <v>0.06993006993007</v>
+        <v>0.06644514567978321</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.3733539654536731</v>
+        <v>0.3608228613228149</v>
       </c>
       <c r="R32" t="n">
-        <v>0.375385077520563</v>
+        <v>0.3731320384211682</v>
       </c>
       <c r="S32" t="n">
-        <v>0.2512609570257634</v>
+        <v>0.2660451002560171</v>
       </c>
       <c r="T32" t="n">
         <v>1</v>
       </c>
       <c r="U32" t="n">
-        <v>0.08780337817415779</v>
+        <v>0.07064986531730172</v>
       </c>
       <c r="V32" t="n">
         <v>0</v>
       </c>
       <c r="W32" t="n">
-        <v>0.08780337817415779</v>
+        <v>0.07064986531730172</v>
       </c>
       <c r="X32" t="n">
-        <v>0.375385077520563</v>
+        <v>0.3731320384211682</v>
       </c>
       <c r="Y32" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
@@ -3383,36 +3565,36 @@
         </is>
       </c>
       <c r="AA32" t="n">
-        <v>4.488890876543051</v>
+        <v>4.461948818205066</v>
       </c>
       <c r="AB32" t="n">
-        <v>4.488890876543051</v>
+        <v>4.461948818205066</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>ALOjHNNj</t>
+          <t>tYhtcc5C</t>
         </is>
       </c>
       <c r="B33" s="2" t="n">
-        <v>45515.67708333334</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>catanzaro</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>cosenza</t>
+          <t>sassuolo</t>
         </is>
       </c>
       <c r="E33" t="n">
         <v>77</v>
       </c>
       <c r="F33" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -3421,59 +3603,59 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="I33" t="n">
-        <v>1.29</v>
+        <v>2.75</v>
       </c>
       <c r="J33" t="n">
-        <v>5.5</v>
+        <v>3.2</v>
       </c>
       <c r="K33" t="n">
-        <v>9.5</v>
+        <v>2.5</v>
       </c>
       <c r="L33" t="n">
-        <v>0.7297486033519555</v>
+        <v>0.337909186906019</v>
       </c>
       <c r="M33" t="n">
-        <v>0.171159217877095</v>
+        <v>0.2903907074973601</v>
       </c>
       <c r="N33" t="n">
-        <v>0.09909217877094974</v>
+        <v>0.3717001055966209</v>
       </c>
       <c r="O33" t="n">
-        <v>0.06227513816253083</v>
+        <v>0.07613636363636367</v>
       </c>
       <c r="P33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.4739078815334473</v>
+        <v>0.3108635204583117</v>
       </c>
       <c r="R33" t="n">
-        <v>0.4223234754116267</v>
+        <v>0.3578218819267945</v>
       </c>
       <c r="S33" t="n">
-        <v>0.1037686430549262</v>
+        <v>0.3313145976148938</v>
       </c>
       <c r="T33" t="n">
         <v>1</v>
       </c>
       <c r="U33" t="n">
-        <v>-0.2558407218185082</v>
+        <v>0.06743117442943442</v>
       </c>
       <c r="V33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
-        <v>-0.2558407218185082</v>
+        <v>0.06743117442943442</v>
       </c>
       <c r="X33" t="n">
-        <v>0.4739078815334473</v>
+        <v>0.3578218819267945</v>
       </c>
       <c r="Y33" t="n">
-        <v>1.29</v>
+        <v>3.2</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
@@ -3481,36 +3663,36 @@
         </is>
       </c>
       <c r="AA33" t="n">
-        <v>5.667036046793323</v>
+        <v>4.278868493702087</v>
       </c>
       <c r="AB33" t="n">
-        <v>5.667036046793323</v>
+        <v>4.278868493702087</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>Aeu0r0Mk</t>
+          <t>x0nkeyzP</t>
         </is>
       </c>
       <c r="B34" s="2" t="n">
-        <v>45516.54166666666</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>frosinone</t>
+          <t>cesena</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>pisa</t>
+          <t>carrarese</t>
         </is>
       </c>
       <c r="E34" t="n">
         <v>77</v>
       </c>
       <c r="F34" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -3519,96 +3701,78 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="I34" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="J34" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K34" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="L34" t="n">
-        <v>0.5196419691695674</v>
+        <v>0.5008809239913865</v>
       </c>
       <c r="M34" t="n">
-        <v>0.2834410740924913</v>
+        <v>0.2851168336566354</v>
       </c>
       <c r="N34" t="n">
-        <v>0.1969169567379413</v>
+        <v>0.2140022423519781</v>
       </c>
       <c r="O34" t="n">
-        <v>0.06911217437533224</v>
-      </c>
-      <c r="P34" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q34" t="n">
-        <v>0.4203876243472634</v>
-      </c>
-      <c r="R34" t="n">
-        <v>0.3820936974019588</v>
-      </c>
-      <c r="S34" t="n">
-        <v>0.1975186782507778</v>
-      </c>
+        <v>0.0791797304499382</v>
+      </c>
+      <c r="P34" t="inlineStr"/>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr"/>
+      <c r="S34" t="inlineStr"/>
       <c r="T34" t="n">
         <v>1</v>
       </c>
-      <c r="U34" t="n">
-        <v>-0.099254344822304</v>
-      </c>
+      <c r="U34" t="inlineStr"/>
       <c r="V34" t="n">
-        <v>1</v>
-      </c>
-      <c r="W34" t="n">
-        <v>-0.099254344822304</v>
-      </c>
-      <c r="X34" t="n">
-        <v>0.4203876243472634</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="W34" t="inlineStr"/>
+      <c r="X34" t="inlineStr"/>
       <c r="Y34" t="n">
-        <v>1.8</v>
+        <v>1.296197411003236</v>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA34" t="n">
-        <v>5.02703566164179</v>
-      </c>
-      <c r="AB34" t="n">
-        <v>5.02703566164179</v>
-      </c>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr"/>
+      <c r="AB34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>42SH31wI</t>
+          <t>SORbFvLt</t>
         </is>
       </c>
       <c r="B35" s="2" t="n">
-        <v>45516.5625</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>cosenza</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>mantova</t>
+          <t>cremonese</t>
         </is>
       </c>
       <c r="E35" t="n">
         <v>77</v>
       </c>
       <c r="F35" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -3617,59 +3781,59 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="I35" t="n">
-        <v>1.44</v>
+        <v>3.2</v>
       </c>
       <c r="J35" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="K35" t="n">
-        <v>8</v>
+        <v>2.2</v>
       </c>
       <c r="L35" t="n">
-        <v>0.6493506493506493</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="M35" t="n">
-        <v>0.2337662337662338</v>
+        <v>0.2894736842105263</v>
       </c>
       <c r="N35" t="n">
-        <v>0.1168831168831169</v>
+        <v>0.4210526315789473</v>
       </c>
       <c r="O35" t="n">
-        <v>0.06944444444444442</v>
+        <v>0.07954545454545459</v>
       </c>
       <c r="P35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.3819362896169821</v>
+        <v>0.3280777917885559</v>
       </c>
       <c r="R35" t="n">
-        <v>0.3698354440655963</v>
+        <v>0.3757227652145619</v>
       </c>
       <c r="S35" t="n">
-        <v>0.2482282663174216</v>
+        <v>0.2961994429968819</v>
       </c>
       <c r="T35" t="n">
         <v>1</v>
       </c>
       <c r="U35" t="n">
-        <v>-0.2674143597336673</v>
+        <v>0.08624908100403561</v>
       </c>
       <c r="V35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>-0.2674143597336673</v>
+        <v>0.08624908100403561</v>
       </c>
       <c r="X35" t="n">
-        <v>0.3819362896169821</v>
+        <v>0.3757227652145619</v>
       </c>
       <c r="Y35" t="n">
-        <v>1.44</v>
+        <v>3.2</v>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
@@ -3677,36 +3841,36 @@
         </is>
       </c>
       <c r="AA35" t="n">
-        <v>4.567230901149658</v>
+        <v>4.492928978480201</v>
       </c>
       <c r="AB35" t="n">
-        <v>4.567230901149658</v>
+        <v>4.492928978480201</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>fNwTkrUF</t>
+          <t>lvG7DIkg</t>
         </is>
       </c>
       <c r="B36" s="2" t="n">
-        <v>45516.65625</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>salernitana</t>
+          <t>frosinone</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>spezia</t>
+          <t>sampdoria</t>
         </is>
       </c>
       <c r="E36" t="n">
         <v>77</v>
       </c>
       <c r="F36" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -3715,59 +3879,59 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="I36" t="n">
-        <v>1.95</v>
+        <v>2.5</v>
       </c>
       <c r="J36" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K36" t="n">
-        <v>4.1</v>
+        <v>2.75</v>
       </c>
       <c r="L36" t="n">
-        <v>0.481786133960047</v>
+        <v>0.3717001055966209</v>
       </c>
       <c r="M36" t="n">
-        <v>0.2890716803760282</v>
+        <v>0.2903907074973601</v>
       </c>
       <c r="N36" t="n">
-        <v>0.2291421856639248</v>
+        <v>0.337909186906019</v>
       </c>
       <c r="O36" t="n">
-        <v>0.06441525953721094</v>
+        <v>0.07613636363636367</v>
       </c>
       <c r="P36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.4440924956845936</v>
+        <v>0.3773957808071001</v>
       </c>
       <c r="R36" t="n">
-        <v>0.3844438367580741</v>
+        <v>0.3827954136711872</v>
       </c>
       <c r="S36" t="n">
-        <v>0.1714636675573319</v>
+        <v>0.2398088055217128</v>
       </c>
       <c r="T36" t="n">
         <v>1</v>
       </c>
       <c r="U36" t="n">
-        <v>-0.03769363827545341</v>
+        <v>0.09240470617382712</v>
       </c>
       <c r="V36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W36" t="n">
-        <v>-0.03769363827545341</v>
+        <v>0.09240470617382712</v>
       </c>
       <c r="X36" t="n">
-        <v>0.4440924956845936</v>
+        <v>0.3827954136711872</v>
       </c>
       <c r="Y36" t="n">
-        <v>1.95</v>
+        <v>3.2</v>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
@@ -3775,36 +3939,36 @@
         </is>
       </c>
       <c r="AA36" t="n">
-        <v>5.310500793976304</v>
+        <v>4.57750438925476</v>
       </c>
       <c r="AB36" t="n">
-        <v>5.310500793976304</v>
+        <v>4.57750438925476</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>8KIdPmPc</t>
+          <t>IXMN9zkI</t>
         </is>
       </c>
       <c r="B37" s="2" t="n">
-        <v>45516.67708333334</v>
+        <v>45522.64583333334</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>reggiana</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>carrarese</t>
+          <t>mantova</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>77</v>
       </c>
       <c r="F37" t="n">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -3813,59 +3977,59 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>coppa italia</t>
+          <t>serie b</t>
         </is>
       </c>
       <c r="I37" t="n">
-        <v>1.33</v>
+        <v>2.55</v>
       </c>
       <c r="J37" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="K37" t="n">
-        <v>9</v>
+        <v>2.75</v>
       </c>
       <c r="L37" t="n">
-        <v>0.7073247406475951</v>
+        <v>0.3636557534392663</v>
       </c>
       <c r="M37" t="n">
-        <v>0.1881483810122603</v>
+        <v>0.2991361842806867</v>
       </c>
       <c r="N37" t="n">
-        <v>0.1045268783401446</v>
+        <v>0.3372080622800468</v>
       </c>
       <c r="O37" t="n">
-        <v>0.06299081035923138</v>
+        <v>0.07837387154275222</v>
       </c>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.4432416002942154</v>
+        <v>0.3586562694507874</v>
       </c>
       <c r="R37" t="n">
-        <v>0.3602216223860056</v>
+        <v>0.3685918036221668</v>
       </c>
       <c r="S37" t="n">
-        <v>0.1965367773197789</v>
+        <v>0.2727519269270458</v>
       </c>
       <c r="T37" t="n">
         <v>1</v>
       </c>
       <c r="U37" t="n">
-        <v>-0.2640831403533797</v>
+        <v>0.06945561934148003</v>
       </c>
       <c r="V37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>-0.2640831403533797</v>
+        <v>0.06945561934148003</v>
       </c>
       <c r="X37" t="n">
-        <v>0.4432416002942154</v>
+        <v>0.3685918036221668</v>
       </c>
       <c r="Y37" t="n">
-        <v>1.33</v>
+        <v>3.1</v>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
@@ -3873,29 +4037,29 @@
         </is>
       </c>
       <c r="AA37" t="n">
-        <v>5.300325705025008</v>
+        <v>4.407656253617215</v>
       </c>
       <c r="AB37" t="n">
-        <v>5.300325705025008</v>
+        <v>4.407656253617215</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>8KfYbJz0</t>
+          <t>4CX22Dbk</t>
         </is>
       </c>
       <c r="B38" s="2" t="n">
-        <v>45520.64583333334</v>
+        <v>45527.64583333334</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>brescia</t>
+          <t>modena</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>palermo</t>
+          <t>bari</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -3914,2211 +4078,47 @@
           <t>serie b</t>
         </is>
       </c>
-      <c r="I38" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J38" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K38" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="L38" t="n">
-        <v>0.3445218492716909</v>
-      </c>
-      <c r="M38" t="n">
-        <v>0.2906903103229892</v>
-      </c>
-      <c r="N38" t="n">
-        <v>0.3647878404053199</v>
-      </c>
-      <c r="O38" t="n">
-        <v>0.07502723311546844</v>
-      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="O38" t="inlineStr"/>
       <c r="P38" t="n">
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.3367780039401967</v>
+        <v>0.3757608572110147</v>
       </c>
       <c r="R38" t="n">
-        <v>0.3764672773068026</v>
+        <v>0.3768820209585328</v>
       </c>
       <c r="S38" t="n">
-        <v>0.2867547187530007</v>
+        <v>0.2473571218304522</v>
       </c>
       <c r="T38" t="n">
         <v>1</v>
       </c>
-      <c r="U38" t="n">
-        <v>0.08577696698381337</v>
-      </c>
+      <c r="U38" t="inlineStr"/>
       <c r="V38" t="n">
         <v>0</v>
       </c>
-      <c r="W38" t="n">
-        <v>0.08577696698381337</v>
-      </c>
+      <c r="W38" t="inlineStr"/>
       <c r="X38" t="n">
-        <v>0.3764672773068026</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>3.2</v>
-      </c>
+        <v>0.6231179790414672</v>
+      </c>
+      <c r="Y38" t="inlineStr"/>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
         </is>
       </c>
       <c r="AA38" t="n">
-        <v>4.501831925716168</v>
+        <v>7.451304749789808</v>
       </c>
       <c r="AB38" t="n">
-        <v>4.501831925716168</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EL1P0u6m</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="n">
-        <v>45521.64583333334</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>bari</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>juve stabia</t>
-        </is>
-      </c>
-      <c r="E39" t="n">
-        <v>77</v>
-      </c>
-      <c r="F39" t="n">
-        <v>774</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I39" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J39" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K39" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L39" t="n">
-        <v>0.4882740930743861</v>
-      </c>
-      <c r="M39" t="n">
-        <v>0.2854525467204104</v>
-      </c>
-      <c r="N39" t="n">
-        <v>0.2262733602052034</v>
-      </c>
-      <c r="O39" t="n">
-        <v>0.07791053619038224</v>
-      </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr"/>
-      <c r="R39" t="inlineStr"/>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="n">
-        <v>1</v>
-      </c>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="n">
-        <v>0</v>
-      </c>
-      <c r="W39" t="inlineStr"/>
-      <c r="X39" t="inlineStr"/>
-      <c r="Y39" t="n">
-        <v>1.298333333333333</v>
-      </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA39" t="inlineStr"/>
-      <c r="AB39" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>M5TEBdK5</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="n">
-        <v>45521.64583333334</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>pisa</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>spezia</t>
-        </is>
-      </c>
-      <c r="E40" t="n">
-        <v>77</v>
-      </c>
-      <c r="F40" t="n">
-        <v>774</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J40" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K40" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L40" t="n">
-        <v>0.3717001055966209</v>
-      </c>
-      <c r="M40" t="n">
-        <v>0.2903907074973601</v>
-      </c>
-      <c r="N40" t="n">
-        <v>0.337909186906019</v>
-      </c>
-      <c r="O40" t="n">
-        <v>0.07613636363636367</v>
-      </c>
-      <c r="P40" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0.3756920060779301</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0.3707025927836255</v>
-      </c>
-      <c r="S40" t="n">
-        <v>0.2536054011384444</v>
-      </c>
-      <c r="T40" t="n">
-        <v>1</v>
-      </c>
-      <c r="U40" t="n">
-        <v>0.003991900481309207</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1</v>
-      </c>
-      <c r="W40" t="n">
-        <v>0.003991900481309207</v>
-      </c>
-      <c r="X40" t="n">
-        <v>0.3756920060779301</v>
-      </c>
-      <c r="Y40" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA40" t="n">
-        <v>4.492561157764714</v>
-      </c>
-      <c r="AB40" t="n">
-        <v>4.492561157764714</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>joLV7EJU</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="n">
-        <v>45521.64583333334</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>salernitana</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>cittadella</t>
-        </is>
-      </c>
-      <c r="E41" t="n">
-        <v>77</v>
-      </c>
-      <c r="F41" t="n">
-        <v>774</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I41" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="J41" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K41" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="L41" t="n">
-        <v>0.5038814396612561</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0.2741707833450953</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0.2219477769936486</v>
-      </c>
-      <c r="O41" t="n">
-        <v>0.07275342569460208</v>
-      </c>
-      <c r="P41" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>0.451473230128809</v>
-      </c>
-      <c r="R41" t="n">
-        <v>0.3906070948948772</v>
-      </c>
-      <c r="S41" t="n">
-        <v>0.1579196749763142</v>
-      </c>
-      <c r="T41" t="n">
-        <v>1</v>
-      </c>
-      <c r="U41" t="n">
-        <v>-0.05240820953244713</v>
-      </c>
-      <c r="V41" t="n">
-        <v>1</v>
-      </c>
-      <c r="W41" t="n">
-        <v>-0.05240820953244713</v>
-      </c>
-      <c r="X41" t="n">
-        <v>0.451473230128809</v>
-      </c>
-      <c r="Y41" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA41" t="n">
-        <v>5.3987603266345</v>
-      </c>
-      <c r="AB41" t="n">
-        <v>5.3987603266345</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
-        <is>
-          <t>WvwvCQVo</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="n">
-        <v>45521.64583333334</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>sudtirol</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>modena</t>
-        </is>
-      </c>
-      <c r="E42" t="n">
-        <v>77</v>
-      </c>
-      <c r="F42" t="n">
-        <v>774</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I42" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="J42" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K42" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L42" t="n">
-        <v>0.3565379226699568</v>
-      </c>
-      <c r="M42" t="n">
-        <v>0.3024821731038665</v>
-      </c>
-      <c r="N42" t="n">
-        <v>0.3409799042261768</v>
-      </c>
-      <c r="O42" t="n">
-        <v>0.06644514567978321</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>0.3608228613228148</v>
-      </c>
-      <c r="R42" t="n">
-        <v>0.3731320384211683</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0.2660451002560169</v>
-      </c>
-      <c r="T42" t="n">
-        <v>1</v>
-      </c>
-      <c r="U42" t="n">
-        <v>0.07064986531730177</v>
-      </c>
-      <c r="V42" t="n">
-        <v>0</v>
-      </c>
-      <c r="W42" t="n">
-        <v>0.07064986531730177</v>
-      </c>
-      <c r="X42" t="n">
-        <v>0.3731320384211683</v>
-      </c>
-      <c r="Y42" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA42" t="n">
-        <v>4.461948818205067</v>
-      </c>
-      <c r="AB42" t="n">
-        <v>4.461948818205067</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="inlineStr">
-        <is>
-          <t>tYhtcc5C</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="n">
-        <v>45522.64583333334</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>catanzaro</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>sassuolo</t>
-        </is>
-      </c>
-      <c r="E43" t="n">
-        <v>77</v>
-      </c>
-      <c r="F43" t="n">
-        <v>774</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I43" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="J43" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K43" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0.337909186906019</v>
-      </c>
-      <c r="M43" t="n">
-        <v>0.2903907074973601</v>
-      </c>
-      <c r="N43" t="n">
-        <v>0.3717001055966209</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0.07613636363636367</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0.3108635204583116</v>
-      </c>
-      <c r="R43" t="n">
-        <v>0.3578218819267946</v>
-      </c>
-      <c r="S43" t="n">
-        <v>0.3313145976148936</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1</v>
-      </c>
-      <c r="U43" t="n">
-        <v>0.06743117442943458</v>
-      </c>
-      <c r="V43" t="n">
-        <v>0</v>
-      </c>
-      <c r="W43" t="n">
-        <v>0.06743117442943458</v>
-      </c>
-      <c r="X43" t="n">
-        <v>0.3578218819267946</v>
-      </c>
-      <c r="Y43" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA43" t="n">
-        <v>4.278868493702089</v>
-      </c>
-      <c r="AB43" t="n">
-        <v>4.278868493702089</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>x0nkeyzP</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="n">
-        <v>45522.64583333334</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>cesena</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>carrarese</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>77</v>
-      </c>
-      <c r="F44" t="n">
-        <v>774</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I44" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="J44" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="K44" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="L44" t="n">
-        <v>0.5008809239913865</v>
-      </c>
-      <c r="M44" t="n">
-        <v>0.2851168336566354</v>
-      </c>
-      <c r="N44" t="n">
-        <v>0.2140022423519781</v>
-      </c>
-      <c r="O44" t="n">
-        <v>0.0791797304499382</v>
-      </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr"/>
-      <c r="R44" t="inlineStr"/>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="n">
-        <v>1</v>
-      </c>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="n">
-        <v>0</v>
-      </c>
-      <c r="W44" t="inlineStr"/>
-      <c r="X44" t="inlineStr"/>
-      <c r="Y44" t="n">
-        <v>1.296197411003236</v>
-      </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr"/>
-      <c r="AB44" t="inlineStr"/>
-    </row>
-    <row r="45">
-      <c r="A45" s="1" t="inlineStr">
-        <is>
-          <t>SORbFvLt</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="n">
-        <v>45522.64583333334</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>cosenza</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>cremonese</t>
-        </is>
-      </c>
-      <c r="E45" t="n">
-        <v>77</v>
-      </c>
-      <c r="F45" t="n">
-        <v>774</v>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I45" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="J45" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K45" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L45" t="n">
-        <v>0.2894736842105263</v>
-      </c>
-      <c r="M45" t="n">
-        <v>0.2894736842105263</v>
-      </c>
-      <c r="N45" t="n">
-        <v>0.4210526315789473</v>
-      </c>
-      <c r="O45" t="n">
-        <v>0.07954545454545459</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q45" t="n">
-        <v>0.3280777917885559</v>
-      </c>
-      <c r="R45" t="n">
-        <v>0.3757227652145617</v>
-      </c>
-      <c r="S45" t="n">
-        <v>0.2961994429968821</v>
-      </c>
-      <c r="T45" t="n">
-        <v>1</v>
-      </c>
-      <c r="U45" t="n">
-        <v>0.08624908100403533</v>
-      </c>
-      <c r="V45" t="n">
-        <v>0</v>
-      </c>
-      <c r="W45" t="n">
-        <v>0.08624908100403533</v>
-      </c>
-      <c r="X45" t="n">
-        <v>0.3757227652145617</v>
-      </c>
-      <c r="Y45" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA45" t="n">
-        <v>4.492928978480197</v>
-      </c>
-      <c r="AB45" t="n">
-        <v>4.492928978480197</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="1" t="inlineStr">
-        <is>
-          <t>lvG7DIkg</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="n">
-        <v>45522.64583333334</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>frosinone</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>sampdoria</t>
-        </is>
-      </c>
-      <c r="E46" t="n">
-        <v>77</v>
-      </c>
-      <c r="F46" t="n">
-        <v>774</v>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I46" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="J46" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K46" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L46" t="n">
-        <v>0.3717001055966209</v>
-      </c>
-      <c r="M46" t="n">
-        <v>0.2903907074973601</v>
-      </c>
-      <c r="N46" t="n">
-        <v>0.337909186906019</v>
-      </c>
-      <c r="O46" t="n">
-        <v>0.07613636363636367</v>
-      </c>
-      <c r="P46" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q46" t="n">
-        <v>0.3773957808071</v>
-      </c>
-      <c r="R46" t="n">
-        <v>0.3827954136711871</v>
-      </c>
-      <c r="S46" t="n">
-        <v>0.2398088055217128</v>
-      </c>
-      <c r="T46" t="n">
-        <v>1</v>
-      </c>
-      <c r="U46" t="n">
-        <v>0.09240470617382701</v>
-      </c>
-      <c r="V46" t="n">
-        <v>0</v>
-      </c>
-      <c r="W46" t="n">
-        <v>0.09240470617382701</v>
-      </c>
-      <c r="X46" t="n">
-        <v>0.3827954136711871</v>
-      </c>
-      <c r="Y46" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="Z46" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA46" t="n">
-        <v>4.577504389254758</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>4.577504389254758</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="1" t="inlineStr">
-        <is>
-          <t>IXMN9zkI</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="n">
-        <v>45522.64583333334</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>reggiana</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>mantova</t>
-        </is>
-      </c>
-      <c r="E47" t="n">
-        <v>77</v>
-      </c>
-      <c r="F47" t="n">
-        <v>774</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I47" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="J47" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K47" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0.3636557534392663</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0.2991361842806867</v>
-      </c>
-      <c r="N47" t="n">
-        <v>0.3372080622800468</v>
-      </c>
-      <c r="O47" t="n">
-        <v>0.07837387154275222</v>
-      </c>
-      <c r="P47" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>0.3553690977034535</v>
-      </c>
-      <c r="R47" t="n">
-        <v>0.3685930125120004</v>
-      </c>
-      <c r="S47" t="n">
-        <v>0.2760378897845459</v>
-      </c>
-      <c r="T47" t="n">
-        <v>1</v>
-      </c>
-      <c r="U47" t="n">
-        <v>0.06945682823131366</v>
-      </c>
-      <c r="V47" t="n">
-        <v>0</v>
-      </c>
-      <c r="W47" t="n">
-        <v>0.06945682823131366</v>
-      </c>
-      <c r="X47" t="n">
-        <v>0.3685930125120004</v>
-      </c>
-      <c r="Y47" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA47" t="n">
-        <v>4.407670709638165</v>
-      </c>
-      <c r="AB47" t="n">
-        <v>4.407670709638165</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="1" t="inlineStr">
-        <is>
-          <t>4CX22Dbk</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="n">
-        <v>45527.64583333334</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>modena</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>bari</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>77</v>
-      </c>
-      <c r="F48" t="n">
-        <v>774</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
-      <c r="N48" t="inlineStr"/>
-      <c r="O48" t="inlineStr"/>
-      <c r="P48" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>0.3757608572110148</v>
-      </c>
-      <c r="R48" t="n">
-        <v>0.3768820209585328</v>
-      </c>
-      <c r="S48" t="n">
-        <v>0.2473571218304522</v>
-      </c>
-      <c r="T48" t="n">
-        <v>1</v>
-      </c>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="n">
-        <v>0</v>
-      </c>
-      <c r="W48" t="inlineStr"/>
-      <c r="X48" t="n">
-        <v>0.6231179790414672</v>
-      </c>
-      <c r="Y48" t="inlineStr"/>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA48" t="n">
         <v>7.451304749789808</v>
-      </c>
-      <c r="AB48" t="n">
-        <v>7.451304749789808</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="1" t="inlineStr">
-        <is>
-          <t>CjGqFjre</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="n">
-        <v>45528.60416666666</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>sudtirol</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>salernitana</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>77</v>
-      </c>
-      <c r="F49" t="n">
-        <v>774</v>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
-      <c r="N49" t="inlineStr"/>
-      <c r="O49" t="inlineStr"/>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0.3137424962042789</v>
-      </c>
-      <c r="R49" t="n">
-        <v>0.3776364466040546</v>
-      </c>
-      <c r="S49" t="n">
-        <v>0.3086210571916663</v>
-      </c>
-      <c r="T49" t="n">
-        <v>1</v>
-      </c>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="n">
-        <v>0</v>
-      </c>
-      <c r="W49" t="inlineStr"/>
-      <c r="X49" t="n">
-        <v>0.6223635533959454</v>
-      </c>
-      <c r="Y49" t="inlineStr"/>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA49" t="n">
-        <v>7.442283255329823</v>
-      </c>
-      <c r="AB49" t="n">
-        <v>7.442283255329823</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="1" t="inlineStr">
-        <is>
-          <t>0IkylEqd</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="n">
-        <v>45528.64583333334</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>brescia</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>cittadella</t>
-        </is>
-      </c>
-      <c r="E50" t="n">
-        <v>77</v>
-      </c>
-      <c r="F50" t="n">
-        <v>774</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
-      <c r="N50" t="inlineStr"/>
-      <c r="O50" t="inlineStr"/>
-      <c r="P50" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q50" t="n">
-        <v>0.3890088333497214</v>
-      </c>
-      <c r="R50" t="n">
-        <v>0.3678489634003708</v>
-      </c>
-      <c r="S50" t="n">
-        <v>0.2431422032499077</v>
-      </c>
-      <c r="T50" t="n">
-        <v>1</v>
-      </c>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W50" t="inlineStr"/>
-      <c r="X50" t="n">
-        <v>0.6109911666502786</v>
-      </c>
-      <c r="Y50" t="inlineStr"/>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA50" t="n">
-        <v>7.306291160374087</v>
-      </c>
-      <c r="AB50" t="n">
-        <v>7.306291160374087</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="1" t="inlineStr">
-        <is>
-          <t>CEhO9e6F</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="n">
-        <v>45528.64583333334</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>cremonese</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>carrarese</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>77</v>
-      </c>
-      <c r="F51" t="n">
-        <v>774</v>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q51" t="n">
-        <v>0.4327026951974696</v>
-      </c>
-      <c r="R51" t="n">
-        <v>0.3652339324847403</v>
-      </c>
-      <c r="S51" t="n">
-        <v>0.2020633723177898</v>
-      </c>
-      <c r="T51" t="n">
-        <v>1</v>
-      </c>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W51" t="inlineStr"/>
-      <c r="X51" t="n">
-        <v>0.5672973048025305</v>
-      </c>
-      <c r="Y51" t="inlineStr"/>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA51" t="n">
-        <v>6.783795756175327</v>
-      </c>
-      <c r="AB51" t="n">
-        <v>6.783795756175327</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="1" t="inlineStr">
-        <is>
-          <t>CxyB0iT1</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="n">
-        <v>45528.64583333334</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>pisa</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>palermo</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>77</v>
-      </c>
-      <c r="F52" t="n">
-        <v>774</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0.354437542674017</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0.3704708076174809</v>
-      </c>
-      <c r="S52" t="n">
-        <v>0.275091649708502</v>
-      </c>
-      <c r="T52" t="n">
-        <v>1</v>
-      </c>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="n">
-        <v>0</v>
-      </c>
-      <c r="W52" t="inlineStr"/>
-      <c r="X52" t="n">
-        <v>0.6295291923825191</v>
-      </c>
-      <c r="Y52" t="inlineStr"/>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA52" t="n">
-        <v>7.527970655809055</v>
-      </c>
-      <c r="AB52" t="n">
-        <v>7.527970655809055</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="1" t="inlineStr">
-        <is>
-          <t>CSXdOfL8</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="n">
-        <v>45528.64583333334</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>sampdoria</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>reggiana</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>77</v>
-      </c>
-      <c r="F53" t="n">
-        <v>774</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0.4490753614139523</v>
-      </c>
-      <c r="R53" t="n">
-        <v>0.3975072312824112</v>
-      </c>
-      <c r="S53" t="n">
-        <v>0.1534174073036365</v>
-      </c>
-      <c r="T53" t="n">
-        <v>1</v>
-      </c>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W53" t="inlineStr"/>
-      <c r="X53" t="n">
-        <v>0.5509246385860477</v>
-      </c>
-      <c r="Y53" t="inlineStr"/>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA53" t="n">
-        <v>6.588009838180683</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>6.588009838180683</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>ptW4MYkL</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="n">
-        <v>45528.64583333334</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>sassuolo</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>cesena</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>77</v>
-      </c>
-      <c r="F54" t="n">
-        <v>774</v>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr"/>
-      <c r="R54" t="inlineStr"/>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="n">
-        <v>1</v>
-      </c>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="n">
-        <v>0</v>
-      </c>
-      <c r="W54" t="inlineStr"/>
-      <c r="X54" t="inlineStr"/>
-      <c r="Y54" t="inlineStr"/>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA54" t="inlineStr"/>
-      <c r="AB54" t="inlineStr"/>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="inlineStr">
-        <is>
-          <t>4QCyHCDr</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="n">
-        <v>45528.64583333334</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>spezia</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>frosinone</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>77</v>
-      </c>
-      <c r="F55" t="n">
-        <v>774</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q55" t="n">
-        <v>0.3456922516554832</v>
-      </c>
-      <c r="R55" t="n">
-        <v>0.3768957475976318</v>
-      </c>
-      <c r="S55" t="n">
-        <v>0.2774120007468848</v>
-      </c>
-      <c r="T55" t="n">
-        <v>1</v>
-      </c>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="n">
-        <v>0</v>
-      </c>
-      <c r="W55" t="inlineStr"/>
-      <c r="X55" t="n">
-        <v>0.6231042524023682</v>
-      </c>
-      <c r="Y55" t="inlineStr"/>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA55" t="n">
-        <v>7.451140605318685</v>
-      </c>
-      <c r="AB55" t="n">
-        <v>7.451140605318685</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="inlineStr">
-        <is>
-          <t>hCxNBHy3</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="n">
-        <v>45529.64583333334</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>catanzaro</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>juve stabia</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>77</v>
-      </c>
-      <c r="F56" t="n">
-        <v>774</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr"/>
-      <c r="R56" t="inlineStr"/>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="n">
-        <v>1</v>
-      </c>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="n">
-        <v>0</v>
-      </c>
-      <c r="W56" t="inlineStr"/>
-      <c r="X56" t="inlineStr"/>
-      <c r="Y56" t="inlineStr"/>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA56" t="inlineStr"/>
-      <c r="AB56" t="inlineStr"/>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="inlineStr">
-        <is>
-          <t>KvdW7ZzS</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="n">
-        <v>45529.64583333334</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>mantova</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>cosenza</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>77</v>
-      </c>
-      <c r="F57" t="n">
-        <v>774</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q57" t="n">
-        <v>0.4144769306926992</v>
-      </c>
-      <c r="R57" t="n">
-        <v>0.3632828037410173</v>
-      </c>
-      <c r="S57" t="n">
-        <v>0.2222402655662838</v>
-      </c>
-      <c r="T57" t="n">
-        <v>1</v>
-      </c>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W57" t="inlineStr"/>
-      <c r="X57" t="n">
-        <v>0.5855230693073008</v>
-      </c>
-      <c r="Y57" t="inlineStr"/>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA57" t="n">
-        <v>7.001741201806432</v>
-      </c>
-      <c r="AB57" t="n">
-        <v>7.001741201806432</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="inlineStr">
-        <is>
-          <t>Y54hDUC7</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="n">
-        <v>45531.64583333334</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>bari</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>sassuolo</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>77</v>
-      </c>
-      <c r="F58" t="n">
-        <v>774</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
-        <v>0.303302606240299</v>
-      </c>
-      <c r="R58" t="n">
-        <v>0.3794820466945786</v>
-      </c>
-      <c r="S58" t="n">
-        <v>0.3172153470651222</v>
-      </c>
-      <c r="T58" t="n">
-        <v>1</v>
-      </c>
-      <c r="U58" t="inlineStr"/>
-      <c r="V58" t="n">
-        <v>0</v>
-      </c>
-      <c r="W58" t="inlineStr"/>
-      <c r="X58" t="n">
-        <v>0.6205179533054214</v>
-      </c>
-      <c r="Y58" t="inlineStr"/>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA58" t="n">
-        <v>7.420213391863696</v>
-      </c>
-      <c r="AB58" t="n">
-        <v>7.420213391863696</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="inlineStr">
-        <is>
-          <t>v3ivyY4E</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="n">
-        <v>45531.64583333334</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>carrarese</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>sudtirol</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>77</v>
-      </c>
-      <c r="F59" t="n">
-        <v>774</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
-      <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q59" t="n">
-        <v>0.3721384289361635</v>
-      </c>
-      <c r="R59" t="n">
-        <v>0.3751764575966294</v>
-      </c>
-      <c r="S59" t="n">
-        <v>0.2526851134672073</v>
-      </c>
-      <c r="T59" t="n">
-        <v>1</v>
-      </c>
-      <c r="U59" t="inlineStr"/>
-      <c r="V59" t="n">
-        <v>0</v>
-      </c>
-      <c r="W59" t="inlineStr"/>
-      <c r="X59" t="n">
-        <v>0.6248235424033706</v>
-      </c>
-      <c r="Y59" t="inlineStr"/>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA59" t="n">
-        <v>7.471700040580755</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>7.471700040580755</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="inlineStr">
-        <is>
-          <t>W0WITkcl</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="n">
-        <v>45531.64583333334</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>cittadella</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>pisa</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>77</v>
-      </c>
-      <c r="F60" t="n">
-        <v>774</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q60" t="n">
-        <v>0.3694349518469551</v>
-      </c>
-      <c r="R60" t="n">
-        <v>0.3660894300422443</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0.2644756181108006</v>
-      </c>
-      <c r="T60" t="n">
-        <v>1</v>
-      </c>
-      <c r="U60" t="inlineStr"/>
-      <c r="V60" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W60" t="inlineStr"/>
-      <c r="X60" t="n">
-        <v>0.6305650481530449</v>
-      </c>
-      <c r="Y60" t="inlineStr"/>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA60" t="n">
-        <v>7.540357518783044</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>7.540357518783044</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="inlineStr">
-        <is>
-          <t>YPSZP7dD</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="n">
-        <v>45531.64583333334</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>cremonese</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>palermo</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>77</v>
-      </c>
-      <c r="F61" t="n">
-        <v>774</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q61" t="n">
-        <v>0.3649253957792764</v>
-      </c>
-      <c r="R61" t="n">
-        <v>0.3701258744827766</v>
-      </c>
-      <c r="S61" t="n">
-        <v>0.264948729737947</v>
-      </c>
-      <c r="T61" t="n">
-        <v>1</v>
-      </c>
-      <c r="U61" t="inlineStr"/>
-      <c r="V61" t="n">
-        <v>0</v>
-      </c>
-      <c r="W61" t="inlineStr"/>
-      <c r="X61" t="n">
-        <v>0.6298741255172234</v>
-      </c>
-      <c r="Y61" t="inlineStr"/>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA61" t="n">
-        <v>7.532095399423315</v>
-      </c>
-      <c r="AB61" t="n">
-        <v>7.532095399423315</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="inlineStr">
-        <is>
-          <t>EL5MmBlK</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="n">
-        <v>45531.64583333334</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>frosinone</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>modena</t>
-        </is>
-      </c>
-      <c r="E62" t="n">
-        <v>77</v>
-      </c>
-      <c r="F62" t="n">
-        <v>774</v>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q62" t="n">
-        <v>0.4411561310487624</v>
-      </c>
-      <c r="R62" t="n">
-        <v>0.3891545663301597</v>
-      </c>
-      <c r="S62" t="n">
-        <v>0.1696893026210779</v>
-      </c>
-      <c r="T62" t="n">
-        <v>1</v>
-      </c>
-      <c r="U62" t="inlineStr"/>
-      <c r="V62" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W62" t="inlineStr"/>
-      <c r="X62" t="n">
-        <v>0.5588438689512376</v>
-      </c>
-      <c r="Y62" t="inlineStr"/>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA62" t="n">
-        <v>6.68270875687597</v>
-      </c>
-      <c r="AB62" t="n">
-        <v>6.68270875687597</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="inlineStr">
-        <is>
-          <t>tWk1tTtf</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="n">
-        <v>45531.64583333334</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>reggiana</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>brescia</t>
-        </is>
-      </c>
-      <c r="E63" t="n">
-        <v>77</v>
-      </c>
-      <c r="F63" t="n">
-        <v>774</v>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
-      <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>0.3592825889470761</v>
-      </c>
-      <c r="R63" t="n">
-        <v>0.3547347492945213</v>
-      </c>
-      <c r="S63" t="n">
-        <v>0.2859826617584027</v>
-      </c>
-      <c r="T63" t="n">
-        <v>1</v>
-      </c>
-      <c r="U63" t="inlineStr"/>
-      <c r="V63" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W63" t="inlineStr"/>
-      <c r="X63" t="n">
-        <v>0.6407174110529239</v>
-      </c>
-      <c r="Y63" t="inlineStr"/>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA63" t="n">
-        <v>7.661760451200156</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>7.661760451200156</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>Eql9v7B6</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="n">
-        <v>45531.64583333334</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>salernitana</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>sampdoria</t>
-        </is>
-      </c>
-      <c r="E64" t="n">
-        <v>77</v>
-      </c>
-      <c r="F64" t="n">
-        <v>774</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>serie b</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q64" t="n">
-        <v>0.4082351488621532</v>
-      </c>
-      <c r="R64" t="n">
-        <v>0.3819978722007473</v>
-      </c>
-      <c r="S64" t="n">
-        <v>0.2097669789370997</v>
-      </c>
-      <c r="T64" t="n">
-        <v>1</v>
-      </c>
-      <c r="U64" t="inlineStr"/>
-      <c r="V64" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W64" t="inlineStr"/>
-      <c r="X64" t="n">
-        <v>0.5917648511378468</v>
-      </c>
-      <c r="Y64" t="inlineStr"/>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
-        </is>
-      </c>
-      <c r="AA64" t="n">
-        <v>7.076381029520348</v>
-      </c>
-      <c r="AB64" t="n">
-        <v>7.076381029520348</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
+          <t>t4ZkclrT</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45523.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1590214067278287</v>
+        <v>0.2377922257573662</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2446483180428135</v>
+        <v>0.2642135841748513</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5963302752293578</v>
+        <v>0.4979941900677826</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04807692307692313</v>
+        <v>0.05133798720186156</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2314832776181089</v>
+        <v>0.2527326558877114</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5248373906071366</v>
+        <v>0.4284080897598317</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2436793317747547</v>
+        <v>0.3188592543524569</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2801890725643231</v>
+        <v>0.1641945055849804</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2801890725643231</v>
+        <v>0.1641945055849804</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5248373906071366</v>
+        <v>0.4284080897598317</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>6.276056016733864</v>
+        <v>5.122945158774464</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.276056016733864</v>
+        <v>5.122945158774464</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>EirZ0Wr4</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45523.65625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.3</v>
+        <v>1.33</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>5</v>
       </c>
       <c r="K3" t="n">
-        <v>2.25</v>
+        <v>9.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2858844550327576</v>
+        <v>0.7112375533428166</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2948183442525313</v>
+        <v>0.1891891891891892</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4192972007147112</v>
+        <v>0.09957325746799432</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0599747474747474</v>
+        <v>0.05714285714285694</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2719125388965054</v>
+        <v>0.4827603290337771</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3953919798438414</v>
+        <v>0.46684612543233</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3326954812596531</v>
+        <v>0.05039354553389294</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1005736355913101</v>
+        <v>-0.2284772243090395</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1005736355913101</v>
+        <v>-0.2284772243090395</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3953919798438414</v>
+        <v>0.4827603290337771</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.2</v>
+        <v>1.33</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>4.728135339588956</v>
+        <v>5.772894465784766</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.728135339588956</v>
+        <v>5.772894465784766</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45521.65625</v>
+        <v>45528.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>ac milan</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>torino</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J4" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K4" t="n">
         <v>1.73</v>
       </c>
-      <c r="J4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5.25</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.5439668439257036</v>
+        <v>0.2082831687936431</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2767831294092551</v>
+        <v>0.2499398025523718</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1792500266650414</v>
+        <v>0.5417770286539851</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06262851961593885</v>
+        <v>0.06692357096981372</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4386509541393382</v>
+        <v>0.227761609718552</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4976983767847179</v>
+        <v>0.5077089800370997</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06365066907594362</v>
+        <v>0.2645294102443485</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2209152473754628</v>
+        <v>0.2577691774847279</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2209152473754628</v>
+        <v>0.2577691774847279</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4976983767847179</v>
+        <v>0.5077089800370997</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>5.951525078129471</v>
+        <v>6.071232835041698</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.951525078129471</v>
+        <v>6.071232835041698</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45521.65625</v>
+        <v>45528.5625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,22 +907,22 @@
         </is>
       </c>
       <c r="I5" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J5" t="n">
+        <v>3</v>
+      </c>
+      <c r="K5" t="n">
         <v>2.4</v>
       </c>
-      <c r="J5" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="K5" t="n">
-        <v>3</v>
-      </c>
       <c r="L5" t="n">
+        <v>0.2941176470588235</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.3137254901960784</v>
+      </c>
+      <c r="N5" t="n">
         <v>0.392156862745098</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0.2941176470588235</v>
-      </c>
-      <c r="N5" t="n">
-        <v>0.3137254901960784</v>
       </c>
       <c r="O5" t="n">
         <v>0.0625</v>
@@ -931,32 +931,32 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.344449568285591</v>
+        <v>0.2494446214443811</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3531011333277493</v>
+        <v>0.4992820272245245</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3024492983866596</v>
+        <v>0.2512733513310944</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.0589834862689258</v>
+        <v>0.185556537028446</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0589834862689258</v>
+        <v>0.185556537028446</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3531011333277493</v>
+        <v>0.4992820272245245</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4.222417327724275</v>
+        <v>5.970462522467523</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.222417327724275</v>
+        <v>5.970462522467523</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45522.5625</v>
+        <v>45528.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.85</v>
+        <v>1.22</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>5.5</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>13</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5078597339782346</v>
+        <v>0.7600722865950887</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2684401451027811</v>
+        <v>0.1685978526629106</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2237001209189843</v>
+        <v>0.07132986074200064</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0643500643500643</v>
+        <v>0.07841338988879976</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4278588366379965</v>
+        <v>0.3627153120391268</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3641550725654393</v>
+        <v>0.5968965904987151</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2079860907965644</v>
+        <v>0.04038809746215791</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.08000089734023808</v>
+        <v>0.4282987378358045</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.08000089734023808</v>
+        <v>0.4282987378358045</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4278588366379965</v>
+        <v>0.5968965904987151</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.85</v>
+        <v>5.5</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>5.116377137094424</v>
+        <v>7.137746862573573</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.116377137094424</v>
+        <v>7.137746862573573</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45522.5625</v>
+        <v>45528.65625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.2</v>
+        <v>2.55</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>1.91</v>
+        <v>2.9</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2255174329768023</v>
+        <v>0.3663929248262792</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2785803583831088</v>
+        <v>0.3114339861023373</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4959022086400889</v>
+        <v>0.3221730890713834</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05577309457814539</v>
+        <v>0.07031778228532803</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2319022240814298</v>
+        <v>0.391341276448307</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5171297872874008</v>
+        <v>0.3695979301265662</v>
       </c>
       <c r="S7" t="n">
-        <v>0.250967988631169</v>
+        <v>0.2390607934251268</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.238549428904292</v>
+        <v>0.0249483516220278</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.238549428904292</v>
+        <v>0.0249483516220278</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5171297872874008</v>
+        <v>0.391341276448307</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>2.55</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1162,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>6.183887754610871</v>
+        <v>4.679696638626475</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.183887754610871</v>
+        <v>4.679696638626475</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45529.5625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>1.44</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="K8" t="n">
-        <v>1.95</v>
+        <v>6.25</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2411347517730496</v>
+        <v>0.6520784141452969</v>
       </c>
       <c r="M8" t="n">
-        <v>0.276595744680851</v>
+        <v>0.1976827192356268</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4822695035460993</v>
+        <v>0.1502388666190764</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06334841628959298</v>
+        <v>0.06497076023391801</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2449743860139734</v>
+        <v>0.4853421236630436</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4925779135540977</v>
+        <v>0.4169765865326327</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2624477004319288</v>
+        <v>0.09768128980432346</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2159821688732467</v>
+        <v>-0.1667362904822533</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2159821688732467</v>
+        <v>-0.1667362904822533</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4925779135540977</v>
+        <v>0.4853421236630436</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.4</v>
+        <v>1.44</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1261,29 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.890294086126743</v>
+        <v>5.803767814381814</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.890294086126743</v>
+        <v>5.803767814381814</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45529.5625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>2.55</v>
       </c>
       <c r="L9" t="n">
-        <v>0.620779043590968</v>
+        <v>0.3148148148148148</v>
       </c>
       <c r="M9" t="n">
-        <v>0.243536394024149</v>
+        <v>0.3148148148148148</v>
       </c>
       <c r="N9" t="n">
-        <v>0.135684562384883</v>
+        <v>0.3703703703703704</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05286217050922937</v>
+        <v>0.05882352941176472</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4682671614856357</v>
+        <v>0.302511274028195</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4659843737347973</v>
+        <v>0.3719493457137158</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06574846477956688</v>
+        <v>0.3255393802580892</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.1525118821053323</v>
+        <v>0.05713453089890103</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1525118821053323</v>
+        <v>0.05713453089890103</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4682671614856357</v>
+        <v>0.3719493457137158</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>3</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1360,29 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>5.59958377371151</v>
+        <v>4.447806065010658</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.59958377371151</v>
+        <v>4.447806065010658</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45523.5625</v>
+        <v>45529.65625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,56 +1402,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>1.53</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
-        <v>1.85</v>
+        <v>6.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.23125</v>
+        <v>0.6180910495661476</v>
       </c>
       <c r="M10" t="n">
-        <v>0.25625</v>
+        <v>0.2364198264590515</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5125</v>
+        <v>0.1454891239748009</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05471324983520098</v>
+        <v>0.05744092508798393</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2653962771145651</v>
+        <v>0.4047304121164458</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4059516244084848</v>
+        <v>0.5445959389614711</v>
       </c>
       <c r="S10" t="n">
-        <v>0.32865209847695</v>
+        <v>0.05067364892208341</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1497016244084848</v>
+        <v>0.3081761125024196</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1497016244084848</v>
+        <v>0.3081761125024196</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4059516244084848</v>
+        <v>0.5445959389614711</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,29 +1459,29 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>4.854408585341962</v>
+        <v>6.512330639122518</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.854408585341962</v>
+        <v>6.512330639122518</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45529.65625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1501,56 +1501,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>9.5</v>
+        <v>4.1</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7112375533428166</v>
+        <v>0.4984369572768322</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1891891891891892</v>
+        <v>0.2705800625217089</v>
       </c>
       <c r="N11" t="n">
-        <v>0.09957325746799432</v>
+        <v>0.2309829802014589</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05714285714285694</v>
+        <v>0.05593251421236012</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4892916279083425</v>
+        <v>0.4698015650685075</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4557959799799634</v>
+        <v>0.4356256451304839</v>
       </c>
       <c r="S11" t="n">
-        <v>0.05491239211169398</v>
+        <v>0.09457278980100894</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>-0.2219459254344741</v>
+        <v>-0.02863539220832478</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2219459254344741</v>
+        <v>-0.02863539220832478</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4892916279083425</v>
+        <v>0.4698015650685075</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.33</v>
+        <v>1.9</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1558,29 +1558,29 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>5.850996366168397</v>
+        <v>5.617932319395803</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.850996366168397</v>
+        <v>5.617932319395803</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45530.5625</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1607,16 +1607,16 @@
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2220031739458087</v>
+        <v>0.3940887808828412</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5005966417442625</v>
+        <v>0.380857289313438</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2774001843099286</v>
+        <v>0.2250539298037209</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
@@ -1624,11 +1624,11 @@
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="inlineStr"/>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X12" t="inlineStr"/>
       <c r="Y12" t="n">
-        <v>0.4994033582557375</v>
+        <v>0.6059112191171588</v>
       </c>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr">
@@ -1637,29 +1637,29 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>5.97191341061324</v>
+        <v>7.245544658980489</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.97191341061324</v>
+        <v>7.245544658980489</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45530.65625</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1678,67 +1678,87 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.1985723556132381</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2774172615184945</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.5240103828682673</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06019951840385285</v>
+      </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2494837292078461</v>
+        <v>0.2416078849512996</v>
       </c>
       <c r="R13" t="n">
-        <v>0.502432093224054</v>
+        <v>0.495480836323102</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2480841775681001</v>
+        <v>0.2629112787255984</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.2180635748046075</v>
+      </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="n">
+        <v>0.2180635748046075</v>
+      </c>
       <c r="Y13" t="n">
-        <v>0.497567906775946</v>
-      </c>
-      <c r="Z13" t="inlineStr"/>
+        <v>0.495480836323102</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.4</v>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>5.949964905210752</v>
+        <v>5.925007515917724</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.949964905210752</v>
+        <v>5.925007515917724</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.65625</v>
+        <v>45534.5625</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1768,13 +1788,13 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.348306813742376</v>
+        <v>0.2975947611767382</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6158339184450761</v>
+        <v>0.3631868868116307</v>
       </c>
       <c r="S14" t="n">
-        <v>0.035859267812548</v>
+        <v>0.3392183520116311</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
@@ -1786,7 +1806,7 @@
       </c>
       <c r="X14" t="inlineStr"/>
       <c r="Y14" t="n">
-        <v>0.3841660815549239</v>
+        <v>0.6368131131883692</v>
       </c>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr">
@@ -1795,29 +1815,29 @@
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>4.593894967694148</v>
+        <v>7.61507248166427</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.593894967694148</v>
+        <v>7.61507248166427</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45528.65625</v>
+        <v>45534.65625</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1844,16 +1864,16 @@
       <c r="N15" t="inlineStr"/>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.3892469351462832</v>
+        <v>0.4181744824774969</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3715979936945291</v>
+        <v>0.5170559113682618</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2391550711591876</v>
+        <v>0.06476960615424135</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
@@ -1861,11 +1881,11 @@
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="inlineStr"/>
       <c r="W15" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X15" t="inlineStr"/>
       <c r="Y15" t="n">
-        <v>0.6107530648537167</v>
+        <v>0.4829440886317382</v>
       </c>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr">
@@ -1874,29 +1894,29 @@
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>7.303443916180645</v>
+        <v>5.775091880738533</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.303443916180645</v>
+        <v>5.775091880738533</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1926,13 +1946,13 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4790567292970755</v>
+        <v>0.4323510492548664</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4230092988772037</v>
+        <v>0.3628227709264047</v>
       </c>
       <c r="S16" t="n">
-        <v>0.09793397182572103</v>
+        <v>0.2048261798187286</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
@@ -1944,7 +1964,7 @@
       </c>
       <c r="X16" t="inlineStr"/>
       <c r="Y16" t="n">
-        <v>0.5209432707029245</v>
+        <v>0.5676489507451336</v>
       </c>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr">
@@ -1953,29 +1973,29 @@
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>6.229489756227077</v>
+        <v>6.788000772192348</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.229489756227077</v>
+        <v>6.788000772192348</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2002,16 +2022,16 @@
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.3027372133461338</v>
+        <v>0.364542629520531</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3705511897512255</v>
+        <v>0.3639671860521788</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3267115969026403</v>
+        <v>0.2714901844272901</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
@@ -2019,11 +2039,11 @@
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="inlineStr"/>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X17" t="inlineStr"/>
       <c r="Y17" t="n">
-        <v>0.6294488102487745</v>
+        <v>0.635457370479469</v>
       </c>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr">
@@ -2032,10 +2052,484 @@
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>7.527009438519368</v>
+        <v>7.598860379901678</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.527009438519368</v>
+        <v>7.598860379901678</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45535.65625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>77</v>
+      </c>
+      <c r="F18" t="n">
+        <v>771</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2871984069033288</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.4118390211731897</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.3009625719234813</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="n">
+        <v>0.5881609788268103</v>
+      </c>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>7.03328557766038</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>7.03328557766038</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45535.65625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>77</v>
+      </c>
+      <c r="F19" t="n">
+        <v>771</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.4856329309544024</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.4553411577455251</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.05902591130007253</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="n">
+        <v>0.5143670690455977</v>
+      </c>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>6.15085090404664</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>6.15085090404664</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>nZgYbEaC</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45536.5625</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>77</v>
+      </c>
+      <c r="F20" t="n">
+        <v>771</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.4491487214532779</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.3811947650146077</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.1696565135321141</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="n">
+        <v>0.5508512785467221</v>
+      </c>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>6.587132591771724</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>6.587132591771724</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>r1mschUO</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45536.5625</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>77</v>
+      </c>
+      <c r="F21" t="n">
+        <v>771</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.4286117247174237</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3710820883539895</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2003061869285867</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="n">
+        <v>0.5713882752825763</v>
+      </c>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>6.832715974808895</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>6.832715974808895</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>hCGaFZqg</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>77</v>
+      </c>
+      <c r="F22" t="n">
+        <v>771</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.4399391426956292</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.3988231712623833</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.1612376860419872</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="n">
+        <v>0.5600608573043708</v>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>6.697261620701356</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>6.697261620701356</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>77</v>
+      </c>
+      <c r="F23" t="n">
+        <v>771</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.431918581091773</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.3862514823214682</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.1818299365867588</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="n">
+        <v>0.5680814189082271</v>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB23" t="n">
+        <v>6.793172268098706</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>6.793172268098706</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>O2Fteteo</t>
+          <t>8x0Cb1B6</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45528.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1590214067278287</v>
+        <v>0.2082831687936431</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2446483180428135</v>
+        <v>0.2499398025523718</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5963302752293578</v>
+        <v>0.5417770286539851</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04807692307692313</v>
+        <v>0.06692357096981372</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2314832776181089</v>
+        <v>0.227761609718552</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5248373906071366</v>
+        <v>0.5077089800370994</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2436793317747547</v>
+        <v>0.2645294102443486</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2801890725643231</v>
+        <v>0.2577691774847276</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2801890725643231</v>
+        <v>0.2577691774847276</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5248373906071366</v>
+        <v>0.5077089800370994</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>6.276056016733864</v>
+        <v>6.071232835041694</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.276056016733864</v>
+        <v>6.071232835041694</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Sf88FVcc</t>
+          <t>GrNwFMem</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45521.5625</v>
+        <v>45528.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>2.25</v>
+        <v>2.4</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2858844550327576</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2948183442525313</v>
+        <v>0.3137254901960784</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4192972007147112</v>
+        <v>0.392156862745098</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0599747474747474</v>
+        <v>0.0625</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2719125388965054</v>
+        <v>0.2494446214443811</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3953919798438414</v>
+        <v>0.4992820272245244</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3326954812596531</v>
+        <v>0.2512733513310944</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1005736355913101</v>
+        <v>0.185556537028446</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1005736355913101</v>
+        <v>0.185556537028446</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3953919798438414</v>
+        <v>0.4992820272245244</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>4.728135339588956</v>
+        <v>5.970462522467522</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.728135339588956</v>
+        <v>5.970462522467522</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0lGMiS5j</t>
+          <t>AsIP75lK</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45521.65625</v>
+        <v>45528.65625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.73</v>
+        <v>1.22</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="K4" t="n">
-        <v>5.25</v>
+        <v>13</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5439668439257036</v>
+        <v>0.765685019206146</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2767831294092551</v>
+        <v>0.1624583866837388</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1792500266650414</v>
+        <v>0.07185659411011523</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06262851961593885</v>
+        <v>0.07050825154887885</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4386509541393382</v>
+        <v>0.3548142223011568</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4976983767847179</v>
+        <v>0.6079036799981532</v>
       </c>
       <c r="S4" t="n">
-        <v>0.06365066907594362</v>
+        <v>0.03728209770069008</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2209152473754628</v>
+        <v>0.4454452933144144</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2209152473754628</v>
+        <v>0.4454452933144144</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4976983767847179</v>
+        <v>0.6079036799981532</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>5.951525078129471</v>
+        <v>7.269370697910006</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.951525078129471</v>
+        <v>7.269370697910006</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hKOA02XN</t>
+          <t>6D3e2qCs</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45521.65625</v>
+        <v>45528.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K5" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="L5" t="n">
-        <v>0.392156862745098</v>
+        <v>0.3663929248262792</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.3114339861023373</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3137254901960784</v>
+        <v>0.3221730890713834</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0625</v>
+        <v>0.07031778228532803</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.344449568285591</v>
+        <v>0.3913412764483071</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3531011333277493</v>
+        <v>0.3695979301265658</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3024492983866596</v>
+        <v>0.239060793425127</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.0589834862689258</v>
+        <v>0.02494835162202785</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0589834862689258</v>
+        <v>0.02494835162202785</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3531011333277493</v>
+        <v>0.3913412764483071</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4.222417327724275</v>
+        <v>4.679696638626476</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.222417327724275</v>
+        <v>4.679696638626476</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>4xHh663n</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45522.5625</v>
+        <v>45529.5625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="J6" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="K6" t="n">
-        <v>4.2</v>
+        <v>6.25</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5078597339782346</v>
+        <v>0.6520784141452969</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2684401451027811</v>
+        <v>0.1976827192356268</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2237001209189843</v>
+        <v>0.1502388666190764</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0643500643500643</v>
+        <v>0.06497076023391801</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4278588366379965</v>
+        <v>0.4853421236630436</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3641550725654393</v>
+        <v>0.4169765865326328</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2079860907965644</v>
+        <v>0.09768128980432349</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.08000089734023808</v>
+        <v>-0.1667362904822533</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.08000089734023808</v>
+        <v>-0.1667362904822533</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4278588366379965</v>
+        <v>0.4853421236630436</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.85</v>
+        <v>1.44</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>5.116377137094424</v>
+        <v>5.803767814381814</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.116377137094424</v>
+        <v>5.803767814381814</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>6RvR2hEi</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45522.5625</v>
+        <v>45529.5625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>4.2</v>
+        <v>3.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="K7" t="n">
-        <v>1.91</v>
+        <v>2.45</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2255174329768023</v>
+        <v>0.2964905203711174</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2785803583831088</v>
+        <v>0.3162565550625252</v>
       </c>
       <c r="N7" t="n">
-        <v>0.4959022086400889</v>
+        <v>0.3872529245663574</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05577309457814539</v>
+        <v>0.05399659863945572</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2319022240814298</v>
+        <v>0.3011335445351196</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5171297872874008</v>
+        <v>0.3943942906419498</v>
       </c>
       <c r="S7" t="n">
-        <v>0.250967988631169</v>
+        <v>0.3044721648229305</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.238549428904292</v>
+        <v>0.07813773557942455</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.238549428904292</v>
+        <v>0.07813773557942455</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5171297872874008</v>
+        <v>0.3943942906419498</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1162,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>6.183887754610871</v>
+        <v>4.71620487611508</v>
       </c>
       <c r="AC7" t="n">
-        <v>6.183887754610871</v>
+        <v>4.71620487611508</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>YH892O2B</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45529.65625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>1.53</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="K8" t="n">
-        <v>1.95</v>
+        <v>6.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2411347517730496</v>
+        <v>0.6180910495661476</v>
       </c>
       <c r="M8" t="n">
-        <v>0.276595744680851</v>
+        <v>0.2364198264590515</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4822695035460993</v>
+        <v>0.1454891239748009</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06334841628959298</v>
+        <v>0.05744092508798393</v>
       </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2449743860139734</v>
+        <v>0.4047304121164457</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4925779135540977</v>
+        <v>0.544595938961471</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2624477004319288</v>
+        <v>0.0506736489220834</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2159821688732467</v>
+        <v>0.3081761125024195</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2159821688732467</v>
+        <v>0.3081761125024195</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4925779135540977</v>
+        <v>0.544595938961471</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1261,29 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>5.890294086126743</v>
+        <v>6.512330639122516</v>
       </c>
       <c r="AC8" t="n">
-        <v>5.890294086126743</v>
+        <v>6.512330639122516</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>8jyraADG</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45522.65625</v>
+        <v>45529.65625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="J9" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="L9" t="n">
-        <v>0.620779043590968</v>
+        <v>0.4984369572768322</v>
       </c>
       <c r="M9" t="n">
-        <v>0.243536394024149</v>
+        <v>0.2705800625217089</v>
       </c>
       <c r="N9" t="n">
-        <v>0.135684562384883</v>
+        <v>0.2309829802014589</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05286217050922937</v>
+        <v>0.05593251421236012</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4682671614856357</v>
+        <v>0.4698015650685076</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4659843737347973</v>
+        <v>0.4356256451304839</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06574846477956688</v>
+        <v>0.09457278980100886</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.1525118821053323</v>
+        <v>-0.02863539220832462</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1525118821053323</v>
+        <v>-0.02863539220832462</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4682671614856357</v>
+        <v>0.4698015650685076</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.53</v>
+        <v>1.9</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1360,29 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>5.59958377371151</v>
+        <v>5.617932319395805</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.59958377371151</v>
+        <v>5.617932319395805</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>t4ZkclrT</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45523.5625</v>
+        <v>45530.5625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,56 +1402,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>1.85</v>
+        <v>3.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.23125</v>
+        <v>0.4509283819628648</v>
       </c>
       <c r="M10" t="n">
-        <v>0.25625</v>
+        <v>0.2785145888594165</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5125</v>
+        <v>0.2705570291777188</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05471324983520098</v>
+        <v>0.05602240896358524</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2653962771145651</v>
+        <v>0.4077903325582086</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4059516244084848</v>
+        <v>0.3705398372557717</v>
       </c>
       <c r="S10" t="n">
-        <v>0.32865209847695</v>
+        <v>0.2216698301860197</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1497016244084848</v>
+        <v>-0.04313804940465615</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1497016244084848</v>
+        <v>-0.04313804940465615</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4059516244084848</v>
+        <v>0.4077903325582086</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,29 +1459,29 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>4.854408585341962</v>
+        <v>4.876396034316858</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.854408585341962</v>
+        <v>4.876396034316858</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>EirZ0Wr4</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45523.65625</v>
+        <v>45530.65625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>juventus</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>como</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1501,56 +1501,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.33</v>
+        <v>5.25</v>
       </c>
       <c r="J11" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="K11" t="n">
-        <v>9.5</v>
+        <v>1.7</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7112375533428166</v>
+        <v>0.1789473684210526</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1891891891891892</v>
+        <v>0.2684210526315789</v>
       </c>
       <c r="N11" t="n">
-        <v>0.09957325746799432</v>
+        <v>0.5526315789473685</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05714285714285694</v>
+        <v>0.06442577030812324</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4892916279083425</v>
+        <v>0.2447844449708477</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4557959799799634</v>
+        <v>0.4906401072297463</v>
       </c>
       <c r="S11" t="n">
-        <v>0.05491239211169398</v>
+        <v>0.2645754477994058</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>-0.2219459254344741</v>
+        <v>0.2222190545981673</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2219459254344741</v>
+        <v>0.2222190545981673</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4892916279083425</v>
+        <v>0.4906401072297463</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.33</v>
+        <v>3.5</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1558,29 +1558,29 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>5.850996366168397</v>
+        <v>5.867121611644423</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.850996366168397</v>
+        <v>5.867121611644423</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45534.5625</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1599,67 +1599,87 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
+      <c r="I12" t="n">
+        <v>3.77</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.68</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.2612136217442544</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2676019983629997</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.4711843798927459</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0154600193462342</v>
+      </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2220031739458087</v>
+        <v>0.2975947611767379</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5005966417442625</v>
+        <v>0.3631868868116307</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2774001843099286</v>
+        <v>0.3392183520116314</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.095584888448631</v>
+      </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>0.095584888448631</v>
+      </c>
       <c r="Y12" t="n">
-        <v>0.4994033582557375</v>
-      </c>
-      <c r="Z12" t="inlineStr"/>
+        <v>0.3631868868116307</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.68</v>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>5.97191341061324</v>
+        <v>4.343023738335729</v>
       </c>
       <c r="AC12" t="n">
-        <v>5.97191341061324</v>
+        <v>4.343023738335729</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45534.65625</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1678,67 +1698,87 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
+      <c r="I13" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="K13" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.5593495980395171</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2316365394234235</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.2090138625370595</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.01579016088195551</v>
+      </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.2494837292078461</v>
+        <v>0.4159339070538805</v>
       </c>
       <c r="R13" t="n">
-        <v>0.502432093224054</v>
+        <v>0.5210881830161578</v>
       </c>
       <c r="S13" t="n">
-        <v>0.2480841775681001</v>
+        <v>0.06297790992996173</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.2894516435927342</v>
+      </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="n">
+        <v>0.2894516435927342</v>
+      </c>
       <c r="Y13" t="n">
-        <v>0.497567906775946</v>
-      </c>
-      <c r="Z13" t="inlineStr"/>
+        <v>0.5210881830161578</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>4.25</v>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>5.949964905210752</v>
+        <v>6.231222631612185</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.949964905210752</v>
+        <v>6.231222631612185</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45528.65625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1757,67 +1797,87 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="I14" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="K14" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6048129009018994</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2416286834485529</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.1535584156495476</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.01435821160641315</v>
+      </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.348306813742376</v>
+        <v>0.4323510492548665</v>
       </c>
       <c r="R14" t="n">
-        <v>0.6158339184450761</v>
+        <v>0.3628227709264049</v>
       </c>
       <c r="S14" t="n">
-        <v>0.035859267812548</v>
+        <v>0.2048261798187285</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.1724618516470329</v>
+      </c>
       <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.1724618516470329</v>
+      </c>
       <c r="Y14" t="n">
-        <v>0.3841660815549239</v>
-      </c>
-      <c r="Z14" t="inlineStr"/>
+        <v>0.4323510492548665</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.63</v>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>4.593894967694148</v>
+        <v>5.170095447807653</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.593894967694148</v>
+        <v>5.170095447807653</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45528.65625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1836,67 +1896,87 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="I15" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.4559666492965086</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2813965607087024</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.262636789994789</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.01534391534391522</v>
+      </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.3892469351462832</v>
+        <v>0.3641919878950581</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3715979936945291</v>
+        <v>0.3644408345692408</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2391550711591876</v>
+        <v>0.2713671775357012</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.08304427386053836</v>
+      </c>
       <c r="W15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.08304427386053836</v>
+      </c>
       <c r="Y15" t="n">
-        <v>0.6107530648537167</v>
-      </c>
-      <c r="Z15" t="inlineStr"/>
+        <v>0.3644408345692408</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.5</v>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>7.303443916180645</v>
+        <v>4.358018566276084</v>
       </c>
       <c r="AC15" t="n">
-        <v>7.303443916180645</v>
+        <v>4.358018566276084</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1915,67 +1995,87 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
+      <c r="I16" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3700853556983106</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2719411729716869</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.3579734713300023</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.01581930718307589</v>
+      </c>
       <c r="P16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4790567292970755</v>
+        <v>0.287198406903329</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4230092988772037</v>
+        <v>0.4118390211731896</v>
       </c>
       <c r="S16" t="n">
-        <v>0.09793397182572103</v>
+        <v>0.3009625719234814</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.1398978482015028</v>
+      </c>
       <c r="W16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="X16" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.1398978482015028</v>
+      </c>
       <c r="Y16" t="n">
-        <v>0.5209432707029245</v>
-      </c>
-      <c r="Z16" t="inlineStr"/>
+        <v>0.4118390211731896</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.62</v>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>6.229489756227077</v>
+        <v>4.924810642339619</v>
       </c>
       <c r="AC16" t="n">
-        <v>6.229489756227077</v>
+        <v>4.924810642339619</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1994,48 +2094,464 @@
           <t>serie a</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
+      <c r="I17" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.66</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.639030356665776</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2111817058509217</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.1497879374833021</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.01614992555083106</v>
+      </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.3027372133461338</v>
+        <v>0.4856329309544022</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3705511897512255</v>
+        <v>0.4553411577455253</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3267115969026403</v>
+        <v>0.05902591130007249</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-0.1533974257113738</v>
+      </c>
       <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.1533974257113738</v>
+      </c>
       <c r="Y17" t="n">
-        <v>0.6294488102487745</v>
-      </c>
-      <c r="Z17" t="inlineStr"/>
+        <v>0.4856329309544022</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.54</v>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>7.527009438519368</v>
+        <v>5.807245315953358</v>
       </c>
       <c r="AC17" t="n">
-        <v>7.527009438519368</v>
+        <v>5.807245315953358</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>nZgYbEaC</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45536.5625</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>77</v>
+      </c>
+      <c r="F18" t="n">
+        <v>771</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="K18" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.6390356425329264</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.215814668750155</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.1451496887169184</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.01614152033341609</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.4491487214532782</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3811947650146074</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.1696565135321142</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-0.1898869210796482</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.1898869210796482</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.4491487214532782</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>5.370963628228279</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>5.370963628228279</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>r1mschUO</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45536.5625</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>77</v>
+      </c>
+      <c r="F19" t="n">
+        <v>771</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.457992565055762</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2862453531598513</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.2557620817843866</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.01555421322863193</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.4286117247174239</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3710820883539895</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.2003061869285866</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>-0.02938084033833815</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.02938084033833815</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.4286117247174239</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>5.125380245191107</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>5.125380245191107</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>hCGaFZqg</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>77</v>
+      </c>
+      <c r="F20" t="n">
+        <v>771</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.69</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.5084777611444821</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2673297714418144</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.2241924674137034</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.01373935482560085</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.4444813455119924</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.3979370637554646</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.1575815907325429</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>-0.0639964156324897</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.0639964156324897</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.4444813455119924</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>5.31515069762747</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>5.31515069762747</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>77</v>
+      </c>
+      <c r="F21" t="n">
+        <v>771</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="K21" t="n">
+        <v>4.49</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.4879726526597545</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2924939935824048</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.2195333537578406</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.01450255921549548</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.445501270182507</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3785793296003209</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1759194002171721</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>-0.04247138247724752</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.04247138247724752</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.445501270182507</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>5.327347054974636</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5.327347054974636</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -613,64 +613,64 @@
         <v>4.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K2" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2082831687936431</v>
+        <v>0.2069849407241269</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2499398025523718</v>
+        <v>0.2451137455943608</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5417770286539851</v>
+        <v>0.5479013136815124</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06692357096981372</v>
+        <v>0.07361541107671132</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.227761609718552</v>
+        <v>0.1611302974373451</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5077089800370994</v>
+        <v>0.3489183406711817</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2645294102443486</v>
+        <v>0.4899513618914735</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2577691774847276</v>
+        <v>-0.05794995179003892</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2577691774847276</v>
+        <v>-0.05794995179003892</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5077089800370994</v>
+        <v>0.4899513618914735</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.75</v>
+        <v>1.7</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>6.071232835041694</v>
+        <v>7.784599690070459</v>
       </c>
       <c r="AC2" t="n">
-        <v>6.071232835041694</v>
+        <v>7.784599690070459</v>
       </c>
     </row>
     <row r="3">
@@ -709,67 +709,67 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="J3" t="n">
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>2.4</v>
+        <v>2.35</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2941176470588235</v>
+        <v>0.2853673345476624</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3137254901960784</v>
+        <v>0.3139040680024286</v>
       </c>
       <c r="N3" t="n">
-        <v>0.392156862745098</v>
+        <v>0.4007285974499089</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0625</v>
+        <v>0.06189555125725343</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2494446214443811</v>
+        <v>0.2473964910885989</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4992820272245244</v>
+        <v>0.5366351868481504</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2512733513310944</v>
+        <v>0.2159683220632509</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.185556537028446</v>
+        <v>0.2227311188457217</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.185556537028446</v>
+        <v>0.2227311188457217</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4992820272245244</v>
+        <v>0.5366351868481504</v>
       </c>
       <c r="Z3" t="n">
         <v>3</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5.970462522467522</v>
+        <v>8.526336355289789</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.970462522467522</v>
+        <v>8.526336355289789</v>
       </c>
     </row>
     <row r="4">
@@ -808,7 +808,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="J4" t="n">
         <v>5.75</v>
@@ -817,58 +817,58 @@
         <v>13</v>
       </c>
       <c r="L4" t="n">
-        <v>0.765685019206146</v>
+        <v>0.7686375321336761</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1624583866837388</v>
+        <v>0.1604113110539846</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07185659411011523</v>
+        <v>0.07095115681233934</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07050825154887885</v>
+        <v>0.08416945373467111</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3548142223011568</v>
+        <v>0.5221684715876772</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6079036799981532</v>
+        <v>0.3143532580490948</v>
       </c>
       <c r="S4" t="n">
-        <v>0.03728209770069008</v>
+        <v>0.1634782703632281</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.4454452933144144</v>
+        <v>-0.2464690605459989</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4454452933144144</v>
+        <v>0.2464690605459989</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6079036799981532</v>
+        <v>0.4778315284123228</v>
       </c>
       <c r="Z4" t="n">
-        <v>5.75</v>
+        <v>3.986666666666666</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &lt; -0.2</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>7.269370697910006</v>
+        <v>7.592033530888314</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.269370697910006</v>
+        <v>7.592033530888314</v>
       </c>
     </row>
     <row r="5">
@@ -931,43 +931,43 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3913412764483071</v>
+        <v>0.4232531465071245</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3695979301265658</v>
+        <v>0.3872790360206924</v>
       </c>
       <c r="S5" t="n">
-        <v>0.239060793425127</v>
+        <v>0.1894678174721829</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.02494835162202785</v>
+        <v>0.05686022168084531</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.02494835162202785</v>
+        <v>0.05686022168084531</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3913412764483071</v>
+        <v>0.4232531465071245</v>
       </c>
       <c r="Z5" t="n">
         <v>2.55</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4.679696638626476</v>
+        <v>6.724864077121464</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.679696638626476</v>
+        <v>6.724864077121464</v>
       </c>
     </row>
     <row r="6">
@@ -1006,67 +1006,67 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
         <v>4.75</v>
       </c>
       <c r="K6" t="n">
-        <v>6.25</v>
+        <v>6.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6520784141452969</v>
+        <v>0.6621983914209115</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1976827192356268</v>
+        <v>0.1951742627345844</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1502388666190764</v>
+        <v>0.142627345844504</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06497076023391801</v>
+        <v>0.07865818392134183</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4853421236630436</v>
+        <v>0.612149970858894</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4169765865326328</v>
+        <v>0.2630621682794289</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09768128980432349</v>
+        <v>0.1247878608616769</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.1667362904822533</v>
+        <v>-0.05004842056201753</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1667362904822533</v>
+        <v>-0.05004842056201753</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4853421236630436</v>
+        <v>0.612149970858894</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>5.803767814381814</v>
+        <v>9.726154153400092</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.803767814381814</v>
+        <v>9.726154153400092</v>
       </c>
     </row>
     <row r="7">
@@ -1105,67 +1105,67 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
         <v>2.45</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2964905203711174</v>
+        <v>0.30625</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3162565550625252</v>
+        <v>0.30625</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3872529245663574</v>
+        <v>0.3875</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05399659863945572</v>
+        <v>0.05332455562870297</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3011335445351196</v>
+        <v>0.3423940561969125</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3943942906419498</v>
+        <v>0.3868601733755462</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3044721648229305</v>
+        <v>0.2707457704275413</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.07813773557942455</v>
+        <v>0.08061017337554616</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.07813773557942455</v>
+        <v>0.08061017337554616</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3943942906419498</v>
+        <v>0.3868601733755462</v>
       </c>
       <c r="Z7" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4.71620487611508</v>
+        <v>6.146633768163611</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.71620487611508</v>
+        <v>6.146633768163611</v>
       </c>
     </row>
     <row r="8">
@@ -1204,67 +1204,67 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K8" t="n">
         <v>6.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6180910495661476</v>
+        <v>0.6263219741480611</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2364198264590515</v>
+        <v>0.2291421856639248</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1454891239748009</v>
+        <v>0.1445358401880141</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05744092508798393</v>
+        <v>0.06441525953721072</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4047304121164457</v>
+        <v>0.4906738836434155</v>
       </c>
       <c r="R8" t="n">
-        <v>0.544595938961471</v>
+        <v>0.3237213004645519</v>
       </c>
       <c r="S8" t="n">
-        <v>0.0506736489220834</v>
+        <v>0.1856048158920323</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3081761125024195</v>
+        <v>-0.1356480905046456</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3081761125024195</v>
+        <v>-0.1356480905046456</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.544595938961471</v>
+        <v>0.4906738836434155</v>
       </c>
       <c r="Z8" t="n">
-        <v>4</v>
+        <v>1.5</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>6.512330639122516</v>
+        <v>7.796079487951872</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.512330639122516</v>
+        <v>7.796079487951872</v>
       </c>
     </row>
     <row r="9">
@@ -1327,43 +1327,43 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4698015650685076</v>
+        <v>0.5077785756551436</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4356256451304839</v>
+        <v>0.3279300497663408</v>
       </c>
       <c r="S9" t="n">
-        <v>0.09457278980100886</v>
+        <v>0.1642913745785154</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.02863539220832462</v>
+        <v>0.009341618378311378</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.02863539220832462</v>
+        <v>0.009341618378311378</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4698015650685076</v>
+        <v>0.5077785756551436</v>
       </c>
       <c r="Z9" t="n">
         <v>1.9</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>5.617932319395805</v>
+        <v>8.067847647997814</v>
       </c>
       <c r="AC9" t="n">
-        <v>5.617932319395805</v>
+        <v>8.067847647997814</v>
       </c>
     </row>
     <row r="10">
@@ -1402,67 +1402,67 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="J10" t="n">
         <v>3.4</v>
       </c>
       <c r="K10" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L10" t="n">
-        <v>0.4509283819628648</v>
+        <v>0.4603234298608499</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2785145888594165</v>
+        <v>0.2775479503572771</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2705570291777188</v>
+        <v>0.2621286197818729</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05602240896358524</v>
+        <v>0.05970030288538197</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4077903325582086</v>
+        <v>0.3875247714313318</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3705398372557717</v>
+        <v>0.4773304199145214</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2216698301860197</v>
+        <v>0.1351448086541466</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.04313804940465615</v>
+        <v>0.1997824695572443</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.04313804940465615</v>
+        <v>0.1997824695572443</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4077903325582086</v>
+        <v>0.4773304199145214</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>4.876396034316858</v>
+        <v>7.584071660874081</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.876396034316858</v>
+        <v>7.584071660874081</v>
       </c>
     </row>
     <row r="11">
@@ -1501,67 +1501,67 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="J11" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="L11" t="n">
-        <v>0.1789473684210526</v>
+        <v>0.171786153098837</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2684210526315789</v>
+        <v>0.2624510672343344</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5526315789473685</v>
+        <v>0.5657627796668286</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06442577030812324</v>
+        <v>0.05839835480554045</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2447844449708477</v>
+        <v>0.2064711616103093</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4906401072297463</v>
+        <v>0.3726241564025167</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2645754477994058</v>
+        <v>0.4209046819871741</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2222190545981673</v>
+        <v>-0.1448580976796545</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2222190545981673</v>
+        <v>-0.1448580976796545</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4906401072297463</v>
+        <v>0.4209046819871741</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.5</v>
+        <v>1.67</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>5.867121611644423</v>
+        <v>6.687550462758663</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.867121611644423</v>
+        <v>6.687550462758663</v>
       </c>
     </row>
     <row r="12">
@@ -1600,67 +1600,67 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3.77</v>
+        <v>3.8</v>
       </c>
       <c r="J12" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="K12" t="n">
-        <v>2.09</v>
+        <v>1.9</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2612136217442544</v>
+        <v>0.2447552447552447</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2676019983629997</v>
+        <v>0.2657342657342657</v>
       </c>
       <c r="N12" t="n">
-        <v>0.4711843798927459</v>
+        <v>0.4895104895104894</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0154600193462342</v>
+        <v>0.07518796992481214</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2975947611767379</v>
+        <v>0.1936345853165756</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3631868868116307</v>
+        <v>0.4361463595751254</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3392183520116314</v>
+        <v>0.3702190551082988</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.095584888448631</v>
+        <v>0.1704120938408597</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.095584888448631</v>
+        <v>0.1704120938408597</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.3631868868116307</v>
+        <v>0.4361463595751254</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.68</v>
+        <v>3.5</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>4.343023738335729</v>
+        <v>6.929718089702827</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.343023738335729</v>
+        <v>6.929718089702827</v>
       </c>
     </row>
     <row r="13">
@@ -1699,67 +1699,67 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="J13" t="n">
-        <v>4.25</v>
+        <v>3.9</v>
       </c>
       <c r="K13" t="n">
-        <v>4.71</v>
+        <v>4.33</v>
       </c>
       <c r="L13" t="n">
-        <v>0.5593495980395171</v>
+        <v>0.5513024344538721</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2316365394234235</v>
+        <v>0.2360705296251196</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2090138625370595</v>
+        <v>0.2126270359210083</v>
       </c>
       <c r="O13" t="n">
-        <v>0.01579016088195551</v>
+        <v>0.08615953383692743</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4159339070538805</v>
+        <v>0.3935526852620704</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5210881830161578</v>
+        <v>0.371993721964238</v>
       </c>
       <c r="S13" t="n">
-        <v>0.06297790992996173</v>
+        <v>0.2344535927736916</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2894516435927342</v>
+        <v>-0.1577497491918016</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>0.2894516435927342</v>
+        <v>-0.1577497491918016</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.5210881830161578</v>
+        <v>0.3935526852620704</v>
       </c>
       <c r="Z13" t="n">
-        <v>4.25</v>
+        <v>1.67</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>6.231222631612185</v>
+        <v>6.252967845400383</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.231222631612185</v>
+        <v>6.252967845400383</v>
       </c>
     </row>
     <row r="14">
@@ -1798,67 +1798,67 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.63</v>
+        <v>1.55</v>
       </c>
       <c r="J14" t="n">
-        <v>4.08</v>
+        <v>3.8</v>
       </c>
       <c r="K14" t="n">
-        <v>6.42</v>
+        <v>5.75</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6048129009018994</v>
+        <v>0.5961394175022167</v>
       </c>
       <c r="M14" t="n">
-        <v>0.2416286834485529</v>
+        <v>0.2431621308232726</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1535584156495476</v>
+        <v>0.1606984516745106</v>
       </c>
       <c r="O14" t="n">
-        <v>0.01435821160641315</v>
+        <v>0.08223222853768375</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.4323510492548665</v>
+        <v>0.4075709952077734</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3628227709264049</v>
+        <v>0.5033898896900657</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2048261798187285</v>
+        <v>0.08903911510216062</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>-0.1724618516470329</v>
+        <v>0.2602277588667931</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1724618516470329</v>
+        <v>0.2602277588667931</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.4323510492548665</v>
+        <v>0.5033898896900657</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.63</v>
+        <v>3.8</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>5.170095447807653</v>
+        <v>7.998117944070326</v>
       </c>
       <c r="AC14" t="n">
-        <v>5.170095447807653</v>
+        <v>7.998117944070326</v>
       </c>
     </row>
     <row r="15">
@@ -1897,67 +1897,67 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K15" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4559666492965086</v>
+        <v>0.4417349590245853</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2813965607087024</v>
+        <v>0.2854287427543474</v>
       </c>
       <c r="N15" t="n">
-        <v>0.262636789994789</v>
+        <v>0.2728362982210674</v>
       </c>
       <c r="O15" t="n">
-        <v>0.01534391534391522</v>
+        <v>0.07800043094160736</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.3641919878950581</v>
+        <v>0.4104221367688528</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3644408345692408</v>
+        <v>0.4561838127363048</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2713671775357012</v>
+        <v>0.1333940504948426</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.08304427386053836</v>
+        <v>0.1707550699819573</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.08304427386053836</v>
+        <v>0.1707550699819573</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.3644408345692408</v>
+        <v>0.4561838127363048</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>4.358018566276084</v>
+        <v>7.248083470025761</v>
       </c>
       <c r="AC15" t="n">
-        <v>4.358018566276084</v>
+        <v>7.248083470025761</v>
       </c>
     </row>
     <row r="16">
@@ -1996,67 +1996,67 @@
         </is>
       </c>
       <c r="I16" t="n">
-        <v>2.66</v>
+        <v>2.5</v>
       </c>
       <c r="J16" t="n">
-        <v>3.62</v>
+        <v>3.4</v>
       </c>
       <c r="K16" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="L16" t="n">
-        <v>0.3700853556983106</v>
+        <v>0.3682310469314079</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2719411729716869</v>
+        <v>0.2707581227436823</v>
       </c>
       <c r="N16" t="n">
-        <v>0.3579734713300023</v>
+        <v>0.3610108303249098</v>
       </c>
       <c r="O16" t="n">
-        <v>0.01581930718307589</v>
+        <v>0.08627450980392171</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.287198406903329</v>
+        <v>0.2795094227396802</v>
       </c>
       <c r="R16" t="n">
-        <v>0.4118390211731896</v>
+        <v>0.3115092711484589</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3009625719234814</v>
+        <v>0.4089813061118608</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1398978482015028</v>
+        <v>0.04797047578695102</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X16" t="n">
-        <v>0.1398978482015028</v>
+        <v>0.04797047578695102</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.4118390211731896</v>
+        <v>0.4089813061118608</v>
       </c>
       <c r="Z16" t="n">
-        <v>3.62</v>
+        <v>2.55</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>4.924810642339619</v>
+        <v>6.498105723213031</v>
       </c>
       <c r="AC16" t="n">
-        <v>4.924810642339619</v>
+        <v>6.498105723213031</v>
       </c>
     </row>
     <row r="17">
@@ -2095,67 +2095,67 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="J17" t="n">
-        <v>4.66</v>
+        <v>4.33</v>
       </c>
       <c r="K17" t="n">
-        <v>6.57</v>
+        <v>5.5</v>
       </c>
       <c r="L17" t="n">
-        <v>0.639030356665776</v>
+        <v>0.6207739668538242</v>
       </c>
       <c r="M17" t="n">
-        <v>0.2111817058509217</v>
+        <v>0.2121814020655104</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1497879374833021</v>
+        <v>0.1670446310806654</v>
       </c>
       <c r="O17" t="n">
-        <v>0.01614992555083106</v>
+        <v>0.08844073971094746</v>
       </c>
       <c r="P17" t="n">
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4856329309544022</v>
+        <v>0.4792232529054484</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4553411577455253</v>
+        <v>0.4005628360649574</v>
       </c>
       <c r="S17" t="n">
-        <v>0.05902591130007249</v>
+        <v>0.1202139110295941</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>-0.1533974257113738</v>
+        <v>-0.1415507139483758</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.1533974257113738</v>
+        <v>-0.1415507139483758</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.4856329309544022</v>
+        <v>0.4792232529054484</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>5.807245315953358</v>
+        <v>7.614145966735057</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.807245315953358</v>
+        <v>7.614145966735057</v>
       </c>
     </row>
     <row r="18">
@@ -2194,67 +2194,67 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="J18" t="n">
-        <v>4.56</v>
+        <v>4.33</v>
       </c>
       <c r="K18" t="n">
-        <v>6.78</v>
+        <v>5.75</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6390356425329264</v>
+        <v>0.6253155146562052</v>
       </c>
       <c r="M18" t="n">
-        <v>0.215814668750155</v>
+        <v>0.213733709397502</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1451496887169184</v>
+        <v>0.1609507759462928</v>
       </c>
       <c r="O18" t="n">
-        <v>0.01614152033341609</v>
+        <v>0.08053560137102656</v>
       </c>
       <c r="P18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.4491487214532782</v>
+        <v>0.3783718791484379</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3811947650146074</v>
+        <v>0.4305596769287864</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1696565135321142</v>
+        <v>0.1910684439227755</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>-0.1898869210796482</v>
+        <v>0.2168259675312844</v>
       </c>
       <c r="W18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.1898869210796482</v>
+        <v>0.2168259675312844</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.4491487214532782</v>
+        <v>0.4305596769287864</v>
       </c>
       <c r="Z18" t="n">
-        <v>1.54</v>
+        <v>4.33</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>5.370963628228279</v>
+        <v>6.840953997223694</v>
       </c>
       <c r="AC18" t="n">
-        <v>5.370963628228279</v>
+        <v>6.840953997223694</v>
       </c>
     </row>
     <row r="19">
@@ -2293,67 +2293,67 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="J19" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="K19" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L19" t="n">
-        <v>0.457992565055762</v>
+        <v>0.4513970877607241</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2862453531598513</v>
+        <v>0.298504525777253</v>
       </c>
       <c r="N19" t="n">
-        <v>0.2557620817843866</v>
+        <v>0.2500983864620228</v>
       </c>
       <c r="O19" t="n">
-        <v>0.01555421322863193</v>
+        <v>0.08065579348034113</v>
       </c>
       <c r="P19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.4286117247174239</v>
+        <v>0.3379584018994157</v>
       </c>
       <c r="R19" t="n">
-        <v>0.3710820883539895</v>
+        <v>0.4105416940307048</v>
       </c>
       <c r="S19" t="n">
-        <v>0.2003061869285866</v>
+        <v>0.2514999040698795</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>-0.02938084033833815</v>
+        <v>0.1120371682534518</v>
       </c>
       <c r="W19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.02938084033833815</v>
+        <v>0.1120371682534518</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.4286117247174239</v>
+        <v>0.4105416940307048</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>5.125380245191107</v>
+        <v>6.522897970473105</v>
       </c>
       <c r="AC19" t="n">
-        <v>5.125380245191107</v>
+        <v>6.522897970473105</v>
       </c>
     </row>
     <row r="20">
@@ -2392,67 +2392,67 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="J20" t="n">
-        <v>3.69</v>
+        <v>3.4</v>
       </c>
       <c r="K20" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="L20" t="n">
-        <v>0.5084777611444821</v>
+        <v>0.5038814396612561</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2673297714418144</v>
+        <v>0.2741707833450953</v>
       </c>
       <c r="N20" t="n">
-        <v>0.2241924674137034</v>
+        <v>0.2219477769936486</v>
       </c>
       <c r="O20" t="n">
-        <v>0.01373935482560085</v>
+        <v>0.07275342569460208</v>
       </c>
       <c r="P20" t="n">
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.4444813455119924</v>
+        <v>0.3737144766483231</v>
       </c>
       <c r="R20" t="n">
-        <v>0.3979370637554646</v>
+        <v>0.3732335341397709</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1575815907325429</v>
+        <v>0.2530519892119061</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>-0.0639964156324897</v>
+        <v>-0.130166963012933</v>
       </c>
       <c r="W20" t="n">
         <v>1</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.0639964156324897</v>
+        <v>-0.130166963012933</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.4444813455119924</v>
+        <v>0.3737144766483231</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.94</v>
+        <v>1.85</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>5.31515069762747</v>
+        <v>5.937768165109796</v>
       </c>
       <c r="AC20" t="n">
-        <v>5.31515069762747</v>
+        <v>5.937768165109796</v>
       </c>
     </row>
     <row r="21">
@@ -2491,67 +2491,67 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>2.02</v>
+        <v>1.75</v>
       </c>
       <c r="J21" t="n">
-        <v>3.37</v>
+        <v>3.5</v>
       </c>
       <c r="K21" t="n">
-        <v>4.49</v>
+        <v>4.2</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4879726526597545</v>
+        <v>0.5217391304347826</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2924939935824048</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="N21" t="n">
-        <v>0.2195333537578406</v>
+        <v>0.2173913043478261</v>
       </c>
       <c r="O21" t="n">
-        <v>0.01450255921549548</v>
+        <v>0.09523809523809512</v>
       </c>
       <c r="P21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.445501270182507</v>
+        <v>0.4158686899707409</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3785793296003209</v>
+        <v>0.4301014299472289</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1759194002171721</v>
+        <v>0.1540298800820306</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>-0.04247138247724752</v>
+        <v>0.1692318647298376</v>
       </c>
       <c r="W21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.04247138247724752</v>
+        <v>0.1692318647298376</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.445501270182507</v>
+        <v>0.4301014299472289</v>
       </c>
       <c r="Z21" t="n">
-        <v>2.02</v>
+        <v>3.5</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.2</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>5.327347054974636</v>
+        <v>6.833673133064369</v>
       </c>
       <c r="AC21" t="n">
-        <v>5.327347054974636</v>
+        <v>6.833673133064369</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8x0Cb1B6</t>
+          <t>M7MVoOR0</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45529.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,86 +610,86 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>1.42</v>
       </c>
       <c r="J2" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="K2" t="n">
-        <v>1.67</v>
+        <v>7</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1906936911218955</v>
+        <v>0.6658656253129068</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2383671139023694</v>
+        <v>0.1990587764093321</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5709391949757351</v>
+        <v>0.1350755982777611</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04880239520958085</v>
+        <v>0.05760881075929269</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.177736023467203</v>
+        <v>0.4871383652464762</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3668998997003179</v>
+        <v>0.4134855108631623</v>
       </c>
       <c r="S2" t="n">
-        <v>0.455364076832479</v>
+        <v>0.09937612389036149</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1155751181432561</v>
+        <v>-0.1787272600664306</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1155751181432561</v>
+        <v>-0.1787272600664306</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.455364076832479</v>
+        <v>0.4871383652464762</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.67</v>
+        <v>1.42</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.2</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>7.235059083608656</v>
+        <v>4.504232759138154</v>
       </c>
       <c r="AC2" t="n">
-        <v>7.235059083608656</v>
+        <v>4.504232759138154</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GrNwFMem</t>
+          <t>dbt7KrYP</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45528.5625</v>
+        <v>45529.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,86 +709,86 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2882865057380293</v>
+        <v>0.2798289933929266</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3068856351404828</v>
+        <v>0.2973183054799844</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4048278591214879</v>
+        <v>0.4228527011270889</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05114286308521043</v>
+        <v>0.05106209150326801</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.195898782992606</v>
+        <v>0.296795106668703</v>
       </c>
       <c r="R3" t="n">
-        <v>0.56509723527495</v>
+        <v>0.3972514661731673</v>
       </c>
       <c r="S3" t="n">
-        <v>0.239003981732444</v>
+        <v>0.3059534271581297</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2582116001344673</v>
+        <v>0.09993316069318281</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2582116001344673</v>
+        <v>0.09993316069318281</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.56509723527495</v>
+        <v>0.3972514661731673</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.2</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>8.978556046049855</v>
+        <v>7.261201837605509</v>
       </c>
       <c r="AC3" t="n">
-        <v>8.978556046049855</v>
+        <v>7.261201837605509</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AsIP75lK</t>
+          <t>UilLdutJ</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45528.65625</v>
+        <v>45529.65625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,86 +808,86 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.2</v>
+        <v>1.45</v>
       </c>
       <c r="J4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K4" t="n">
         <v>7</v>
       </c>
-      <c r="K4" t="n">
-        <v>13</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.7913043478260869</v>
+        <v>0.6538661131292164</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1356521739130435</v>
+        <v>0.210690192008303</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07304347826086957</v>
+        <v>0.1354436948624805</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05311355311355315</v>
+        <v>0.05473453749315826</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5216999983655525</v>
+        <v>0.4134914419577893</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3123335874324227</v>
+        <v>0.5305119879743958</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1659664142020247</v>
+        <v>0.05599657006781505</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.2696043494605345</v>
+        <v>0.3198217959660928</v>
       </c>
       <c r="W4" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2696043494605345</v>
+        <v>0.3198217959660928</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4783000016344475</v>
+        <v>0.5305119879743958</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.2</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>7.599476874826944</v>
+        <v>12.41881768035136</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.599476874826944</v>
+        <v>12.41881768035136</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6D3e2qCs</t>
+          <t>2uc40Ntf</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45528.65625</v>
+        <v>45529.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,67 +907,1255 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>2.88</v>
+        <v>4.1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3647654845563001</v>
+        <v>0.4984369572768322</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3059323418859291</v>
+        <v>0.2705800625217089</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3293021735577709</v>
+        <v>0.2309829802014589</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05441825199889694</v>
+        <v>0.05593251421236012</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4375892145995566</v>
+        <v>0.4739882954102477</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3986172205627716</v>
+        <v>0.4229181611875265</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1637935648376717</v>
+        <v>0.1030935434022259</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.07282373004325648</v>
+        <v>-0.02444866186658451</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.07282373004325648</v>
+        <v>-0.02444866186658451</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4375892145995566</v>
+        <v>0.4739882954102477</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.6</v>
+        <v>1.9</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.2</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>6.95264291377647</v>
+        <v>6.565363924740206</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.95264291377647</v>
+        <v>6.565363924740206</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>0hYMmpcl</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45530.5625</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>77</v>
+      </c>
+      <c r="F6" t="n">
+        <v>771</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.4473684210526316</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2763157894736842</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.2763157894736842</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.06442577030812324</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.4092633779582805</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3821466677655259</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.2085899542761935</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>-0.03810504309435103</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.03810504309435103</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.4092633779582805</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>5.420633377469721</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>5.420633377469721</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>fZZxp2dD</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45530.65625</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>77</v>
+      </c>
+      <c r="F7" t="n">
+        <v>771</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.1889456293181136</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.2553319315109642</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.5557224391709222</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.05850556438791732</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.2324751117409399</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.5345253574679436</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.2329995307911163</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.2791934259569794</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.2791934259569794</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.5345253574679436</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>11.88406882718736</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>11.88406882718736</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>EaryFQkA</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45534.5625</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>77</v>
+      </c>
+      <c r="F8" t="n">
+        <v>771</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.2560834298957126</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2711471610660486</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.4727694090382387</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.08471593765711427</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.2975947611767379</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3631868868116307</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.3392183520116314</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.09203972574558206</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.09203972574558206</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.3631868868116307</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>6.648420198470709</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>6.648420198470709</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WdSjHeFt</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45534.65625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>77</v>
+      </c>
+      <c r="F9" t="n">
+        <v>771</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.528123658222413</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2464577071704595</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.2254186346071276</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.08199767711962824</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.4156206291348301</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.5214453905650241</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.06293398030014599</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.2749876833945647</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.2749876833945647</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.5214453905650241</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>11.63161728594584</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>11.63161728594584</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>ELeQ0zVa</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>77</v>
+      </c>
+      <c r="F10" t="n">
+        <v>771</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5961394175022167</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2431621308232726</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.1606984516745106</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.08223222853768375</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.4323510492548665</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3628227709264049</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2048261798187285</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>-0.1637883682473502</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.1637883682473502</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.4323510492548665</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>3.922260921732502</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>3.922260921732502</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>d4DGBiqI</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45535.5625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>77</v>
+      </c>
+      <c r="F11" t="n">
+        <v>771</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.4417349590245853</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2854287427543474</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.2728362982210674</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.07800043094160736</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.3641919878950581</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3644408345692408</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2713671775357012</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.07901209181489338</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.07901209181489338</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.3644408345692408</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>6.476469765863448</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>6.476469765863448</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>0xK7DDE5</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45535.65625</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>77</v>
+      </c>
+      <c r="F12" t="n">
+        <v>771</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.3425692695214105</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2720403022670025</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3853904282115869</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.08115468409586057</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.3014186925256958</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.3995571376651378</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.2990241698091664</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.1275168353981353</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.1275168353981353</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.3995571376651378</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>7.697724939491898</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>7.697724939491898</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>SjzlgqTj</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45535.65625</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>77</v>
+      </c>
+      <c r="F13" t="n">
+        <v>771</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K13" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6207739668538242</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2121814020655104</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.1670446310806654</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.08844073971094746</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4924294811901441</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.4422684721013385</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.06530204670851754</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.1283444856636802</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.1283444856636802</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4924294811901441</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>5.317329812114272</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>5.317329812114272</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>nZgYbEaC</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45536.5625</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>77</v>
+      </c>
+      <c r="F14" t="n">
+        <v>771</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="J14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K14" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.6253155146562052</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.213733709397502</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.1609507759462928</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.08053560137102656</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.4491487214532782</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3811947650146074</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.1696565135321142</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.1761667932029269</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.1761667932029269</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.4491487214532782</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>3.986802430995884</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>3.986802430995884</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>r1mschUO</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45536.5625</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>77</v>
+      </c>
+      <c r="F15" t="n">
+        <v>771</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.4482827877083752</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2964450692910223</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.2552721430006025</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.08816330098784864</v>
+      </c>
+      <c r="P15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.4286117247174239</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3710820883539895</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2003061869285866</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-0.01967106299095134</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.01967106299095134</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.4286117247174239</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.972430610164642</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.972430610164642</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>hCGaFZqg</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>77</v>
+      </c>
+      <c r="F16" t="n">
+        <v>771</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K16" t="n">
+        <v>4</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4916847433116414</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.274765003615329</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.2335502530730297</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.07043343653250767</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.4444813455119924</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3979370637554646</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.1575815907325429</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>-0.04720339779964899</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.04720339779964899</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4444813455119924</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>5.802100885843487</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5.802100885843487</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6ZvTGnLc</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45536.65625</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>77</v>
+      </c>
+      <c r="F17" t="n">
+        <v>771</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.5080174927113702</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2689504373177842</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2230320699708455</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.09357564163876941</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.4233629189166165</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.366992783464725</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2096442976186587</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-0.08465457379475366</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.08465457379475366</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.4233629189166165</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>4.946713001792631</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.946713001792631</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -634,43 +634,43 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4871383652464762</v>
+        <v>0.6299941404289507</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4134855108631623</v>
+        <v>0.2625197467596195</v>
       </c>
       <c r="S2" t="n">
-        <v>0.09937612389036149</v>
+        <v>0.1074861128114303</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1787272600664306</v>
+        <v>-0.03587148488395608</v>
       </c>
       <c r="W2" t="n">
         <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1787272600664306</v>
+        <v>-0.03587148488395608</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4871383652464762</v>
+        <v>0.6299941404289507</v>
       </c>
       <c r="Z2" t="n">
         <v>1.42</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.504232759138154</v>
+        <v>8.676946721777972</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.504232759138154</v>
+        <v>8.676946721777972</v>
       </c>
     </row>
     <row r="3">
@@ -733,43 +733,43 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.296795106668703</v>
+        <v>0.3096268775847986</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3972514661731673</v>
+        <v>0.3635790846516872</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3059534271581297</v>
+        <v>0.3267940377635143</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.09993316069318281</v>
+        <v>0.06626077917170275</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.09993316069318281</v>
+        <v>0.06626077917170275</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3972514661731673</v>
+        <v>0.3635790846516872</v>
       </c>
       <c r="Z3" t="n">
         <v>3.2</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>7.261201837605509</v>
+        <v>6.277655905699413</v>
       </c>
       <c r="AC3" t="n">
-        <v>7.261201837605509</v>
+        <v>6.277655905699413</v>
       </c>
     </row>
     <row r="4">
@@ -829,46 +829,46 @@
         <v>0.05473453749315826</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4134914419577893</v>
+        <v>0.4530604260846444</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5305119879743958</v>
+        <v>0.3271292930905851</v>
       </c>
       <c r="S4" t="n">
-        <v>0.05599657006781505</v>
+        <v>0.2198102808247704</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3198217959660928</v>
+        <v>-0.200805687044572</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.3198217959660928</v>
+        <v>-0.200805687044572</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5305119879743958</v>
+        <v>0.4530604260846444</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.5</v>
+        <v>1.45</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>12.41881768035136</v>
+        <v>3.684089321520494</v>
       </c>
       <c r="AC4" t="n">
-        <v>12.41881768035136</v>
+        <v>3.684089321520494</v>
       </c>
     </row>
     <row r="5">
@@ -931,43 +931,43 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4739882954102477</v>
+        <v>0.5399574698548413</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4229181611875265</v>
+        <v>0.3279534257770783</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1030935434022259</v>
+        <v>0.1320891043680803</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.02444866186658451</v>
+        <v>0.04152051257800904</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.02444866186658451</v>
+        <v>0.04152051257800904</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4739882954102477</v>
+        <v>0.5399574698548413</v>
       </c>
       <c r="Z5" t="n">
         <v>1.9</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>6.565363924740206</v>
+        <v>8.492275839621946</v>
       </c>
       <c r="AC5" t="n">
-        <v>6.565363924740206</v>
+        <v>8.492275839621946</v>
       </c>
     </row>
     <row r="6">
@@ -1027,46 +1027,46 @@
         <v>0.06442577030812324</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4092633779582805</v>
+        <v>0.3116787579932877</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3821466677655259</v>
+        <v>0.5181862778996099</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2085899542761935</v>
+        <v>0.1701349641071023</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.03810504309435103</v>
+        <v>0.2418704884259257</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.03810504309435103</v>
+        <v>0.2418704884259257</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4092633779582805</v>
+        <v>0.5181862778996099</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>5.420633377469721</v>
+        <v>11.10035445607421</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.420633377469721</v>
+        <v>11.10035445607421</v>
       </c>
     </row>
     <row r="7">
@@ -1126,46 +1126,46 @@
         <v>0.05850556438791732</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2324751117409399</v>
+        <v>0.267329570534093</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5345253574679436</v>
+        <v>0.3127621238781438</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2329995307911163</v>
+        <v>0.4199083055877632</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2791934259569794</v>
+        <v>-0.1358141335831591</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2791934259569794</v>
+        <v>-0.1358141335831591</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5345253574679436</v>
+        <v>0.4199083055877632</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>11.88406882718736</v>
+        <v>4.149092736061956</v>
       </c>
       <c r="AC7" t="n">
-        <v>11.88406882718736</v>
+        <v>4.149092736061956</v>
       </c>
     </row>
     <row r="8">
@@ -1228,43 +1228,43 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2975947611767379</v>
+        <v>0.1936345853165756</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3631868868116307</v>
+        <v>0.4361463595751254</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3392183520116314</v>
+        <v>0.3702190551082988</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.09203972574558206</v>
+        <v>0.1649991985090767</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.09203972574558206</v>
+        <v>0.1649991985090767</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3631868868116307</v>
+        <v>0.4361463595751254</v>
       </c>
       <c r="Z8" t="n">
         <v>3.4</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>6.648420198470709</v>
+        <v>8.77951367591818</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.648420198470709</v>
+        <v>8.77951367591818</v>
       </c>
     </row>
     <row r="9">
@@ -1324,46 +1324,46 @@
         <v>0.08199767711962824</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4156206291348301</v>
+        <v>0.3935526852620704</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5214453905650241</v>
+        <v>0.371993721964238</v>
       </c>
       <c r="S9" t="n">
-        <v>0.06293398030014599</v>
+        <v>0.2344535927736916</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2749876833945647</v>
+        <v>-0.1345709729603426</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2749876833945647</v>
+        <v>-0.1345709729603426</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5214453905650241</v>
+        <v>0.3935526852620704</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.75</v>
+        <v>1.75</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>11.63161728594584</v>
+        <v>3.782334335484263</v>
       </c>
       <c r="AC9" t="n">
-        <v>11.63161728594584</v>
+        <v>3.782334335484263</v>
       </c>
     </row>
     <row r="10">
@@ -1423,46 +1423,46 @@
         <v>0.08223222853768375</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4323510492548665</v>
+        <v>0.4075709952077734</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3628227709264049</v>
+        <v>0.5033898896900657</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2048261798187285</v>
+        <v>0.08903911510216062</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.1637883682473502</v>
+        <v>0.2602277588667931</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1637883682473502</v>
+        <v>0.2602277588667931</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4323510492548665</v>
+        <v>0.5033898896900657</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.55</v>
+        <v>3.8</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>3.922260921732502</v>
+        <v>11.15235985448032</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.922260921732502</v>
+        <v>11.15235985448032</v>
       </c>
     </row>
     <row r="11">
@@ -1525,43 +1525,43 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.3641919878950581</v>
+        <v>0.4104221367688528</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3644408345692408</v>
+        <v>0.4561838127363048</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2713671775357012</v>
+        <v>0.1333940504948426</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.07901209181489338</v>
+        <v>0.1707550699819573</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.07901209181489338</v>
+        <v>0.1707550699819573</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.3644408345692408</v>
+        <v>0.4561838127363048</v>
       </c>
       <c r="Z11" t="n">
         <v>3.25</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>6.476469765863448</v>
+        <v>9.156215862812502</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.476469765863448</v>
+        <v>9.156215862812502</v>
       </c>
     </row>
     <row r="12">
@@ -1621,46 +1621,46 @@
         <v>0.08115468409586057</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.3014186925256958</v>
+        <v>0.2701756319800689</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3995571376651378</v>
+        <v>0.3158037836299356</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2990241698091664</v>
+        <v>0.4140205843899953</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1275168353981353</v>
+        <v>0.02863015617840836</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X12" t="n">
-        <v>0.1275168353981353</v>
+        <v>0.02863015617840836</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.3995571376651378</v>
+        <v>0.4140205843899953</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>7.697724939491898</v>
+        <v>6.464754131862461</v>
       </c>
       <c r="AC12" t="n">
-        <v>7.697724939491898</v>
+        <v>6.464754131862461</v>
       </c>
     </row>
     <row r="13">
@@ -1723,43 +1723,43 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.4924294811901441</v>
+        <v>0.529849157913343</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4422684721013385</v>
+        <v>0.3184139663759257</v>
       </c>
       <c r="S13" t="n">
-        <v>0.06530204670851754</v>
+        <v>0.1517368757107315</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>-0.1283444856636802</v>
+        <v>-0.09092480894048127</v>
       </c>
       <c r="W13" t="n">
         <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.1283444856636802</v>
+        <v>-0.09092480894048127</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4924294811901441</v>
+        <v>0.529849157913343</v>
       </c>
       <c r="Z13" t="n">
         <v>1.48</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>5.317329812114272</v>
+        <v>6.410331528992118</v>
       </c>
       <c r="AC13" t="n">
-        <v>5.317329812114272</v>
+        <v>6.410331528992118</v>
       </c>
     </row>
     <row r="14">
@@ -1798,67 +1798,67 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="J14" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="K14" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="L14" t="n">
-        <v>0.6253155146562052</v>
+        <v>0.6088400411164703</v>
       </c>
       <c r="M14" t="n">
-        <v>0.213733709397502</v>
+        <v>0.221791729263857</v>
       </c>
       <c r="N14" t="n">
-        <v>0.1609507759462928</v>
+        <v>0.1693682296196727</v>
       </c>
       <c r="O14" t="n">
-        <v>0.08053560137102656</v>
+        <v>0.07350819115524998</v>
       </c>
       <c r="P14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.4491487214532782</v>
+        <v>0.37309299949497</v>
       </c>
       <c r="R14" t="n">
-        <v>0.3811947650146074</v>
+        <v>0.4350278896394806</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1696565135321142</v>
+        <v>0.1918791108655493</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>-0.1761667932029269</v>
+        <v>0.2132361603756235</v>
       </c>
       <c r="W14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1761667932029269</v>
+        <v>0.2132361603756235</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.4491487214532782</v>
+        <v>0.4350278896394806</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.48</v>
+        <v>4.2</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>3.986802430995884</v>
+        <v>9.467662226186684</v>
       </c>
       <c r="AC14" t="n">
-        <v>3.986802430995884</v>
+        <v>9.467662226186684</v>
       </c>
     </row>
     <row r="15">
@@ -1918,46 +1918,46 @@
         <v>0.08816330098784864</v>
       </c>
       <c r="P15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.4286117247174239</v>
+        <v>0.3379584018994157</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3710820883539895</v>
+        <v>0.4105416940307048</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2003061869285866</v>
+        <v>0.2514999040698795</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>-0.01967106299095134</v>
+        <v>0.1140966247396826</v>
       </c>
       <c r="W15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.01967106299095134</v>
+        <v>0.1140966247396826</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.4286117247174239</v>
+        <v>0.4105416940307048</v>
       </c>
       <c r="Z15" t="n">
-        <v>2.05</v>
+        <v>3.1</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>5.972430610164642</v>
+        <v>7.662153088570553</v>
       </c>
       <c r="AC15" t="n">
-        <v>5.972430610164642</v>
+        <v>7.662153088570553</v>
       </c>
     </row>
     <row r="16">
@@ -2020,43 +2020,43 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.4444813455119924</v>
+        <v>0.3737144766483231</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3979370637554646</v>
+        <v>0.3732335341397709</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1575815907325429</v>
+        <v>0.2530519892119061</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>-0.04720339779964899</v>
+        <v>-0.1179702666633182</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.04720339779964899</v>
+        <v>-0.1179702666633182</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.4444813455119924</v>
+        <v>0.3737144766483231</v>
       </c>
       <c r="Z16" t="n">
         <v>1.9</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>5.802100885843487</v>
+        <v>3.735051783890487</v>
       </c>
       <c r="AC16" t="n">
-        <v>5.802100885843487</v>
+        <v>3.735051783890487</v>
       </c>
     </row>
     <row r="17">
@@ -2116,46 +2116,46 @@
         <v>0.09357564163876941</v>
       </c>
       <c r="P17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4233629189166165</v>
+        <v>0.4004031360012256</v>
       </c>
       <c r="R17" t="n">
-        <v>0.366992783464725</v>
+        <v>0.440533898257623</v>
       </c>
       <c r="S17" t="n">
-        <v>0.2096442976186587</v>
+        <v>0.1590629657411515</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>-0.08465457379475366</v>
+        <v>0.1715834609398388</v>
       </c>
       <c r="W17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.08465457379475366</v>
+        <v>0.1715834609398388</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.4233629189166165</v>
+        <v>0.440533898257623</v>
       </c>
       <c r="Z17" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>4.946713001792631</v>
+        <v>8.939752866955878</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.946713001792631</v>
+        <v>8.939752866955878</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,10 +565,15 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>dif_prob_limited</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>multiplier</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -577,20 +582,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>M7MVoOR0</t>
+          <t>0hYMmpcl</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45530.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +615,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.42</v>
+        <v>2.1</v>
       </c>
       <c r="J2" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6658656253129068</v>
+        <v>0.4473684210526316</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1990587764093321</v>
+        <v>0.2763157894736842</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1350755982777611</v>
+        <v>0.2763157894736842</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05760881075929269</v>
+        <v>0.06442577030812324</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6299941404289507</v>
+        <v>0.3116787579932877</v>
       </c>
       <c r="R2" t="n">
-        <v>0.2625197467596195</v>
+        <v>0.5181862778996099</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1074861128114303</v>
+        <v>0.1701349641071023</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.03587148488395608</v>
+        <v>0.2418704884259257</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.03587148488395608</v>
+        <v>0.2418704884259257</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6299941404289507</v>
+        <v>0.5181862778996099</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.42</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +672,32 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>8.676946721777972</v>
+        <v>0.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>8.676946721777972</v>
+        <v>9.758619166339734</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>9.758619166339734</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>dbt7KrYP</t>
+          <t>fZZxp2dD</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45529.5625</v>
+        <v>45530.65625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +717,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.4</v>
+        <v>4.75</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="K3" t="n">
-        <v>2.25</v>
+        <v>1.75</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2798289933929266</v>
+        <v>0.198659834450138</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2973183054799844</v>
+        <v>0.2621206148994876</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4228527011270889</v>
+        <v>0.5392195506503745</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05106209150326801</v>
+        <v>0.05973266499582275</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3096268775847986</v>
+        <v>0.3053679739992727</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3635790846516872</v>
+        <v>0.3049944837058366</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3267940377635143</v>
+        <v>0.3896375422948907</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.06626077917170275</v>
+        <v>-0.1495820083554838</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>0.06626077917170275</v>
+        <v>-0.1495820083554838</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3635790846516872</v>
+        <v>0.3896375422948907</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.2</v>
+        <v>1.75</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +774,32 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>6.277655905699413</v>
+        <v>-0.1495820083554838</v>
       </c>
       <c r="AC3" t="n">
-        <v>6.277655905699413</v>
+        <v>3.50592433872007</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>3.50592433872007</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UilLdutJ</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45529.65625</v>
+        <v>45534.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +819,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.45</v>
+        <v>3.6</v>
       </c>
       <c r="J4" t="n">
-        <v>4.5</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>7</v>
+        <v>1.95</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6538661131292164</v>
+        <v>0.2560834298957126</v>
       </c>
       <c r="M4" t="n">
-        <v>0.210690192008303</v>
+        <v>0.2711471610660486</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1354436948624805</v>
+        <v>0.4727694090382387</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05473453749315826</v>
+        <v>0.08471593765711427</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4530604260846444</v>
+        <v>0.2108571490481769</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3271292930905851</v>
+        <v>0.3957389287674579</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2198102808247704</v>
+        <v>0.3934039221843652</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.200805687044572</v>
+        <v>0.1245917677014093</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.200805687044572</v>
+        <v>0.1245917677014093</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4530604260846444</v>
+        <v>0.3957389287674579</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.45</v>
+        <v>3.4</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +876,32 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>3.684089321520494</v>
+        <v>0.1245917677014093</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.684089321520494</v>
+        <v>7.599241821243864</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>7.599241821243864</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2uc40Ntf</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45529.65625</v>
+        <v>45534.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +921,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4984369572768322</v>
+        <v>0.5355704697986577</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2705800625217089</v>
+        <v>0.2438255033557047</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2309829802014589</v>
+        <v>0.2206040268456375</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05593251421236012</v>
+        <v>0.07928781491300518</v>
       </c>
       <c r="P5" t="n">
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5399574698548413</v>
+        <v>0.3992443537488397</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3279534257770783</v>
+        <v>0.3843085722277485</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1320891043680803</v>
+        <v>0.216447074023412</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.04152051257800904</v>
+        <v>-0.1363261160498181</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04152051257800904</v>
+        <v>-0.1363261160498181</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5399574698548413</v>
+        <v>0.3992443537488397</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +978,32 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>8.492275839621946</v>
+        <v>-0.1363261160498181</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.492275839621946</v>
+        <v>3.839825866605747</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.839825866605747</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45530.5625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1023,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.1</v>
+        <v>1.55</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.5961394175022167</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2763157894736842</v>
+        <v>0.2431621308232726</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2763157894736842</v>
+        <v>0.1606984516745106</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06442577030812324</v>
+        <v>0.08223222853768375</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3116787579932877</v>
+        <v>0.408460400545195</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5181862778996099</v>
+        <v>0.5037801391864014</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1701349641071023</v>
+        <v>0.08775946026840357</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2418704884259257</v>
+        <v>0.2606180083631288</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2418704884259257</v>
+        <v>0.2606180083631288</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5181862778996099</v>
+        <v>0.5037801391864014</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1080,32 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>11.10035445607421</v>
+        <v>0.15</v>
       </c>
       <c r="AC6" t="n">
-        <v>11.10035445607421</v>
+        <v>9.548222715515303</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>9.548222715515303</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45530.65625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1125,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>5</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>1.7</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1889456293181136</v>
+        <v>0.4417349590245853</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2553319315109642</v>
+        <v>0.2854287427543474</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5557224391709222</v>
+        <v>0.2728362982210674</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05850556438791732</v>
+        <v>0.07800043094160736</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.267329570534093</v>
+        <v>0.4211570902915869</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3127621238781438</v>
+        <v>0.441383952088532</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4199083055877632</v>
+        <v>0.1374589576198811</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.1358141335831591</v>
+        <v>0.1559552093341846</v>
       </c>
       <c r="W7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1358141335831591</v>
+        <v>0.1559552093341846</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4199083055877632</v>
+        <v>0.441383952088532</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.7</v>
+        <v>3.25</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1182,32 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4.149092736061956</v>
+        <v>0.15</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.149092736061956</v>
+        <v>8.636948947317281</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>8.636948947317281</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45534.5625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1227,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.6</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
         <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>1.95</v>
+        <v>2.4</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2560834298957126</v>
+        <v>0.3425692695214105</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2711471610660486</v>
+        <v>0.2720403022670025</v>
       </c>
       <c r="N8" t="n">
-        <v>0.4727694090382387</v>
+        <v>0.3853904282115869</v>
       </c>
       <c r="O8" t="n">
-        <v>0.08471593765711427</v>
+        <v>0.08115468409586057</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1936345853165756</v>
+        <v>0.2701756319800689</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4361463595751254</v>
+        <v>0.3158037836299356</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3702190551082988</v>
+        <v>0.4140205843899953</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1649991985090767</v>
+        <v>0.02863015617840836</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>0.1649991985090767</v>
+        <v>0.02863015617840836</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4361463595751254</v>
+        <v>0.4140205843899953</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.4</v>
+        <v>2.4</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1284,32 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>8.77951367591818</v>
+        <v>0.02863015617840836</v>
       </c>
       <c r="AC8" t="n">
-        <v>8.77951367591818</v>
+        <v>6.464754131862461</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>6.464754131862461</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1329,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="J9" t="n">
-        <v>3.75</v>
+        <v>4.33</v>
       </c>
       <c r="K9" t="n">
-        <v>4.1</v>
+        <v>5.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.528123658222413</v>
+        <v>0.6207739668538242</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2464577071704595</v>
+        <v>0.2121814020655104</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2254186346071276</v>
+        <v>0.1670446310806654</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08199767711962824</v>
+        <v>0.08844073971094746</v>
       </c>
       <c r="P9" t="n">
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3935526852620704</v>
+        <v>0.529849157913343</v>
       </c>
       <c r="R9" t="n">
-        <v>0.371993721964238</v>
+        <v>0.3184139663759257</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2344535927736916</v>
+        <v>0.1517368757107315</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.1345709729603426</v>
+        <v>-0.09092480894048127</v>
       </c>
       <c r="W9" t="n">
         <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1345709729603426</v>
+        <v>-0.09092480894048127</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.3935526852620704</v>
+        <v>0.529849157913343</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.75</v>
+        <v>1.48</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1386,32 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>3.782334335484263</v>
+        <v>-0.09092480894048127</v>
       </c>
       <c r="AC9" t="n">
-        <v>3.782334335484263</v>
+        <v>6.410331528992118</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>6.410331528992118</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,56 +1431,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="J10" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="K10" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5961394175022167</v>
+        <v>0.6088400411164703</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2431621308232726</v>
+        <v>0.221791729263857</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1606984516745106</v>
+        <v>0.1693682296196727</v>
       </c>
       <c r="O10" t="n">
-        <v>0.08223222853768375</v>
+        <v>0.07350819115524998</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4075709952077734</v>
+        <v>0.4751085563624848</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5033898896900657</v>
+        <v>0.3813915965199271</v>
       </c>
       <c r="S10" t="n">
-        <v>0.08903911510216062</v>
+        <v>0.1434998471175884</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2602277588667931</v>
+        <v>-0.1337314847539855</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2602277588667931</v>
+        <v>-0.1337314847539855</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.5033898896900657</v>
+        <v>0.4751085563624848</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.8</v>
+        <v>1.53</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,29 +1488,32 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>11.15235985448032</v>
+        <v>-0.1337314847539855</v>
       </c>
       <c r="AC10" t="n">
-        <v>11.15235985448032</v>
+        <v>4.985688787892389</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>4.985688787892389</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1501,56 +1533,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="J11" t="n">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="K11" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4417349590245853</v>
+        <v>0.4482827877083752</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2854287427543474</v>
+        <v>0.2964450692910223</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2728362982210674</v>
+        <v>0.2552721430006025</v>
       </c>
       <c r="O11" t="n">
-        <v>0.07800043094160736</v>
+        <v>0.08816330098784864</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4104221367688528</v>
+        <v>0.4007882309120315</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4561838127363048</v>
+        <v>0.3631538989066805</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1333940504948426</v>
+        <v>0.2360578701812881</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1707550699819573</v>
+        <v>-0.04749455679634373</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1707550699819573</v>
+        <v>-0.04749455679634373</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4561838127363048</v>
+        <v>0.4007882309120315</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1558,29 +1590,32 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>9.156215862812502</v>
+        <v>-0.04749455679634373</v>
       </c>
       <c r="AC11" t="n">
-        <v>9.156215862812502</v>
+        <v>5.159726461922225</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>5.159726461922225</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1600,56 +1635,56 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.7</v>
+        <v>1.9</v>
       </c>
       <c r="J12" t="n">
         <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>2.4</v>
+        <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3425692695214105</v>
+        <v>0.4916847433116414</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2720403022670025</v>
+        <v>0.274765003615329</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3853904282115869</v>
+        <v>0.2335502530730297</v>
       </c>
       <c r="O12" t="n">
-        <v>0.08115468409586057</v>
+        <v>0.07043343653250767</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2701756319800689</v>
+        <v>0.3742319055023551</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3158037836299356</v>
+        <v>0.3729476351612947</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4140205843899953</v>
+        <v>0.2528204593363501</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.02863015617840836</v>
+        <v>-0.1174528378092863</v>
       </c>
       <c r="W12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X12" t="n">
-        <v>0.02863015617840836</v>
+        <v>-0.1174528378092863</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4140205843899953</v>
+        <v>0.3742319055023551</v>
       </c>
       <c r="Z12" t="n">
-        <v>2.4</v>
+        <v>1.9</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1657,29 +1692,32 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>6.464754131862461</v>
+        <v>-0.1174528378092863</v>
       </c>
       <c r="AC12" t="n">
-        <v>6.464754131862461</v>
+        <v>3.750165506812321</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>3.750165506812321</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1699,56 +1737,56 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>1.48</v>
+        <v>1.8</v>
       </c>
       <c r="J13" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>5.5</v>
+        <v>4.1</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6207739668538242</v>
+        <v>0.5080174927113702</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2121814020655104</v>
+        <v>0.2689504373177842</v>
       </c>
       <c r="N13" t="n">
-        <v>0.1670446310806654</v>
+        <v>0.2230320699708455</v>
       </c>
       <c r="O13" t="n">
-        <v>0.08844073971094746</v>
+        <v>0.09357564163876941</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.529849157913343</v>
+        <v>0.4004031360012256</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3184139663759257</v>
+        <v>0.440533898257623</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1517368757107315</v>
+        <v>0.1590629657411515</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>-0.09092480894048127</v>
+        <v>0.1715834609398388</v>
       </c>
       <c r="W13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.09092480894048127</v>
+        <v>0.1715834609398388</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.529849157913343</v>
+        <v>0.440533898257623</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.48</v>
+        <v>3.4</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1756,406 +1794,13 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>6.410331528992118</v>
+        <v>0.15</v>
       </c>
       <c r="AC13" t="n">
-        <v>6.410331528992118</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>fiorentina</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>monza</t>
-        </is>
-      </c>
-      <c r="E14" t="n">
-        <v>77</v>
-      </c>
-      <c r="F14" t="n">
-        <v>771</v>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="J14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K14" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0.6088400411164703</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0.221791729263857</v>
-      </c>
-      <c r="N14" t="n">
-        <v>0.1693682296196727</v>
-      </c>
-      <c r="O14" t="n">
-        <v>0.07350819115524998</v>
-      </c>
-      <c r="P14" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>0.37309299949497</v>
-      </c>
-      <c r="R14" t="n">
-        <v>0.4350278896394806</v>
-      </c>
-      <c r="S14" t="n">
-        <v>0.1918791108655493</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1</v>
-      </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="n">
-        <v>0.2132361603756235</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0.2132361603756235</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.4350278896394806</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB14" t="n">
-        <v>9.467662226186684</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>9.467662226186684</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>genoa</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>verona</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>77</v>
-      </c>
-      <c r="F15" t="n">
-        <v>771</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I15" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="J15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K15" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.4482827877083752</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0.2964450692910223</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.2552721430006025</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0.08816330098784864</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>0.3379584018994157</v>
-      </c>
-      <c r="R15" t="n">
-        <v>0.4105416940307048</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0.2514999040698795</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1</v>
-      </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="n">
-        <v>0.1140966247396826</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>0.1140966247396826</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.4105416940307048</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>7.662153088570553</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>7.662153088570553</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>juventus</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>as roma</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>77</v>
-      </c>
-      <c r="F16" t="n">
-        <v>771</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J16" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K16" t="n">
-        <v>4</v>
-      </c>
-      <c r="L16" t="n">
-        <v>0.4916847433116414</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.274765003615329</v>
-      </c>
-      <c r="N16" t="n">
-        <v>0.2335502530730297</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0.07043343653250767</v>
-      </c>
-      <c r="P16" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>0.3737144766483231</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0.3732335341397709</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0.2530519892119061</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1</v>
-      </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="n">
-        <v>-0.1179702666633182</v>
-      </c>
-      <c r="W16" t="n">
-        <v>1</v>
-      </c>
-      <c r="X16" t="n">
-        <v>-0.1179702666633182</v>
-      </c>
-      <c r="Y16" t="n">
-        <v>0.3737144766483231</v>
-      </c>
-      <c r="Z16" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB16" t="n">
-        <v>3.735051783890487</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>3.735051783890487</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>udinese</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>como</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>77</v>
-      </c>
-      <c r="F17" t="n">
-        <v>771</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K17" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.5080174927113702</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0.2689504373177842</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0.2230320699708455</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0.09357564163876941</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>0.4004031360012256</v>
-      </c>
-      <c r="R17" t="n">
-        <v>0.440533898257623</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0.1590629657411515</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1</v>
-      </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="n">
-        <v>0.1715834609398388</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>0.1715834609398388</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.440533898257623</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB17" t="n">
-        <v>8.939752866955878</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>8.939752866955878</v>
+        <v>8.624534218249805</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>8.624534218249805</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,15 +565,10 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>dif_prob_limited</t>
+          <t>multiplier</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>multiplier</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -672,12 +667,9 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0.15</v>
+        <v>9.758619166339734</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.758619166339734</v>
-      </c>
-      <c r="AD2" t="n">
         <v>9.758619166339734</v>
       </c>
     </row>
@@ -774,12 +766,9 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-0.1495820083554838</v>
+        <v>3.50592433872007</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.50592433872007</v>
-      </c>
-      <c r="AD3" t="n">
         <v>3.50592433872007</v>
       </c>
     </row>
@@ -876,12 +865,9 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0.1245917677014093</v>
+        <v>7.599241821243864</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.599241821243864</v>
-      </c>
-      <c r="AD4" t="n">
         <v>7.599241821243864</v>
       </c>
     </row>
@@ -945,29 +931,29 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3992443537488397</v>
+        <v>0.3992443537488325</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3843085722277485</v>
+        <v>0.3843085722277583</v>
       </c>
       <c r="S5" t="n">
-        <v>0.216447074023412</v>
+        <v>0.2164470740234089</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.1363261160498181</v>
+        <v>-0.1363261160498252</v>
       </c>
       <c r="W5" t="n">
         <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1363261160498181</v>
+        <v>-0.1363261160498252</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3992443537488397</v>
+        <v>0.3992443537488325</v>
       </c>
       <c r="Z5" t="n">
         <v>1.73</v>
@@ -978,13 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-0.1363261160498181</v>
+        <v>3.839825866605539</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.839825866605747</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>3.839825866605747</v>
+        <v>3.839825866605539</v>
       </c>
     </row>
     <row r="6">
@@ -1080,12 +1063,9 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0.15</v>
+        <v>9.548222715515303</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.548222715515303</v>
-      </c>
-      <c r="AD6" t="n">
         <v>9.548222715515303</v>
       </c>
     </row>
@@ -1182,12 +1162,9 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>0.15</v>
+        <v>8.636948947317281</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.636948947317281</v>
-      </c>
-      <c r="AD7" t="n">
         <v>8.636948947317281</v>
       </c>
     </row>
@@ -1284,12 +1261,9 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>0.02863015617840836</v>
+        <v>6.464754131862461</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.464754131862461</v>
-      </c>
-      <c r="AD8" t="n">
         <v>6.464754131862461</v>
       </c>
     </row>
@@ -1386,12 +1360,9 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>-0.09092480894048127</v>
+        <v>6.410331528992118</v>
       </c>
       <c r="AC9" t="n">
-        <v>6.410331528992118</v>
-      </c>
-      <c r="AD9" t="n">
         <v>6.410331528992118</v>
       </c>
     </row>
@@ -1488,12 +1459,9 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>-0.1337314847539855</v>
+        <v>4.985688787892389</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.985688787892389</v>
-      </c>
-      <c r="AD10" t="n">
         <v>4.985688787892389</v>
       </c>
     </row>
@@ -1590,12 +1558,9 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>-0.04749455679634373</v>
+        <v>5.159726461922225</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.159726461922225</v>
-      </c>
-      <c r="AD11" t="n">
         <v>5.159726461922225</v>
       </c>
     </row>
@@ -1692,12 +1657,9 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>-0.1174528378092863</v>
+        <v>3.750165506812321</v>
       </c>
       <c r="AC12" t="n">
-        <v>3.750165506812321</v>
-      </c>
-      <c r="AD12" t="n">
         <v>3.750165506812321</v>
       </c>
     </row>
@@ -1794,12 +1756,9 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>0.15</v>
+        <v>8.624534218249805</v>
       </c>
       <c r="AC13" t="n">
-        <v>8.624534218249805</v>
-      </c>
-      <c r="AD13" t="n">
         <v>8.624534218249805</v>
       </c>
     </row>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>0hYMmpcl</t>
+          <t>EaryFQkA</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45530.5625</v>
+        <v>45534.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,53 +610,53 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
       <c r="J2" t="n">
         <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4473684210526316</v>
+        <v>0.2591463414634146</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2763157894736842</v>
+        <v>0.274390243902439</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2763157894736842</v>
+        <v>0.4664634146341464</v>
       </c>
       <c r="O2" t="n">
-        <v>0.06442577030812324</v>
+        <v>0.07189542483660127</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3116787579932877</v>
+        <v>0.192076971736161</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5181862778996099</v>
+        <v>0.440257744885126</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1701349641071023</v>
+        <v>0.3676652833787132</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2418704884259257</v>
+        <v>0.165867500982687</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2418704884259257</v>
+        <v>0.165867500982687</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5181862778996099</v>
+        <v>0.440257744885126</v>
       </c>
       <c r="Z2" t="n">
         <v>3.4</v>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>9.758619166339734</v>
+        <v>2.196169694435367</v>
       </c>
       <c r="AC2" t="n">
-        <v>9.758619166339734</v>
+        <v>2.196169694435367</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>fZZxp2dD</t>
+          <t>WdSjHeFt</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45530.65625</v>
+        <v>45534.65625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K3" t="n">
         <v>4.75</v>
       </c>
-      <c r="J3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K3" t="n">
-        <v>1.75</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.198659834450138</v>
+        <v>0.5693343167988197</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2621206148994876</v>
+        <v>0.2364927162087406</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5392195506503745</v>
+        <v>0.1941729669924396</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05973266499582275</v>
+        <v>0.08422052281701409</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3053679739992727</v>
+        <v>0.3690156550322785</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3049944837058366</v>
+        <v>0.4045176207318785</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3896375422948907</v>
+        <v>0.2264667242358431</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.1495820083554838</v>
+        <v>0.168024904523138</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1495820083554838</v>
+        <v>0.168024904523138</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3896375422948907</v>
+        <v>0.4045176207318785</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.75</v>
+        <v>3.9</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.50592433872007</v>
+        <v>2.050884636916369</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.50592433872007</v>
+        <v>2.050884636916369</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45534.5625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="J4" t="n">
         <v>3.6</v>
       </c>
-      <c r="J4" t="n">
-        <v>3.4</v>
-      </c>
       <c r="K4" t="n">
-        <v>1.95</v>
+        <v>5.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2560834298957126</v>
+        <v>0.5686433793663688</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2711471610660486</v>
+        <v>0.255889520714866</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4727694090382387</v>
+        <v>0.1754670999187652</v>
       </c>
       <c r="O4" t="n">
-        <v>0.08471593765711427</v>
+        <v>0.08553791887125217</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2108571490481769</v>
+        <v>0.4611177657755759</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3957389287674579</v>
+        <v>0.3812382020105381</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3934039221843652</v>
+        <v>0.157644032213886</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1245917677014093</v>
+        <v>-0.1075256135907928</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1245917677014093</v>
+        <v>-0.1075256135907928</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3957389287674579</v>
+        <v>0.4611177657755759</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>7.599241821243864</v>
+        <v>1.43736647215213</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.599241821243864</v>
+        <v>1.43736647215213</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.73</v>
+        <v>2.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8</v>
+        <v>3.2</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>3.25</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5355704697986577</v>
+        <v>0.422936152907686</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2438255033557047</v>
+        <v>0.2907686051240341</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2206040268456375</v>
+        <v>0.2862952419682798</v>
       </c>
       <c r="O5" t="n">
-        <v>0.07928781491300518</v>
+        <v>0.0747377622377623</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3992443537488325</v>
+        <v>0.3643385543031154</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3843085722277583</v>
+        <v>0.4539557341479734</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2164470740234089</v>
+        <v>0.1817057115489108</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.1363261160498252</v>
+        <v>0.1631871290239393</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1363261160498252</v>
+        <v>0.1631871290239393</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3992443537488325</v>
+        <v>0.4539557341479734</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.73</v>
+        <v>3.2</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>3.839825866605539</v>
+        <v>2.251852577612105</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.839825866605539</v>
+        <v>2.251852577612105</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.55</v>
+        <v>2.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>5.75</v>
+        <v>2.35</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5961394175022167</v>
+        <v>0.3397831171592601</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2431621308232726</v>
+        <v>0.2698277695088242</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1606984516745106</v>
+        <v>0.3903891133319158</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08223222853768375</v>
+        <v>0.0900199323228108</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.408460400545195</v>
+        <v>0.2755417528022642</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5037801391864014</v>
+        <v>0.3119780634014583</v>
       </c>
       <c r="S6" t="n">
-        <v>0.08775946026840357</v>
+        <v>0.4124801837962774</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2606180083631288</v>
+        <v>0.0220910704643616</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2606180083631288</v>
+        <v>0.0220910704643616</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5037801391864014</v>
+        <v>0.4124801837962774</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.8</v>
+        <v>2.35</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>9.548222715515303</v>
+        <v>1.766549813890983</v>
       </c>
       <c r="AC6" t="n">
-        <v>9.548222715515303</v>
+        <v>1.766549813890983</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>1.44</v>
       </c>
       <c r="J7" t="n">
-        <v>3.25</v>
+        <v>4.33</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>5.75</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4417349590245853</v>
+        <v>0.6317126205512437</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2854287427543474</v>
+        <v>0.2100845666498362</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2728362982210674</v>
+        <v>0.1582028127989202</v>
       </c>
       <c r="O7" t="n">
-        <v>0.07800043094160736</v>
+        <v>0.09930437013979532</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4211570902915869</v>
+        <v>0.5093270547347218</v>
       </c>
       <c r="R7" t="n">
-        <v>0.441383952088532</v>
+        <v>0.2984430895688789</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1374589576198811</v>
+        <v>0.1922298556963995</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1559552093341846</v>
+        <v>-0.1223855658165218</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1559552093341846</v>
+        <v>-0.1223855658165218</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.441383952088532</v>
+        <v>0.5093270547347218</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.25</v>
+        <v>1.44</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1162,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>8.636948947317281</v>
+        <v>1.572932881624008</v>
       </c>
       <c r="AC7" t="n">
-        <v>8.636948947317281</v>
+        <v>1.572932881624008</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.7</v>
+        <v>1.62</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K8" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3425692695214105</v>
+        <v>0.574915973819211</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2720403022670025</v>
+        <v>0.2388112506633646</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3853904282115869</v>
+        <v>0.1862727755174244</v>
       </c>
       <c r="O8" t="n">
-        <v>0.08115468409586057</v>
+        <v>0.07369420702754037</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2701756319800689</v>
+        <v>0.4791085079664594</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3158037836299356</v>
+        <v>0.3798535798145141</v>
       </c>
       <c r="S8" t="n">
-        <v>0.4140205843899953</v>
+        <v>0.1410379122190265</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.02863015617840836</v>
+        <v>-0.09580746585275157</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02863015617840836</v>
+        <v>-0.09580746585275157</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4140205843899953</v>
+        <v>0.4791085079664594</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.4</v>
+        <v>1.62</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1261,29 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>6.464754131862461</v>
+        <v>1.558134317379585</v>
       </c>
       <c r="AC8" t="n">
-        <v>6.464754131862461</v>
+        <v>1.558134317379585</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.48</v>
+        <v>2</v>
       </c>
       <c r="J9" t="n">
-        <v>4.33</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>5.5</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6207739668538242</v>
+        <v>0.463395937140667</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2121814020655104</v>
+        <v>0.2989651207359141</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1670446310806654</v>
+        <v>0.237638942123419</v>
       </c>
       <c r="O9" t="n">
-        <v>0.08844073971094746</v>
+        <v>0.07899090157154665</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.529849157913343</v>
+        <v>0.3704447514747158</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3184139663759257</v>
+        <v>0.4077449801290536</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1517368757107315</v>
+        <v>0.2218102683962306</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.09092480894048127</v>
+        <v>0.1087798593931395</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.09092480894048127</v>
+        <v>0.1087798593931395</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.529849157913343</v>
+        <v>0.4077449801290536</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.48</v>
+        <v>3.1</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1360,29 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>6.410331528992118</v>
+        <v>2.064003984058046</v>
       </c>
       <c r="AC9" t="n">
-        <v>6.410331528992118</v>
+        <v>2.064003984058046</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45536.5625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,56 +1402,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.53</v>
+        <v>1.75</v>
       </c>
       <c r="J10" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>5.5</v>
+        <v>4.33</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6088400411164703</v>
+        <v>0.5251667677380231</v>
       </c>
       <c r="M10" t="n">
-        <v>0.221791729263857</v>
+        <v>0.2625833838690115</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1693682296196727</v>
+        <v>0.2122498483929654</v>
       </c>
       <c r="O10" t="n">
-        <v>0.07350819115524998</v>
+        <v>0.08808973935994713</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4751085563624848</v>
+        <v>0.3694247516053549</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3813915965199271</v>
+        <v>0.3851395916103322</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1434998471175884</v>
+        <v>0.2454356567843127</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.1337314847539855</v>
+        <v>0.1225562077413207</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1337314847539855</v>
+        <v>0.1225562077413207</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4751085563624848</v>
+        <v>0.3851395916103322</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.53</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,29 +1459,29 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>4.985688787892389</v>
+        <v>1.9721121608204</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.985688787892389</v>
+        <v>1.9721121608204</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45536.5625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1501,56 +1501,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="J11" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="K11" t="n">
         <v>3.6</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4482827877083752</v>
+        <v>0.4626168224299065</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2964450692910223</v>
+        <v>0.2803738317757009</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2552721430006025</v>
+        <v>0.2570093457943925</v>
       </c>
       <c r="O11" t="n">
-        <v>0.08816330098784864</v>
+        <v>0.08080808080808088</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4007882309120315</v>
+        <v>0.3419065449955382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3631538989066805</v>
+        <v>0.4604020439379574</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2360578701812881</v>
+        <v>0.1976914110665043</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>-0.04749455679634373</v>
+        <v>0.1800282121622565</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.04749455679634373</v>
+        <v>0.1800282121622565</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4007882309120315</v>
+        <v>0.4604020439379574</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.05</v>
+        <v>3.3</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1558,208 +1558,10 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>5.159726461922225</v>
+        <v>2.278057088950883</v>
       </c>
       <c r="AC11" t="n">
-        <v>5.159726461922225</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>juventus</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>as roma</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>77</v>
-      </c>
-      <c r="F12" t="n">
-        <v>771</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="J12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0.4916847433116414</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0.274765003615329</v>
-      </c>
-      <c r="N12" t="n">
-        <v>0.2335502530730297</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0.07043343653250767</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0.3742319055023551</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0.3729476351612947</v>
-      </c>
-      <c r="S12" t="n">
-        <v>0.2528204593363501</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="n">
-        <v>-0.1174528378092863</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>-0.1174528378092863</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>0.3742319055023551</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB12" t="n">
-        <v>3.750165506812321</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>3.750165506812321</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>udinese</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>como</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>77</v>
-      </c>
-      <c r="F13" t="n">
-        <v>771</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I13" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="J13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K13" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0.5080174927113702</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0.2689504373177842</v>
-      </c>
-      <c r="N13" t="n">
-        <v>0.2230320699708455</v>
-      </c>
-      <c r="O13" t="n">
-        <v>0.09357564163876941</v>
-      </c>
-      <c r="P13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q13" t="n">
-        <v>0.4004031360012256</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0.440533898257623</v>
-      </c>
-      <c r="S13" t="n">
-        <v>0.1590629657411515</v>
-      </c>
-      <c r="T13" t="n">
-        <v>1</v>
-      </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="n">
-        <v>0.1715834609398388</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>0.1715834609398388</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0.440533898257623</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB13" t="n">
-        <v>8.624534218249805</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>8.624534218249805</v>
+        <v>2.278057088950883</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>EaryFQkA</t>
+          <t>ELeQ0zVa</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45534.5625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3.6</v>
+        <v>1.62</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>2</v>
+        <v>5.75</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2591463414634146</v>
+        <v>0.5835193829916785</v>
       </c>
       <c r="M2" t="n">
-        <v>0.274390243902439</v>
+        <v>0.2520803734524051</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4664634146341464</v>
+        <v>0.1644002435559164</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07189542483660127</v>
+        <v>0.05786366076221139</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.192076971736161</v>
+        <v>0.4303029010699506</v>
       </c>
       <c r="R2" t="n">
-        <v>0.440257744885126</v>
+        <v>0.4600072380500901</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3676652833787132</v>
+        <v>0.1096898608799593</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.165867500982687</v>
+        <v>0.2079268645976849</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.165867500982687</v>
+        <v>0.2079268645976849</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.440257744885126</v>
+        <v>0.4600072380500901</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>3.75</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>2.196169694435367</v>
+        <v>2.276452186967843</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.196169694435367</v>
+        <v>2.276452186967843</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WdSjHeFt</t>
+          <t>d4DGBiqI</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45534.65625</v>
+        <v>45535.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.62</v>
+        <v>2.25</v>
       </c>
       <c r="J3" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5693343167988197</v>
+        <v>0.4228527011270889</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2364927162087406</v>
+        <v>0.2973183054799844</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1941729669924396</v>
+        <v>0.2798289933929266</v>
       </c>
       <c r="O3" t="n">
-        <v>0.08422052281701409</v>
+        <v>0.05106209150326801</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3690156550322785</v>
+        <v>0.3654488747004993</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4045176207318785</v>
+        <v>0.4495875931871142</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2264667242358431</v>
+        <v>0.1849635321123865</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.168024904523138</v>
+        <v>0.1522692877071297</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.168024904523138</v>
+        <v>0.1522692877071297</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4045176207318785</v>
+        <v>0.4495875931871142</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2.050884636916369</v>
+        <v>2.234095907041282</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.050884636916369</v>
+        <v>2.234095907041282</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>0xK7DDE5</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.62</v>
+        <v>2.9</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>5.25</v>
+        <v>2.4</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5686433793663688</v>
+        <v>0.3266613290632506</v>
       </c>
       <c r="M4" t="n">
-        <v>0.255889520714866</v>
+        <v>0.2786228983186549</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1754670999187652</v>
+        <v>0.3947157726180944</v>
       </c>
       <c r="O4" t="n">
-        <v>0.08553791887125217</v>
+        <v>0.05561189993238691</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4611177657755759</v>
+        <v>0.3320283417355943</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3812382020105381</v>
+        <v>0.3453296657883106</v>
       </c>
       <c r="S4" t="n">
-        <v>0.157644032213886</v>
+        <v>0.322641992476095</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.1075256135907928</v>
+        <v>0.06670676746965576</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1075256135907928</v>
+        <v>0.06670676746965576</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4611177657755759</v>
+        <v>0.3453296657883106</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.62</v>
+        <v>3.4</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>1.43736647215213</v>
+        <v>1.674944850474646</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.43736647215213</v>
+        <v>1.674944850474646</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>SjzlgqTj</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45535.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.2</v>
+        <v>1.48</v>
       </c>
       <c r="J5" t="n">
-        <v>3.2</v>
+        <v>4.33</v>
       </c>
       <c r="K5" t="n">
-        <v>3.25</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
-        <v>0.422936152907686</v>
+        <v>0.643819671016857</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2907686051240341</v>
+        <v>0.2200584556824361</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2862952419682798</v>
+        <v>0.1361218733007069</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0747377622377623</v>
+        <v>0.0494797007499086</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3643385543031154</v>
+        <v>0.5061864550305712</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4539557341479734</v>
+        <v>0.3036078548501754</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1817057115489108</v>
+        <v>0.1902056901192534</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1631871290239393</v>
+        <v>-0.1376332159862858</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1631871290239393</v>
+        <v>-0.1376332159862858</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4539557341479734</v>
+        <v>0.5061864550305712</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.2</v>
+        <v>1.48</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2.251852577612105</v>
+        <v>1.498183898404188</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.251852577612105</v>
+        <v>1.498183898404188</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.7</v>
+        <v>1.67</v>
       </c>
       <c r="J6" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
-        <v>2.35</v>
+        <v>5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3397831171592601</v>
+        <v>0.5674708261793209</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2698277695088242</v>
+        <v>0.2429939178767861</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3903891133319158</v>
+        <v>0.1895352559438931</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0900199323228108</v>
+        <v>0.05521265161983724</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2755417528022642</v>
+        <v>0.4017898345438949</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3119780634014583</v>
+        <v>0.4042744950534848</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4124801837962774</v>
+        <v>0.1939356704026204</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.0220910704643616</v>
+        <v>0.1612805771766987</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0220910704643616</v>
+        <v>0.1612805771766987</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4124801837962774</v>
+        <v>0.4042744950534848</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.35</v>
+        <v>3.9</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>1.766549813890983</v>
+        <v>2.04989632115064</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.766549813890983</v>
+        <v>2.04989632115064</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.44</v>
+        <v>2</v>
       </c>
       <c r="J7" t="n">
-        <v>4.33</v>
+        <v>3.3</v>
       </c>
       <c r="K7" t="n">
-        <v>5.75</v>
+        <v>3.9</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6317126205512437</v>
+        <v>0.471947194719472</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2100845666498362</v>
+        <v>0.286028602860286</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1582028127989202</v>
+        <v>0.2420242024202421</v>
       </c>
       <c r="O7" t="n">
-        <v>0.09930437013979532</v>
+        <v>0.05944055944055937</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5093270547347218</v>
+        <v>0.250718210002577</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2984430895688789</v>
+        <v>0.4444843561198077</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1922298556963995</v>
+        <v>0.3047974338776155</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.1223855658165218</v>
+        <v>0.1584557532595217</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1223855658165218</v>
+        <v>0.1584557532595217</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5093270547347218</v>
+        <v>0.4444843561198077</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.44</v>
+        <v>3.3</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1162,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>1.572932881624008</v>
+        <v>2.213351040916095</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.572932881624008</v>
+        <v>2.213351040916095</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45536.5625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.62</v>
+        <v>1.75</v>
       </c>
       <c r="J8" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
         <v>5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.574915973819211</v>
+        <v>0.5446293494704992</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2388112506633646</v>
+        <v>0.264750378214826</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1862727755174244</v>
+        <v>0.1906202723146747</v>
       </c>
       <c r="O8" t="n">
-        <v>0.07369420702754037</v>
+        <v>0.04920634920634925</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4791085079664594</v>
+        <v>0.3793679277017606</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3798535798145141</v>
+        <v>0.4314688135302905</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1410379122190265</v>
+        <v>0.1891632587679486</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.09580746585275157</v>
+        <v>0.1667184353154645</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.09580746585275157</v>
+        <v>0.1667184353154645</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4791085079664594</v>
+        <v>0.4314688135302905</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.62</v>
+        <v>3.6</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1261,29 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>1.558134317379585</v>
+        <v>2.160442331207901</v>
       </c>
       <c r="AC8" t="n">
-        <v>1.558134317379585</v>
+        <v>2.160442331207901</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45536.5625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0.463395937140667</v>
+        <v>0.4652011310772599</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2989651207359141</v>
+        <v>0.2804889172671714</v>
       </c>
       <c r="N9" t="n">
-        <v>0.237638942123419</v>
+        <v>0.2543099516555687</v>
       </c>
       <c r="O9" t="n">
-        <v>0.07899090157154665</v>
+        <v>0.04858919177427068</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3704447514747158</v>
+        <v>0.3893097338466229</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4077449801290536</v>
+        <v>0.4100645711018675</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2218102683962306</v>
+        <v>0.2006256950515095</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1087798593931395</v>
+        <v>0.1295756538346961</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1087798593931395</v>
+        <v>0.1295756538346961</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4077449801290536</v>
+        <v>0.4100645711018675</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,208 +1360,10 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>2.064003984058046</v>
+        <v>2.073433215653907</v>
       </c>
       <c r="AC9" t="n">
-        <v>2.064003984058046</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>juventus</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>as roma</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>77</v>
-      </c>
-      <c r="F10" t="n">
-        <v>771</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="J10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.5251667677380231</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.2625833838690115</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.2122498483929654</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.08808973935994713</v>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.3694247516053549</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.3851395916103322</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.2454356567843127</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="n">
-        <v>0.1225562077413207</v>
-      </c>
-      <c r="W10" t="n">
-        <v>0</v>
-      </c>
-      <c r="X10" t="n">
-        <v>0.1225562077413207</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.3851395916103322</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.9721121608204</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.9721121608204</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>udinese</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>como</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>77</v>
-      </c>
-      <c r="F11" t="n">
-        <v>771</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I11" t="n">
-        <v>2</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L11" t="n">
-        <v>0.4626168224299065</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.2803738317757009</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.2570093457943925</v>
-      </c>
-      <c r="O11" t="n">
-        <v>0.08080808080808088</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0.3419065449955382</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0.4604020439379574</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0.1976914110665043</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1</v>
-      </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="n">
-        <v>0.1800282121622565</v>
-      </c>
-      <c r="W11" t="n">
-        <v>0</v>
-      </c>
-      <c r="X11" t="n">
-        <v>0.1800282121622565</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>0.4604020439379574</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB11" t="n">
-        <v>2.278057088950883</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>2.278057088950883</v>
+        <v>2.073433215653907</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC9"/>
+  <dimension ref="A1:AC5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>ELeQ0zVa</t>
+          <t>nZgYbEaC</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,53 +610,53 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="J2" t="n">
         <v>3.75</v>
       </c>
       <c r="K2" t="n">
-        <v>5.75</v>
+        <v>5.25</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5835193829916785</v>
+        <v>0.5670771224886585</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2520803734524051</v>
+        <v>0.2525383452149492</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1644002435559164</v>
+        <v>0.1803845322963923</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05786366076221139</v>
+        <v>0.05594525235243797</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4303029010699506</v>
+        <v>0.4024491637615304</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4600072380500901</v>
+        <v>0.405139952451053</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1096898608799593</v>
+        <v>0.1924108837874164</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2079268645976849</v>
+        <v>0.1526016072361038</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2079268645976849</v>
+        <v>0.1526016072361038</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4600072380500901</v>
+        <v>0.405139952451053</v>
       </c>
       <c r="Z2" t="n">
         <v>3.75</v>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>2.276452186967843</v>
+        <v>2.933449201148771</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.276452186967843</v>
+        <v>2.933449201148771</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>d4DGBiqI</t>
+          <t>r1mschUO</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45535.5625</v>
+        <v>45536.5625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3.9</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4228527011270889</v>
+        <v>0.471947194719472</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2973183054799844</v>
+        <v>0.286028602860286</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2798289933929266</v>
+        <v>0.2420242024202421</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05106209150326801</v>
+        <v>0.05944055944055937</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3654488747004993</v>
+        <v>0.250718210002577</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4495875931871142</v>
+        <v>0.4444843561198077</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1849635321123865</v>
+        <v>0.3047974338776155</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1522692877071297</v>
+        <v>0.1584557532595217</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1522692877071297</v>
+        <v>0.1584557532595217</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4495875931871142</v>
+        <v>0.4444843561198077</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>2.234095907041282</v>
+        <v>3.161930058684915</v>
       </c>
       <c r="AC3" t="n">
-        <v>2.234095907041282</v>
+        <v>3.161930058684915</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>0xK7DDE5</t>
+          <t>hCGaFZqg</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.9</v>
+        <v>1.75</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3266613290632506</v>
+        <v>0.5446293494704992</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2786228983186549</v>
+        <v>0.264750378214826</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3947157726180944</v>
+        <v>0.1906202723146747</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05561189993238691</v>
+        <v>0.04920634920634925</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3320283417355943</v>
+        <v>0.3793679277017606</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3453296657883106</v>
+        <v>0.4314688135302905</v>
       </c>
       <c r="S4" t="n">
-        <v>0.322641992476095</v>
+        <v>0.1891632587679486</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.06670676746965576</v>
+        <v>0.1667184353154645</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.06670676746965576</v>
+        <v>0.1667184353154645</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3453296657883106</v>
+        <v>0.4314688135302905</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>1.674944850474646</v>
+        <v>3.086346187667631</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.674944850474646</v>
+        <v>3.086346187667631</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>SjzlgqTj</t>
+          <t>6ZvTGnLc</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45535.65625</v>
+        <v>45536.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.48</v>
+        <v>2.05</v>
       </c>
       <c r="J5" t="n">
-        <v>4.33</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>7</v>
+        <v>3.7</v>
       </c>
       <c r="L5" t="n">
-        <v>0.643819671016857</v>
+        <v>0.4636078864934587</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2200584556824361</v>
+        <v>0.2795282845034089</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1361218733007069</v>
+        <v>0.2568638290031325</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0494797007499086</v>
+        <v>0.05219279537787425</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5061864550305712</v>
+        <v>0.3893097338466229</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3036078548501754</v>
+        <v>0.4100645711018675</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1902056901192534</v>
+        <v>0.2006256950515095</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.1376332159862858</v>
+        <v>0.1305362865984586</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1376332159862858</v>
+        <v>0.1305362865984586</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5061864550305712</v>
+        <v>0.4100645711018675</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.48</v>
+        <v>3.4</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,406 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>1.498183898404188</v>
+        <v>2.962047451152752</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.498183898404188</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>nZgYbEaC</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>fiorentina</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>monza</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>77</v>
-      </c>
-      <c r="F6" t="n">
-        <v>771</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="J6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="K6" t="n">
-        <v>5</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.5674708261793209</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0.2429939178767861</v>
-      </c>
-      <c r="N6" t="n">
-        <v>0.1895352559438931</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0.05521265161983724</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0.4017898345438949</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0.4042744950534848</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0.1939356704026204</v>
-      </c>
-      <c r="T6" t="n">
-        <v>1</v>
-      </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="n">
-        <v>0.1612805771766987</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.1612805771766987</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.4042744950534848</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>2.04989632115064</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>2.04989632115064</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>r1mschUO</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>45536.5625</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>genoa</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>verona</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>77</v>
-      </c>
-      <c r="F7" t="n">
-        <v>771</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
-        <v>2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L7" t="n">
-        <v>0.471947194719472</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0.286028602860286</v>
-      </c>
-      <c r="N7" t="n">
-        <v>0.2420242024202421</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0.05944055944055937</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0.250718210002577</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0.4444843561198077</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0.3047974338776155</v>
-      </c>
-      <c r="T7" t="n">
-        <v>1</v>
-      </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="n">
-        <v>0.1584557532595217</v>
-      </c>
-      <c r="W7" t="n">
-        <v>0</v>
-      </c>
-      <c r="X7" t="n">
-        <v>0.1584557532595217</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.4444843561198077</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>2.213351040916095</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>2.213351040916095</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>hCGaFZqg</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>juventus</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>as roma</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>77</v>
-      </c>
-      <c r="F8" t="n">
-        <v>771</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="K8" t="n">
-        <v>5</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.5446293494704992</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.264750378214826</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.1906202723146747</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.04920634920634925</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.3793679277017606</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.4314688135302905</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.1891632587679486</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="n">
-        <v>0.1667184353154645</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.1667184353154645</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.4314688135302905</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>2.160442331207901</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>2.160442331207901</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>6ZvTGnLc</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45536.65625</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>udinese</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>como</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>77</v>
-      </c>
-      <c r="F9" t="n">
-        <v>771</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K9" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.4652011310772599</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.2804889172671714</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.2543099516555687</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.04858919177427068</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.3893097338466229</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.4100645711018675</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.2006256950515095</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
-        <v>0.1295756538346961</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.1295756538346961</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.4100645711018675</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>2.073433215653907</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>2.073433215653907</v>
+        <v>2.962047451152752</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nZgYbEaC</t>
+          <t>n7VN5MCd</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45536.5625</v>
+        <v>45549.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>como</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.67</v>
+        <v>2.75</v>
       </c>
       <c r="J2" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>5.25</v>
+        <v>2.38</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5670771224886585</v>
+        <v>0.3373493975903614</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2525383452149492</v>
+        <v>0.2728561304039688</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1803845322963923</v>
+        <v>0.3897944720056697</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05594525235243797</v>
+        <v>0.07792207792207795</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4024491637615304</v>
+        <v>0.3196180911655166</v>
       </c>
       <c r="R2" t="n">
-        <v>0.405139952451053</v>
+        <v>0.4565681698419376</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1924108837874164</v>
+        <v>0.2238137389925456</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1526016072361038</v>
+        <v>0.1837120394379688</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1526016072361038</v>
+        <v>0.1837120394379688</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.405139952451053</v>
+        <v>0.4565681698419376</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>2.933449201148771</v>
+        <v>3.23210319295793</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.933449201148771</v>
+        <v>3.23210319295793</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>r1mschUO</t>
+          <t>v1I9TP43</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45536.5625</v>
+        <v>45549.54166666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="K3" t="n">
-        <v>3.9</v>
+        <v>1.7</v>
       </c>
       <c r="L3" t="n">
-        <v>0.471947194719472</v>
+        <v>0.2063106796116505</v>
       </c>
       <c r="M3" t="n">
-        <v>0.286028602860286</v>
+        <v>0.2475728155339806</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2420242024202421</v>
+        <v>0.546116504854369</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05944055944055937</v>
+        <v>0.0771241830065359</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.250718210002577</v>
+        <v>0.1809065950226122</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4444843561198077</v>
+        <v>0.4182380459344619</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3047974338776155</v>
+        <v>0.4008553590429255</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1584557532595217</v>
+        <v>0.1706652304004813</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1584557532595217</v>
+        <v>0.1706652304004813</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4444843561198077</v>
+        <v>0.4182380459344619</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.3</v>
+        <v>3.75</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.161930058684915</v>
+        <v>3.009512461793752</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.161930058684915</v>
+        <v>3.009512461793752</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hCGaFZqg</t>
+          <t>SQjcKLRk</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45536.65625</v>
+        <v>45549.65625</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.75</v>
+        <v>1.33</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5446293494704992</v>
+        <v>0.7044320516583504</v>
       </c>
       <c r="M4" t="n">
-        <v>0.264750378214826</v>
+        <v>0.1784561197534488</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1906202723146747</v>
+        <v>0.1171118285882008</v>
       </c>
       <c r="O4" t="n">
-        <v>0.04920634920634925</v>
+        <v>0.06735588972431072</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3793679277017606</v>
+        <v>0.5821637641353162</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4314688135302905</v>
+        <v>0.2717988184361287</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1891632587679486</v>
+        <v>0.146037417428555</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1667184353154645</v>
+        <v>-0.1222682875230342</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1667184353154645</v>
+        <v>-0.1222682875230342</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4314688135302905</v>
+        <v>0.5821637641353162</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.6</v>
+        <v>1.33</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>3.086346187667631</v>
+        <v>2.670705439025742</v>
       </c>
       <c r="AC4" t="n">
-        <v>3.086346187667631</v>
+        <v>2.670705439025742</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6ZvTGnLc</t>
+          <t>zTBIR3ZF</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45536.65625</v>
+        <v>45550.3125</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,53 +907,53 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.05</v>
+        <v>3</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.7</v>
+        <v>2.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4636078864934587</v>
+        <v>0.3080724876441515</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2795282845034089</v>
+        <v>0.271828665568369</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2568638290031325</v>
+        <v>0.4200988467874794</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05219279537787425</v>
+        <v>0.08199643493761144</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3893097338466229</v>
+        <v>0.2916787444987826</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4100645711018675</v>
+        <v>0.3914264359529562</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2006256950515095</v>
+        <v>0.3168948195482612</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1305362865984586</v>
+        <v>0.1195977703845871</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1305362865984586</v>
+        <v>0.1195977703845871</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4100645711018675</v>
+        <v>0.3914264359529562</v>
       </c>
       <c r="Z5" t="n">
         <v>3.4</v>
@@ -964,10 +964,604 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2.962047451152752</v>
+        <v>2.853812055401166</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.962047451152752</v>
+        <v>2.853812055401166</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>zFWqD4KM</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>77</v>
+      </c>
+      <c r="F6" t="n">
+        <v>771</v>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.5141081156586115</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0.2721748847604414</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0.213716999580947</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.08062008483146932</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0.4330129043264651</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.3802888094880458</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.186698286185489</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="n">
+        <v>-0.08109521133214637</v>
+      </c>
+      <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.08109521133214637</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.4330129043264651</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
+        <v>2.043656753688145</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>2.043656753688145</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>4WHcOkpL</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>45550.41666666666</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>77</v>
+      </c>
+      <c r="F7" t="n">
+        <v>771</v>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K7" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.5521375611295157</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0.263448493453226</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0.1844139454172582</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.08451668092386666</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.4184066531156443</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.4335194243415411</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.1480739225428145</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="n">
+        <v>0.1700709308883151</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.1700709308883151</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.4335194243415411</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.098254496675743</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3.098254496675743</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>6cNF7rrp</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45550.54166666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>77</v>
+      </c>
+      <c r="F8" t="n">
+        <v>771</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.2399855647780585</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2674124864669793</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.492601948754962</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.06844033159822649</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.1176801958086907</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.3683172495010466</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.5140025546902626</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>0.02140060593530058</v>
+      </c>
+      <c r="W8" t="n">
+        <v>2</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0.02140060593530058</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.5140025546902626</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.109193731774307</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.109193731774307</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>Esk5Iad2</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45550.65625</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>77</v>
+      </c>
+      <c r="F9" t="n">
+        <v>771</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1247848746590466</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2161400831276789</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.6590750422132745</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.06850556766309945</v>
+      </c>
+      <c r="P9" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.1442498988557838</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3723805125631658</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.48336958858105</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>-0.1757054536322245</v>
+      </c>
+      <c r="W9" t="n">
+        <v>2</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.1757054536322245</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.48336958858105</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>1.786667450294801</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.786667450294801</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>WIJkQBF8</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45551.5625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>77</v>
+      </c>
+      <c r="F10" t="n">
+        <v>771</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.3928158806848019</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2715050940027308</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.3356790253124671</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.08328592558880432</v>
+      </c>
+      <c r="P10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.3615354959617441</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3247154521612346</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.3137490518770212</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>-0.03128038472305789</v>
+      </c>
+      <c r="W10" t="n">
+        <v>1</v>
+      </c>
+      <c r="X10" t="n">
+        <v>-0.03128038472305789</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.3615354959617441</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.917857788792297</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.917857788792297</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rgFQPs4S</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45551.65625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>77</v>
+      </c>
+      <c r="F11" t="n">
+        <v>771</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.5794365379029917</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2439732791170491</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1765901829799593</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0786340852130325</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4951057180317847</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3489093800379721</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.1559849019302434</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-0.08433081987120694</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.08433081987120694</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4951057180317847</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>2.385452370207988</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.385452370207988</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC11"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -610,53 +610,53 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="J2" t="n">
         <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3373493975903614</v>
+        <v>0.3539159761835367</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2728561304039688</v>
+        <v>0.2737644168713828</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3897944720056697</v>
+        <v>0.3723196069450807</v>
       </c>
       <c r="O2" t="n">
-        <v>0.07792207792207795</v>
+        <v>0.0743457839409527</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3196180911655166</v>
+        <v>0.3089695952704163</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4565681698419376</v>
+        <v>0.4856569960486514</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2238137389925456</v>
+        <v>0.2053734086809321</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1837120394379688</v>
+        <v>0.2118925791772686</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1837120394379688</v>
+        <v>0.2118925791772686</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4565681698419376</v>
+        <v>0.4856569960486514</v>
       </c>
       <c r="Z2" t="n">
         <v>3.4</v>
@@ -667,10 +667,10 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>3.23210319295793</v>
+        <v>2.122607195533341</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.23210319295793</v>
+        <v>2.122607195533341</v>
       </c>
     </row>
     <row r="3">
@@ -712,53 +712,53 @@
         <v>4.5</v>
       </c>
       <c r="J3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2063106796116505</v>
+        <v>0.2088709677419355</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2475728155339806</v>
+        <v>0.2540322580645161</v>
       </c>
       <c r="N3" t="n">
-        <v>0.546116504854369</v>
+        <v>0.5370967741935484</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0771241830065359</v>
+        <v>0.06392106392106389</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1809065950226122</v>
+        <v>0.1914118179780041</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4182380459344619</v>
+        <v>0.4243451942616086</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4008553590429255</v>
+        <v>0.3842429877603872</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1706652304004813</v>
+        <v>0.1703129361970925</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1706652304004813</v>
+        <v>0.1703129361970925</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4182380459344619</v>
+        <v>0.4243451942616086</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,10 +766,10 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.009512461793752</v>
+        <v>1.900393728397571</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.009512461793752</v>
+        <v>1.900393728397571</v>
       </c>
     </row>
     <row r="4">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="J4" t="n">
-        <v>5.25</v>
+        <v>5.5</v>
       </c>
       <c r="K4" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7044320516583504</v>
+        <v>0.7213392994908193</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1784561197534488</v>
+        <v>0.169186853880574</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1171118285882008</v>
+        <v>0.1094738466286067</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06735588972431072</v>
+        <v>0.07465903909132354</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5821637641353162</v>
+        <v>0.6023473623194928</v>
       </c>
       <c r="R4" t="n">
-        <v>0.2717988184361287</v>
+        <v>0.2625780084712329</v>
       </c>
       <c r="S4" t="n">
-        <v>0.146037417428555</v>
+        <v>0.1350746292092746</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.1222682875230342</v>
+        <v>-0.1189919371713265</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1222682875230342</v>
+        <v>-0.1189919371713265</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5821637641353162</v>
+        <v>0.6023473623194928</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,10 +865,10 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>2.670705439025742</v>
+        <v>1.751833770178929</v>
       </c>
       <c r="AC4" t="n">
-        <v>2.670705439025742</v>
+        <v>1.751833770178929</v>
       </c>
     </row>
     <row r="5">
@@ -907,53 +907,53 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="J5" t="n">
         <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3080724876441515</v>
+        <v>0.298184784825617</v>
       </c>
       <c r="M5" t="n">
-        <v>0.271828665568369</v>
+        <v>0.2718743626351214</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4200988467874794</v>
+        <v>0.4299408525392617</v>
       </c>
       <c r="O5" t="n">
-        <v>0.08199643493761144</v>
+        <v>0.08181457128988123</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.2916787444987826</v>
+        <v>0.2875236211621962</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3914264359529562</v>
+        <v>0.3902074778533958</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3168948195482612</v>
+        <v>0.3222689009844079</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1195977703845871</v>
+        <v>0.1183331152182744</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.1195977703845871</v>
+        <v>0.1183331152182744</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3914264359529562</v>
+        <v>0.3902074778533958</v>
       </c>
       <c r="Z5" t="n">
         <v>3.4</v>
@@ -964,10 +964,10 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2.853812055401166</v>
+        <v>1.776667788169701</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.853812055401166</v>
+        <v>1.776667788169701</v>
       </c>
     </row>
     <row r="6">
@@ -1012,47 +1012,47 @@
         <v>3.4</v>
       </c>
       <c r="K6" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5141081156586115</v>
+        <v>0.5182926829268292</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2721748847604414</v>
+        <v>0.274390243902439</v>
       </c>
       <c r="N6" t="n">
-        <v>0.213716999580947</v>
+        <v>0.2073170731707317</v>
       </c>
       <c r="O6" t="n">
-        <v>0.08062008483146932</v>
+        <v>0.0718954248366015</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4330129043264651</v>
+        <v>0.4301417353548152</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3802888094880458</v>
+        <v>0.3828190467446993</v>
       </c>
       <c r="S6" t="n">
-        <v>0.186698286185489</v>
+        <v>0.1870392179004853</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.08109521133214637</v>
+        <v>-0.08815094757201397</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.08109521133214637</v>
+        <v>-0.08815094757201397</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4330129043264651</v>
+        <v>0.4301417353548152</v>
       </c>
       <c r="Z6" t="n">
         <v>1.8</v>
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>2.043656753688145</v>
+        <v>1.239483369705341</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.043656753688145</v>
+        <v>1.239483369705341</v>
       </c>
     </row>
     <row r="7">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5521375611295157</v>
+        <v>0.5253218884120171</v>
       </c>
       <c r="M7" t="n">
-        <v>0.263448493453226</v>
+        <v>0.2703862660944206</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1844139454172582</v>
+        <v>0.2042918454935622</v>
       </c>
       <c r="O7" t="n">
-        <v>0.08451668092386666</v>
+        <v>0.08776844070961731</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4184066531156443</v>
+        <v>0.4590704442820542</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4335194243415411</v>
+        <v>0.3865836887297784</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1480739225428145</v>
+        <v>0.1543458669881672</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1700709308883151</v>
+        <v>-0.06625144412996292</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1700709308883151</v>
+        <v>-0.06625144412996292</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4335194243415411</v>
+        <v>0.4590704442820542</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.5</v>
+        <v>1.75</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,10 +1162,10 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>3.098254496675743</v>
+        <v>1.423700974957322</v>
       </c>
       <c r="AC7" t="n">
-        <v>3.098254496675743</v>
+        <v>1.423700974957322</v>
       </c>
     </row>
     <row r="8">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K8" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2399855647780585</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2674124864669793</v>
+        <v>0.2592592592592593</v>
       </c>
       <c r="N8" t="n">
-        <v>0.492601948754962</v>
+        <v>0.5185185185185186</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06844033159822649</v>
+        <v>0.0714285714285714</v>
       </c>
       <c r="P8" t="n">
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.1176801958086907</v>
+        <v>0.1193018395820829</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3683172495010466</v>
+        <v>0.3765403032909824</v>
       </c>
       <c r="S8" t="n">
-        <v>0.5140025546902626</v>
+        <v>0.5041578571269347</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.02140060593530058</v>
+        <v>-0.01436066139158387</v>
       </c>
       <c r="W8" t="n">
         <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>0.02140060593530058</v>
+        <v>-0.01436066139158387</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.5140025546902626</v>
+        <v>0.5041578571269347</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,10 +1261,10 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>3.109193731774307</v>
+        <v>1.775180795302141</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.109193731774307</v>
+        <v>1.775180795302141</v>
       </c>
     </row>
     <row r="9">
@@ -1327,29 +1327,29 @@
         <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1442498988557838</v>
+        <v>0.1417789159906767</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3723805125631658</v>
+        <v>0.3872012806201899</v>
       </c>
       <c r="S9" t="n">
-        <v>0.48336958858105</v>
+        <v>0.471019803389133</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>-0.1757054536322245</v>
+        <v>-0.1880552388241415</v>
       </c>
       <c r="W9" t="n">
         <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.1757054536322245</v>
+        <v>-0.1880552388241415</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.48336958858105</v>
+        <v>0.471019803389133</v>
       </c>
       <c r="Z9" t="n">
         <v>1.42</v>
@@ -1360,10 +1360,10 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>1.786667450294801</v>
+        <v>1.025553566129884</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.786667450294801</v>
+        <v>1.025553566129884</v>
       </c>
     </row>
     <row r="10">
@@ -1402,56 +1402,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3928158806848019</v>
+        <v>0.4233870967741936</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2715050940027308</v>
+        <v>0.2661290322580646</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3356790253124671</v>
+        <v>0.3104838709677419</v>
       </c>
       <c r="O10" t="n">
-        <v>0.08328592558880432</v>
+        <v>0.07359307359307343</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.3615354959617441</v>
+        <v>0.3336379529780812</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3247154521612346</v>
+        <v>0.3278329503521971</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3137490518770212</v>
+        <v>0.3385290966697218</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.03128038472305789</v>
+        <v>0.02804522570197981</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.03128038472305789</v>
+        <v>0.02804522570197981</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3615354959617441</v>
+        <v>0.3385290966697218</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.35</v>
+        <v>3</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,10 +1459,10 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>1.917857788792297</v>
+        <v>1.328581916742432</v>
       </c>
       <c r="AC10" t="n">
-        <v>1.917857788792297</v>
+        <v>1.328581916742432</v>
       </c>
     </row>
     <row r="11">
@@ -1525,29 +1525,29 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4951057180317847</v>
+        <v>0.4839144128269762</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3489093800379721</v>
+        <v>0.3492781926884865</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1559849019302434</v>
+        <v>0.1668073944845373</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>-0.08433081987120694</v>
+        <v>-0.09552212507601543</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.08433081987120694</v>
+        <v>-0.09552212507601543</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4951057180317847</v>
+        <v>0.4839144128269762</v>
       </c>
       <c r="Z11" t="n">
         <v>1.6</v>
@@ -1558,10 +1558,1000 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>2.385452370207988</v>
+        <v>1.407657161498948</v>
       </c>
       <c r="AC11" t="n">
-        <v>2.385452370207988</v>
+        <v>1.407657161498948</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2ucWYubt</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45555.5625</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>77</v>
+      </c>
+      <c r="F12" t="n">
+        <v>771</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4192972007147112</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2858844550327576</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.2948183442525313</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.0599747474747474</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.3188434149291295</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.5476585774195694</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.133498007651301</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.2617741223868117</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.2617741223868117</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.5476585774195694</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>2.347320643234432</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>2.347320643234432</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>44gmVcc5</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45555.65625</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>77</v>
+      </c>
+      <c r="F13" t="n">
+        <v>771</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.3409090909090908</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2840909090909091</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.3749999999999999</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06666666666666687</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.4255817245971176</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.4405870927631126</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1338311826397697</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.1564961836722036</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.1564961836722036</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4405870927631126</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.959259533571954</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.959259533571954</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>S66wtFBN</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45556.41666666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>77</v>
+      </c>
+      <c r="F14" t="n">
+        <v>771</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.3015157722244982</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2920934043424826</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.4063908234330194</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06986325385694236</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.2492674127821233</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.5264294730343777</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.2243031141834989</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.2343360686918951</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.2343360686918951</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.5264294730343777</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>2.270379617981157</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>2.270379617981157</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Yqo4RFdU</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45556.54166666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>77</v>
+      </c>
+      <c r="F15" t="n">
+        <v>771</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.4697535474234503</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2763256161314414</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.2539208364451083</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06438791732909377</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.3688990566650745</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.4296804333706382</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2014205099642874</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.1533548172391968</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.1533548172391968</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.4296804333706382</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>1.919730331561407</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1.919730331561407</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>O8QDoJsn</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45556.65625</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>77</v>
+      </c>
+      <c r="F16" t="n">
+        <v>771</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.4059040590405905</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2829028290282903</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.3111931119311193</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.07114624505928857</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.4735478360109923</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3752722889906695</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.1511798749983382</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.06764377697040186</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.06764377697040186</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4735478360109923</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.961450507083459</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1.961450507083459</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>A50vXJSh</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45557.3125</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>77</v>
+      </c>
+      <c r="F17" t="n">
+        <v>771</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K17" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.415347137637028</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.3014616321559074</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2831912302070646</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.07005539263603766</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.4459875135554204</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3606242233502502</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.1933882630943295</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.03064037591839236</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.03064037591839236</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.4459875135554204</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.727451041505089</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1.727451041505089</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pOEMqcCb</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45557.41666666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>77</v>
+      </c>
+      <c r="F18" t="n">
+        <v>771</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K18" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.3565379226699568</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.3024821731038665</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.3409799042261768</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06644514567978321</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.2537771013452354</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.4765028477428349</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.26972005091193</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.1740206746389684</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.1740206746389684</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.4765028477428349</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.08942965100813</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.08942965100813</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45557.54166666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>77</v>
+      </c>
+      <c r="F19" t="n">
+        <v>771</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.5645371577574968</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2177314211212516</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.2177314211212516</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.06069615964376096</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.5856564105087019</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.2403956741041537</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.1739479153871447</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.02111925275120508</v>
+      </c>
+      <c r="W19" t="n">
+        <v>1</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.02111925275120508</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.5856564105087019</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>2.199147961348698</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.199147961348698</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45557.65625</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>77</v>
+      </c>
+      <c r="F20" t="n">
+        <v>771</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.5220012055455093</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2610006027727547</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.216998191681736</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.0642802155504234</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.2729407836627935</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.4937365504835345</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.2333226658536719</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.2327359477107798</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.2327359477107798</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.4937365504835345</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>2.151890070144066</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2.151890070144066</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45558.65625</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>77</v>
+      </c>
+      <c r="F21" t="n">
+        <v>771</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J21" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.6676557863501484</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2077151335311573</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.1246290801186944</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.06984126984126982</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.5328099397732543</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3400502490343925</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1271398111923535</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>-0.1348458465768941</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.1348458465768941</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.5328099397732543</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>1.442348428315066</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.442348428315066</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>2ucWYubt</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.3125</v>
+        <v>45555.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,53 +610,53 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3.25</v>
+        <v>2.2</v>
       </c>
       <c r="J2" t="n">
         <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>2.25</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2916053019145803</v>
+        <v>0.4322033898305084</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2871870397643594</v>
+        <v>0.288135593220339</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4212076583210604</v>
+        <v>0.2796610169491525</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05516705516705511</v>
+        <v>0.05169340463458116</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2326194891789036</v>
+        <v>0.2775226542060031</v>
       </c>
       <c r="R2" t="n">
-        <v>0.403308017591094</v>
+        <v>0.5764589331654681</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3640724932300026</v>
+        <v>0.1460184126285289</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1161209778267346</v>
+        <v>0.2883233399451292</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1161209778267346</v>
+        <v>0.2883233399451292</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.403308017591094</v>
+        <v>0.5764589331654681</v>
       </c>
       <c r="Z2" t="n">
         <v>3.3</v>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>1.824148310216259</v>
+        <v>7.198857679317757</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.824148310216259</v>
+        <v>7.198857679317757</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
+          <t>44gmVcc5</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45555.65625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.8</v>
+        <v>2.63</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>2.55</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.3565186997553303</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.2757777001048585</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.3677036001398113</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.06650264668605077</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4393181061941691</v>
+        <v>0.3775832588820104</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2865210615616871</v>
+        <v>0.5190510053814275</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2741608322441434</v>
+        <v>0.1033657357365621</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.08699768327951513</v>
+        <v>0.243273305276569</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.08699768327951513</v>
+        <v>0.243273305276569</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4393181061941691</v>
+        <v>0.5190510053814275</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.8</v>
+        <v>3.4</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>1.276921252298795</v>
+        <v>6.587924063809171</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.276921252298795</v>
+        <v>6.587924063809171</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>S66wtFBN</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45556.41666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K4" t="n">
-        <v>4.75</v>
+        <v>2.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5281969817315331</v>
+        <v>0.2922077922077922</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2716441620333598</v>
+        <v>0.2922077922077922</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2001588562351072</v>
+        <v>0.4155844155844156</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05179615705931484</v>
+        <v>0.06944444444444442</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4767671582930659</v>
+        <v>0.3094677840958384</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3738645380054927</v>
+        <v>0.4602613269681881</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1493683037014412</v>
+        <v>0.2302708889359735</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.05142982343846714</v>
+        <v>0.1680535347603959</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.05142982343846714</v>
+        <v>0.1680535347603959</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4767671582930659</v>
+        <v>0.4602613269681881</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,24 +865,24 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>1.541557760912237</v>
+        <v>5.962285895458978</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.541557760912237</v>
+        <v>5.962285895458978</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
+          <t>Yqo4RFdU</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45550.54166666666</v>
+        <v>45556.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.33</v>
+        <v>2.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2192875590858145</v>
+        <v>0.4322033898305084</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2532040348910872</v>
+        <v>0.2796610169491525</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5275084060230983</v>
+        <v>0.288135593220339</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05316910443931233</v>
+        <v>0.05169340463458116</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1392337546671757</v>
+        <v>0.4389887190646548</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3145600305593597</v>
+        <v>0.3926018364682338</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5462062147734645</v>
+        <v>0.1684094444671113</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.0186978087503662</v>
+        <v>0.006785329234146376</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0186978087503662</v>
+        <v>0.006785329234146376</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5462062147734645</v>
+        <v>0.4389887190646548</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2.047391823554364</v>
+        <v>4.743915370914945</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.047391823554364</v>
+        <v>4.743915370914945</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Esk5Iad2</t>
+          <t>O8QDoJsn</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45550.65625</v>
+        <v>45556.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>7.5</v>
+        <v>2.2</v>
       </c>
       <c r="J6" t="n">
-        <v>4.75</v>
+        <v>3.3</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4</v>
+        <v>3.2</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1260066319279962</v>
+        <v>0.4247787610619469</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1989578398863098</v>
+        <v>0.2831858407079646</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6750355281856941</v>
+        <v>0.2920353982300885</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05814536340852117</v>
+        <v>0.07007575757575757</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1395660530224141</v>
+        <v>0.3054538545428889</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3898655581565675</v>
+        <v>0.5564234368347367</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4705683888210183</v>
+        <v>0.1381227086223745</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.2044671393646758</v>
+        <v>0.2732375961267721</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2044671393646758</v>
+        <v>0.2732375961267721</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4705683888210183</v>
+        <v>0.5564234368347367</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0.9644355495576187</v>
+        <v>6.985640469006857</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.9644355495576187</v>
+        <v>6.985640469006857</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WIJkQBF8</t>
+          <t>A50vXJSh</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45551.5625</v>
+        <v>45557.3125</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4228527011270889</v>
+        <v>0.40822528363047</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2798289933929266</v>
+        <v>0.3028768233387358</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2973183054799844</v>
+        <v>0.2888978930307942</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05106209150326801</v>
+        <v>0.0650555615492503</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2251742554276786</v>
+        <v>0.4347211919839138</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4645508589612548</v>
+        <v>0.2824665331267162</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3102748856110667</v>
+        <v>0.2828122748893699</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1847218655683282</v>
+        <v>0.02649590835344384</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1847218655683282</v>
+        <v>0.02649590835344384</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4645508589612548</v>
+        <v>0.4347211919839138</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>2.3</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1162,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>2.046111842871492</v>
+        <v>4.908259913220919</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.046111842871492</v>
+        <v>4.908259913220919</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rgFQPs4S</t>
+          <t>pOEMqcCb</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45551.65625</v>
+        <v>45557.41666666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="J8" t="n">
-        <v>3.75</v>
+        <v>3.1</v>
       </c>
       <c r="K8" t="n">
-        <v>5.75</v>
+        <v>2.35</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5835193829916785</v>
+        <v>0.3012820512820513</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2520803734524051</v>
+        <v>0.3012820512820513</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1644002435559164</v>
+        <v>0.3974358974358974</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05786366076221139</v>
+        <v>0.07069320521619771</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6025262557861536</v>
+        <v>0.2333713801161809</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2583309516313541</v>
+        <v>0.4380083148330444</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1391427925824921</v>
+        <v>0.3286203050507744</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.0190068727944751</v>
+        <v>0.1367262635509931</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0190068727944751</v>
+        <v>0.1367262635509931</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6025262557861536</v>
+        <v>0.4380083148330444</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.62</v>
+        <v>3.1</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,10 +1261,1297 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>2.252633708618753</v>
+        <v>5.72546994190597</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.252633708618753</v>
+        <v>5.72546994190597</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>WvDUsysB</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45557.54166666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>77</v>
+      </c>
+      <c r="F9" t="n">
+        <v>771</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.5769230769230769</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2115384615384615</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.2115384615384615</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.05050505050505061</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.5052372641138604</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.2959801968487892</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.1987825390373504</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>-0.07168581280921649</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.07168581280921649</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.5052372641138604</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.613842824129503</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.613842824129503</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>xIieTySH</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45557.65625</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>77</v>
+      </c>
+      <c r="F10" t="n">
+        <v>771</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.543564639689755</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2474649543850726</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.2089704059251724</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.06341479903998914</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.2557063597216027</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.5217335832591334</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2225600570192638</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.2742686288740608</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.2742686288740608</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.5217335832591334</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>6.616471985062756</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>6.616471985062756</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>OAeKROjD</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45558.65625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>77</v>
+      </c>
+      <c r="F11" t="n">
+        <v>771</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6227217496962333</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2278250303766707</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.149453219927096</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.0705691056910569</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.5488498300850696</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3266654091251674</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.124484760789763</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-0.07387191961116368</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.07387191961116368</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.5488498300850696</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>5.054702082683543</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>5.054702082683543</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CCDxBZAc</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45562.65625</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>77</v>
+      </c>
+      <c r="F12" t="n">
+        <v>771</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6880733944954128</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.1871559633027523</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1247706422018349</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.06862745098039214</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.5176630828673841</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.300003163106478</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.1823337540261379</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.1704103116280288</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.1704103116280288</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.5176630828673841</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>3.695454603878112</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>3.695454603878112</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pIgDNCf3</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45563.41666666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>77</v>
+      </c>
+      <c r="F13" t="n">
+        <v>771</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.1626762873073139</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2338471630042637</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.6034765496884225</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06907433380084149</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.2186852808865267</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3654410972539509</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.4158736218595226</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.1876029278288998</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.1876029278288998</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4158736218595226</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>2.429250554791003</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>2.429250554791003</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>KIQjmWIj</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45563.54166666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>77</v>
+      </c>
+      <c r="F14" t="n">
+        <v>771</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.2178142152435212</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2857986521225596</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.4963871326339193</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0602929747210772</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.1710576396699431</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.3874691227888246</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.4414732375412324</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.05491389509268696</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.05491389509268696</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.4414732375412324</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>4.113754072070238</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.113754072070238</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Whh3dzd4</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45563.65625</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>77</v>
+      </c>
+      <c r="F15" t="n">
+        <v>771</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.3403900302429868</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2925226822400667</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.3670872875169465</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06829322638146174</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.3700260457997705</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3831462942809805</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.246827659919249</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.09062361204091379</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.09062361204091379</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.3831462942809805</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.041846535155089</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.041846535155089</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>WxCQa92d</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45564.3125</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>77</v>
+      </c>
+      <c r="F16" t="n">
+        <v>771</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3565379226699568</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.3024821731038665</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.3409799042261768</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06644514567978321</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1904838587575262</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3647063716599583</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4448097695825153</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.1038298653563385</v>
+      </c>
+      <c r="W16" t="n">
+        <v>2</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.1038298653563385</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4448097695825153</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>5.797850839478927</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>5.797850839478927</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>OC8I1VXq</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>77</v>
+      </c>
+      <c r="F17" t="n">
+        <v>771</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>7</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.6585824796153043</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2078193602341626</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.1335981601505331</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.06930471719204112</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.5506145445530105</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3519292549251983</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.09745620052179116</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-0.1079679350622937</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.1079679350622937</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.5506145445530105</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>4.710633251666668</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>4.710633251666668</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>77</v>
+      </c>
+      <c r="F18" t="n">
+        <v>771</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.4266958424507659</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2888402625820569</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.2844638949671772</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06526806526806528</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.40087452672835</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3853220487082537</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.2138034245633965</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-0.02582131572241586</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.02582131572241586</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.40087452672835</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>3.991306132315379</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>3.991306132315379</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45564.54166666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>77</v>
+      </c>
+      <c r="F19" t="n">
+        <v>771</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2844638949671772</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2888402625820569</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.4266958424507659</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.06526806526806528</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1449942249913165</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3161612615973919</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.5388445134112917</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.1121486709605258</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.1121486709605258</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.5388445134112917</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>6.798566041164167</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>6.798566041164167</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45564.65625</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>77</v>
+      </c>
+      <c r="F20" t="n">
+        <v>771</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K20" t="n">
+        <v>7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.6500776404176282</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2161921021250311</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.1337302574573407</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.06824846951867736</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.4826360333300638</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.4305786488219374</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.08678531784799882</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>-0.1674416070875644</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.1674416070875644</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.4826360333300638</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>3.354290563088688</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>3.354290563088688</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>vuXo7iAM</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45565.65625</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>77</v>
+      </c>
+      <c r="F21" t="n">
+        <v>771</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.4378536585365854</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2852682926829269</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.2768780487804878</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.06226422915889396</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.5210384725531383</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3312309741299987</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.1477305533168629</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.08318481401655292</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.08318481401655292</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.5210384725531383</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>6.430127881068065</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>6.430127881068065</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zTBIR3ZF</t>
+          <t>OAeKROjD</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45550.3125</v>
+        <v>45558.65625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3.25</v>
+        <v>1.48</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>4.33</v>
       </c>
       <c r="K2" t="n">
-        <v>2.25</v>
+        <v>6.25</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2916053019145803</v>
+        <v>0.6334721412704321</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2871870397643594</v>
+        <v>0.2165216556767297</v>
       </c>
       <c r="N2" t="n">
-        <v>0.4212076583210604</v>
+        <v>0.1500062030528383</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05516705516705511</v>
+        <v>0.06662255789276572</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2326194891789036</v>
+        <v>0.3867874089168166</v>
       </c>
       <c r="R2" t="n">
-        <v>0.403308017591094</v>
+        <v>0.3710029627361938</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3640724932300026</v>
+        <v>0.2422096283469896</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1161209778267346</v>
+        <v>-0.2466847323536154</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1161209778267346</v>
+        <v>-0.2466847323536154</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.403308017591094</v>
+        <v>0.3867874089168166</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.3</v>
+        <v>1.48</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>1.824148310216259</v>
+        <v>1.878896575423982</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.824148310216259</v>
+        <v>1.878896575423982</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>zFWqD4KM</t>
+          <t>CCDxBZAc</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45562.65625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="J3" t="n">
-        <v>3.6</v>
+        <v>5.25</v>
       </c>
       <c r="K3" t="n">
-        <v>4.5</v>
+        <v>7.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.6989748369058714</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2631578947368421</v>
+        <v>0.1770736253494874</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2105263157894737</v>
+        <v>0.1239515377446412</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05555555555555558</v>
+        <v>0.07568922305764403</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4393181061941691</v>
+        <v>0.5516144715110304</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2865210615616871</v>
+        <v>0.3215636754423617</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2741608322441434</v>
+        <v>0.1268218530466079</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.08699768327951513</v>
+        <v>-0.147360365394841</v>
       </c>
       <c r="W3" t="n">
         <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.08699768327951513</v>
+        <v>-0.147360365394841</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4393181061941691</v>
+        <v>0.5516144715110304</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.8</v>
+        <v>1.33</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>1.276921252298795</v>
+        <v>5.42139289708825</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.276921252298795</v>
+        <v>5.42139289708825</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>4WHcOkpL</t>
+          <t>pIgDNCf3</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45550.41666666666</v>
+        <v>45563.41666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>4.75</v>
+        <v>1.5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5281969817315331</v>
+        <v>0.1547169811320755</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2716441620333598</v>
+        <v>0.2264150943396227</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2001588562351072</v>
+        <v>0.6188679245283019</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05179615705931484</v>
+        <v>0.0772357723577235</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4767671582930659</v>
+        <v>0.1407836331480519</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3738645380054927</v>
+        <v>0.4221012018591552</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1493683037014412</v>
+        <v>0.4371151649927928</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.05142982343846714</v>
+        <v>-0.1817527595355091</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.05142982343846714</v>
+        <v>-0.1817527595355091</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4767671582930659</v>
+        <v>0.4371151649927928</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>1.541557760912237</v>
+        <v>3.424628000517036</v>
       </c>
       <c r="AC4" t="n">
-        <v>1.541557760912237</v>
+        <v>3.424628000517036</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>6cNF7rrp</t>
+          <t>KIQjmWIj</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45550.54166666666</v>
+        <v>45563.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.33</v>
+        <v>4.5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2192875590858145</v>
+        <v>0.2064566519135642</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2532040348910872</v>
+        <v>0.2858630564957043</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5275084060230983</v>
+        <v>0.5076802915907315</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05316910443931233</v>
+        <v>0.07636261734622396</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.1392337546671757</v>
+        <v>0.3320141076950835</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3145600305593597</v>
+        <v>0.3790377300990898</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5462062147734645</v>
+        <v>0.2889481622058268</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.0186978087503662</v>
+        <v>0.09317467360338549</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0186978087503662</v>
+        <v>0.09317467360338549</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5462062147734645</v>
+        <v>0.3790377300990898</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.8</v>
+        <v>3.25</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>2.047391823554364</v>
+        <v>5.083219753609731</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.047391823554364</v>
+        <v>5.083219753609731</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>Esk5Iad2</t>
+          <t>Whh3dzd4</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45550.65625</v>
+        <v>45563.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>7.5</v>
+        <v>3</v>
       </c>
       <c r="J6" t="n">
-        <v>4.75</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>1.4</v>
+        <v>2.38</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1260066319279962</v>
+        <v>0.3141116751269035</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1989578398863098</v>
+        <v>0.2899492385786802</v>
       </c>
       <c r="N6" t="n">
-        <v>0.6750355281856941</v>
+        <v>0.3959390862944163</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05814536340852117</v>
+        <v>0.06119370825253179</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1395660530224141</v>
+        <v>0.3677523027985431</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3898655581565675</v>
+        <v>0.3888262886441129</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4705683888210183</v>
+        <v>0.2434214085573441</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.2044671393646758</v>
+        <v>0.09887705006543268</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2044671393646758</v>
+        <v>0.09887705006543268</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4705683888210183</v>
+        <v>0.3888262886441129</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.4</v>
+        <v>3.25</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0.9644355495576187</v>
+        <v>5.214492685574628</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.9644355495576187</v>
+        <v>5.214492685574628</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WIJkQBF8</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45551.5625</v>
+        <v>45564.3125</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.25</v>
+        <v>2.75</v>
       </c>
       <c r="J7" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2</v>
+        <v>2.7</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4228527011270889</v>
+        <v>0.3441611842105263</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2798289933929266</v>
+        <v>0.3053042763157894</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2973183054799844</v>
+        <v>0.3505345394736841</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05106209150326801</v>
+        <v>0.05658737916802448</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2251742554276786</v>
+        <v>0.4378840346908894</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4645508589612548</v>
+        <v>0.3651667074585944</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3102748856110667</v>
+        <v>0.1969492578505162</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1847218655683282</v>
+        <v>0.09372285048036316</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1847218655683282</v>
+        <v>0.09372285048036316</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4645508589612548</v>
+        <v>0.4378840346908894</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.4</v>
+        <v>2.75</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1162,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>2.046111842871492</v>
+        <v>5.872398967641462</v>
       </c>
       <c r="AC7" t="n">
-        <v>2.046111842871492</v>
+        <v>5.872398967641462</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rgFQPs4S</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45551.65625</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.75</v>
+        <v>4.75</v>
       </c>
       <c r="K8" t="n">
-        <v>5.75</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5835193829916785</v>
+        <v>0.6690140845070423</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2520803734524051</v>
+        <v>0.1971830985915493</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1644002435559164</v>
+        <v>0.1338028169014084</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05786366076221139</v>
+        <v>0.06766917293233088</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.6025262557861536</v>
+        <v>0.487702311608233</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2583309516313541</v>
+        <v>0.3320774123961673</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1391427925824921</v>
+        <v>0.1802202759956</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.0190068727944751</v>
+        <v>-0.1813117728988093</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.0190068727944751</v>
+        <v>-0.1813117728988093</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.6025262557861536</v>
+        <v>0.487702311608233</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.62</v>
+        <v>1.4</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,10 +1261,1396 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>2.252633708618753</v>
+        <v>4.108958858211064</v>
       </c>
       <c r="AC8" t="n">
-        <v>2.252633708618753</v>
+        <v>4.108958858211064</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>h8tCfEQG</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45564.41666666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>77</v>
+      </c>
+      <c r="F9" t="n">
+        <v>771</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4266958424507659</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2888402625820569</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.2844638949671772</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.06526806526806528</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.3706641291075206</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3739962239464513</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.2553396469460279</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.08515596136439441</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.08515596136439441</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.3739962239464513</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>5.015608849396219</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>5.015608849396219</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>0YqKhheT</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45564.54166666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>77</v>
+      </c>
+      <c r="F10" t="n">
+        <v>771</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2844638949671772</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2888402625820569</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.4266958424507659</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.06526806526806528</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.283179633684656</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3783621777071274</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.3384581886082167</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.08952191512507046</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.08952191512507046</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.3783621777071274</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>5.074160018942885</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>5.074160018942885</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>WETw9DuA</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45564.65625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>77</v>
+      </c>
+      <c r="F11" t="n">
+        <v>771</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K11" t="n">
+        <v>8</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6728971962616822</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2093457943925233</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.1177570093457944</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06150793650793651</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.5927423185729692</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.2629712806694237</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.144286400757607</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>-0.08015487768871299</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>-0.08015487768871299</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.5927423185729692</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>6.874235460079252</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>6.874235460079252</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vuXo7iAM</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45565.65625</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>77</v>
+      </c>
+      <c r="F12" t="n">
+        <v>771</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4415584415584415</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2792207792207792</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.2792207792207792</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.05335157318741457</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.4354236745886679</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.355077973981165</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.2094983514301671</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.006134766969773664</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.006134766969773664</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4354236745886679</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>5.757130971218705</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>5.757130971218705</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>z3jsi9f5</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45569.5625</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>77</v>
+      </c>
+      <c r="F13" t="n">
+        <v>771</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="J13" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K13" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6471238938053098</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2085176991150442</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.144358407079646</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06572354848216921</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.3807951109694707</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3713259172087673</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.2478789718217618</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.2663287828358391</v>
+      </c>
+      <c r="W13" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.2663287828358391</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.6192048890305293</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.659090909090909</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>8.304066517675851</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>8.304066517675851</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8SWavWAa</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45569.65625</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>77</v>
+      </c>
+      <c r="F14" t="n">
+        <v>771</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.4603234298608499</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2775479503572771</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.2621286197818729</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.05970030288538197</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3646889468749105</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.376808570749315</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.2585024823757745</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.09926062039203781</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.09926062039203781</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.376808570749315</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>5.053324822469876</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>5.053324822469876</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>WUqjkmPH</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45570.41666666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>77</v>
+      </c>
+      <c r="F15" t="n">
+        <v>771</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.4689603590127151</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2842183994016455</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.2468212415856395</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06618819776714502</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.366967809925877</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3768738347457878</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.2561583553283352</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.09265543534414228</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.09265543534414228</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.3768738347457878</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.054200068414346</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>5.054200068414346</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>EB8yv2aJ</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45570.54166666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>77</v>
+      </c>
+      <c r="F16" t="n">
+        <v>771</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K16" t="n">
+        <v>6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.6264014466546112</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.216998191681736</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.1566003616636528</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.0642802155504234</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.4690041039744517</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.3495857899250586</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.1814101061004897</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>-0.1573973426801594</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.1573973426801594</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4690041039744517</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>4.178912859032295</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>4.178912859032295</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>ttV7xAuC</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45570.65625</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>77</v>
+      </c>
+      <c r="F17" t="n">
+        <v>771</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.6965944272445821</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2058823529411765</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.09752321981424149</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.07936507936507931</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.3687691030089816</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3778563752403633</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.2533745217506556</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.1719740222991868</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.1719740222991868</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.3778563752403633</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>5.06737677578182</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>5.06737677578182</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>x8OGzlAO</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45571.3125</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>77</v>
+      </c>
+      <c r="F18" t="n">
+        <v>771</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.6676557863501484</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2077151335311573</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.1246290801186944</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06984126984126982</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.4452259396352466</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.3547929447640126</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.1999811156007407</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-0.2224298467149018</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.2224298467149018</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.4452259396352466</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>2.9878859296242</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>2.9878859296242</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>77</v>
+      </c>
+      <c r="F19" t="n">
+        <v>771</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K19" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.5389221556886228</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.251497005988024</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.2095808383233533</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.0603174603174601</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2884561946384767</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3718053828229426</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.3397384225385808</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.1203083768349186</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.1203083768349186</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.3718053828229426</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>4.986227798403936</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>4.986227798403936</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>77</v>
+      </c>
+      <c r="F20" t="n">
+        <v>771</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="J20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.6263219741480611</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2291421856639248</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.1445358401880141</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.06441525953721072</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.5401047277622434</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.3495822726155097</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.110312999622247</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>-0.08621724638581774</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.08621724638581774</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.5401047277622434</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>6.087018858638833</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>6.087018858638833</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45571.54166666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>77</v>
+      </c>
+      <c r="F21" t="n">
+        <v>771</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.2492917847025495</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.28328611898017</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.4674220963172804</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.06969696969696981</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.3563723800574224</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3741454843807208</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2694821355618568</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.09085936540055078</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.09085936540055078</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.3741454843807208</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>5.017610559325497</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>5.017610559325497</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45571.65625</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>77</v>
+      </c>
+      <c r="F22" t="n">
+        <v>771</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K22" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.3480113636363636</v>
+      </c>
+      <c r="M22" t="n">
+        <v>0.2684659090909091</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0.3835227272727272</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.06424792139077851</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.3581358117196171</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.3758257404424035</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.2660384478379793</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="n">
+        <v>0.1073598313514945</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0.1073598313514945</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0.3758257404424035</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB22" t="n">
+        <v>5.040144228471404</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>5.040144228471404</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC10"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CCDxBZAc</t>
+          <t>WxCQa92d</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45562.65625</v>
+        <v>45564.3125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.33</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
-        <v>5.75</v>
+        <v>3.1</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>2.55</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7155356795644564</v>
+        <v>0.3254425689584192</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1655065137079526</v>
+        <v>0.3044462741869082</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1189578067275909</v>
+        <v>0.3701111568546728</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05079274272638123</v>
+        <v>0.05956509411328481</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5379100508717075</v>
+        <v>0.3362669684838246</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3181153758188626</v>
+        <v>0.3880135316220744</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1439745733094297</v>
+        <v>0.275719499894101</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1776256286927489</v>
+        <v>0.08356725743516619</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1776256286927489</v>
+        <v>0.08356725743516619</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.5379100508717075</v>
+        <v>0.3880135316220744</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.33</v>
+        <v>3.1</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.831721874387481</v>
+        <v>5.577852768386192</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.831721874387481</v>
+        <v>5.577852768386192</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pIgDNCf3</t>
+          <t>OC8I1VXq</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45563.41666666666</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>7</v>
+        <v>1.4</v>
       </c>
       <c r="J3" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="K3" t="n">
-        <v>1.48</v>
+        <v>8</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1361218733007069</v>
+        <v>0.6803939122649956</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2200584556824361</v>
+        <v>0.2005371530886303</v>
       </c>
       <c r="N3" t="n">
-        <v>0.643819671016857</v>
+        <v>0.1190689346463742</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0494797007499086</v>
+        <v>0.04981203007518786</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1303368445467272</v>
+        <v>0.4070506636913135</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4411545989602798</v>
+        <v>0.4087514570960236</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4285085564929927</v>
+        <v>0.1841978792126631</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2210961432778437</v>
+        <v>0.2082143040073934</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2210961432778437</v>
+        <v>0.2082143040073934</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4411545989602798</v>
+        <v>0.4087514570960236</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.33</v>
+        <v>4.75</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5.916260028373514</v>
+        <v>5.875968905037116</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.916260028373514</v>
+        <v>5.875968905037116</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>KIQjmWIj</t>
+          <t>h8tCfEQG</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45563.54166666666</v>
+        <v>45564.41666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>como</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>2.05</v>
       </c>
       <c r="J4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1722141823444284</v>
+        <v>0.4636078864934587</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2706222865412445</v>
+        <v>0.2795282845034089</v>
       </c>
       <c r="N4" t="n">
-        <v>0.557163531114327</v>
+        <v>0.2568638290031325</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05576776165011466</v>
+        <v>0.05219279537787425</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3130277397140973</v>
+        <v>0.2813615869247901</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3839189676342548</v>
+        <v>0.4140755156130079</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3030532926516478</v>
+        <v>0.3045628974622018</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1132966810930103</v>
+        <v>0.134547231109599</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1132966810930103</v>
+        <v>0.134547231109599</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3839189676342548</v>
+        <v>0.4140755156130079</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>5.148681318753459</v>
+        <v>5.952504417636032</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.148681318753459</v>
+        <v>5.952504417636032</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>Whh3dzd4</t>
+          <t>0YqKhheT</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45563.65625</v>
+        <v>45564.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,53 +907,53 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="J5" t="n">
         <v>3.3</v>
       </c>
       <c r="K5" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.316546762589928</v>
+        <v>0.2796610169491525</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2877697841726619</v>
+        <v>0.288135593220339</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3956834532374101</v>
+        <v>0.4322033898305084</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05303030303030298</v>
+        <v>0.05169340463458116</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3598350434428372</v>
+        <v>0.3692795928007899</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3877683667329928</v>
+        <v>0.3839254600294552</v>
       </c>
       <c r="S5" t="n">
-        <v>0.25239658982417</v>
+        <v>0.2467949471697545</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.0999985825603309</v>
+        <v>0.09578986680911616</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0999985825603309</v>
+        <v>0.09578986680911616</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3877683667329928</v>
+        <v>0.3839254600294552</v>
       </c>
       <c r="Z5" t="n">
         <v>3.3</v>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>5.200305049016715</v>
+        <v>5.519085071922291</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.200305049016715</v>
+        <v>5.519085071922291</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>WETw9DuA</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45564.3125</v>
+        <v>45564.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.9</v>
+        <v>1.33</v>
       </c>
       <c r="J6" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>2.55</v>
+        <v>8.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.3254425689584192</v>
+        <v>0.7030022330659168</v>
       </c>
       <c r="M6" t="n">
-        <v>0.3044462741869082</v>
+        <v>0.1869985939955339</v>
       </c>
       <c r="N6" t="n">
-        <v>0.3701111568546728</v>
+        <v>0.1099991729385493</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05956509411328481</v>
+        <v>0.06952675807164965</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.3945361489316285</v>
+        <v>0.477692409231123</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3666792673988766</v>
+        <v>0.3399916092321667</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2387845836694949</v>
+        <v>0.1823159815367103</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.06909357997320931</v>
+        <v>-0.2253098238347938</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.06909357997320931</v>
+        <v>-0.2253098238347938</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3945361489316285</v>
+        <v>0.477692409231123</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.9</v>
+        <v>1.33</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>5.291066789678363</v>
+        <v>3.628102599309686</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.291066789678363</v>
+        <v>3.628102599309686</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>vuXo7iAM</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45565.65625</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="J7" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>3.4</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6803939122649956</v>
+        <v>0.4543429844097995</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2005371530886303</v>
+        <v>0.2650334075723831</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1190689346463742</v>
+        <v>0.2806236080178174</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04981203007518786</v>
+        <v>0.04808590102707755</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4934507323769057</v>
+        <v>0.3912921197873209</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3338048311124552</v>
+        <v>0.3113614735688288</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1727444365106393</v>
+        <v>0.2973464066438502</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.1869431798880899</v>
+        <v>-0.06305086462247866</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.1869431798880899</v>
+        <v>-0.06305086462247866</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4934507323769057</v>
+        <v>0.3912921197873209</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,307 +1162,10 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4.110528112951733</v>
+        <v>4.718601916190526</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.110528112951733</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>h8tCfEQG</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>45564.41666666666</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>como</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>verona</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>77</v>
-      </c>
-      <c r="F8" t="n">
-        <v>771</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="K8" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="L8" t="n">
-        <v>0.4543429844097996</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0.2806236080178174</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.2650334075723831</v>
-      </c>
-      <c r="O8" t="n">
-        <v>0.04808590102707733</v>
-      </c>
-      <c r="P8" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>0.3702193275959159</v>
-      </c>
-      <c r="R8" t="n">
-        <v>0.3740984140826293</v>
-      </c>
-      <c r="S8" t="n">
-        <v>0.2556822583214551</v>
-      </c>
-      <c r="T8" t="n">
-        <v>1</v>
-      </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="n">
-        <v>0.09347480606481184</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>0.09347480606481184</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.3740984140826293</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB8" t="n">
-        <v>5.016979306418289</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>5.016979306418289</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>0YqKhheT</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>45564.54166666666</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>empoli</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>fiorentina</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>77</v>
-      </c>
-      <c r="F9" t="n">
-        <v>771</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.2796610169491525</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0.288135593220339</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0.4322033898305084</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0.05169340463458116</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>0.285699455092448</v>
-      </c>
-      <c r="R9" t="n">
-        <v>0.3760631779410959</v>
-      </c>
-      <c r="S9" t="n">
-        <v>0.3382373669664561</v>
-      </c>
-      <c r="T9" t="n">
-        <v>1</v>
-      </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="n">
-        <v>0.0879275847207569</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0.0879275847207569</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0.3760631779410959</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB9" t="n">
-        <v>5.043328468159852</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>5.043328468159852</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>WETw9DuA</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>45564.65625</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>napoli</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>monza</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>77</v>
-      </c>
-      <c r="F10" t="n">
-        <v>771</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>italy</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>serie a</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="J10" t="n">
-        <v>5</v>
-      </c>
-      <c r="K10" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0.6983240223463686</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0.1899441340782123</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.111731843575419</v>
-      </c>
-      <c r="O10" t="n">
-        <v>0.05294117647058827</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0.5615282149312811</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0.2661786494530103</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0.1722931356157086</v>
-      </c>
-      <c r="T10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="n">
-        <v>-0.1367958074150875</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1</v>
-      </c>
-      <c r="X10" t="n">
-        <v>-0.1367958074150875</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>0.5615282149312811</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB10" t="n">
-        <v>5.696024412451278</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>5.696024412451278</v>
+        <v>4.718601916190526</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:AC13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,12 +510,12 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>prob_class_0</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>prob_class_1</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>prob_class_0</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>WxCQa92d</t>
+          <t>z3jsi9f5</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45564.3125</v>
+        <v>45569.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,81 +610,81 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>1.5</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
       <c r="K2" t="n">
-        <v>2.55</v>
+        <v>6.5</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3254425689584192</v>
+        <v>0.6297577854671281</v>
       </c>
       <c r="M2" t="n">
-        <v>0.3044462741869082</v>
+        <v>0.2249134948096886</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3701111568546728</v>
+        <v>0.1453287197231834</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05956509411328481</v>
+        <v>0.0586080586080584</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3362669684838246</v>
+        <v>0.3936810245795515</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3880135316220744</v>
+        <v>0.4687831093694965</v>
       </c>
       <c r="S2" t="n">
-        <v>0.275719499894101</v>
+        <v>0.137535866050952</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.08356725743516619</v>
+        <v>-0.1609746760976316</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.08356725743516619</v>
+        <v>-0.1609746760976316</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3880135316220744</v>
+        <v>0.4687831093694965</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.1</v>
+        <v>1.5</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>5.577852768386192</v>
+        <v>3.078084332718649</v>
       </c>
       <c r="AC2" t="n">
-        <v>5.577852768386192</v>
+        <v>3.078084332718649</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OC8I1VXq</t>
+          <t>8SWavWAa</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45569.65625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -709,86 +709,86 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="J3" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>8</v>
+        <v>2.9</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6803939122649956</v>
+        <v>0.3783122706889523</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2005371530886303</v>
+        <v>0.2955564614757439</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1190689346463742</v>
+        <v>0.3261312678353037</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04981203007518786</v>
+        <v>0.05732758620689671</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4070506636913135</v>
+        <v>0.4444433120048706</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4087514570960236</v>
+        <v>0.3791275440654793</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1841978792126631</v>
+        <v>0.1764291439296498</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2082143040073934</v>
+        <v>0.1488868505291267</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.2082143040073934</v>
+        <v>0.1488868505291267</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4087514570960236</v>
+        <v>0.4444433120048706</v>
       </c>
       <c r="Z3" t="n">
-        <v>4.75</v>
+        <v>3.2</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>5.875968905037116</v>
+        <v>4.444433120048706</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.875968905037116</v>
+        <v>4.444433120048706</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>h8tCfEQG</t>
+          <t>WUqjkmPH</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45564.41666666666</v>
+        <v>45570.41666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,86 +808,86 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.05</v>
+        <v>2.2</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K4" t="n">
-        <v>3.7</v>
+        <v>3.3</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4636078864934587</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2795282845034089</v>
+        <v>0.2857142857142858</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2568638290031325</v>
+        <v>0.2857142857142858</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05219279537787425</v>
+        <v>0.06060606060606055</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2813615869247901</v>
+        <v>0.4324486093021525</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4140755156130079</v>
+        <v>0.3856705418658141</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3045628974622018</v>
+        <v>0.1818808488320333</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.134547231109599</v>
+        <v>0.1467343235878667</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.134547231109599</v>
+        <v>0.1467343235878667</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4140755156130079</v>
+        <v>0.4324486093021525</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>5.952504417636032</v>
+        <v>4.324486093021525</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.952504417636032</v>
+        <v>4.324486093021525</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>0YqKhheT</t>
+          <t>EB8yv2aJ</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45564.54166666666</v>
+        <v>45570.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,86 +907,86 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>3.4</v>
+        <v>1.45</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="K5" t="n">
-        <v>2.2</v>
+        <v>6.5</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2796610169491525</v>
+        <v>0.6543046357615894</v>
       </c>
       <c r="M5" t="n">
-        <v>0.288135593220339</v>
+        <v>0.1997350993377483</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4322033898305084</v>
+        <v>0.1459602649006622</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05169340463458116</v>
+        <v>0.05402764204942079</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3692795928007899</v>
+        <v>0.4974187979266894</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3839254600294552</v>
+        <v>0.413374283578173</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2467949471697545</v>
+        <v>0.08920691849513776</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.09578986680911616</v>
+        <v>0.2976836985889411</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.09578986680911616</v>
+        <v>0.2976836985889411</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3839254600294552</v>
+        <v>0.4974187979266894</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.3</v>
+        <v>4.75</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>5.519085071922291</v>
+        <v>4.974187979266894</v>
       </c>
       <c r="AC5" t="n">
-        <v>5.519085071922291</v>
+        <v>4.974187979266894</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WETw9DuA</t>
+          <t>ttV7xAuC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45564.65625</v>
+        <v>45570.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,81 +1006,81 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="J6" t="n">
         <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>8.5</v>
+        <v>11</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7030022330659168</v>
+        <v>0.7255936675461742</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1869985939955339</v>
+        <v>0.1886543535620053</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1099991729385493</v>
+        <v>0.0857519788918206</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06952675807164965</v>
+        <v>0.06013986013985995</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.477692409231123</v>
+        <v>0.5505240387259208</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3399916092321667</v>
+        <v>0.3536317679701654</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1823159815367103</v>
+        <v>0.09584419330391367</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.2253098238347938</v>
+        <v>0.3618696851639155</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.2253098238347938</v>
+        <v>0.3618696851639155</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.477692409231123</v>
+        <v>0.5505240387259208</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.33</v>
+        <v>5</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>3.628102599309686</v>
+        <v>5.505240387259208</v>
       </c>
       <c r="AC6" t="n">
-        <v>3.628102599309686</v>
+        <v>5.505240387259208</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>vuXo7iAM</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45565.65625</v>
+        <v>45571.3125</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1105,67 +1105,661 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.1</v>
+        <v>1.38</v>
       </c>
       <c r="J7" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>3.4</v>
+        <v>8</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4543429844097995</v>
+        <v>0.6903693476009666</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2650334075723831</v>
+        <v>0.1905419399378667</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2806236080178174</v>
+        <v>0.1190887124611667</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04808590102707755</v>
+        <v>0.04963768115942035</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3912921197873209</v>
+        <v>0.4643301129039018</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3113614735688288</v>
+        <v>0.4456248333799684</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2973464066438502</v>
+        <v>0.09004505371612988</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.06305086462247866</v>
+        <v>0.2737881729660351</v>
       </c>
       <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0.2737881729660351</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.4643301129039018</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>4.643301129039018</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>4.643301129039018</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>dzYLoEIP</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>77</v>
+      </c>
+      <c r="F8" t="n">
+        <v>771</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J8" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K8" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.5257095980311731</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2557506152584085</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.2185397867104184</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.0567727080429159</v>
+      </c>
+      <c r="P8" t="n">
         <v>1</v>
       </c>
-      <c r="X7" t="n">
-        <v>-0.06305086462247866</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.3912921197873209</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
-        </is>
-      </c>
-      <c r="AB7" t="n">
-        <v>4.718601916190526</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>4.718601916190526</v>
+      <c r="Q8" t="n">
+        <v>0.4029705325841423</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.4567827165677181</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.1402467508481397</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>-0.06892688146345505</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.06892688146345505</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.4567827165677181</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.87855835104263</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>3.87855835104263</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>SW3Qfiet</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45571.41666666666</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>77</v>
+      </c>
+      <c r="F9" t="n">
+        <v>771</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>6</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.6045340050377834</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.23727959697733</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.1581863979848867</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.05360934182590227</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.4934002569841841</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.4066116629530556</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.09998808006276047</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>0.2561206600068541</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0.2561206600068541</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.4934002569841841</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>4.934002569841841</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>4.934002569841841</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>lnhZhVPh</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45571.54166666666</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>77</v>
+      </c>
+      <c r="F10" t="n">
+        <v>771</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.2255174329768023</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2785803583831088</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.4959022086400889</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.05577309457814539</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.4887359728070411</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.3255577443522703</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.1857062828406884</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.2101556144239323</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.2101556144239323</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.4887359728070411</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>4.887359728070411</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>4.887359728070411</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>SIOithtm</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45571.65625</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>77</v>
+      </c>
+      <c r="F11" t="n">
+        <v>771</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.3057915057915058</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2633204633204633</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.4308880308880308</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05490387748452275</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4864114727927307</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3336638005531591</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.17992472665411</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.2230910094722673</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.2230910094722673</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4864114727927307</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.864114727927307</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>4.864114727927307</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Cl5M5C3L</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>77</v>
+      </c>
+      <c r="F12" t="n">
+        <v>771</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4814305364511692</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2682255845942228</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.250343878954608</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.06520146520146519</v>
+      </c>
+      <c r="P12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.4354198513195021</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.463089200731846</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.1014909479486519</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>-0.01834133571932323</v>
+      </c>
+      <c r="W12" t="n">
+        <v>1</v>
+      </c>
+      <c r="X12" t="n">
+        <v>-0.01834133571932323</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.463089200731846</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>4.447478650125228</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>4.447478650125228</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>EXLhbUee</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45584.41666666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>77</v>
+      </c>
+      <c r="F13" t="n">
+        <v>771</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.3210702341137124</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2909698996655518</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.3879598662207357</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.07399425287356332</v>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.483526184929107</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3310842080653153</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.1853896070055777</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.1925562852635552</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.1925562852635552</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.483526184929107</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>4.83526184929107</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>4.83526184929107</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC13"/>
+  <dimension ref="A1:AC15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,20 +577,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>z3jsi9f5</t>
+          <t>x8OGzlAO</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45569.5625</v>
+        <v>45571.3125</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,56 +610,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>6.5</v>
+        <v>8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6297577854671281</v>
+        <v>0.6903693476009666</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2249134948096886</v>
+        <v>0.1905419399378667</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1453287197231834</v>
+        <v>0.1190887124611667</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0586080586080584</v>
+        <v>0.04963768115942035</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3936810245795515</v>
+        <v>0.4643301129039018</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4687831093694965</v>
+        <v>0.4456248333799684</v>
       </c>
       <c r="S2" t="n">
-        <v>0.137535866050952</v>
+        <v>0.09004505371612988</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1609746760976316</v>
+        <v>0.2737881729660351</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1609746760976316</v>
+        <v>0.2737881729660351</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4687831093694965</v>
+        <v>0.4643301129039018</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.5</v>
+        <v>5</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -667,29 +667,29 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>3.078084332718649</v>
+        <v>4.302491149284828</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.078084332718649</v>
+        <v>4.302491149284828</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8SWavWAa</t>
+          <t>dzYLoEIP</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45569.65625</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,56 +709,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.5</v>
+        <v>1.83</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="K3" t="n">
-        <v>2.9</v>
+        <v>4.33</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3783122706889523</v>
+        <v>0.5215865398702301</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2955564614757439</v>
+        <v>0.2579738832331138</v>
       </c>
       <c r="N3" t="n">
-        <v>0.3261312678353037</v>
+        <v>0.2204395768966561</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05732758620689671</v>
+        <v>0.04766523991905425</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4444433120048706</v>
+        <v>0.4029705325841423</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3791275440654793</v>
+        <v>0.4567827165677181</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1764291439296498</v>
+        <v>0.1402467508481397</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1488868505291267</v>
+        <v>-0.064803823302512</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1488868505291267</v>
+        <v>-0.064803823302512</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4444433120048706</v>
+        <v>0.4567827165677181</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.2</v>
+        <v>1.83</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -766,29 +766,29 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>4.444433120048706</v>
+        <v>3.632083451217061</v>
       </c>
       <c r="AC3" t="n">
-        <v>4.444433120048706</v>
+        <v>3.632083451217061</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>WUqjkmPH</t>
+          <t>SW3Qfiet</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45570.41666666666</v>
+        <v>45571.41666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,56 +808,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.2</v>
+        <v>1.57</v>
       </c>
       <c r="J4" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
-        <v>3.3</v>
+        <v>6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.6045340050377834</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2857142857142858</v>
+        <v>0.23727959697733</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2857142857142858</v>
+        <v>0.1581863979848867</v>
       </c>
       <c r="O4" t="n">
-        <v>0.06060606060606055</v>
+        <v>0.05360934182590227</v>
       </c>
       <c r="P4" t="n">
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4324486093021525</v>
+        <v>0.4934002569841841</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3856705418658141</v>
+        <v>0.4066116629530556</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1818808488320333</v>
+        <v>0.09998808006276047</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1467343235878667</v>
+        <v>0.2561206600068541</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1467343235878667</v>
+        <v>0.2561206600068541</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4324486093021525</v>
+        <v>0.4934002569841841</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -865,29 +865,29 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>4.324486093021525</v>
+        <v>4.571855625415056</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.324486093021525</v>
+        <v>4.571855625415056</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EB8yv2aJ</t>
+          <t>lnhZhVPh</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45570.54166666666</v>
+        <v>45571.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,56 +907,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.45</v>
+        <v>4.1</v>
       </c>
       <c r="J5" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="K5" t="n">
-        <v>6.5</v>
+        <v>1.91</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6543046357615894</v>
+        <v>0.2297541128604281</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1997350993377483</v>
+        <v>0.2770564302140457</v>
       </c>
       <c r="N5" t="n">
-        <v>0.1459602649006622</v>
+        <v>0.4931894569255263</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05402764204942079</v>
+        <v>0.06158029550729749</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4974187979266894</v>
+        <v>0.4887359728070411</v>
       </c>
       <c r="R5" t="n">
-        <v>0.413374283578173</v>
+        <v>0.3255577443522703</v>
       </c>
       <c r="S5" t="n">
-        <v>0.08920691849513776</v>
+        <v>0.1857062828406884</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2976836985889411</v>
+        <v>0.2116795425929954</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.2976836985889411</v>
+        <v>0.2116795425929954</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4974187979266894</v>
+        <v>0.4887359728070411</v>
       </c>
       <c r="Z5" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4.974187979266894</v>
+        <v>4.528636284622356</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.974187979266894</v>
+        <v>4.528636284622356</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ttV7xAuC</t>
+          <t>SIOithtm</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45570.65625</v>
+        <v>45571.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,56 +1006,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.3</v>
+        <v>3.2</v>
       </c>
       <c r="J6" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="K6" t="n">
-        <v>11</v>
+        <v>2.15</v>
       </c>
       <c r="L6" t="n">
-        <v>0.7255936675461742</v>
+        <v>0.296097934200459</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1886543535620053</v>
+        <v>0.2631981637337414</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0857519788918206</v>
+        <v>0.4407039020657995</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06013986013985995</v>
+        <v>0.05539405684754528</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5505240387259208</v>
+        <v>0.4864114727927307</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3536317679701654</v>
+        <v>0.3336638005531591</v>
       </c>
       <c r="S6" t="n">
-        <v>0.09584419330391367</v>
+        <v>0.17992472665411</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3618696851639155</v>
+        <v>0.2232133090589893</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3618696851639155</v>
+        <v>0.2232133090589893</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.5505240387259208</v>
+        <v>0.4864114727927307</v>
       </c>
       <c r="Z6" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1063,29 +1063,29 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>5.505240387259208</v>
+        <v>4.507097425823092</v>
       </c>
       <c r="AC6" t="n">
-        <v>5.505240387259208</v>
+        <v>4.507097425823092</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>Cl5M5C3L</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45571.3125</v>
+        <v>45584.41666666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>como</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,56 +1105,56 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.38</v>
+        <v>1.95</v>
       </c>
       <c r="J7" t="n">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>3.75</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6903693476009666</v>
+        <v>0.4814305364511692</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1905419399378667</v>
+        <v>0.2682255845942228</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1190887124611667</v>
+        <v>0.250343878954608</v>
       </c>
       <c r="O7" t="n">
-        <v>0.04963768115942035</v>
+        <v>0.06520146520146519</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4643301129039018</v>
+        <v>0.4225339281016023</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4456248333799684</v>
+        <v>0.4748572347263693</v>
       </c>
       <c r="S7" t="n">
-        <v>0.09004505371612988</v>
+        <v>0.1026088371720284</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2737881729660351</v>
+        <v>-0.006573301724799974</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0.2737881729660351</v>
+        <v>-0.006573301724799974</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4643301129039018</v>
+        <v>0.4748572347263693</v>
       </c>
       <c r="Z7" t="n">
-        <v>5</v>
+        <v>1.95</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1162,29 +1162,29 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4.643301129039018</v>
+        <v>4.33912731718204</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.643301129039018</v>
+        <v>4.33912731718204</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>EXLhbUee</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45584.41666666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
           <t>bologna</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>parma</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,56 +1204,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.8</v>
+        <v>2.9</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="K8" t="n">
-        <v>4.33</v>
+        <v>2.45</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5257095980311731</v>
+        <v>0.3236326109391125</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2557506152584085</v>
+        <v>0.2932920536635707</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2185397867104184</v>
+        <v>0.3830753353973168</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0567727080429159</v>
+        <v>0.06549085151301903</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4029705325841423</v>
+        <v>0.4934150520430539</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4567827165677181</v>
+        <v>0.3269035398215585</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1402467508481397</v>
+        <v>0.1796814081353877</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.06892688146345505</v>
+        <v>0.2001229983794832</v>
       </c>
       <c r="W8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.06892688146345505</v>
+        <v>0.2001229983794832</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4567827165677181</v>
+        <v>0.4934150520430539</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1261,29 +1261,29 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>3.87855835104263</v>
+        <v>4.571992716695745</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.87855835104263</v>
+        <v>4.571992716695745</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>SznSCTAl</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45584.54166666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,56 +1303,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="J9" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>6</v>
+        <v>8.5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6045340050377834</v>
+        <v>0.6807261078483717</v>
       </c>
       <c r="M9" t="n">
-        <v>0.23727959697733</v>
+        <v>0.2087560064068339</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1581863979848867</v>
+        <v>0.1105178857447944</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05360934182590227</v>
+        <v>0.06450696220517194</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.4934002569841841</v>
+        <v>0.5188114147443916</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4066116629530556</v>
+        <v>0.380670454550161</v>
       </c>
       <c r="S9" t="n">
-        <v>0.09998808006276047</v>
+        <v>0.1005181307054474</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2561206600068541</v>
+        <v>0.3100554083375577</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2561206600068541</v>
+        <v>0.3100554083375577</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4934002569841841</v>
+        <v>0.5188114147443916</v>
       </c>
       <c r="Z9" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1360,29 +1360,29 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>4.934002569841841</v>
+        <v>4.807315868716142</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.934002569841841</v>
+        <v>4.807315868716142</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>2g2mKBIE</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45571.54166666666</v>
+        <v>45584.65625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,56 +1402,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.2</v>
+        <v>1.8</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K10" t="n">
-        <v>1.91</v>
+        <v>4.75</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2255174329768023</v>
+        <v>0.5196419691695674</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2785803583831088</v>
+        <v>0.2834410740924913</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4959022086400889</v>
+        <v>0.1969169567379413</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05577309457814539</v>
+        <v>0.06911217437533224</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4887359728070411</v>
+        <v>0.4230778862300282</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3255577443522703</v>
+        <v>0.4755061707450107</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1857062828406884</v>
+        <v>0.1014159430249609</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2101556144239323</v>
+        <v>-0.04413579842455667</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.2101556144239323</v>
+        <v>-0.04413579842455667</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4887359728070411</v>
+        <v>0.4755061707450107</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.4</v>
+        <v>1.8</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1459,29 +1459,29 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>4.887359728070411</v>
+        <v>3.997085602235251</v>
       </c>
       <c r="AC10" t="n">
-        <v>4.887359728070411</v>
+        <v>3.997085602235251</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45571.65625</v>
+        <v>45585.3125</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1501,53 +1501,53 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="J11" t="n">
         <v>3.6</v>
       </c>
       <c r="K11" t="n">
-        <v>2.2</v>
+        <v>1.67</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3057915057915058</v>
+        <v>0.171786153098837</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2633204633204633</v>
+        <v>0.2624510672343344</v>
       </c>
       <c r="N11" t="n">
-        <v>0.4308880308880308</v>
+        <v>0.5657627796668286</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05490387748452275</v>
+        <v>0.05839835480554045</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4864114727927307</v>
+        <v>0.5139346781513106</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3336638005531591</v>
+        <v>0.3064001502974576</v>
       </c>
       <c r="S11" t="n">
-        <v>0.17992472665411</v>
+        <v>0.1796651715512319</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2230910094722673</v>
+        <v>0.2514836109169762</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2230910094722673</v>
+        <v>0.2514836109169762</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4864114727927307</v>
+        <v>0.5139346781513106</v>
       </c>
       <c r="Z11" t="n">
         <v>3.6</v>
@@ -1558,29 +1558,29 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>4.864114727927307</v>
+        <v>4.762127940029149</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.864114727927307</v>
+        <v>4.762127940029149</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45584.41666666666</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1600,56 +1600,56 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="J12" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K12" t="n">
-        <v>3.75</v>
+        <v>2.35</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4814305364511692</v>
+        <v>0.3125319693094629</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2682255845942228</v>
+        <v>0.2884910485933505</v>
       </c>
       <c r="N12" t="n">
-        <v>0.250343878954608</v>
+        <v>0.3989769820971867</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06520146520146519</v>
+        <v>0.06655755591925794</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4354198513195021</v>
+        <v>0.4944813074094251</v>
       </c>
       <c r="R12" t="n">
-        <v>0.463089200731846</v>
+        <v>0.3301614250938594</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1014909479486519</v>
+        <v>0.1753572674967152</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>-0.01834133571932323</v>
+        <v>0.2059902588160747</v>
       </c>
       <c r="W12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.01834133571932323</v>
+        <v>0.2059902588160747</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.463089200731846</v>
+        <v>0.4944813074094251</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
@@ -1657,29 +1657,29 @@
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>4.447478650125228</v>
+        <v>4.581872658033169</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.447478650125228</v>
+        <v>4.581872658033169</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45584.41666666666</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1699,56 +1699,56 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.9</v>
+        <v>5.5</v>
       </c>
       <c r="J13" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="K13" t="n">
-        <v>2.4</v>
+        <v>1.57</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3210702341137124</v>
+        <v>0.1691062748563853</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2909698996655518</v>
+        <v>0.2384832081307998</v>
       </c>
       <c r="N13" t="n">
-        <v>0.3879598662207357</v>
+        <v>0.5924105170128148</v>
       </c>
       <c r="O13" t="n">
-        <v>0.07399425287356332</v>
+        <v>0.07517111338767402</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.483526184929107</v>
+        <v>0.5070788369417855</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3310842080653153</v>
+        <v>0.3135282387804085</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1853896070055777</v>
+        <v>0.1793929242778057</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1925562852635552</v>
+        <v>0.2685956288109856</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1925562852635552</v>
+        <v>0.2685956288109856</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.483526184929107</v>
+        <v>0.5070788369417855</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.2</v>
+        <v>3.9</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1756,10 +1756,208 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>4.83526184929107</v>
+        <v>4.698601592490737</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.83526184929107</v>
+        <v>4.698601592490737</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>GMBD7YY8</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45585.54166666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>77</v>
+      </c>
+      <c r="F14" t="n">
+        <v>771</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.3355537052456287</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.3030807660283097</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3613655287260616</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06433888691953205</v>
+      </c>
+      <c r="P14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.4105293093793976</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.4358061249405536</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.1536645656800489</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.1002524196949249</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.1002524196949249</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.4358061249405536</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>4.038187365523959</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>4.038187365523959</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>0lpzB7u1</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45585.65625</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>77</v>
+      </c>
+      <c r="F15" t="n">
+        <v>771</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.2266614763960649</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2655177294925331</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.5078207941114021</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.07606481217036976</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.4672624578399334</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3457214341121675</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.1870161080478991</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.2017447283474003</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.2017447283474003</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.4672624578399334</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>4.329662310024379</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>4.329662310024379</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC15"/>
+  <dimension ref="A1:AD24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,14 +510,14 @@
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
+          <t>prob_class_1</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
           <t>prob_class_0</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>prob_class_1</t>
-        </is>
-      </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>prob_class_2</t>
@@ -565,10 +565,15 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>multiplier</t>
+          <t>stake_to_bet_raw</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>stake_to_bet_norm</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>stake_to_bet</t>
         </is>
@@ -577,20 +582,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>x8OGzlAO</t>
+          <t>Cl5M5C3L</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45571.3125</v>
+        <v>45584.41666666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>como</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -610,86 +615,89 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.38</v>
+        <v>1.91</v>
       </c>
       <c r="J2" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="K2" t="n">
-        <v>8</v>
+        <v>3.8</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6903693476009666</v>
+        <v>0.491838642410297</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1905419399378667</v>
+        <v>0.2609477241676854</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1190887124611667</v>
+        <v>0.2472136334220177</v>
       </c>
       <c r="O2" t="n">
-        <v>0.04963768115942035</v>
+        <v>0.06449588193870359</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.4643301129039018</v>
+        <v>0.3707099854946136</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4456248333799684</v>
+        <v>0.3809841573238373</v>
       </c>
       <c r="S2" t="n">
-        <v>0.09004505371612988</v>
+        <v>0.2483058571815491</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2737881729660351</v>
+        <v>0.1200364331561519</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.2737881729660351</v>
+        <v>0.1200364331561519</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4643301129039018</v>
+        <v>0.3809841573238373</v>
       </c>
       <c r="Z2" t="n">
-        <v>5</v>
+        <v>3.6</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>4.302491149284828</v>
+        <v>14.29011409099286</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.302491149284828</v>
+        <v>0.2858022818198571</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>4.421678553541527</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>dzYLoEIP</t>
+          <t>EXLhbUee</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45584.41666666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>bologna</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>parma</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -709,86 +717,89 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>1.83</v>
+        <v>3.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="K3" t="n">
-        <v>4.33</v>
+        <v>2.35</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5215865398702301</v>
+        <v>0.3041456016177958</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2579738832331138</v>
+        <v>0.2946410515672397</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2204395768966561</v>
+        <v>0.4012133468149647</v>
       </c>
       <c r="O3" t="n">
-        <v>0.04766523991905425</v>
+        <v>0.06061256005490723</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.4029705325841423</v>
+        <v>0.2415841668844223</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4567827165677181</v>
+        <v>0.4831582605838776</v>
       </c>
       <c r="S3" t="n">
-        <v>0.1402467508481397</v>
+        <v>0.2752576172351837</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.064803823302512</v>
+        <v>0.1885172090166379</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.064803823302512</v>
+        <v>0.1885172090166379</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4567827165677181</v>
+        <v>0.4831582605838776</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.83</v>
+        <v>3.2</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>3.632083451217061</v>
+        <v>24.82301972129128</v>
       </c>
       <c r="AC3" t="n">
-        <v>3.632083451217061</v>
+        <v>0.4964603944258257</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>4.813990811434202</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>SW3Qfiet</t>
+          <t>SznSCTAl</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45571.41666666666</v>
+        <v>45584.54166666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -808,86 +819,89 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6045340050377834</v>
+        <v>0.676056338028169</v>
       </c>
       <c r="M4" t="n">
-        <v>0.23727959697733</v>
+        <v>0.2073239436619718</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1581863979848867</v>
+        <v>0.1166197183098591</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05360934182590227</v>
+        <v>0.07185990338164272</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4934002569841841</v>
+        <v>0.6114410161972046</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4066116629530556</v>
+        <v>0.1967238336801529</v>
       </c>
       <c r="S4" t="n">
-        <v>0.09998808006276047</v>
+        <v>0.1918351799249649</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.2561206600068541</v>
+        <v>-0.06461532183096441</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2561206600068541</v>
+        <v>-0.06461532183096441</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4934002569841841</v>
+        <v>0.6114410161972046</v>
       </c>
       <c r="Z4" t="n">
-        <v>4</v>
+        <v>1.38</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>4.571855625415056</v>
+        <v>-41.10826253890993</v>
       </c>
       <c r="AC4" t="n">
-        <v>4.571855625415056</v>
+        <v>-0.8221652507781987</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>2.364330063299158</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lnhZhVPh</t>
+          <t>2g2mKBIE</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45571.54166666666</v>
+        <v>45584.65625</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -907,86 +921,89 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>4.1</v>
+        <v>2</v>
       </c>
       <c r="J5" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K5" t="n">
-        <v>1.91</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2297541128604281</v>
+        <v>0.4713975380159305</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2770564302140457</v>
+        <v>0.3041274438812455</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4931894569255263</v>
+        <v>0.224475018102824</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06158029550729749</v>
+        <v>0.0606758832565284</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4887359728070411</v>
+        <v>0.4005041122436523</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3255577443522703</v>
+        <v>0.3911901116371155</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1857062828406884</v>
+        <v>0.2083057314157486</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.2116795425929954</v>
+        <v>-0.07089342577227814</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.2116795425929954</v>
+        <v>-0.07089342577227814</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4887359728070411</v>
+        <v>0.4005041122436523</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>4.528636284622356</v>
+        <v>-19.89917755126953</v>
       </c>
       <c r="AC5" t="n">
-        <v>4.528636284622356</v>
+        <v>-0.3979835510253906</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>3.11158646863163</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>SIOithtm</t>
+          <t>8Kjh0jRr</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45571.65625</v>
+        <v>45585.3125</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1006,86 +1023,89 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="L6" t="n">
-        <v>0.296097934200459</v>
+        <v>0.1705075845974329</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2631981637337414</v>
+        <v>0.2679404900816802</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4407039020657995</v>
+        <v>0.5615519253208868</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05539405684754528</v>
+        <v>0.06633486274204836</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4864114727927307</v>
+        <v>0.197742834687233</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3336638005531591</v>
+        <v>0.3996880054473877</v>
       </c>
       <c r="S6" t="n">
-        <v>0.17992472665411</v>
+        <v>0.4025692045688629</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2232133090589893</v>
+        <v>-0.1589827207520239</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>0.2232133090589893</v>
+        <v>-0.1589827207520239</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4864114727927307</v>
+        <v>0.4025692045688629</v>
       </c>
       <c r="Z6" t="n">
-        <v>3.6</v>
+        <v>1.67</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>4.507097425823092</v>
+        <v>-48.91185498059687</v>
       </c>
       <c r="AC6" t="n">
-        <v>4.507097425823092</v>
+        <v>-0.9782370996119374</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>2.116032311931075</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Cl5M5C3L</t>
+          <t>AJ5eIkmR</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45584.41666666666</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1105,86 +1125,89 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.95</v>
+        <v>3</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
-        <v>3.75</v>
+        <v>2.35</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4814305364511692</v>
+        <v>0.3125319693094629</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2682255845942228</v>
+        <v>0.2884910485933505</v>
       </c>
       <c r="N7" t="n">
-        <v>0.250343878954608</v>
+        <v>0.3989769820971867</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06520146520146519</v>
+        <v>0.06655755591925794</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.4225339281016023</v>
+        <v>0.2050438672304153</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4748572347263693</v>
+        <v>0.3989062011241913</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1026088371720284</v>
+        <v>0.396049976348877</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.006573301724799974</v>
+        <v>0.1104151525308408</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.006573301724799974</v>
+        <v>0.1104151525308408</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4748572347263693</v>
+        <v>0.3989062011241913</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>4.33912731718204</v>
+        <v>13.17534016238319</v>
       </c>
       <c r="AC7" t="n">
-        <v>4.33912731718204</v>
+        <v>0.2635068032476637</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>4.379317847126009</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>EXLhbUee</t>
+          <t>dGwq9oAD</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45584.41666666666</v>
+        <v>45585.41666666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1204,86 +1227,89 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.9</v>
+        <v>5.25</v>
       </c>
       <c r="J8" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="K8" t="n">
-        <v>2.45</v>
+        <v>1.65</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3236326109391125</v>
+        <v>0.1797462911201892</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2932920536635707</v>
+        <v>0.2483336916792087</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3830753353973168</v>
+        <v>0.571920017200602</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06549085151301903</v>
+        <v>0.05969469127363869</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4934150520430539</v>
+        <v>0.2844262421131134</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3269035398215585</v>
+        <v>0.3307288587093353</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1796814081353877</v>
+        <v>0.3848448693752289</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2001229983794832</v>
+        <v>-0.1870751478253732</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>0.2001229983794832</v>
+        <v>-0.1870751478253732</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4934150520430539</v>
+        <v>0.3848448693752289</v>
       </c>
       <c r="Z8" t="n">
-        <v>3.2</v>
+        <v>1.65</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>4.571992716695745</v>
+        <v>-56.15476392782652</v>
       </c>
       <c r="AC8" t="n">
-        <v>4.571992716695745</v>
+        <v>-1.12309527855653</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1.900712209893403</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>SznSCTAl</t>
+          <t>GMBD7YY8</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45584.54166666666</v>
+        <v>45585.54166666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1303,86 +1329,89 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.38</v>
+        <v>2.8</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>8.5</v>
+        <v>2.6</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6807261078483717</v>
+        <v>0.3355537052456287</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2087560064068339</v>
+        <v>0.3030807660283097</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1105178857447944</v>
+        <v>0.3613655287260616</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06450696220517194</v>
+        <v>0.06433888691953205</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5188114147443916</v>
+        <v>0.2580694854259491</v>
       </c>
       <c r="R9" t="n">
-        <v>0.380670454550161</v>
+        <v>0.493230402469635</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1005181307054474</v>
+        <v>0.2487001568078995</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.3100554083375577</v>
+        <v>0.1901496364413253</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3100554083375577</v>
+        <v>0.1901496364413253</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.5188114147443916</v>
+        <v>0.493230402469635</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>4.807315868716142</v>
+        <v>25.19115465027946</v>
       </c>
       <c r="AC9" t="n">
-        <v>4.807315868716142</v>
+        <v>0.5038230930055891</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>4.827389785450539</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2g2mKBIE</t>
+          <t>0lpzB7u1</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45584.65625</v>
+        <v>45585.65625</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1402,86 +1431,89 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.8</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
       <c r="K10" t="n">
-        <v>4.75</v>
+        <v>1.9</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5196419691695674</v>
+        <v>0.2309829802014589</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2834410740924913</v>
+        <v>0.2705800625217089</v>
       </c>
       <c r="N10" t="n">
-        <v>0.1969169567379413</v>
+        <v>0.4984369572768322</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06911217437533224</v>
+        <v>0.05593251421236012</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4230778862300282</v>
+        <v>0.2348176240921021</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4755061707450107</v>
+        <v>0.3905291259288788</v>
       </c>
       <c r="S10" t="n">
-        <v>0.1014159430249609</v>
+        <v>0.3746532499790192</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>-0.04413579842455667</v>
+        <v>0.1199490634071699</v>
       </c>
       <c r="W10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.04413579842455667</v>
+        <v>0.1199490634071699</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4755061707450107</v>
+        <v>0.3905291259288788</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.8</v>
+        <v>3.5</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>3.997085602235251</v>
+        <v>14.67407763004303</v>
       </c>
       <c r="AC10" t="n">
-        <v>3.997085602235251</v>
+        <v>0.2934815526008606</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>4.436238437977979</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>McP0d8Q7</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45585.3125</v>
+        <v>45586.65625</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1501,86 +1533,89 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>5.5</v>
+        <v>2.25</v>
       </c>
       <c r="J11" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>1.67</v>
+        <v>3.5</v>
       </c>
       <c r="L11" t="n">
-        <v>0.171786153098837</v>
+        <v>0.4179104477611941</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2624510672343344</v>
+        <v>0.3134328358208956</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5657627796668286</v>
+        <v>0.2686567164179105</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05839835480554045</v>
+        <v>0.06349206349206327</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5139346781513106</v>
+        <v>0.2818354666233063</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3064001502974576</v>
+        <v>0.4845733940601349</v>
       </c>
       <c r="S11" t="n">
-        <v>0.1796651715512319</v>
+        <v>0.2335911393165588</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.2514836109169762</v>
+        <v>0.1711405582392393</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.2514836109169762</v>
+        <v>0.1711405582392393</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.5139346781513106</v>
+        <v>0.4845733940601349</v>
       </c>
       <c r="Z11" t="n">
-        <v>3.6</v>
+        <v>3</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>4.762127940029149</v>
+        <v>22.68600910902023</v>
       </c>
       <c r="AC11" t="n">
-        <v>4.762127940029149</v>
+        <v>0.4537201821804047</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>4.735745385533121</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>AJ5eIkmR</t>
+          <t>I5fXHFho</t>
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45590.5625</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1600,86 +1635,89 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>3</v>
+        <v>2.1</v>
       </c>
       <c r="J12" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>2.35</v>
+        <v>3.5</v>
       </c>
       <c r="L12" t="n">
-        <v>0.3125319693094629</v>
+        <v>0.4509283819628648</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2884910485933505</v>
+        <v>0.2785145888594165</v>
       </c>
       <c r="N12" t="n">
-        <v>0.3989769820971867</v>
+        <v>0.2705570291777188</v>
       </c>
       <c r="O12" t="n">
-        <v>0.06655755591925794</v>
+        <v>0.05602240896358524</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.4944813074094251</v>
+        <v>0.2727443277835846</v>
       </c>
       <c r="R12" t="n">
-        <v>0.3301614250938594</v>
+        <v>0.5135457515716553</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1753572674967152</v>
+        <v>0.2137099206447601</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2059902588160747</v>
+        <v>0.2350311627122388</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.2059902588160747</v>
+        <v>0.2350311627122388</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.4944813074094251</v>
+        <v>0.5135457515716553</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>4.581872658033169</v>
+        <v>31.08564813931783</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.581872658033169</v>
+        <v>0.6217129627863566</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>5.038423912602905</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>dGwq9oAD</t>
+          <t>bLD0NyVN</t>
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45590.65625</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1699,86 +1737,89 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>5.5</v>
+        <v>2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="K13" t="n">
-        <v>1.57</v>
+        <v>3.75</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1691062748563853</v>
+        <v>0.4713493530499075</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2384832081307998</v>
+        <v>0.2772643253234751</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5924105170128148</v>
+        <v>0.2513863216266174</v>
       </c>
       <c r="O13" t="n">
-        <v>0.07517111338767402</v>
+        <v>0.0607843137254902</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5070788369417855</v>
+        <v>0.3790987432003021</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3135282387804085</v>
+        <v>0.4228127300739288</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1793929242778057</v>
+        <v>0.1980884820222855</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2685956288109856</v>
+        <v>0.1455484047504538</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.2685956288109856</v>
+        <v>0.1455484047504538</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.5070788369417855</v>
+        <v>0.4228127300739288</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>4.698601592490737</v>
+        <v>18.23180342713992</v>
       </c>
       <c r="AC13" t="n">
-        <v>4.698601592490737</v>
+        <v>0.3646360685427983</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4.570320891610544</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>GMBD7YY8</t>
+          <t>UuMqRJVb</t>
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>45585.54166666666</v>
+        <v>45591.41666666666</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1798,86 +1839,89 @@
         </is>
       </c>
       <c r="I14" t="n">
-        <v>2.8</v>
+        <v>1.36</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>4.75</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6</v>
+        <v>9</v>
       </c>
       <c r="L14" t="n">
-        <v>0.3355537052456287</v>
+        <v>0.6956875508543532</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3030807660283097</v>
+        <v>0.199186330349878</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3613655287260616</v>
+        <v>0.1051261187957689</v>
       </c>
       <c r="O14" t="n">
-        <v>0.06433888691953205</v>
+        <v>0.05693154454764349</v>
       </c>
       <c r="P14" t="n">
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.4105293093793976</v>
+        <v>0.5880753993988037</v>
       </c>
       <c r="R14" t="n">
-        <v>0.4358061249405536</v>
+        <v>0.2146428823471069</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1536645656800489</v>
+        <v>0.1972817182540894</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1002524196949249</v>
+        <v>-0.1076121514555495</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>0.1002524196949249</v>
+        <v>-0.1076121514555495</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.4358061249405536</v>
+        <v>0.5880753993988037</v>
       </c>
       <c r="Z14" t="n">
-        <v>2.8</v>
+        <v>1.36</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>4.038187365523959</v>
+        <v>-55.61596022711856</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.038187365523959</v>
+        <v>-1.112319204542371</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.91620968213335</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0lpzB7u1</t>
+          <t>8f71RSPs</t>
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>45585.65625</v>
+        <v>45591.54166666666</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1897,68 +1941,911 @@
         </is>
       </c>
       <c r="I15" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K15" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2266614763960649</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2655177294925331</v>
+        <v>0.2631578947368421</v>
       </c>
       <c r="N15" t="n">
-        <v>0.5078207941114021</v>
+        <v>0.4736842105263158</v>
       </c>
       <c r="O15" t="n">
-        <v>0.07606481217036976</v>
+        <v>0.05555555555555558</v>
       </c>
       <c r="P15" t="n">
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.4672624578399334</v>
+        <v>0.2532491683959961</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3457214341121675</v>
+        <v>0.4272058010101318</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1870161080478991</v>
+        <v>0.3195449709892273</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2017447283474003</v>
+        <v>0.1640479062732897</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.2017447283474003</v>
+        <v>0.1640479062732897</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.4672624578399334</v>
+        <v>0.4272058010101318</v>
       </c>
       <c r="Z15" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>20.69003398601826</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.4138006797203652</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4.661985844183937</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>OMVUWl2K</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45591.65625</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>77</v>
+      </c>
+      <c r="F16" t="n">
+        <v>771</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="J16" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="K16" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.6590750422132745</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2161400831276789</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.1247848746590466</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06850556766309945</v>
+      </c>
+      <c r="P16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.5402875542640686</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.2680294513702393</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.1916830092668533</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>-0.1187874879492059</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1</v>
+      </c>
+      <c r="X16" t="n">
+        <v>-0.1187874879492059</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.5402875542640686</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>-55.42658879643396</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>-1.108531775928679</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1.92167662372342</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>jeAhPc0B</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45592.35416666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>77</v>
+      </c>
+      <c r="F17" t="n">
+        <v>771</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>2</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="K17" t="n">
+        <v>4</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.4727272727272727</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2909090909090909</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.2363636363636364</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.05769230769230771</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.4993608295917511</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.3011950552463531</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.1994441449642181</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.02663355686447838</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.02663355686447838</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.4993608295917511</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>-0.1278340816497803</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-0.002556681632995605</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>3.86713875579124</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>OjcQLOgJ</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>77</v>
+      </c>
+      <c r="F18" t="n">
+        <v>771</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.5958549222797929</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2383419689119171</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.1658031088082902</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.04891304347826075</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.5561535358428955</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.2530986368656158</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.1907478421926498</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-0.03970138643689736</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.03970138643689736</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.5561535358428955</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>-18.35905710856118</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.3671811421712236</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>3.16909025635755</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xY3xTu1n</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>77</v>
+      </c>
+      <c r="F19" t="n">
+        <v>771</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.4192972007147112</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2948183442525313</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.2858844550327576</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.0599747474747474</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.3966474533081055</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.4159072637557983</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.1874452829360962</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>0.1210889195032671</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.1210889195032671</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.4159072637557983</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>15.04105654629794</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.3008211309259589</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>4.450139054942939</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>jwaINpP6</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45592.58333333334</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>77</v>
+      </c>
+      <c r="F20" t="n">
+        <v>771</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="J20" t="n">
         <v>3.5</v>
       </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.5</t>
-        </is>
-      </c>
-      <c r="AB15" t="n">
-        <v>4.329662310024379</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>4.329662310024379</v>
-      </c>
+      <c r="K20" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.5615519253208868</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2679404900816802</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.1705075845974329</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.06633486274204836</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.5426689982414246</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.2397459447383881</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.2175850570201874</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>-0.01888292707946226</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>-0.01888292707946226</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.5426689982414246</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>-13.99145864728673</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>-0.2798291729457345</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>3.33383465403003</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>fB59P6ff</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45592.69791666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>77</v>
+      </c>
+      <c r="F21" t="n">
+        <v>771</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.3820549927641099</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2836468885672938</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.3342981186685962</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.06833642547928265</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.3564672470092773</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.391137421131134</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2523953020572662</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.1074905325638403</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.1074905325638403</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.391137421131134</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>12.64145607533662</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.2528291215067324</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4.358986096114766</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Ug79dz7j</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45594.60416666666</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>77</v>
+      </c>
+      <c r="F22" t="n">
+        <v>771</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.2392067015171051</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.4226315915584564</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.3381616771221161</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="n">
+        <v>0.5773684084415436</v>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>4CLi9Djd</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45594.60416666666</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>77</v>
+      </c>
+      <c r="F23" t="n">
+        <v>771</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.3399296402931213</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.454637885093689</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.2054324597120285</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="n">
+        <v>0.545362114906311</v>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>WIDwXGr3</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45594.69791666666</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>77</v>
+      </c>
+      <c r="F24" t="n">
+        <v>771</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.3984679281711578</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.4165040552616119</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.1850280165672302</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="n">
+        <v>0.5834959447383881</v>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD24"/>
+  <dimension ref="A1:AD29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -717,56 +717,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3041456016177958</v>
+        <v>0.2606635071090047</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2946410515672397</v>
+        <v>0.3127962085308056</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4012133468149647</v>
+        <v>0.4265402843601895</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06061256005490723</v>
+        <v>0.06565656565656575</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2415841668844223</v>
+        <v>0.2407787889242172</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4831582605838776</v>
+        <v>0.4815475344657898</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2752576172351837</v>
+        <v>0.277673751115799</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1885172090166379</v>
+        <v>0.1687513259349842</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1885172090166379</v>
+        <v>0.1687513259349842</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4831582605838776</v>
+        <v>0.4815475344657898</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -774,13 +774,13 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>24.82301972129128</v>
+        <v>22.23213016986847</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.4964603944258257</v>
+        <v>0.4446426033973694</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.813990811434202</v>
+        <v>4.719028315433033</v>
       </c>
     </row>
     <row r="4">
@@ -843,29 +843,29 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6114410161972046</v>
+        <v>0.6118006706237793</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1967238336801529</v>
+        <v>0.1970229148864746</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1918351799249649</v>
+        <v>0.1911764591932297</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.06461532183096441</v>
+        <v>-0.0642556674043897</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.06461532183096441</v>
+        <v>-0.0642556674043897</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6114410161972046</v>
+        <v>0.6118006706237793</v>
       </c>
       <c r="Z4" t="n">
         <v>1.38</v>
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>-41.10826253890993</v>
+        <v>-40.97765119452228</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.8221652507781987</v>
+        <v>-0.8195530238904456</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.364330063299158</v>
+        <v>2.368622800881497</v>
       </c>
     </row>
     <row r="5">
@@ -921,56 +921,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>3.75</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4713975380159305</v>
+        <v>0.4592557701365992</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3041274438812455</v>
+        <v>0.2896844088553933</v>
       </c>
       <c r="N5" t="n">
-        <v>0.224475018102824</v>
+        <v>0.2510598210080076</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0606758832565284</v>
+        <v>0.06216385240775479</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4005041122436523</v>
+        <v>0.3887141346931458</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3911901116371155</v>
+        <v>0.4021904170513153</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2083057314157486</v>
+        <v>0.2090954631567001</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.07089342577227814</v>
+        <v>0.112506008195922</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.07089342577227814</v>
+        <v>0.112506008195922</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4005041122436523</v>
+        <v>0.4021904170513153</v>
       </c>
       <c r="Z5" t="n">
-        <v>2</v>
+        <v>3.25</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-19.89917755126953</v>
+        <v>13.64972690741221</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.3979835510253906</v>
+        <v>0.2729945381482443</v>
       </c>
       <c r="AD5" t="n">
-        <v>3.11158646863163</v>
+        <v>4.397359967987123</v>
       </c>
     </row>
     <row r="6">
@@ -1029,50 +1029,50 @@
         <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1705075845974329</v>
+        <v>0.1693548387096774</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2679404900816802</v>
+        <v>0.2661290322580645</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5615519253208868</v>
+        <v>0.564516129032258</v>
       </c>
       <c r="O6" t="n">
-        <v>0.06633486274204836</v>
+        <v>0.07359307359307365</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.197742834687233</v>
+        <v>0.1967838853597641</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3996880054473877</v>
+        <v>0.3952086269855499</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4025692045688629</v>
+        <v>0.4080075025558472</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.1589827207520239</v>
+        <v>-0.1565086264764108</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1589827207520239</v>
+        <v>-0.1565086264764108</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4025692045688629</v>
+        <v>0.4080075025558472</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1080,13 +1080,13 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>-48.91185498059687</v>
+        <v>-50.27501858197727</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.9782370996119374</v>
+        <v>-1.005500371639545</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.116032311931075</v>
+        <v>2.074365822863361</v>
       </c>
     </row>
     <row r="7">
@@ -1149,29 +1149,29 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2050438672304153</v>
+        <v>0.2051650583744049</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3989062011241913</v>
+        <v>0.4007787704467773</v>
       </c>
       <c r="S7" t="n">
-        <v>0.396049976348877</v>
+        <v>0.3940562009811401</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1104151525308408</v>
+        <v>0.1122877218534269</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1104151525308408</v>
+        <v>0.1122877218534269</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.3989062011241913</v>
+        <v>0.4007787704467773</v>
       </c>
       <c r="Z7" t="n">
         <v>3.25</v>
@@ -1182,13 +1182,13 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>13.17534016238319</v>
+        <v>13.44582239786784</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.2635068032476637</v>
+        <v>0.2689164479573568</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.379317847126009</v>
+        <v>4.389607765574908</v>
       </c>
     </row>
     <row r="8">
@@ -1251,29 +1251,29 @@
         <v>2</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2844262421131134</v>
+        <v>0.2839991748332977</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3307288587093353</v>
+        <v>0.3246980309486389</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3848448693752289</v>
+        <v>0.391302764415741</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.1870751478253732</v>
+        <v>-0.1806172527848611</v>
       </c>
       <c r="W8" t="n">
         <v>2</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1870751478253732</v>
+        <v>-0.1806172527848611</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3848448693752289</v>
+        <v>0.391302764415741</v>
       </c>
       <c r="Z8" t="n">
         <v>1.65</v>
@@ -1284,13 +1284,13 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>-56.15476392782652</v>
+        <v>-54.51545210985038</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.12309527855653</v>
+        <v>-1.090309042197008</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.900712209893403</v>
+        <v>1.948125900469534</v>
       </c>
     </row>
     <row r="9">
@@ -1329,53 +1329,53 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.8</v>
+        <v>2.75</v>
       </c>
       <c r="J9" t="n">
         <v>3.1</v>
       </c>
       <c r="K9" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3355537052456287</v>
+        <v>0.3409799042261768</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3030807660283097</v>
+        <v>0.3024821731038665</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3613655287260616</v>
+        <v>0.3565379226699568</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06433888691953205</v>
+        <v>0.06644514567978321</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2580694854259491</v>
+        <v>0.2547066509723663</v>
       </c>
       <c r="R9" t="n">
-        <v>0.493230402469635</v>
+        <v>0.4998339414596558</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2487001568078995</v>
+        <v>0.2454594075679779</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1901496364413253</v>
+        <v>0.1973517683557893</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1901496364413253</v>
+        <v>0.1973517683557893</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.493230402469635</v>
+        <v>0.4998339414596558</v>
       </c>
       <c r="Z9" t="n">
         <v>3.1</v>
@@ -1386,13 +1386,13 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>25.19115465027946</v>
+        <v>26.16596278690156</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.5038230930055891</v>
+        <v>0.5233192557380313</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.827389785450539</v>
+        <v>4.862751560675377</v>
       </c>
     </row>
     <row r="10">
@@ -1431,56 +1431,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J10" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="K10" t="n">
-        <v>1.9</v>
+        <v>1.83</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2309829802014589</v>
+        <v>0.2264963612060003</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2705800625217089</v>
+        <v>0.2536759245507204</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4984369572768322</v>
+        <v>0.5198277142432793</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05593251421236012</v>
+        <v>0.05120999219359867</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2348176240921021</v>
+        <v>0.2347460687160492</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3905291259288788</v>
+        <v>0.3904101252555847</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3746532499790192</v>
+        <v>0.3748438358306885</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1199490634071699</v>
+        <v>0.1367342007048644</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1199490634071699</v>
+        <v>0.1367342007048644</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3905291259288788</v>
+        <v>0.3904101252555847</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.5</v>
+        <v>3.75</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1488,13 +1488,13 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>14.67407763004303</v>
+        <v>16.87410798939792</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.2934815526008606</v>
+        <v>0.3374821597879583</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.436238437977979</v>
+        <v>4.519337485526357</v>
       </c>
     </row>
     <row r="11">
@@ -1557,29 +1557,29 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2818354666233063</v>
+        <v>0.2750804722309113</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4845733940601349</v>
+        <v>0.4914714097976685</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2335911393165588</v>
+        <v>0.2334481477737427</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1711405582392393</v>
+        <v>0.1780385739767729</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1711405582392393</v>
+        <v>0.1780385739767729</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4845733940601349</v>
+        <v>0.4914714097976685</v>
       </c>
       <c r="Z11" t="n">
         <v>3</v>
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>22.68600910902023</v>
+        <v>23.72071146965027</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.4537201821804047</v>
+        <v>0.4744142293930054</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.735745385533121</v>
+        <v>4.773727756281637</v>
       </c>
     </row>
     <row r="12">
@@ -1737,25 +1737,25 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K13" t="n">
-        <v>3.75</v>
+        <v>3.5</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4713493530499075</v>
+        <v>0.4471544715447154</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2772643253234751</v>
+        <v>0.2845528455284553</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2513863216266174</v>
+        <v>0.2682926829268292</v>
       </c>
       <c r="O13" t="n">
-        <v>0.0607843137254902</v>
+        <v>0.06493506493506507</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1774,19 +1774,19 @@
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1455484047504538</v>
+        <v>0.1382598845454736</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1455484047504538</v>
+        <v>0.1382598845454736</v>
       </c>
       <c r="Y13" t="n">
         <v>0.4228127300739288</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
@@ -1794,13 +1794,13 @@
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>18.23180342713992</v>
+        <v>17.186174314955</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.3646360685427983</v>
+        <v>0.3437234862991001</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.570320891610544</v>
+        <v>4.531077175621822</v>
       </c>
     </row>
     <row r="14">
@@ -2169,29 +2169,29 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4993608295917511</v>
+        <v>0.4984340965747833</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3011950552463531</v>
+        <v>0.3016817271709442</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1994441449642181</v>
+        <v>0.1998841911554337</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.02663355686447838</v>
+        <v>0.02570682384751061</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>0.02663355686447838</v>
+        <v>0.02570682384751061</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.4993608295917511</v>
+        <v>0.4984340965747833</v>
       </c>
       <c r="Z17" t="n">
         <v>2</v>
@@ -2202,13 +2202,13 @@
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>-0.1278340816497803</v>
+        <v>-0.313180685043335</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.002556681632995605</v>
+        <v>-0.006263613700866699</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.86713875579124</v>
+        <v>3.859962008037489</v>
       </c>
     </row>
     <row r="18">
@@ -2253,47 +2253,47 @@
         <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>5.75</v>
+        <v>5.5</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5958549222797929</v>
+        <v>0.5913978494623655</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2383419689119171</v>
+        <v>0.2365591397849462</v>
       </c>
       <c r="N18" t="n">
-        <v>0.1658031088082902</v>
+        <v>0.1720430107526882</v>
       </c>
       <c r="O18" t="n">
-        <v>0.04891304347826075</v>
+        <v>0.05681818181818188</v>
       </c>
       <c r="P18" t="n">
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5561535358428955</v>
+        <v>0.5579578280448914</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2530986368656158</v>
+        <v>0.2512670159339905</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1907478421926498</v>
+        <v>0.1907751858234406</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>-0.03970138643689736</v>
+        <v>-0.03344002141747415</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.03970138643689736</v>
+        <v>-0.03344002141747415</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.5561535358428955</v>
+        <v>0.5579578280448914</v>
       </c>
       <c r="Z18" t="n">
         <v>1.6</v>
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>-18.35905710856118</v>
+        <v>-17.87791252136229</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.3671811421712236</v>
+        <v>-0.3575582504272459</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.16909025635755</v>
+        <v>3.187122113791959</v>
       </c>
     </row>
     <row r="19">
@@ -2373,29 +2373,29 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.3966474533081055</v>
+        <v>0.3982662856578827</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4159072637557983</v>
+        <v>0.4135233759880066</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1874452829360962</v>
+        <v>0.1882103085517883</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1210889195032671</v>
+        <v>0.1187050317354753</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1210889195032671</v>
+        <v>0.1187050317354753</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.4159072637557983</v>
+        <v>0.4135233759880066</v>
       </c>
       <c r="Z19" t="n">
         <v>3.2</v>
@@ -2406,13 +2406,13 @@
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>15.04105654629794</v>
+        <v>14.69430923461914</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.3008211309259589</v>
+        <v>0.2938861846923828</v>
       </c>
       <c r="AD19" t="n">
-        <v>4.450139054942939</v>
+        <v>4.437005171721267</v>
       </c>
     </row>
     <row r="20">
@@ -2577,29 +2577,29 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.3564672470092773</v>
+        <v>0.355811208486557</v>
       </c>
       <c r="R21" t="n">
-        <v>0.391137421131134</v>
+        <v>0.3904175758361816</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2523953020572662</v>
+        <v>0.2537712454795837</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1074905325638403</v>
+        <v>0.1067706872688879</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.1074905325638403</v>
+        <v>0.1067706872688879</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.391137421131134</v>
+        <v>0.3904175758361816</v>
       </c>
       <c r="Z21" t="n">
         <v>3.3</v>
@@ -2610,13 +2610,13 @@
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>12.64145607533662</v>
+        <v>12.53817392432171</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.2528291215067324</v>
+        <v>0.2507634784864342</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.358986096114766</v>
+        <v>4.355049644522281</v>
       </c>
     </row>
     <row r="22">
@@ -2817,13 +2817,13 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.3984679281711578</v>
+        <v>0.3932410478591919</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4165040552616119</v>
+        <v>0.4201231896877289</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1850280165672302</v>
+        <v>0.1866357922554016</v>
       </c>
       <c r="T24" t="n">
         <v>1</v>
@@ -2835,7 +2835,7 @@
       </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="n">
-        <v>0.5834959447383881</v>
+        <v>0.5798768103122711</v>
       </c>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
@@ -2846,6 +2846,386 @@
       <c r="AB24" t="inlineStr"/>
       <c r="AC24" t="inlineStr"/>
       <c r="AD24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45595.60416666666</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>77</v>
+      </c>
+      <c r="F25" t="n">
+        <v>771</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.2193145006895065</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.3615515828132629</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.4191339612007141</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="n">
+        <v>0.5808660387992859</v>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45595.60416666666</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>77</v>
+      </c>
+      <c r="F26" t="n">
+        <v>771</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.4081339836120605</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.3379647433757782</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.2539012432098389</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="n">
+        <v>0.5918660163879395</v>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45595.69791666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>77</v>
+      </c>
+      <c r="F27" t="n">
+        <v>771</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.4542271494865417</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.3409821391105652</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.2047907114028931</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="n">
+        <v>0.5457728505134583</v>
+      </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45595.69791666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>77</v>
+      </c>
+      <c r="F28" t="n">
+        <v>771</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.5638784170150757</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.2269687056541443</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.2091528922319412</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="n">
+        <v>0.4361215829849243</v>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45596.60416666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>77</v>
+      </c>
+      <c r="F29" t="n">
+        <v>771</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.2376536726951599</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.4278645217418671</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.3344818353652954</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="n">
+        <v>0.5721354782581329</v>
+      </c>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD29"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -636,49 +636,49 @@
         <v>0.06449588193870359</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.3707099854946136</v>
+        <v>0.4555390179157257</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3809841573238373</v>
+        <v>0.3114481568336487</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2483058571815491</v>
+        <v>0.233012855052948</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1200364331561519</v>
+        <v>-0.0362996244945713</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1200364331561519</v>
+        <v>-0.0362996244945713</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.3809841573238373</v>
+        <v>0.4555390179157257</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.6</v>
+        <v>1.91</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>14.29011409099286</v>
+        <v>-14.27697536054549</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.2858022818198571</v>
+        <v>-0.2855395072109097</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.421678553541527</v>
+        <v>3.322997153937215</v>
       </c>
     </row>
     <row r="3">
@@ -717,70 +717,70 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2606635071090047</v>
+        <v>0.2478111914731633</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3127962085308056</v>
+        <v>0.303768557289684</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4265402843601895</v>
+        <v>0.4484202512371526</v>
       </c>
       <c r="O3" t="n">
-        <v>0.06565656565656575</v>
+        <v>0.06192901608860857</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2407787889242172</v>
+        <v>0.229819729924202</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4815475344657898</v>
+        <v>0.419565886259079</v>
       </c>
       <c r="S3" t="n">
-        <v>0.277673751115799</v>
+        <v>0.3506143987178802</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1687513259349842</v>
+        <v>0.1157973289693949</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1687513259349842</v>
+        <v>0.1157973289693949</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4815475344657898</v>
+        <v>0.419565886259079</v>
       </c>
       <c r="Z3" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>22.23213016986847</v>
+        <v>14.31686892395928</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.4446426033973694</v>
+        <v>0.2863373784791856</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.719028315433033</v>
+        <v>4.422693615227984</v>
       </c>
     </row>
     <row r="4">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="J4" t="n">
         <v>4.5</v>
@@ -828,61 +828,61 @@
         <v>8</v>
       </c>
       <c r="L4" t="n">
-        <v>0.676056338028169</v>
+        <v>0.6728971962616822</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2073239436619718</v>
+        <v>0.2093457943925233</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1166197183098591</v>
+        <v>0.1177570093457944</v>
       </c>
       <c r="O4" t="n">
-        <v>0.07185990338164272</v>
+        <v>0.06150793650793651</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6118006706237793</v>
+        <v>0.5407603979110718</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1970229148864746</v>
+        <v>0.2689046859741211</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1911764591932297</v>
+        <v>0.1903348863124847</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.0642556674043897</v>
+        <v>-0.1321367983506104</v>
       </c>
       <c r="W4" t="n">
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.0642556674043897</v>
+        <v>-0.1321367983506104</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.6118006706237793</v>
+        <v>0.5407603979110718</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>-40.97765119452228</v>
+        <v>-60.7338607311249</v>
       </c>
       <c r="AC4" t="n">
-        <v>-0.8195530238904456</v>
+        <v>-1.214677214622498</v>
       </c>
       <c r="AD4" t="n">
-        <v>2.368622800881497</v>
+        <v>1.772444826141101</v>
       </c>
     </row>
     <row r="5">
@@ -927,64 +927,64 @@
         <v>3.25</v>
       </c>
       <c r="K5" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4592557701365992</v>
+        <v>0.4607779125081616</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2896844088553933</v>
+        <v>0.290644529428225</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2510598210080076</v>
+        <v>0.2485775580636135</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06216385240775479</v>
+        <v>0.05865508047793022</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.3887141346931458</v>
+        <v>0.4482164680957794</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4021904170513153</v>
+        <v>0.3220472037792206</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2090954631567001</v>
+        <v>0.2297362983226776</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.112506008195922</v>
+        <v>-0.01256144441238222</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>0.112506008195922</v>
+        <v>-0.01256144441238222</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4021904170513153</v>
+        <v>0.4482164680957794</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>13.64972690741221</v>
+        <v>-7.729165752728784</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.2729945381482443</v>
+        <v>-0.1545833150545757</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.397359967987123</v>
+        <v>3.573403001735672</v>
       </c>
     </row>
     <row r="6">
@@ -1023,70 +1023,70 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>5.5</v>
+        <v>5.75</v>
       </c>
       <c r="J6" t="n">
         <v>3.5</v>
       </c>
       <c r="K6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1693548387096774</v>
+        <v>0.1643123199100429</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2661290322580645</v>
+        <v>0.2699416684236418</v>
       </c>
       <c r="N6" t="n">
-        <v>0.564516129032258</v>
+        <v>0.5657460116663153</v>
       </c>
       <c r="O6" t="n">
-        <v>0.07359307359307365</v>
+        <v>0.05842972440212746</v>
       </c>
       <c r="P6" t="n">
         <v>2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1967838853597641</v>
+        <v>0.2226104885339737</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3952086269855499</v>
+        <v>0.3797981739044189</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4080075025558472</v>
+        <v>0.3975913524627686</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.1565086264764108</v>
+        <v>-0.1681546592035468</v>
       </c>
       <c r="W6" t="n">
         <v>2</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1565086264764108</v>
+        <v>-0.1681546592035468</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4080075025558472</v>
+        <v>0.3975913524627686</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>-50.27501858197727</v>
+        <v>-50.1526031921159</v>
       </c>
       <c r="AC6" t="n">
-        <v>-1.005500371639545</v>
+        <v>-1.003052063842318</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.074365822863361</v>
+        <v>2.078086237775435</v>
       </c>
     </row>
     <row r="7">
@@ -1149,46 +1149,46 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2051650583744049</v>
+        <v>0.2736625373363495</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4007787704467773</v>
+        <v>0.3879785537719727</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3940562009811401</v>
+        <v>0.3383588790893555</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1122877218534269</v>
+        <v>0.0994875051786222</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1122877218534269</v>
+        <v>0.0994875051786222</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4007787704467773</v>
+        <v>0.3879785537719727</v>
       </c>
       <c r="Z7" t="n">
         <v>3.25</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>13.44582239786784</v>
+        <v>11.59690221150716</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.2689164479573568</v>
+        <v>0.2319380442301432</v>
       </c>
       <c r="AD7" t="n">
-        <v>4.389607765574908</v>
+        <v>4.319128672295433</v>
       </c>
     </row>
     <row r="8">
@@ -1248,49 +1248,49 @@
         <v>0.05969469127363869</v>
       </c>
       <c r="P8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.2839991748332977</v>
+        <v>0.277310848236084</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3246980309486389</v>
+        <v>0.4322807788848877</v>
       </c>
       <c r="S8" t="n">
-        <v>0.391302764415741</v>
+        <v>0.2904083728790283</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.1806172527848611</v>
+        <v>0.183947087205679</v>
       </c>
       <c r="W8" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1806172527848611</v>
+        <v>0.183947087205679</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.391302764415741</v>
+        <v>0.4322807788848877</v>
       </c>
       <c r="Z8" t="n">
-        <v>1.65</v>
+        <v>3.8</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>-54.51545210985038</v>
+        <v>22.9523914200919</v>
       </c>
       <c r="AC8" t="n">
-        <v>-1.090309042197008</v>
+        <v>0.459047828401838</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.948125900469534</v>
+        <v>4.745540953559955</v>
       </c>
     </row>
     <row r="9">
@@ -1350,49 +1350,49 @@
         <v>0.06644514567978321</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2547066509723663</v>
+        <v>0.4131496548652649</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4998339414596558</v>
+        <v>0.3523286283016205</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2454594075679779</v>
+        <v>0.234521672129631</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1973517683557893</v>
+        <v>0.07216975063908809</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1973517683557893</v>
+        <v>0.07216975063908809</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4998339414596558</v>
+        <v>0.4131496548652649</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>26.16596278690156</v>
+        <v>7.780660050255911</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.5233192557380313</v>
+        <v>0.1556132010051182</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.862751560675377</v>
+        <v>4.172756163879149</v>
       </c>
     </row>
     <row r="10">
@@ -1437,64 +1437,64 @@
         <v>3.75</v>
       </c>
       <c r="K10" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2264963612060003</v>
+        <v>0.2245508982035928</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2536759245507204</v>
+        <v>0.2514970059880239</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5198277142432793</v>
+        <v>0.5239520958083832</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05120999219359867</v>
+        <v>0.06031746031746033</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2347460687160492</v>
+        <v>0.2289363145828247</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3904101252555847</v>
+        <v>0.3368021845817566</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3748438358306885</v>
+        <v>0.4342615604400635</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1367342007048644</v>
+        <v>-0.08969053536831972</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1367342007048644</v>
+        <v>-0.08969053536831972</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3904101252555847</v>
+        <v>0.4342615604400635</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.75</v>
+        <v>1.8</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>16.87410798939792</v>
+        <v>-27.29114890098572</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.3374821597879583</v>
+        <v>-0.5458229780197144</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.519337485526357</v>
+        <v>2.840827902245843</v>
       </c>
     </row>
     <row r="11">
@@ -1533,70 +1533,70 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="J11" t="n">
         <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4179104477611941</v>
+        <v>0.3976861894432394</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3134328358208956</v>
+        <v>0.3154977102916365</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2686567164179105</v>
+        <v>0.2868161002651242</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06349206349206327</v>
+        <v>0.05653170359052706</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.2750804722309113</v>
+        <v>0.3031558096408844</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4914714097976685</v>
+        <v>0.4847221970558167</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2334481477737427</v>
+        <v>0.2121219485998154</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1780385739767729</v>
+        <v>0.1692244867641801</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0.1780385739767729</v>
+        <v>0.1692244867641801</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4914714097976685</v>
+        <v>0.4847221970558167</v>
       </c>
       <c r="Z11" t="n">
         <v>3</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>23.72071146965027</v>
+        <v>22.7083295583725</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.4744142293930054</v>
+        <v>0.45416659116745</v>
       </c>
       <c r="AD11" t="n">
-        <v>4.773727756281637</v>
+        <v>4.736566615024762</v>
       </c>
     </row>
     <row r="12">
@@ -1635,70 +1635,70 @@
         </is>
       </c>
       <c r="I12" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="J12" t="n">
         <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4509283819628648</v>
+        <v>0.4603234298608499</v>
       </c>
       <c r="M12" t="n">
-        <v>0.2785145888594165</v>
+        <v>0.2775479503572771</v>
       </c>
       <c r="N12" t="n">
-        <v>0.2705570291777188</v>
+        <v>0.2621286197818729</v>
       </c>
       <c r="O12" t="n">
-        <v>0.05602240896358524</v>
+        <v>0.05970030288538197</v>
       </c>
       <c r="P12" t="n">
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.2727443277835846</v>
+        <v>0.3143502473831177</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5135457515716553</v>
+        <v>0.3924648463726044</v>
       </c>
       <c r="S12" t="n">
-        <v>0.2137099206447601</v>
+        <v>0.293184906244278</v>
       </c>
       <c r="T12" t="n">
         <v>1</v>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.2350311627122388</v>
+        <v>0.1149168960153272</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0.2350311627122388</v>
+        <v>0.1149168960153272</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.5135457515716553</v>
+        <v>0.3924648463726044</v>
       </c>
       <c r="Z12" t="n">
         <v>3.4</v>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB12" t="n">
-        <v>31.08564813931783</v>
+        <v>13.93251990278562</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.6217129627863566</v>
+        <v>0.2786503980557123</v>
       </c>
       <c r="AD12" t="n">
-        <v>5.038423912602905</v>
+        <v>4.408104305573904</v>
       </c>
     </row>
     <row r="13">
@@ -1737,70 +1737,70 @@
         </is>
       </c>
       <c r="I13" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="J13" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="K13" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L13" t="n">
-        <v>0.4471544715447154</v>
+        <v>0.4283464566929133</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2845528455284553</v>
+        <v>0.2944881889763779</v>
       </c>
       <c r="N13" t="n">
-        <v>0.2682926829268292</v>
+        <v>0.2771653543307087</v>
       </c>
       <c r="O13" t="n">
-        <v>0.06493506493506507</v>
+        <v>0.06116310160427818</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.3790987432003021</v>
+        <v>0.390830397605896</v>
       </c>
       <c r="R13" t="n">
-        <v>0.4228127300739288</v>
+        <v>0.3785349428653717</v>
       </c>
       <c r="S13" t="n">
-        <v>0.1980884820222855</v>
+        <v>0.2306346595287323</v>
       </c>
       <c r="T13" t="n">
         <v>1</v>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.1382598845454736</v>
+        <v>-0.03751605908701733</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X13" t="n">
-        <v>0.1382598845454736</v>
+        <v>-0.03751605908701733</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.4228127300739288</v>
+        <v>0.390830397605896</v>
       </c>
       <c r="Z13" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB13" t="n">
-        <v>17.186174314955</v>
+        <v>-11.68109377225239</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.3437234862991001</v>
+        <v>-0.2336218754450478</v>
       </c>
       <c r="AD13" t="n">
-        <v>4.531077175621822</v>
+        <v>3.421832325895922</v>
       </c>
     </row>
     <row r="14">
@@ -1863,46 +1863,46 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.5880753993988037</v>
+        <v>0.4581892788410187</v>
       </c>
       <c r="R14" t="n">
-        <v>0.2146428823471069</v>
+        <v>0.3139846622943878</v>
       </c>
       <c r="S14" t="n">
-        <v>0.1972817182540894</v>
+        <v>0.2278260737657547</v>
       </c>
       <c r="T14" t="n">
         <v>1</v>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>-0.1076121514555495</v>
+        <v>-0.2374982720133345</v>
       </c>
       <c r="W14" t="n">
         <v>1</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.1076121514555495</v>
+        <v>-0.2374982720133345</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.5880753993988037</v>
+        <v>0.4581892788410187</v>
       </c>
       <c r="Z14" t="n">
         <v>1.36</v>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB14" t="n">
-        <v>-55.61596022711856</v>
+        <v>-104.6840502156151</v>
       </c>
       <c r="AC14" t="n">
-        <v>-1.112319204542371</v>
+        <v>-2.093681004312303</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.91620968213335</v>
+        <v>0.849633141370759</v>
       </c>
     </row>
     <row r="15">
@@ -1962,49 +1962,49 @@
         <v>0.05555555555555558</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.2532491683959961</v>
+        <v>0.2810186743736267</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4272058010101318</v>
+        <v>0.3277459740638733</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3195449709892273</v>
+        <v>0.3912353515625</v>
       </c>
       <c r="T15" t="n">
         <v>1</v>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.1640479062732897</v>
+        <v>-0.08244885896381576</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X15" t="n">
-        <v>0.1640479062732897</v>
+        <v>-0.08244885896381576</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.4272058010101318</v>
+        <v>0.3912353515625</v>
       </c>
       <c r="Z15" t="n">
-        <v>3.6</v>
+        <v>2</v>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB15" t="n">
-        <v>20.69003398601826</v>
+        <v>-21.7529296875</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.4138006797203652</v>
+        <v>-0.43505859375</v>
       </c>
       <c r="AD15" t="n">
-        <v>4.661985844183937</v>
+        <v>3.042834635866988</v>
       </c>
     </row>
     <row r="16">
@@ -2067,46 +2067,46 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.5402875542640686</v>
+        <v>0.4912830591201782</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2680294513702393</v>
+        <v>0.2733020484447479</v>
       </c>
       <c r="S16" t="n">
-        <v>0.1916830092668533</v>
+        <v>0.2354148924350739</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>-0.1187874879492059</v>
+        <v>-0.1677919830930963</v>
       </c>
       <c r="W16" t="n">
         <v>1</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.1187874879492059</v>
+        <v>-0.1677919830930963</v>
       </c>
       <c r="Y16" t="n">
-        <v>0.5402875542640686</v>
+        <v>0.4912830591201782</v>
       </c>
       <c r="Z16" t="n">
         <v>1.42</v>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB16" t="n">
-        <v>-55.42658879643396</v>
+        <v>-71.99477524984452</v>
       </c>
       <c r="AC16" t="n">
-        <v>-1.108531775928679</v>
+        <v>-1.43989550499689</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.92167662372342</v>
+        <v>1.483486439464415</v>
       </c>
     </row>
     <row r="17">
@@ -2169,46 +2169,46 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.4984340965747833</v>
+        <v>0.4295498132705688</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3016817271709442</v>
+        <v>0.3659041523933411</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1998841911554337</v>
+        <v>0.2045460790395737</v>
       </c>
       <c r="T17" t="n">
         <v>1</v>
       </c>
       <c r="U17" t="inlineStr"/>
       <c r="V17" t="n">
-        <v>0.02570682384751061</v>
+        <v>-0.04317745945670387</v>
       </c>
       <c r="W17" t="n">
         <v>1</v>
       </c>
       <c r="X17" t="n">
-        <v>0.02570682384751061</v>
+        <v>-0.04317745945670387</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.4984340965747833</v>
+        <v>0.4295498132705688</v>
       </c>
       <c r="Z17" t="n">
         <v>2</v>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB17" t="n">
-        <v>-0.313180685043335</v>
+        <v>-14.09003734588623</v>
       </c>
       <c r="AC17" t="n">
-        <v>-0.006263613700866699</v>
+        <v>-0.2818007469177246</v>
       </c>
       <c r="AD17" t="n">
-        <v>3.859962008037489</v>
+        <v>3.330091872102586</v>
       </c>
     </row>
     <row r="18">
@@ -2271,46 +2271,46 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.5579578280448914</v>
+        <v>0.5241793990135193</v>
       </c>
       <c r="R18" t="n">
-        <v>0.2512670159339905</v>
+        <v>0.2750292420387268</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1907751858234406</v>
+        <v>0.2007913738489151</v>
       </c>
       <c r="T18" t="n">
         <v>1</v>
       </c>
       <c r="U18" t="inlineStr"/>
       <c r="V18" t="n">
-        <v>-0.03344002141747415</v>
+        <v>-0.06721845044884622</v>
       </c>
       <c r="W18" t="n">
         <v>1</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.03344002141747415</v>
+        <v>-0.06721845044884622</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.5579578280448914</v>
+        <v>0.5241793990135193</v>
       </c>
       <c r="Z18" t="n">
         <v>1.6</v>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB18" t="n">
-        <v>-17.87791252136229</v>
+        <v>-26.88549359639485</v>
       </c>
       <c r="AC18" t="n">
-        <v>-0.3575582504272459</v>
+        <v>-0.537709871927897</v>
       </c>
       <c r="AD18" t="n">
-        <v>3.187122113791959</v>
+        <v>2.855436775002356</v>
       </c>
     </row>
     <row r="19">
@@ -2370,49 +2370,49 @@
         <v>0.0599747474747474</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.3982662856578827</v>
+        <v>0.4098120331764221</v>
       </c>
       <c r="R19" t="n">
-        <v>0.4135233759880066</v>
+        <v>0.3692823052406311</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1882103085517883</v>
+        <v>0.2209056466817856</v>
       </c>
       <c r="T19" t="n">
         <v>1</v>
       </c>
       <c r="U19" t="inlineStr"/>
       <c r="V19" t="n">
-        <v>0.1187050317354753</v>
+        <v>-0.009485167538289041</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X19" t="n">
-        <v>0.1187050317354753</v>
+        <v>-0.009485167538289041</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.4135233759880066</v>
+        <v>0.4098120331764221</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.2</v>
+        <v>2.25</v>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB19" t="n">
-        <v>14.69430923461914</v>
+        <v>-6.233834028244018</v>
       </c>
       <c r="AC19" t="n">
-        <v>0.2938861846923828</v>
+        <v>-0.1246766805648803</v>
       </c>
       <c r="AD19" t="n">
-        <v>4.437005171721267</v>
+        <v>3.631021212398295</v>
       </c>
     </row>
     <row r="20">
@@ -2472,49 +2472,49 @@
         <v>0.06633486274204836</v>
       </c>
       <c r="P20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.5426689982414246</v>
+        <v>0.2942396402359009</v>
       </c>
       <c r="R20" t="n">
-        <v>0.2397459447383881</v>
+        <v>0.4335629940032959</v>
       </c>
       <c r="S20" t="n">
-        <v>0.2175850570201874</v>
+        <v>0.2721973657608032</v>
       </c>
       <c r="T20" t="n">
         <v>1</v>
       </c>
       <c r="U20" t="inlineStr"/>
       <c r="V20" t="n">
-        <v>-0.01888292707946226</v>
+        <v>0.1656225039216156</v>
       </c>
       <c r="W20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.01888292707946226</v>
+        <v>0.1656225039216156</v>
       </c>
       <c r="Y20" t="n">
-        <v>0.5426689982414246</v>
+        <v>0.4335629940032959</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.67</v>
+        <v>3.5</v>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB20" t="n">
-        <v>-13.99145864728673</v>
+        <v>20.69881916046143</v>
       </c>
       <c r="AC20" t="n">
-        <v>-0.2798291729457345</v>
+        <v>0.4139763832092285</v>
       </c>
       <c r="AD20" t="n">
-        <v>3.33383465403003</v>
+        <v>4.662311851891576</v>
       </c>
     </row>
     <row r="21">
@@ -2574,49 +2574,49 @@
         <v>0.06833642547928265</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.355811208486557</v>
+        <v>0.4296035468578339</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3904175758361816</v>
+        <v>0.3527367413043976</v>
       </c>
       <c r="S21" t="n">
-        <v>0.2537712454795837</v>
+        <v>0.2176597267389297</v>
       </c>
       <c r="T21" t="n">
         <v>1</v>
       </c>
       <c r="U21" t="inlineStr"/>
       <c r="V21" t="n">
-        <v>0.1067706872688879</v>
+        <v>0.04754855409372394</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X21" t="n">
-        <v>0.1067706872688879</v>
+        <v>0.04754855409372394</v>
       </c>
       <c r="Y21" t="n">
-        <v>0.3904175758361816</v>
+        <v>0.4296035468578339</v>
       </c>
       <c r="Z21" t="n">
-        <v>3.3</v>
+        <v>2.45</v>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
       <c r="AB21" t="n">
-        <v>12.53817392432171</v>
+        <v>3.622668262185724</v>
       </c>
       <c r="AC21" t="n">
-        <v>0.2507634784864342</v>
+        <v>0.07245336524371448</v>
       </c>
       <c r="AD21" t="n">
-        <v>4.355049644522281</v>
+        <v>4.012300195619332</v>
       </c>
     </row>
     <row r="22">
@@ -2665,13 +2665,13 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.2392067015171051</v>
+        <v>0.2258505523204803</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4226315915584564</v>
+        <v>0.4242788851261139</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3381616771221161</v>
+        <v>0.3498705923557281</v>
       </c>
       <c r="T22" t="n">
         <v>1</v>
@@ -2683,12 +2683,12 @@
       </c>
       <c r="X22" t="inlineStr"/>
       <c r="Y22" t="n">
-        <v>0.5773684084415436</v>
+        <v>0.5757211148738861</v>
       </c>
       <c r="Z22" t="inlineStr"/>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.35</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr"/>
@@ -2738,16 +2738,16 @@
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.3399296402931213</v>
+        <v>0.3696960508823395</v>
       </c>
       <c r="R23" t="n">
-        <v>0.454637885093689</v>
+        <v>0.3662590682506561</v>
       </c>
       <c r="S23" t="n">
-        <v>0.2054324597120285</v>
+        <v>0.2640449106693268</v>
       </c>
       <c r="T23" t="n">
         <v>1</v>
@@ -2755,16 +2755,16 @@
       <c r="U23" t="inlineStr"/>
       <c r="V23" t="inlineStr"/>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X23" t="inlineStr"/>
       <c r="Y23" t="n">
-        <v>0.545362114906311</v>
+        <v>0.6303039491176605</v>
       </c>
       <c r="Z23" t="inlineStr"/>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.35</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr"/>
@@ -2817,13 +2817,13 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.3932410478591919</v>
+        <v>0.3659267425537109</v>
       </c>
       <c r="R24" t="n">
-        <v>0.4201231896877289</v>
+        <v>0.4188465178012848</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1866357922554016</v>
+        <v>0.2152266949415207</v>
       </c>
       <c r="T24" t="n">
         <v>1</v>
@@ -2835,12 +2835,12 @@
       </c>
       <c r="X24" t="inlineStr"/>
       <c r="Y24" t="n">
-        <v>0.5798768103122711</v>
+        <v>0.5811534821987152</v>
       </c>
       <c r="Z24" t="inlineStr"/>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.35</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr"/>
@@ -2893,13 +2893,13 @@
         <v>2</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.2193145006895065</v>
+        <v>0.2375688552856445</v>
       </c>
       <c r="R25" t="n">
-        <v>0.3615515828132629</v>
+        <v>0.3329222202301025</v>
       </c>
       <c r="S25" t="n">
-        <v>0.4191339612007141</v>
+        <v>0.4295089244842529</v>
       </c>
       <c r="T25" t="n">
         <v>1</v>
@@ -2911,12 +2911,12 @@
       </c>
       <c r="X25" t="inlineStr"/>
       <c r="Y25" t="n">
-        <v>0.5808660387992859</v>
+        <v>0.5704910755157471</v>
       </c>
       <c r="Z25" t="inlineStr"/>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.35</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr"/>
@@ -2966,16 +2966,16 @@
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.4081339836120605</v>
+        <v>0.2688276767730713</v>
       </c>
       <c r="R26" t="n">
-        <v>0.3379647433757782</v>
+        <v>0.4891399443149567</v>
       </c>
       <c r="S26" t="n">
-        <v>0.2539012432098389</v>
+        <v>0.2420324236154556</v>
       </c>
       <c r="T26" t="n">
         <v>1</v>
@@ -2983,16 +2983,16 @@
       <c r="U26" t="inlineStr"/>
       <c r="V26" t="inlineStr"/>
       <c r="W26" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="X26" t="inlineStr"/>
       <c r="Y26" t="n">
-        <v>0.5918660163879395</v>
+        <v>0.5108600556850433</v>
       </c>
       <c r="Z26" t="inlineStr"/>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.35</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr"/>
@@ -3045,13 +3045,13 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.4542271494865417</v>
+        <v>0.5161313414573669</v>
       </c>
       <c r="R27" t="n">
-        <v>0.3409821391105652</v>
+        <v>0.2838864624500275</v>
       </c>
       <c r="S27" t="n">
-        <v>0.2047907114028931</v>
+        <v>0.199982225894928</v>
       </c>
       <c r="T27" t="n">
         <v>1</v>
@@ -3063,12 +3063,12 @@
       </c>
       <c r="X27" t="inlineStr"/>
       <c r="Y27" t="n">
-        <v>0.5457728505134583</v>
+        <v>0.4838686585426331</v>
       </c>
       <c r="Z27" t="inlineStr"/>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.35</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr"/>
@@ -3121,13 +3121,13 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.5638784170150757</v>
+        <v>0.5492764115333557</v>
       </c>
       <c r="R28" t="n">
-        <v>0.2269687056541443</v>
+        <v>0.2409570813179016</v>
       </c>
       <c r="S28" t="n">
-        <v>0.2091528922319412</v>
+        <v>0.2097665220499039</v>
       </c>
       <c r="T28" t="n">
         <v>1</v>
@@ -3139,12 +3139,12 @@
       </c>
       <c r="X28" t="inlineStr"/>
       <c r="Y28" t="n">
-        <v>0.4361215829849243</v>
+        <v>0.4507235884666443</v>
       </c>
       <c r="Z28" t="inlineStr"/>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.35</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr"/>
@@ -3197,13 +3197,13 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.2376536726951599</v>
+        <v>0.2368633151054382</v>
       </c>
       <c r="R29" t="n">
-        <v>0.4278645217418671</v>
+        <v>0.4070692658424377</v>
       </c>
       <c r="S29" t="n">
-        <v>0.3344818353652954</v>
+        <v>0.3560674488544464</v>
       </c>
       <c r="T29" t="n">
         <v>1</v>
@@ -3215,17 +3215,169 @@
       </c>
       <c r="X29" t="inlineStr"/>
       <c r="Y29" t="n">
-        <v>0.5721354782581329</v>
+        <v>0.5929307341575623</v>
       </c>
       <c r="Z29" t="inlineStr"/>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.35</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr"/>
       <c r="AC29" t="inlineStr"/>
       <c r="AD29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45596.69791666666</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>77</v>
+      </c>
+      <c r="F30" t="n">
+        <v>771</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.5628480911254883</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.2632296681404114</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.1739222705364227</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="n">
+        <v>0.4371519088745117</v>
+      </c>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45596.69791666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>77</v>
+      </c>
+      <c r="F31" t="n">
+        <v>771</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.2143705636262894</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.3562891185283661</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.4293403029441833</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="n">
+        <v>0.5706596970558167</v>
+      </c>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD7"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -582,20 +582,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>8Kjh0jRr</t>
+          <t>I5fXHFho</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45585.3125</v>
+        <v>45590.5625</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -615,56 +615,56 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>2.15</v>
       </c>
       <c r="J2" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K2" t="n">
-        <v>1.65</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1586538461538461</v>
+        <v>0.4415584415584415</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2644230769230769</v>
+        <v>0.2792207792207792</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.2792207792207792</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05050505050505061</v>
+        <v>0.05335157318741457</v>
       </c>
       <c r="P2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.220638781785965</v>
+        <v>0.2978691160678864</v>
       </c>
       <c r="R2" t="n">
-        <v>0.3764342069625854</v>
+        <v>0.4283099472522736</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4029269814491272</v>
+        <v>0.2738209068775177</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-0.1739960954739497</v>
+        <v>0.1490891680314944</v>
       </c>
       <c r="W2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.1739960954739497</v>
+        <v>0.1490891680314944</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4029269814491272</v>
+        <v>0.4283099472522736</v>
       </c>
       <c r="Z2" t="n">
-        <v>1.65</v>
+        <v>3.4</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -672,32 +672,32 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>-51.56468932445234</v>
+        <v>19.01057586073875</v>
       </c>
       <c r="AC2" t="n">
-        <v>-1.031293786489047</v>
+        <v>0.3802115172147751</v>
       </c>
       <c r="AD2" t="n">
-        <v>2.035428065122646</v>
+        <v>4.61121209068254</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AJ5eIkmR</t>
+          <t>bLD0NyVN</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45590.65625</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -717,56 +717,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>3.2</v>
+        <v>2.55</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
       <c r="L3" t="n">
-        <v>0.297530380243042</v>
+        <v>0.3663929248262792</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2885143081144649</v>
+        <v>0.3114339861023373</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4139553116424932</v>
+        <v>0.3221730890713834</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05031291172595509</v>
+        <v>0.07031778228532803</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2760554254055023</v>
+        <v>0.3726544380187988</v>
       </c>
       <c r="R3" t="n">
-        <v>0.3901287317276001</v>
+        <v>0.3990421295166016</v>
       </c>
       <c r="S3" t="n">
-        <v>0.33381587266922</v>
+        <v>0.228303387761116</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.1016144236131352</v>
+        <v>0.08760814341426426</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>0.1016144236131352</v>
+        <v>0.08760814341426426</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3901287317276001</v>
+        <v>0.3990421295166016</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -774,32 +774,32 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>12.49673107396001</v>
+        <v>9.856319427490234</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.2499346214792002</v>
+        <v>0.1971263885498047</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.353469823890078</v>
+        <v>4.263374452285508</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>dGwq9oAD</t>
+          <t>UuMqRJVb</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45585.41666666666</v>
+        <v>45591.41666666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -819,89 +819,89 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.75</v>
+        <v>1.3</v>
       </c>
       <c r="J4" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="K4" t="n">
-        <v>1.57</v>
+        <v>11</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1648842838663405</v>
+        <v>0.7255936675461742</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2312401542027946</v>
+        <v>0.1886543535620053</v>
       </c>
       <c r="N4" t="n">
-        <v>0.6038755619308649</v>
+        <v>0.0857519788918206</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05475815766188674</v>
+        <v>0.06013986013985995</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.2758691310882568</v>
+        <v>0.4400236010551453</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4300333857536316</v>
+        <v>0.3304280042648315</v>
       </c>
       <c r="S4" t="n">
-        <v>0.294097512960434</v>
+        <v>0.229548379778862</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1987932315508369</v>
+        <v>-0.2855700664910289</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.1987932315508369</v>
+        <v>0.2855700664910289</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4300333857536316</v>
+        <v>0.5599763989448547</v>
       </c>
       <c r="Z4" t="n">
-        <v>4.1</v>
+        <v>3.4375</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>24.61731876096418</v>
+        <v>37.9453895947872</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.4923463752192835</v>
+        <v>0.758907791895744</v>
       </c>
       <c r="AD4" t="n">
-        <v>4.806493452737596</v>
+        <v>5.288172023356454</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>GMBD7YY8</t>
+          <t>8f71RSPs</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45585.54166666666</v>
+        <v>45591.54166666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -921,56 +921,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.75</v>
+        <v>3.6</v>
       </c>
       <c r="J5" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="K5" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3463687150837989</v>
+        <v>0.2642238998342847</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3072625698324022</v>
+        <v>0.2717731541152642</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3463687150837989</v>
+        <v>0.4640029460504512</v>
       </c>
       <c r="O5" t="n">
-        <v>0.04985337243401755</v>
+        <v>0.05129694154084397</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4104653000831604</v>
+        <v>0.2795626521110535</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3539402484893799</v>
+        <v>0.3359852731227875</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2355944365262985</v>
+        <v>0.3844521045684814</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.06409658499936149</v>
+        <v>-0.07955084148196973</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06409658499936149</v>
+        <v>-0.07955084148196973</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4104653000831604</v>
+        <v>0.3844521045684814</v>
       </c>
       <c r="Z5" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -978,32 +978,32 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>7.358832870210918</v>
+        <v>-20.17839863186792</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.1471766574042184</v>
+        <v>-0.4035679726373584</v>
       </c>
       <c r="AD5" t="n">
-        <v>4.156515901831464</v>
+        <v>3.109125766749278</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0lpzB7u1</t>
+          <t>OMVUWl2K</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45585.65625</v>
+        <v>45591.65625</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1023,56 +1023,56 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>4.2</v>
+        <v>1.4</v>
       </c>
       <c r="J6" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
       <c r="K6" t="n">
-        <v>1.83</v>
+        <v>8</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2257225722572257</v>
+        <v>0.6728971962616822</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2562256225622562</v>
+        <v>0.2093457943925233</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5180518051805181</v>
+        <v>0.1177570093457944</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05481359579720224</v>
+        <v>0.06150793650793651</v>
       </c>
       <c r="P6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.2276525944471359</v>
+        <v>0.4720059037208557</v>
       </c>
       <c r="R6" t="n">
-        <v>0.336058109998703</v>
+        <v>0.2899166643619537</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4362892806529999</v>
+        <v>0.2380774319171906</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.0817625245275182</v>
+        <v>-0.2008912925408265</v>
       </c>
       <c r="W6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0817625245275182</v>
+        <v>-0.2008912925408265</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4362892806529999</v>
+        <v>0.4720059037208557</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.83</v>
+        <v>1.4</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
@@ -1080,32 +1080,32 @@
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>-24.28802607289279</v>
+        <v>-84.79793369770053</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.4857605214578558</v>
+        <v>-1.695958673954011</v>
       </c>
       <c r="AD6" t="n">
-        <v>2.949701244108895</v>
+        <v>1.203368189855692</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>McP0d8Q7</t>
+          <t>jeAhPc0B</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45586.65625</v>
+        <v>45592.35416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1125,71 +1125,2259 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="J7" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="K7" t="n">
         <v>3.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4125736738703339</v>
+        <v>0.4337464251668255</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3163064833005893</v>
+        <v>0.2936129647283127</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2711198428290766</v>
+        <v>0.2726406101048617</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0538302277432714</v>
+        <v>0.0479520479520481</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.3031558096408844</v>
+        <v>0.4324328005313873</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4847221970558167</v>
+        <v>0.3636555969715118</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2121219485998154</v>
+        <v>0.2039116322994232</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1684157137552273</v>
+        <v>-0.00131362463543816</v>
       </c>
       <c r="W7" t="n">
+        <v>1</v>
+      </c>
+      <c r="X7" t="n">
+        <v>-0.00131362463543816</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0.4324328005313873</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB7" t="n">
+        <v>-4.053986569245649</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>-0.08107973138491298</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>3.724698480247995</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>OjcQLOgJ</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>77</v>
+      </c>
+      <c r="F8" t="n">
+        <v>771</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="J8" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K8" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6180581517347837</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.2306412127205412</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0.151300635544675</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.05749721026622034</v>
+      </c>
+      <c r="P8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.5411063432693481</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.2603448331356049</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.1985488086938858</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="n">
+        <v>-0.07695180846543559</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1</v>
+      </c>
+      <c r="X8" t="n">
+        <v>-0.07695180846543559</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.5411063432693481</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB8" t="n">
+        <v>-32.47307449016931</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>-0.6494614898033862</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>2.663904500114217</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>xY3xTu1n</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>45592.45833333334</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>77</v>
+      </c>
+      <c r="F9" t="n">
+        <v>771</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K9" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.4283464566929133</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.2944881889763779</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0.2771653543307087</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0.06116310160427818</v>
+      </c>
+      <c r="P9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.4190685749053955</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.3535478413105011</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.2273835241794586</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="n">
+        <v>-0.009277881787517817</v>
+      </c>
+      <c r="W9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X9" t="n">
+        <v>-0.009277881787517817</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0.4190685749053955</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB9" t="n">
+        <v>-6.504094600677485</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>-0.1300818920135497</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>3.629854867251872</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>jwaINpP6</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>45592.58333333334</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>77</v>
+      </c>
+      <c r="F10" t="n">
+        <v>771</v>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5292652552926526</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2801992528019925</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0.1905354919053549</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0.04967320261437913</v>
+      </c>
+      <c r="P10" t="n">
         <v>0</v>
       </c>
-      <c r="X7" t="n">
-        <v>0.1684157137552273</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>0.4847221970558167</v>
-      </c>
-      <c r="Z7" t="n">
+      <c r="Q10" t="n">
+        <v>0.3175609707832336</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.4249657392501831</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.2574733197689056</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="n">
+        <v>0.1447664864481906</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0.1447664864481906</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0.4249657392501831</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB10" t="n">
+        <v>18.5368130604426</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0.3707362612088521</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>4.593453983614666</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fB59P6ff</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45592.69791666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>77</v>
+      </c>
+      <c r="F11" t="n">
+        <v>771</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.375767498976668</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2762996316004912</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.3479328694228407</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.06448801742919397</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4372522234916687</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.3422379195690155</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2205098122358322</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="n">
+        <v>0.0614847245150007</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.0614847245150007</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4372522234916687</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>6.208703915278119</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.1241740783055624</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>4.122699472898661</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Ug79dz7j</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45594.60416666666</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>77</v>
+      </c>
+      <c r="F12" t="n">
+        <v>771</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.3452849740932643</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2741968911917099</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.3805181347150259</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.07265128273531629</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.2248663306236267</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.4285325109958649</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.3466011583805084</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.154335619804155</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.154335619804155</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4285325109958649</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>19.04210572441419</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.3808421144882838</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>4.612392815379579</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>4CLi9Djd</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45594.60416666666</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>77</v>
+      </c>
+      <c r="F13" t="n">
+        <v>771</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K13" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.4569015166058744</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2754847379535419</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.2676137454405835</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.06763681082188988</v>
+      </c>
+      <c r="P13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.3805912435054779</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.3563759922981262</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.2630327641963959</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>-0.07631027310039651</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1</v>
+      </c>
+      <c r="X13" t="n">
+        <v>-0.07631027310039651</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.3805912435054779</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>-20.93218579178766</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.4186437158357532</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>3.081066323889005</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WIDwXGr3</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45594.69791666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>77</v>
+      </c>
+      <c r="F14" t="n">
+        <v>771</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K14" t="n">
         <v>3</v>
       </c>
-      <c r="AA7" t="inlineStr">
+      <c r="L14" t="n">
+        <v>0.4210526315789473</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2631578947368421</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.3157894736842105</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.05555555555555558</v>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.3588433563709259</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.4426482617855072</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.1985083669424057</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.1794903670486651</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0.1794903670486651</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.4426482617855072</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AA14" t="inlineStr">
         <is>
           <t>dif_prob_mod_bm &gt; -0.25</t>
         </is>
       </c>
-      <c r="AB7" t="n">
-        <v>22.7083295583725</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.45416659116745</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>4.736566615024762</v>
-      </c>
+      <c r="AB14" t="n">
+        <v>22.82822086260869</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0.4565644172521738</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>4.7530966197799</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>IFm4IHT9</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45595.60416666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>77</v>
+      </c>
+      <c r="F15" t="n">
+        <v>771</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="J15" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.1250930752047655</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2233804914370812</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.6515264333581534</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.06587301587301586</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.2351574152708054</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3027129173278809</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.4621297121047974</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>-0.189396721253356</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>-0.189396721253356</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.4621297121047974</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>-76.03027603842997</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>-1.5206055207686</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1.392642629627297</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>0b5fTYsS</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45595.60416666666</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>77</v>
+      </c>
+      <c r="F16" t="n">
+        <v>771</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.3645833333333334</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.2708333333333334</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.3645833333333334</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.05494505494505475</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.2513548135757446</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.4984703660011292</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.2501748502254486</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.2276370326677958</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.2276370326677958</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4984703660011292</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>29.78585124015808</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.5957170248031616</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>5.005247040408014</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Y96v2dqT</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45595.69791666666</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>77</v>
+      </c>
+      <c r="F17" t="n">
+        <v>771</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="J17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="K17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.6914119359534208</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.197962154294032</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.1106259097525473</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.06346749226006176</v>
+      </c>
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.5110282897949219</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.2891385853290558</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.1998330950737</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>-0.1803836461584989</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1</v>
+      </c>
+      <c r="X17" t="n">
+        <v>-0.1803836461584989</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.5110282897949219</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>-84.72264607747393</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>-1.694452921549479</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.204900115075722</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>rcXrBZLq</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45595.69791666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>77</v>
+      </c>
+      <c r="F18" t="n">
+        <v>771</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.6515264333581534</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.2233804914370812</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.1250930752047655</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06587301587301586</v>
+      </c>
+      <c r="P18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.5958771109580994</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.1989000886678696</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.2052227556705475</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>-0.05564932240005405</v>
+      </c>
+      <c r="W18" t="n">
+        <v>1</v>
+      </c>
+      <c r="X18" t="n">
+        <v>-0.05564932240005405</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.5958771109580994</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>-32.25840005007659</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>-0.6451680010015317</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.671422685218474</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>EssDGebM</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45596.60416666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>77</v>
+      </c>
+      <c r="F19" t="n">
+        <v>771</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.2775479503572772</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2621286197818729</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.46032342986085</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.05970030288538175</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.2464116811752319</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.3537349998950958</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.3998532891273499</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="n">
+        <v>-0.06047014073350016</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>-0.06047014073350016</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.3998532891273499</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>-17.17150069418408</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>-0.3434300138836817</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>3.221867445808109</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>Sp7nVfDF</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45596.69791666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>77</v>
+      </c>
+      <c r="F20" t="n">
+        <v>771</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.5095541401273885</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2547770700636943</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.2356687898089172</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.06081081081081074</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.5693906545639038</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.2513393461704254</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.1792699992656708</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.05983651443651528</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.05983651443651528</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.5693906545639038</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>6.279142463908483</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.1255828492781697</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>4.125423255590963</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45596.69791666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>77</v>
+      </c>
+      <c r="F21" t="n">
+        <v>771</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K21" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.3368721927317272</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2858309514087382</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.3772968558595345</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.06017316017316032</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.2276492267847061</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3900425732135773</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.3823082447052002</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>0.1042116218048391</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0.1042116218048391</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.3900425732135773</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>12.48436920020891</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0.2496873840041782</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>4.364126971422068</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45598.45833333334</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>77</v>
+      </c>
+      <c r="F22" t="n">
+        <v>771</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.4129855930805206</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.3674785494804382</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.2195358276367188</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="n">
+        <v>0.5870144069194794</v>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>pOryx3Qa</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45598.58333333334</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>77</v>
+      </c>
+      <c r="F23" t="n">
+        <v>771</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.2396625280380249</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.2734483778476715</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.4868890643119812</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="n">
+        <v>0.5131109356880188</v>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>Gpn0zjke</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45598.69791666666</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>77</v>
+      </c>
+      <c r="F24" t="n">
+        <v>771</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.2868505120277405</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.3278715014457703</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.3852780163288116</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="n">
+        <v>0.6147219836711884</v>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>CCu9YTJ7</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45599.35416666666</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>77</v>
+      </c>
+      <c r="F25" t="n">
+        <v>771</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.3745722770690918</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.4080421924591064</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.217385545372963</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="n">
+        <v>0.5919578075408936</v>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>b7pTwPem</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45599.45833333334</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>77</v>
+      </c>
+      <c r="F26" t="n">
+        <v>771</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.2918579876422882</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.4497043192386627</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.2584377229213715</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="n">
+        <v>0.5502956807613373</v>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>WvkEqfS8</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45599.58333333334</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>77</v>
+      </c>
+      <c r="F27" t="n">
+        <v>771</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.2537800669670105</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.4154002666473389</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.330819696187973</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="n">
+        <v>0.5845997333526611</v>
+      </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>v5hMsYdL</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45599.69791666666</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>77</v>
+      </c>
+      <c r="F28" t="n">
+        <v>771</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.5549935102462769</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.2028427422046661</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.2421637177467346</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="n">
+        <v>0.4450064897537231</v>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45600.60416666666</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>77</v>
+      </c>
+      <c r="F29" t="n">
+        <v>771</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.3450387716293335</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.3206148743629456</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.3343463540077209</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="n">
+        <v>0.6549612283706665</v>
+      </c>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45600.60416666666</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>77</v>
+      </c>
+      <c r="F30" t="n">
+        <v>771</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.3769363462924957</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.4044265747070312</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.218637079000473</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="n">
+        <v>0.5955734252929688</v>
+      </c>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45600.69791666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>77</v>
+      </c>
+      <c r="F31" t="n">
+        <v>771</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.4868297874927521</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.3316323757171631</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.1815378367900848</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="n">
+        <v>0.5131702125072479</v>
+      </c>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.25</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD10"/>
+  <dimension ref="A1:AD31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -582,20 +582,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>I5fXHFho</t>
+          <t>Ug79dz7j</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45590.5625</v>
+        <v>45594.60416666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -615,89 +615,89 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.15</v>
+        <v>3.1</v>
       </c>
       <c r="J2" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="K2" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4415584415584415</v>
+        <v>0.3055305530553056</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2792207792207792</v>
+        <v>0.2914291429142915</v>
       </c>
       <c r="N2" t="n">
-        <v>0.2792207792207792</v>
+        <v>0.4030403040304031</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05335157318741457</v>
+        <v>0.05580486774721494</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2964670956134796</v>
+        <v>0.170868619901571</v>
       </c>
       <c r="R2" t="n">
-        <v>0.429165244102478</v>
+        <v>0.3777648099170555</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2743677198886871</v>
+        <v>0.4513665701813733</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1499444648816988</v>
+        <v>0.04832626615097024</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1499444648816988</v>
+        <v>0.04832626615097024</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.429165244102478</v>
+        <v>0.4513665701813733</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.4</v>
+        <v>2.35</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>19.13174291451772</v>
+        <v>4.49714369823907</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.3826348582903544</v>
+        <v>0.08994287396478139</v>
       </c>
       <c r="AD2" t="n">
-        <v>4.61574876692797</v>
+        <v>2.009502201525139</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bLD0NyVN</t>
+          <t>4CLi9Djd</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45590.65625</v>
+        <v>45594.60416666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -717,89 +717,89 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.45</v>
+        <v>2.3</v>
       </c>
       <c r="J3" t="n">
         <v>3.1</v>
       </c>
       <c r="K3" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3875</v>
+        <v>0.413495488426834</v>
       </c>
       <c r="M3" t="n">
-        <v>0.30625</v>
+        <v>0.3067869752844252</v>
       </c>
       <c r="N3" t="n">
-        <v>0.30625</v>
+        <v>0.2797175362887406</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05332455562870297</v>
+        <v>0.05148090091576618</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3690598011016846</v>
+        <v>0.3852216767012673</v>
       </c>
       <c r="R3" t="n">
-        <v>0.400352954864502</v>
+        <v>0.2766488072055652</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2305873036384583</v>
+        <v>0.3381295160931672</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.09410295486450193</v>
+        <v>-0.0282738117255667</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.09410295486450193</v>
+        <v>-0.0282738117255667</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.400352954864502</v>
+        <v>0.3852216767012673</v>
       </c>
       <c r="Z3" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>11.48067428952172</v>
+        <v>-8.768472583621945</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.2296134857904344</v>
+        <v>-0.1753694516724389</v>
       </c>
       <c r="AD3" t="n">
-        <v>4.325718095083074</v>
+        <v>1.754883288855256</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>UuMqRJVb</t>
+          <t>WIDwXGr3</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45591.41666666666</v>
+        <v>45594.69791666666</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>napoli</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>lecce</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -819,89 +819,89 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>1.3</v>
+        <v>2.4</v>
       </c>
       <c r="J4" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>12</v>
+        <v>2.9</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7308160779537151</v>
+        <v>0.3947157726180945</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1900121802679659</v>
+        <v>0.2786228983186549</v>
       </c>
       <c r="N4" t="n">
-        <v>0.07917174177831914</v>
+        <v>0.3266613290632506</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05256410256410238</v>
+        <v>0.05561189993238669</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.4473603665828705</v>
+        <v>0.5162237960733164</v>
       </c>
       <c r="R4" t="n">
-        <v>0.323435515165329</v>
+        <v>0.250153697890327</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2292041331529617</v>
+        <v>0.2336225060363566</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.2834557113708446</v>
+        <v>0.1215080234552218</v>
       </c>
       <c r="W4" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.2834557113708446</v>
+        <v>0.1215080234552218</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.5526396334171295</v>
+        <v>0.5162237960733164</v>
       </c>
       <c r="Z4" t="n">
-        <v>3.529411764705882</v>
+        <v>2.4</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &lt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>37.57762326750645</v>
+        <v>17.06693646971138</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.7515524653501289</v>
+        <v>0.3413387293942275</v>
       </c>
       <c r="AD4" t="n">
-        <v>5.2757521695622</v>
+        <v>2.248137230365577</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OMVUWl2K</t>
+          <t>IFm4IHT9</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45591.65625</v>
+        <v>45595.60416666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -921,89 +921,89 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>1.38</v>
+        <v>7.5</v>
       </c>
       <c r="J5" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="K5" t="n">
-        <v>8</v>
+        <v>1.44</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6835147045597626</v>
+        <v>0.1259376855678224</v>
       </c>
       <c r="M5" t="n">
-        <v>0.1985790089036784</v>
+        <v>0.218136868766436</v>
       </c>
       <c r="N5" t="n">
-        <v>0.117906286536559</v>
+        <v>0.6559254456657416</v>
       </c>
       <c r="O5" t="n">
-        <v>0.06016399694889407</v>
+        <v>0.05872465999486787</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.4643748700618744</v>
+        <v>0.07570780962329242</v>
       </c>
       <c r="R5" t="n">
-        <v>0.2941553592681885</v>
+        <v>0.3952464259391488</v>
       </c>
       <c r="S5" t="n">
-        <v>0.2414697855710983</v>
+        <v>0.5290457644375587</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.2191398344978882</v>
+        <v>-0.1268796812281829</v>
       </c>
       <c r="W5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2191398344978882</v>
+        <v>-0.1268796812281829</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.4643748700618744</v>
+        <v>0.5290457644375587</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>-94.51649455647724</v>
+        <v>-54.13047709316262</v>
       </c>
       <c r="AC5" t="n">
-        <v>-1.890329891129545</v>
+        <v>-1.082609541863252</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.018686801508296</v>
+        <v>0.9731250113030584</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>jeAhPc0B</t>
+          <t>0b5fTYsS</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45592.35416666666</v>
+        <v>45595.60416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1023,89 +1023,89 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="K6" t="n">
-        <v>3.4</v>
+        <v>2.63</v>
       </c>
       <c r="L6" t="n">
-        <v>0.4322033898305084</v>
+        <v>0.34997031547485</v>
       </c>
       <c r="M6" t="n">
-        <v>0.288135593220339</v>
+        <v>0.2907445697791062</v>
       </c>
       <c r="N6" t="n">
-        <v>0.2796610169491525</v>
+        <v>0.3592851147460438</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05169340463458116</v>
+        <v>0.05829081494480737</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4226072132587433</v>
+        <v>0.3370448299312765</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3705150783061981</v>
+        <v>0.330507603227984</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2068776786327362</v>
+        <v>0.3324475668407395</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.009596176571765147</v>
+        <v>-0.01292548554357348</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.009596176571765147</v>
+        <v>-0.01292548554357348</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4226072132587433</v>
+        <v>0.3370448299312765</v>
       </c>
       <c r="Z6" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>-5.855344235897059</v>
+        <v>-5.292879952091373</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.1171068847179412</v>
+        <v>-0.1058575990418275</v>
       </c>
       <c r="AD6" t="n">
-        <v>3.654943256597515</v>
+        <v>1.821385714507027</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>OjcQLOgJ</t>
+          <t>Y96v2dqT</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45592.45833333334</v>
+        <v>45595.69791666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1125,89 +1125,89 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.53</v>
+        <v>1.3</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2</v>
+        <v>5.25</v>
       </c>
       <c r="K7" t="n">
-        <v>6.25</v>
+        <v>11</v>
       </c>
       <c r="L7" t="n">
-        <v>0.621470932916652</v>
+        <v>0.7321711568938194</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2263929827053518</v>
+        <v>0.1812995245641839</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1521360843779964</v>
+        <v>0.08652931854199684</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05169000933706802</v>
+        <v>0.05061605061605046</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5411063432693481</v>
+        <v>0.3686698378371922</v>
       </c>
       <c r="R7" t="n">
-        <v>0.2603448331356049</v>
+        <v>0.3893465652921975</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1985488086938858</v>
+        <v>0.2419835968706103</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>-0.08036458964730386</v>
+        <v>0.2080470407280136</v>
       </c>
       <c r="W7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.08036458964730386</v>
+        <v>0.2080470407280136</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.5411063432693481</v>
+        <v>0.3893465652921975</v>
       </c>
       <c r="Z7" t="n">
-        <v>1.53</v>
+        <v>5.25</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>-32.47307449016931</v>
+        <v>24.56634041844792</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.6494614898033862</v>
+        <v>0.4913268083689584</v>
       </c>
       <c r="AD7" t="n">
-        <v>2.663904500114217</v>
+        <v>2.386226711302541</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>xY3xTu1n</t>
+          <t>rcXrBZLq</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45592.45833333334</v>
+        <v>45595.69791666666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1227,89 +1227,89 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.15</v>
+        <v>1.42</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>4.5</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>7.5</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4427206508371961</v>
+        <v>0.6645008860011814</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2928767382461451</v>
+        <v>0.2096869462492617</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2644026109166588</v>
+        <v>0.125812167749557</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05058636453985299</v>
+        <v>0.05978090766823163</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.4190685749053955</v>
+        <v>0.4739940584880189</v>
       </c>
       <c r="R8" t="n">
-        <v>0.3535478413105011</v>
+        <v>0.3163903299716032</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2273835241794586</v>
+        <v>0.209615611540378</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.02365207593180058</v>
+        <v>-0.1905068275131625</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.02365207593180058</v>
+        <v>-0.1905068275131625</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4190685749053955</v>
+        <v>0.4739940584880189</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.15</v>
+        <v>1.42</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>-8.608918604643456</v>
+        <v>-77.84010403500316</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.1721783720928691</v>
+        <v>-1.556802080700063</v>
       </c>
       <c r="AD8" t="n">
-        <v>3.548613603579929</v>
+        <v>0.6696384873862329</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jwaINpP6</t>
+          <t>EssDGebM</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45592.58333333334</v>
+        <v>45596.60416666666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1329,89 +1329,89 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.75</v>
+        <v>4.2</v>
       </c>
       <c r="J9" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>1.8</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5405405405405405</v>
+        <v>0.2267441860465116</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2702702702702702</v>
+        <v>0.2441860465116279</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1891891891891892</v>
+        <v>0.5290697674418605</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05714285714285716</v>
+        <v>0.05006105006105011</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.3175609707832336</v>
+        <v>0.1415643928500184</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4249657392501831</v>
+        <v>0.4243748637096451</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2574733197689056</v>
+        <v>0.4340607434403367</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1546954689799129</v>
+        <v>-0.09500902400152383</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1546954689799129</v>
+        <v>-0.09500902400152383</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4249657392501831</v>
+        <v>0.4340607434403367</v>
       </c>
       <c r="Z9" t="n">
-        <v>3.5</v>
+        <v>1.8</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>19.49520349502563</v>
+        <v>-27.33633272592423</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.3899040699005127</v>
+        <v>-0.5467266545184847</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.629344765866079</v>
+        <v>1.410093012511653</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>fB59P6ff</t>
+          <t>Sp7nVfDF</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45592.69791666666</v>
+        <v>45596.69791666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1431,71 +1431,1959 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>2.8</v>
+        <v>5</v>
       </c>
       <c r="L10" t="n">
-        <v>0.3804956035171863</v>
+        <v>0.5594817432273262</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2797761790567546</v>
+        <v>0.2502944640753828</v>
       </c>
       <c r="N10" t="n">
-        <v>0.3397282174260591</v>
+        <v>0.1902237926972909</v>
       </c>
       <c r="O10" t="n">
-        <v>0.05126050420168071</v>
+        <v>0.05139318885448918</v>
       </c>
       <c r="P10" t="n">
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.4403651058673859</v>
+        <v>0.3658669821574556</v>
       </c>
       <c r="R10" t="n">
-        <v>0.340464174747467</v>
+        <v>0.2910075451463482</v>
       </c>
       <c r="S10" t="n">
-        <v>0.2191707044839859</v>
+        <v>0.3431254726961961</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.05986950235019961</v>
+        <v>-0.1936147610698706</v>
       </c>
       <c r="W10" t="n">
         <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.05986950235019961</v>
+        <v>-0.1936147610698706</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4403651058673859</v>
+        <v>0.3658669821574556</v>
       </c>
       <c r="Z10" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.25</t>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>6.727517644564313</v>
+        <v>-54.00373290461793</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.1345503528912863</v>
+        <v>-1.080074658092359</v>
       </c>
       <c r="AD10" t="n">
-        <v>4.142755687633643</v>
-      </c>
+        <v>0.9749688026659619</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>p2kdKwac</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>45596.69791666666</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>77</v>
+      </c>
+      <c r="F11" t="n">
+        <v>771</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.328058429701765</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.2863055386488131</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0.3856360316494217</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.05841579055864776</v>
+      </c>
+      <c r="P11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.4510690257550043</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.2583583004941464</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.2905726737508489</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.1230105960532393</v>
+      </c>
+      <c r="W11" t="n">
+        <v>1</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0.1230105960532393</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0.4510690257550043</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB11" t="n">
+        <v>15.90844649863896</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0.3181689299727792</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>2.226453622801251</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>rJ8JNC5k</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45598.45833333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>77</v>
+      </c>
+      <c r="F12" t="n">
+        <v>771</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.5885262116716122</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2769535113748764</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.1345202769535114</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.06197478991596639</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.2751044803862663</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.4881884424806867</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.236707077133047</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.2112349311058103</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.2112349311058103</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4881884424806867</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>27.49336268476395</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0.549867253695279</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>2.438864586959651</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pOryx3Qa</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>45598.58333333334</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>77</v>
+      </c>
+      <c r="F13" t="n">
+        <v>771</v>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.2186443350444121</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0.2958531158569702</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0.4855025490986177</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.05626739503760292</v>
+      </c>
+      <c r="P13" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0.1013472789194931</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.412924333617437</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.4857283874630697</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.0002258383644520023</v>
+      </c>
+      <c r="W13" t="n">
+        <v>2</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0.0002258383644520023</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0.4857283874630697</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB13" t="n">
+        <v>-5.561015204948844</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>-0.1112203040989769</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.816244427263321</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>Gpn0zjke</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>45598.69791666666</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>77</v>
+      </c>
+      <c r="F14" t="n">
+        <v>771</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="L14" t="n">
+        <v>0.1705075845974329</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0.2679404900816802</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0.5615519253208868</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.06633486274204836</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0.08500666220843479</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0.4144591460260996</v>
+      </c>
+      <c r="S14" t="n">
+        <v>0.5005341917654655</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>-0.06101773355542128</v>
+      </c>
+      <c r="W14" t="n">
+        <v>2</v>
+      </c>
+      <c r="X14" t="n">
+        <v>-0.06101773355542128</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.5005341917654655</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB14" t="n">
+        <v>-24.49371638084665</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>-0.4898743276169331</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.461242974953789</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>CCu9YTJ7</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>45599.35416666666</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>77</v>
+      </c>
+      <c r="F15" t="n">
+        <v>771</v>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>2</v>
+      </c>
+      <c r="J15" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.472913616398243</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0.2781844802342606</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.2489019033674963</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0.05727554179566563</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.3055810980646634</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.3418019368244705</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0.352616965110866</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
+        <v>0.1037150617433697</v>
+      </c>
+      <c r="W15" t="n">
+        <v>2</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0.1037150617433697</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.352616965110866</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>12.14087383647467</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0.2428174767294933</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>2.155414827430989</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>b7pTwPem</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>45599.45833333334</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>77</v>
+      </c>
+      <c r="F16" t="n">
+        <v>771</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K16" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.2890115403913698</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0.293527345709985</v>
+      </c>
+      <c r="N16" t="n">
+        <v>0.4174611138986453</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.06463675213675213</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0.1773787182611755</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.4214927490488023</v>
+      </c>
+      <c r="S16" t="n">
+        <v>0.4011285326900222</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.1279654033388173</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0.1279654033388173</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0.4214927490488023</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB16" t="n">
+        <v>15.85349077073488</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0.3170698154146976</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>2.225422994146109</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>WvkEqfS8</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>45599.58333333334</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>77</v>
+      </c>
+      <c r="F17" t="n">
+        <v>771</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K17" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.2002929388852227</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0.2798210175602376</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.5198860435545397</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0.0510920502799912</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.1690468772168934</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.422245151232676</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0.4087079715504304</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.1424241336724384</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0.1424241336724384</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.422245151232676</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB17" t="n">
+        <v>18.15139642462909</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0.3630279284925819</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>2.268358508934026</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>v5hMsYdL</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>45599.69791666666</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>77</v>
+      </c>
+      <c r="F18" t="n">
+        <v>771</v>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="J18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="K18" t="n">
+        <v>17</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0.8007536504945832</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0.144135657089025</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.0551106924163919</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.06737053795877324</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0.3346300980921589</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0.4658162526344252</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.1995536492734158</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.3216805955454002</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0.3216805955454002</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0.4658162526344252</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB18" t="n">
+        <v>36.86919349315934</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0.7373838698631867</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>2.601628908615742</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>jqCRLjz2</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>45600.60416666666</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>77</v>
+      </c>
+      <c r="F19" t="n">
+        <v>771</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0.3516483516483516</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.2967032967032967</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0.3516483516483516</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.0532407407407407</v>
+      </c>
+      <c r="P19" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.1314386701201626</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.4188436743798081</v>
+      </c>
+      <c r="S19" t="n">
+        <v>0.4497176555000295</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.09806930385167784</v>
+      </c>
+      <c r="W19" t="n">
+        <v>2</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0.09806930385167784</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.4497176555000295</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB19" t="n">
+        <v>12.6022158735341</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0.2520443174706819</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>2.164152358601197</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
+        <is>
+          <t>vJXfdXBE</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>45600.60416666666</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>77</v>
+      </c>
+      <c r="F20" t="n">
+        <v>771</v>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0.4917509313464608</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0.2846194784459819</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0.2236295902075572</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.064685750549625</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.2460387902576736</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.4018663700052655</v>
+      </c>
+      <c r="S20" t="n">
+        <v>0.3520948397370608</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="n">
+        <v>0.1172468915592836</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0.1172468915592836</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0.4018663700052655</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB20" t="n">
+        <v>14.18082700075549</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0.2836165400151098</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>2.193971704863855</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
+          <t>rXmhxCKr</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>45600.69791666666</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>77</v>
+      </c>
+      <c r="F21" t="n">
+        <v>771</v>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="J21" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K21" t="n">
+        <v>7</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0.6053326927696373</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.2606293538313716</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.1340379533989911</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0.06579621095750121</v>
+      </c>
+      <c r="P21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.3882852370384428</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0.3866764745262674</v>
+      </c>
+      <c r="S21" t="n">
+        <v>0.2250382884352899</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="n">
+        <v>-0.2170474557311945</v>
+      </c>
+      <c r="W21" t="n">
+        <v>1</v>
+      </c>
+      <c r="X21" t="n">
+        <v>-0.2170474557311945</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0.3882852370384428</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB21" t="n">
+        <v>-72.39234228916609</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-1.447846845783322</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0.7320506147438581</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>bR8Aj2ug</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>45603.69791666666</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>genoa</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>como</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>77</v>
+      </c>
+      <c r="F22" t="n">
+        <v>771</v>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0.1668934768055307</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.427371378354226</v>
+      </c>
+      <c r="S22" t="n">
+        <v>0.405735144840243</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
+      </c>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="n">
+        <v>0.5726286216457741</v>
+      </c>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>OYgzob9U</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>45604.69791666666</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>lecce</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>empoli</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>77</v>
+      </c>
+      <c r="F23" t="n">
+        <v>771</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>0.3802306402658026</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.266920816966107</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.3528485427680905</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1</v>
+      </c>
+      <c r="U23" t="inlineStr"/>
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X23" t="inlineStr"/>
+      <c r="Y23" t="n">
+        <v>0.6197693597341974</v>
+      </c>
+      <c r="Z23" t="inlineStr"/>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr"/>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
+        <is>
+          <t>hO2h1JgB</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>45605.45833333334</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>venezia</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>parma</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>77</v>
+      </c>
+      <c r="F24" t="n">
+        <v>771</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.3165749404104712</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.3341765870156249</v>
+      </c>
+      <c r="S24" t="n">
+        <v>0.349248472573904</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="inlineStr"/>
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X24" t="inlineStr"/>
+      <c r="Y24" t="n">
+        <v>0.650751527426096</v>
+      </c>
+      <c r="Z24" t="inlineStr"/>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr"/>
+      <c r="AC24" t="inlineStr"/>
+      <c r="AD24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>E3zhYKPO</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>45605.58333333334</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>cagliari</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>77</v>
+      </c>
+      <c r="F25" t="n">
+        <v>771</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0.08667514933185025</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.4066541629412877</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.506670687726862</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="inlineStr"/>
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="n">
+        <v>-2</v>
+      </c>
+      <c r="X25" t="inlineStr"/>
+      <c r="Y25" t="n">
+        <v>0.493329312273138</v>
+      </c>
+      <c r="Z25" t="inlineStr"/>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr"/>
+      <c r="AC25" t="inlineStr"/>
+      <c r="AD25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
+        <is>
+          <t>S60RnKvI</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>45605.69791666666</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>torino</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>77</v>
+      </c>
+      <c r="F26" t="n">
+        <v>771</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>0.4582425558246235</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0.3250385894639238</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.2167188547114526</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="inlineStr"/>
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X26" t="inlineStr"/>
+      <c r="Y26" t="n">
+        <v>0.5417574441753765</v>
+      </c>
+      <c r="Z26" t="inlineStr"/>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr"/>
+      <c r="AC26" t="inlineStr"/>
+      <c r="AD26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>tjxpzseC</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>45606.35416666666</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>atalanta</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>udinese</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>77</v>
+      </c>
+      <c r="F27" t="n">
+        <v>771</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>0.2684281666753899</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0.4947885573134698</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0.23678327601114</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="n">
+        <v>0.5052114426865302</v>
+      </c>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>pbap3uPb</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>as roma</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>bologna</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>77</v>
+      </c>
+      <c r="F28" t="n">
+        <v>771</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>0.3721709167013377</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0.2665084198910168</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0.3613206634076454</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="n">
+        <v>0.6278290832986624</v>
+      </c>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>hU52hOAt</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>45606.45833333334</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>fiorentina</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>77</v>
+      </c>
+      <c r="F29" t="n">
+        <v>771</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>0.2589004253725197</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0.4288321414280868</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0.3122674331993935</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="n">
+        <v>0.5711678585719131</v>
+      </c>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>voUq51fn</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>45606.58333333334</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>monza</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>lazio</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>77</v>
+      </c>
+      <c r="F30" t="n">
+        <v>771</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>0.3064518869126243</v>
+      </c>
+      <c r="R30" t="n">
+        <v>0.3491154240282095</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0.3444326890591665</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="n">
+        <v>0.6508845759717905</v>
+      </c>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>KtcJltA5</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>45606.69791666666</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>inter</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>napoli</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>77</v>
+      </c>
+      <c r="F31" t="n">
+        <v>771</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>0.5059536670553243</v>
+      </c>
+      <c r="R31" t="n">
+        <v>0.2530292521752283</v>
+      </c>
+      <c r="S31" t="n">
+        <v>0.2410170807694474</v>
+      </c>
+      <c r="T31" t="n">
+        <v>1</v>
+      </c>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="n">
+        <v>-1</v>
+      </c>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="n">
+        <v>0.4940463329446757</v>
+      </c>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &lt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AB11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -565,16 +565,6 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>stake_to_bet_raw</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>stake_to_bet_norm</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
           <t>stake_to_bet</t>
         </is>
       </c>
@@ -582,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rJ8JNC5k</t>
+          <t>bR8Aj2ug</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45598.45833333334</v>
+        <v>45603.69791666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>genoa</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>como</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -615,56 +605,58 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>1.62</v>
+        <v>2.9</v>
       </c>
       <c r="J2" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K2" t="n">
-        <v>6.5</v>
+        <v>2.4</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5840821566110398</v>
+        <v>0.3239263803680982</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2703465982028241</v>
+        <v>0.2846625766871166</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1455712451861361</v>
+        <v>0.3914110429447853</v>
       </c>
       <c r="O2" t="n">
-        <v>0.05684439017772336</v>
+        <v>0.0645245559038663</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.2797471824621441</v>
+        <v>0.1616330260227122</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4898896156098031</v>
+        <v>0.4255251614233782</v>
       </c>
       <c r="S2" t="n">
-        <v>0.230363201928053</v>
+        <v>0.4128418125539094</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="U2" t="n">
+        <v>1</v>
+      </c>
       <c r="V2" t="n">
-        <v>0.219543017406979</v>
+        <v>0.1408625847362616</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.219543017406979</v>
+        <v>0.1408625847362616</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4898896156098031</v>
+        <v>0.4255251614233782</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
@@ -672,32 +664,26 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>28.58454618537244</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.5716909237074488</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>2.458281752523136</v>
+        <v>0.3566595291653734</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pOryx3Qa</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45598.58333333334</v>
+        <v>45604.69791666666</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -717,56 +703,56 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>4.2</v>
+        <v>2.25</v>
       </c>
       <c r="J3" t="n">
         <v>3.25</v>
       </c>
       <c r="K3" t="n">
-        <v>1.95</v>
+        <v>3.3</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2249134948096885</v>
+        <v>0.4212076583210604</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2906574394463667</v>
+        <v>0.2916053019145803</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4844290657439446</v>
+        <v>0.2871870397643594</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05860805860805884</v>
+        <v>0.05516705516705511</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.1004381816416324</v>
+        <v>0.3692435114836438</v>
       </c>
       <c r="R3" t="n">
-        <v>0.4109168448017541</v>
+        <v>0.2730166960722579</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4886449735566135</v>
+        <v>0.3577397924440981</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.004215907812668951</v>
+        <v>-0.05196414683741662</v>
       </c>
       <c r="W3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0.004215907812668951</v>
+        <v>-0.05196414683741662</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.4886449735566135</v>
+        <v>0.3692435114836438</v>
       </c>
       <c r="Z3" t="n">
-        <v>1.95</v>
+        <v>2.25</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
@@ -774,32 +760,26 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>-4.962347533116174</v>
-      </c>
-      <c r="AC3" t="n">
-        <v>-0.09924695066232347</v>
-      </c>
-      <c r="AD3" t="n">
-        <v>1.827725418210511</v>
+        <v>0.1352685800823947</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Gpn0zjke</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45598.69791666666</v>
+        <v>45605.45833333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -819,56 +799,56 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>5.5</v>
+        <v>2.55</v>
       </c>
       <c r="J4" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
       <c r="K4" t="n">
-        <v>1.67</v>
+        <v>2.7</v>
       </c>
       <c r="L4" t="n">
-        <v>0.171786153098837</v>
+        <v>0.3711340206185567</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2624510672343344</v>
+        <v>0.2783505154639175</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5657627796668286</v>
+        <v>0.3505154639175257</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05839835480554045</v>
+        <v>0.05664488017429203</v>
       </c>
       <c r="P4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.08692835253997754</v>
+        <v>0.3561877499891236</v>
       </c>
       <c r="R4" t="n">
-        <v>0.4145091062512288</v>
+        <v>0.3065246375688527</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4985625412087937</v>
+        <v>0.3372876124420239</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.06720023845803491</v>
+        <v>-0.01494627062943316</v>
       </c>
       <c r="W4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.06720023845803491</v>
+        <v>-0.01494627062943316</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.4985625412087937</v>
+        <v>0.3561877499891236</v>
       </c>
       <c r="Z4" t="n">
-        <v>1.67</v>
+        <v>2.55</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
@@ -876,32 +856,26 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>-24.98515763900216</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>-0.4997031527800433</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.452347814282798</v>
+        <v>0.2484338069929679</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>CCu9YTJ7</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45599.35416666666</v>
+        <v>45605.58333333334</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>napoli</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -921,56 +895,56 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="K5" t="n">
-        <v>3.6</v>
+        <v>1.65</v>
       </c>
       <c r="L5" t="n">
-        <v>0.4505119453924914</v>
+        <v>0.1893830703012913</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2866894197952218</v>
+        <v>0.236728837876614</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2627986348122867</v>
+        <v>0.5738880918220947</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05699855699855716</v>
+        <v>0.05606060606060614</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.306991979470997</v>
+        <v>0.08274019555151663</v>
       </c>
       <c r="R5" t="n">
-        <v>0.3520785798309394</v>
+        <v>0.404406029122148</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3409294406980639</v>
+        <v>0.5128537753263354</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.06538916003571754</v>
+        <v>-0.0610343164957593</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>0.06538916003571754</v>
+        <v>-0.0610343164957593</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.3520785798309394</v>
+        <v>0.5128537753263354</v>
       </c>
       <c r="Z5" t="n">
-        <v>3.3</v>
+        <v>1.65</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
@@ -978,32 +952,26 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>7.037361454004342</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>0.1407472290800869</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>2.058187828650175</v>
+        <v>0.2252282882186293</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>b7pTwPem</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45599.45833333334</v>
+        <v>45605.69791666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t>torino</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>fiorentina</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1023,89 +991,83 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>3.2</v>
+        <v>1.57</v>
       </c>
       <c r="J6" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="K6" t="n">
-        <v>2.25</v>
+        <v>6.25</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2948183442525313</v>
+        <v>0.6046811624762779</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2858844550327576</v>
+        <v>0.2434229295096811</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4192972007147112</v>
+        <v>0.151895908014041</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0599747474747474</v>
+        <v>0.05335293156949206</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.1695148853976448</v>
+        <v>0.4491990320618583</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4219507438316012</v>
+        <v>0.3324819716292451</v>
       </c>
       <c r="S6" t="n">
-        <v>0.408534370770754</v>
+        <v>0.2183189963088966</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1360662887988436</v>
+        <v>-0.1554821304144196</v>
       </c>
       <c r="W6" t="n">
+        <v>1</v>
+      </c>
+      <c r="X6" t="n">
+        <v>-0.1554821304144196</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0.4491990320618583</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.35</t>
+        </is>
+      </c>
+      <c r="AB6" t="n">
         <v>0</v>
-      </c>
-      <c r="X6" t="n">
-        <v>0.1360662887988436</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>0.4219507438316012</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
-        </is>
-      </c>
-      <c r="AB6" t="n">
-        <v>17.06249802801235</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0.3412499605602469</v>
-      </c>
-      <c r="AD6" t="n">
-        <v>2.248054313814361</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>WvkEqfS8</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45599.58333333334</v>
+        <v>45606.35416666666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1125,56 +1087,56 @@
         </is>
       </c>
       <c r="I7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="J7" t="n">
         <v>4.75</v>
       </c>
-      <c r="J7" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K7" t="n">
-        <v>1.8</v>
+        <v>8</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2001588562351072</v>
+        <v>0.6835147045597626</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2716441620333598</v>
+        <v>0.1985790089036784</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5281969817315331</v>
+        <v>0.117906286536559</v>
       </c>
       <c r="O7" t="n">
-        <v>0.05179615705931484</v>
+        <v>0.06016399694889407</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.1649672563042259</v>
+        <v>0.2743034273969107</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4210544015011267</v>
+        <v>0.4923804000276243</v>
       </c>
       <c r="S7" t="n">
-        <v>0.4139783421946473</v>
+        <v>0.2333161725754651</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1494102394677669</v>
+        <v>0.293801391123946</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.1494102394677669</v>
+        <v>0.293801391123946</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4210544015011267</v>
+        <v>0.4923804000276243</v>
       </c>
       <c r="Z7" t="n">
-        <v>3.5</v>
+        <v>4.75</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
@@ -1182,32 +1144,26 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>18.94761621015774</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0.3789523242031548</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.283155352789795</v>
+        <v>0.4126951296057076</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>v5hMsYdL</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>45599.69791666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>inter</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1227,56 +1183,56 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>1.18</v>
+        <v>2.05</v>
       </c>
       <c r="J8" t="n">
-        <v>7</v>
+        <v>3.4</v>
       </c>
       <c r="K8" t="n">
-        <v>13</v>
+        <v>3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>0.794066317626527</v>
+        <v>0.4603234298608499</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1338568935427574</v>
+        <v>0.2775479503572771</v>
       </c>
       <c r="N8" t="n">
-        <v>0.07207678883071553</v>
+        <v>0.2621286197818729</v>
       </c>
       <c r="O8" t="n">
-        <v>0.06723784689886392</v>
+        <v>0.05970030288538197</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3432245750470653</v>
+        <v>0.3691151532503577</v>
       </c>
       <c r="R8" t="n">
-        <v>0.4681553384921089</v>
+        <v>0.2669719738686972</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1886200864608257</v>
+        <v>0.3639128728809451</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3342984449493516</v>
+        <v>-0.09120827661049219</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0.3342984449493516</v>
+        <v>-0.09120827661049219</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.4681553384921089</v>
+        <v>0.3691151532503577</v>
       </c>
       <c r="Z8" t="n">
-        <v>7</v>
+        <v>2.05</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
@@ -1284,32 +1240,26 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>37.95145615741271</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>0.7590291231482541</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>2.61978041976762</v>
+        <v>0.00358905403721724</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>jqCRLjz2</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45600.60416666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1329,58 +1279,56 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>2.7</v>
+        <v>1.44</v>
       </c>
       <c r="J9" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="K9" t="n">
-        <v>2.7</v>
+        <v>7</v>
       </c>
       <c r="L9" t="n">
-        <v>0.3483146067415731</v>
+        <v>0.6554307116104868</v>
       </c>
       <c r="M9" t="n">
-        <v>0.303370786516854</v>
+        <v>0.2097378277153558</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3483146067415731</v>
+        <v>0.1348314606741573</v>
       </c>
       <c r="O9" t="n">
-        <v>0.06332138590203096</v>
+        <v>0.05952380952380953</v>
       </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.1250724228574905</v>
+        <v>0.2602123189645497</v>
       </c>
       <c r="R9" t="n">
-        <v>0.413650146070866</v>
+        <v>0.4274435564298052</v>
       </c>
       <c r="S9" t="n">
-        <v>0.4612774310716437</v>
+        <v>0.3123441246056451</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
-      <c r="U9" t="n">
-        <v>1</v>
-      </c>
+      <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1129628243300706</v>
+        <v>0.2177057287144495</v>
       </c>
       <c r="W9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.1129628243300706</v>
+        <v>0.2177057287144495</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4612774310716437</v>
+        <v>0.4274435564298052</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
@@ -1388,32 +1336,26 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>14.43818022902576</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>0.2887636045805152</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>2.198820831647844</v>
+        <v>0.3582674572546474</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vJXfdXBE</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45600.60416666666</v>
+        <v>45606.58333333334</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1433,56 +1375,56 @@
         </is>
       </c>
       <c r="I10" t="n">
-        <v>1.85</v>
+        <v>4.1</v>
       </c>
       <c r="J10" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="K10" t="n">
-        <v>4.33</v>
+        <v>1.83</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5072616073735894</v>
+        <v>0.2315144654925592</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2760099922473943</v>
+        <v>0.2497919232946033</v>
       </c>
       <c r="N10" t="n">
-        <v>0.2167284003790163</v>
+        <v>0.5186936112128375</v>
       </c>
       <c r="O10" t="n">
-        <v>0.06560506981645409</v>
+        <v>0.0535084211929262</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.245003074281116</v>
+        <v>0.2807527424691044</v>
       </c>
       <c r="R10" t="n">
-        <v>0.4009341930254254</v>
+        <v>0.3628947951606609</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3540627326934588</v>
+        <v>0.3563524623702344</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1249242007780311</v>
+        <v>0.1131028718660576</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1249242007780311</v>
+        <v>0.1131028718660576</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.4009341930254254</v>
+        <v>0.3628947951606609</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
@@ -1490,32 +1432,26 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>15.13234401193527</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>0.3026468802387054</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>2.211882465823934</v>
+        <v>0.3041650612283984</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rXmhxCKr</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45600.69791666666</v>
+        <v>45606.69791666666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1535,56 +1471,56 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="J11" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K11" t="n">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6147900930967856</v>
+        <v>0.5180518051805181</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2508343579834885</v>
+        <v>0.2562256225622562</v>
       </c>
       <c r="N11" t="n">
-        <v>0.134375548919726</v>
+        <v>0.2257225722572257</v>
       </c>
       <c r="O11" t="n">
-        <v>0.06311858076563959</v>
+        <v>0.05481359579720224</v>
       </c>
       <c r="P11" t="n">
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.389046897627321</v>
+        <v>0.4930172902943962</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3866252996294882</v>
+        <v>0.259383353039037</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2243278027431906</v>
+        <v>0.2475993566665667</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>-0.2257431954694646</v>
+        <v>-0.02503451488612191</v>
       </c>
       <c r="W11" t="n">
         <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2257431954694646</v>
+        <v>-0.02503451488612191</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.389046897627321</v>
+        <v>0.4930172902943962</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.53</v>
+        <v>1.83</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
@@ -1592,13 +1528,7 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>-76.36948049626395</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>-1.527389609925279</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.686061300695789</v>
+        <v>0.3292969115842702</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -629,10 +629,10 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1616330260227122</v>
+        <v>0.1616330260227123</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4255251614233782</v>
+        <v>0.4255251614233783</v>
       </c>
       <c r="S2" t="n">
         <v>0.4128418125539094</v>
@@ -644,16 +644,16 @@
         <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>0.1408625847362616</v>
+        <v>0.1408625847362617</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1408625847362616</v>
+        <v>0.1408625847362617</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4255251614233782</v>
+        <v>0.4255251614233783</v>
       </c>
       <c r="Z2" t="n">
         <v>3.3</v>
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0.3566595291653734</v>
+        <v>0.851050322846756</v>
       </c>
     </row>
     <row r="3">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0.1352685800823947</v>
+        <v>0.3227738482679543</v>
       </c>
     </row>
     <row r="4">
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0.2484338069929679</v>
+        <v>0.5928053349427814</v>
       </c>
     </row>
     <row r="5">
@@ -919,29 +919,29 @@
         <v>2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.08274019555151663</v>
+        <v>0.08274019555151668</v>
       </c>
       <c r="R5" t="n">
-        <v>0.404406029122148</v>
+        <v>0.4044060291221481</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5128537753263354</v>
+        <v>0.5128537753263355</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.0610343164957593</v>
+        <v>-0.06103431649575919</v>
       </c>
       <c r="W5" t="n">
         <v>2</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.0610343164957593</v>
+        <v>-0.06103431649575919</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5128537753263354</v>
+        <v>0.5128537753263355</v>
       </c>
       <c r="Z5" t="n">
         <v>1.65</v>
@@ -952,7 +952,7 @@
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0.2252282882186293</v>
+        <v>0.5374330186865971</v>
       </c>
     </row>
     <row r="6">
@@ -1144,7 +1144,7 @@
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>0.4126951296057076</v>
+        <v>0.984760800055248</v>
       </c>
     </row>
     <row r="8">
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>0.00358905403721724</v>
+        <v>0.008564093616777896</v>
       </c>
     </row>
     <row r="9">
@@ -1336,7 +1336,7 @@
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>0.3582674572546474</v>
+        <v>0.8548871128596099</v>
       </c>
     </row>
     <row r="10">
@@ -1432,7 +1432,7 @@
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>0.3041650612283984</v>
+        <v>0.7257895903213214</v>
       </c>
     </row>
     <row r="11">
@@ -1528,7 +1528,7 @@
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>0.3292969115842702</v>
+        <v>0.7857584614998165</v>
       </c>
     </row>
   </sheetData>

--- a/data/italy/p6_deployment/predicciones.xlsx
+++ b/data/italy/p6_deployment/predicciones.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB11"/>
+  <dimension ref="A1:AB12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -572,20 +572,20 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>bR8Aj2ug</t>
+          <t>OYgzob9U</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>45603.69791666666</v>
+        <v>45604.69791666666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>genoa</t>
+          <t>lecce</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>como</t>
+          <t>empoli</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -605,85 +605,83 @@
         </is>
       </c>
       <c r="I2" t="n">
-        <v>2.9</v>
+        <v>2.35</v>
       </c>
       <c r="J2" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="K2" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3239263803680982</v>
+        <v>0.4041204437400951</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2846625766871166</v>
+        <v>0.3165610142630745</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3914110429447853</v>
+        <v>0.2793185419968304</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0645245559038663</v>
+        <v>0.05298289528577382</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.1616330260227123</v>
+        <v>0.2939333909711497</v>
       </c>
       <c r="R2" t="n">
-        <v>0.4255251614233783</v>
+        <v>0.4106573401420681</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4128418125539094</v>
+        <v>0.2954092688867823</v>
       </c>
       <c r="T2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
-        <v>1</v>
-      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1408625847362617</v>
+        <v>0.09409632587899358</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0.1408625847362617</v>
+        <v>0.09409632587899358</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.4255251614233783</v>
+        <v>0.4106573401420681</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.3</v>
+        <v>3</v>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB2" t="n">
-        <v>0.851050322846756</v>
+        <v>5.902819827435319</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>OYgzob9U</t>
+          <t>hO2h1JgB</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>45604.69791666666</v>
+        <v>45605.45833333334</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>lecce</t>
+          <t>venezia</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>empoli</t>
+          <t>parma</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -703,83 +701,83 @@
         </is>
       </c>
       <c r="I3" t="n">
-        <v>2.25</v>
+        <v>2.55</v>
       </c>
       <c r="J3" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4212076583210604</v>
+        <v>0.3711340206185567</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2916053019145803</v>
+        <v>0.2783505154639175</v>
       </c>
       <c r="N3" t="n">
-        <v>0.2871870397643594</v>
+        <v>0.3505154639175257</v>
       </c>
       <c r="O3" t="n">
-        <v>0.05516705516705511</v>
+        <v>0.05664488017429203</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3692435114836438</v>
+        <v>0.2498867756386013</v>
       </c>
       <c r="R3" t="n">
-        <v>0.2730166960722579</v>
+        <v>0.3748693937364196</v>
       </c>
       <c r="S3" t="n">
-        <v>0.3577397924440981</v>
+        <v>0.3752438306249791</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-0.05196414683741662</v>
+        <v>0.02472836670745338</v>
       </c>
       <c r="W3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.05196414683741662</v>
+        <v>0.02472836670745338</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.3692435114836438</v>
+        <v>0.3752438306249791</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.25</v>
+        <v>2.7</v>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB3" t="n">
-        <v>0.3227738482679543</v>
+        <v>3.556179730910945</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hO2h1JgB</t>
+          <t>E3zhYKPO</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>45605.45833333334</v>
+        <v>45605.58333333334</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>venezia</t>
+          <t>cagliari</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>parma</t>
+          <t>ac milan</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -799,83 +797,83 @@
         </is>
       </c>
       <c r="I4" t="n">
-        <v>2.55</v>
+        <v>5.5</v>
       </c>
       <c r="J4" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
       <c r="K4" t="n">
-        <v>2.7</v>
+        <v>1.6</v>
       </c>
       <c r="L4" t="n">
-        <v>0.3711340206185567</v>
+        <v>0.173041413874967</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2783505154639175</v>
+        <v>0.2321287259298338</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3505154639175257</v>
+        <v>0.5948298601951991</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05664488017429203</v>
+        <v>0.05072062084257212</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.3561877499891236</v>
+        <v>0.06416446372416562</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3065246375688527</v>
+        <v>0.1884644760211565</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3372876124420239</v>
+        <v>0.7473710602546778</v>
       </c>
       <c r="T4" t="n">
         <v>1</v>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>-0.01494627062943316</v>
+        <v>0.1525412000594787</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.01494627062943316</v>
+        <v>0.1525412000594787</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.3561877499891236</v>
+        <v>0.7473710602546778</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.55</v>
+        <v>1.6</v>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB4" t="n">
-        <v>0.5928053349427814</v>
+        <v>10.18151895369444</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>E3zhYKPO</t>
+          <t>S60RnKvI</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>45605.58333333334</v>
+        <v>45605.69791666666</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>cagliari</t>
+          <t>juventus</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>ac milan</t>
+          <t>torino</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -895,83 +893,83 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>1.55</v>
       </c>
       <c r="J5" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>1.65</v>
+        <v>7</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1893830703012913</v>
+        <v>0.6137517305029996</v>
       </c>
       <c r="M5" t="n">
-        <v>0.236728837876614</v>
+        <v>0.2503461005999077</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5738880918220947</v>
+        <v>0.1359021688970928</v>
       </c>
       <c r="O5" t="n">
-        <v>0.05606060606060614</v>
+        <v>0.05117632791656557</v>
       </c>
       <c r="P5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.08274019555151668</v>
+        <v>0.5787070596671816</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4044060291221481</v>
+        <v>0.2676145090391487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5128537753263355</v>
+        <v>0.1536784312936697</v>
       </c>
       <c r="T5" t="n">
         <v>1</v>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>-0.06103431649575919</v>
+        <v>-0.03504467083581797</v>
       </c>
       <c r="W5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.06103431649575919</v>
+        <v>-0.03504467083581797</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.5128537753263355</v>
+        <v>0.5787070596671816</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.65</v>
+        <v>1.55</v>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB5" t="n">
-        <v>0.5374330186865971</v>
+        <v>3.288962822429323</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>S60RnKvI</t>
+          <t>tjxpzseC</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>45605.69791666666</v>
+        <v>45606.35416666666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>juventus</t>
+          <t>atalanta</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>torino</t>
+          <t>udinese</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -991,83 +989,83 @@
         </is>
       </c>
       <c r="I6" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="J6" t="n">
-        <v>3.9</v>
+        <v>5</v>
       </c>
       <c r="K6" t="n">
-        <v>6.25</v>
+        <v>7.5</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6046811624762779</v>
+        <v>0.6849315068493151</v>
       </c>
       <c r="M6" t="n">
-        <v>0.2434229295096811</v>
+        <v>0.189041095890411</v>
       </c>
       <c r="N6" t="n">
-        <v>0.151895908014041</v>
+        <v>0.126027397260274</v>
       </c>
       <c r="O6" t="n">
-        <v>0.05335293156949206</v>
+        <v>0.05797101449275366</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.4491990320618583</v>
+        <v>0.6210748069468638</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3324819716292451</v>
+        <v>0.2700769638529026</v>
       </c>
       <c r="S6" t="n">
-        <v>0.2183189963088966</v>
+        <v>0.1088482292002337</v>
       </c>
       <c r="T6" t="n">
         <v>1</v>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>-0.1554821304144196</v>
+        <v>-0.06385669990245135</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1554821304144196</v>
+        <v>-0.06385669990245135</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.4491990320618583</v>
+        <v>0.6210748069468638</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>2.742360055027938</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tjxpzseC</t>
+          <t>pbap3uPb</t>
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>45606.35416666666</v>
+        <v>45606.45833333334</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>atalanta</t>
+          <t>as roma</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>udinese</t>
+          <t>bologna</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1087,70 +1085,70 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>1.38</v>
+        <v>2.05</v>
       </c>
       <c r="J7" t="n">
-        <v>4.75</v>
+        <v>3.4</v>
       </c>
       <c r="K7" t="n">
-        <v>8</v>
+        <v>3.6</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6835147045597626</v>
+        <v>0.4603234298608499</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1985790089036784</v>
+        <v>0.2775479503572771</v>
       </c>
       <c r="N7" t="n">
-        <v>0.117906286536559</v>
+        <v>0.2621286197818729</v>
       </c>
       <c r="O7" t="n">
-        <v>0.06016399694889407</v>
+        <v>0.05970030288538197</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.2743034273969107</v>
+        <v>0.2121643271392464</v>
       </c>
       <c r="R7" t="n">
-        <v>0.4923804000276243</v>
+        <v>0.28252457474014</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2333161725754651</v>
+        <v>0.5053110981206135</v>
       </c>
       <c r="T7" t="n">
         <v>1</v>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.293801391123946</v>
+        <v>0.2431824783387406</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X7" t="n">
-        <v>0.293801391123946</v>
+        <v>0.2431824783387406</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.4923804000276243</v>
+        <v>0.5053110981206135</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.75</v>
+        <v>3.6</v>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB7" t="n">
-        <v>0.984760800055248</v>
+        <v>11.08530758606682</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>pbap3uPb</t>
+          <t>hU52hOAt</t>
         </is>
       </c>
       <c r="B8" s="2" t="n">
@@ -1158,12 +1156,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>as roma</t>
+          <t>fiorentina</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>bologna</t>
+          <t>verona</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1183,83 +1181,83 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="J8" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
       </c>
       <c r="K8" t="n">
-        <v>3.6</v>
+        <v>7</v>
       </c>
       <c r="L8" t="n">
-        <v>0.4603234298608499</v>
+        <v>0.6554307116104868</v>
       </c>
       <c r="M8" t="n">
-        <v>0.2775479503572771</v>
+        <v>0.2097378277153558</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2621286197818729</v>
+        <v>0.1348314606741573</v>
       </c>
       <c r="O8" t="n">
-        <v>0.05970030288538197</v>
+        <v>0.05952380952380953</v>
       </c>
       <c r="P8" t="n">
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.3691151532503577</v>
+        <v>0.5616255264882302</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2669719738686972</v>
+        <v>0.3175377770356159</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3639128728809451</v>
+        <v>0.120836696476154</v>
       </c>
       <c r="T8" t="n">
         <v>1</v>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>-0.09120827661049219</v>
+        <v>-0.09380518512225666</v>
       </c>
       <c r="W8" t="n">
         <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.09120827661049219</v>
+        <v>-0.09380518512225666</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.3691151532503577</v>
+        <v>0.5616255264882302</v>
       </c>
       <c r="Z8" t="n">
-        <v>2.05</v>
+        <v>1.44</v>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB8" t="n">
-        <v>0.008564093616777896</v>
+        <v>1.398035894994026</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hU52hOAt</t>
+          <t>voUq51fn</t>
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>45606.45833333334</v>
+        <v>45606.58333333334</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>fiorentina</t>
+          <t>monza</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>verona</t>
+          <t>lazio</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1279,83 +1277,83 @@
         </is>
       </c>
       <c r="I9" t="n">
-        <v>1.44</v>
+        <v>4.1</v>
       </c>
       <c r="J9" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="K9" t="n">
-        <v>7</v>
+        <v>1.83</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6554307116104868</v>
+        <v>0.2315144654925592</v>
       </c>
       <c r="M9" t="n">
-        <v>0.2097378277153558</v>
+        <v>0.2497919232946033</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1348314606741573</v>
+        <v>0.5186936112128375</v>
       </c>
       <c r="O9" t="n">
-        <v>0.05952380952380953</v>
+        <v>0.0535084211929262</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.2602123189645497</v>
+        <v>0.1944810728279434</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4274435564298052</v>
+        <v>0.4216163095235277</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3123441246056451</v>
+        <v>0.3839026176485287</v>
       </c>
       <c r="T9" t="n">
         <v>1</v>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.2177057287144495</v>
+        <v>0.1718243862289244</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.2177057287144495</v>
+        <v>0.1718243862289244</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.4274435564298052</v>
+        <v>0.4216163095235277</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.5</v>
+        <v>3.8</v>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB9" t="n">
-        <v>0.8548871128596099</v>
+        <v>8.31685390829419</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>voUq51fn</t>
+          <t>KtcJltA5</t>
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>45606.58333333334</v>
+        <v>45606.69791666666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>monza</t>
+          <t>inter</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>lazio</t>
+          <t>napoli</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1375,83 +1373,83 @@
         </is>
       </c>
       <c r="I10" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K10" t="n">
         <v>4.1</v>
       </c>
-      <c r="J10" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K10" t="n">
-        <v>1.83</v>
-      </c>
       <c r="L10" t="n">
-        <v>0.2315144654925592</v>
+        <v>0.5125</v>
       </c>
       <c r="M10" t="n">
-        <v>0.2497919232946033</v>
+        <v>0.25625</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5186936112128375</v>
+        <v>0.23125</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0535084211929262</v>
+        <v>0.05471324983520098</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.2807527424691044</v>
+        <v>0.5199129358101434</v>
       </c>
       <c r="R10" t="n">
-        <v>0.3628947951606609</v>
+        <v>0.2471773357794682</v>
       </c>
       <c r="S10" t="n">
-        <v>0.3563524623702344</v>
+        <v>0.2329097284103884</v>
       </c>
       <c r="T10" t="n">
         <v>1</v>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1131028718660576</v>
+        <v>0.007412935810143462</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10" t="n">
-        <v>0.1131028718660576</v>
+        <v>0.007412935810143462</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.3628947951606609</v>
+        <v>0.5199129358101434</v>
       </c>
       <c r="Z10" t="n">
-        <v>3.8</v>
+        <v>1.85</v>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB10" t="n">
-        <v>0.7257895903213214</v>
+        <v>4.121735092880379</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>KtcJltA5</t>
+          <t>WENRFI84</t>
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>45606.69791666666</v>
+        <v>45619.45833333334</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>verona</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>inter</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>napoli</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1471,64 +1469,160 @@
         </is>
       </c>
       <c r="I11" t="n">
-        <v>1.83</v>
+        <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>3.7</v>
+        <v>5.25</v>
       </c>
       <c r="K11" t="n">
-        <v>4.2</v>
+        <v>1.38</v>
       </c>
       <c r="L11" t="n">
-        <v>0.5180518051805181</v>
+        <v>0.1350293542074364</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2562256225622562</v>
+        <v>0.1800391389432485</v>
       </c>
       <c r="N11" t="n">
-        <v>0.2257225722572257</v>
+        <v>0.6849315068493151</v>
       </c>
       <c r="O11" t="n">
-        <v>0.05481359579720224</v>
+        <v>0.05797101449275366</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.4930172902943962</v>
+        <v>0.03250536456456055</v>
       </c>
       <c r="R11" t="n">
-        <v>0.259383353039037</v>
+        <v>0.2018595202117701</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2475993566665667</v>
+        <v>0.7656351152236692</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>-0.02503451488612191</v>
+        <v>0.08070360837435409</v>
       </c>
       <c r="W11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.02503451488612191</v>
+        <v>0.08070360837435409</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.4930172902943962</v>
+        <v>0.7656351152236692</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.83</v>
+        <v>1.38</v>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>dif_prob_mod_bm &gt; -0.35</t>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
         </is>
       </c>
       <c r="AB11" t="n">
-        <v>0.7857584614998165</v>
+        <v>8.163371615408142</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>z7KrCz8T</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>45619.58333333334</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ac milan</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>juventus</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>77</v>
+      </c>
+      <c r="F12" t="n">
+        <v>771</v>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>italy</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>serie a</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.4509283819628648</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0.2785145888594165</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0.2705570291777188</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.05602240896358524</v>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.3327198060038317</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.4494769501082279</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.2178032438879404</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.1709623612488114</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0.1709623612488114</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0.4494769501082279</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>dif_prob_mod_bm &gt; -0.5</t>
+        </is>
+      </c>
+      <c r="AB12" t="n">
+        <v>8.499947963276052</v>
       </c>
     </row>
   </sheetData>
